--- a/Bases/Lista de ações.xlsx
+++ b/Bases/Lista de ações.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D409"/>
+  <dimension ref="A1:D406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Volume no último dia útil (lido em 10/03/2025)</t>
+          <t>Volume no último dia útil (lido em 15/03/2025)</t>
         </is>
       </c>
     </row>
@@ -451,16 +451,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hapvida</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HAPV3</t>
+          <t>B3SA3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>97225000</v>
+        <v>126021900</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Hapvida</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B3SA3</t>
+          <t>HAPV3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>41638200</v>
+        <v>111755000</v>
       </c>
     </row>
     <row r="4">
@@ -487,16 +487,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Magazine Luiza</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>NTCO3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40884800</v>
+        <v>105384100</v>
       </c>
     </row>
     <row r="5">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36134200</v>
+        <v>102051600</v>
       </c>
     </row>
     <row r="6">
@@ -523,16 +523,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ambev</t>
+          <t>Magazine Luiza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ABEV3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30190400</v>
+        <v>65687600</v>
       </c>
     </row>
     <row r="7">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29808500</v>
+        <v>42086800</v>
       </c>
     </row>
     <row r="8">
@@ -559,16 +559,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Petrobras</t>
+          <t>Ambev</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>ABEV3</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28074700</v>
+        <v>41765100</v>
       </c>
     </row>
     <row r="9">
@@ -577,16 +577,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lojas Renner</t>
+          <t>Petrobras</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LREN3</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26935300</v>
+        <v>41510300</v>
       </c>
     </row>
     <row r="10">
@@ -595,16 +595,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Itaúsa</t>
+          <t>Automob</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>AMOB3</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>26623100</v>
+        <v>35798400</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vale</t>
+          <t>Itaúsa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25480600</v>
+        <v>35728500</v>
       </c>
     </row>
     <row r="12">
@@ -631,16 +631,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Marcopolo</t>
+          <t>Grupo CCR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>CCRO3</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24491700</v>
+        <v>32515300</v>
       </c>
     </row>
     <row r="13">
@@ -649,16 +649,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVC</t>
+          <t>Vale</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CVCB3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24316300</v>
+        <v>31782000</v>
       </c>
     </row>
     <row r="14">
@@ -667,16 +667,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Assaí</t>
+          <t>Itaú Unibanco</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ASAI3</t>
+          <t>ITUB4</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22826700</v>
+        <v>31638000</v>
       </c>
     </row>
     <row r="15">
@@ -685,16 +685,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Itaú Unibanco</t>
+          <t>Cemig</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ITUB4</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20645900</v>
+        <v>28449400</v>
       </c>
     </row>
     <row r="16">
@@ -703,16 +703,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vamos Locação</t>
+          <t>Locaweb</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AMOB3</t>
+          <t>LWSA3</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16946700</v>
+        <v>27984300</v>
       </c>
     </row>
     <row r="17">
@@ -721,16 +721,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Banco do Brasil</t>
+          <t>Siderúrgica Nacional</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BBAS3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16830600</v>
+        <v>26742900</v>
       </c>
     </row>
     <row r="18">
@@ -739,16 +739,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Casas Bahia</t>
+          <t>Azevedo &amp; Travassos</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>AZEV4</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16304700</v>
+        <v>23465200</v>
       </c>
     </row>
     <row r="19">
@@ -757,16 +757,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cosan</t>
+          <t>Lojas Renner</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CSAN3</t>
+          <t>LREN3</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16276000</v>
+        <v>23036000</v>
       </c>
     </row>
     <row r="20">
@@ -775,16 +775,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Copel</t>
+          <t>Banco do Brasil</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CPLE6</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16106300</v>
+        <v>22864500</v>
       </c>
     </row>
     <row r="21">
@@ -793,16 +793,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MRV</t>
+          <t>Grupo Vamos</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MRVE3</t>
+          <t>VAMO3</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15874700</v>
+        <v>20637800</v>
       </c>
     </row>
     <row r="22">
@@ -811,16 +811,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RaiaDrogasil</t>
+          <t>Cosan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RADL3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15847100</v>
+        <v>19310200</v>
       </c>
     </row>
     <row r="23">
@@ -829,16 +829,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Raízen</t>
+          <t>Usiminas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RAIZ4</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14323600</v>
+        <v>18908100</v>
       </c>
     </row>
     <row r="24">
@@ -847,16 +847,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3R Petroleum</t>
+          <t>Assaí</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BRAV3</t>
+          <t>ASAI3</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13702800</v>
+        <v>17930500</v>
       </c>
     </row>
     <row r="25">
@@ -865,16 +865,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Localiza</t>
+          <t>CVC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RENT3</t>
+          <t>CVCB3</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13520000</v>
+        <v>17711400</v>
       </c>
     </row>
     <row r="26">
@@ -883,16 +883,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Grupo Vamos</t>
+          <t>Copel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VAMO3</t>
+          <t>CPLE6</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13260500</v>
+        <v>16997000</v>
       </c>
     </row>
     <row r="27">
@@ -901,16 +901,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Locaweb</t>
+          <t>PetroRio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LWSA3</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12582100</v>
+        <v>16461300</v>
       </c>
     </row>
     <row r="28">
@@ -919,16 +919,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Azul</t>
+          <t>Raízen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AZUL4</t>
+          <t>RAIZ4</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11864400</v>
+        <v>15533300</v>
       </c>
     </row>
     <row r="29">
@@ -937,16 +937,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Usiminas</t>
+          <t>RaiaDrogasil</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>RADL3</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11715800</v>
+        <v>14644700</v>
       </c>
     </row>
     <row r="30">
@@ -955,16 +955,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Carrefour Brasil</t>
+          <t>Localiza</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CRFB3</t>
+          <t>RENT3</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11618900</v>
+        <v>14413000</v>
       </c>
     </row>
     <row r="31">
@@ -973,16 +973,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rumo</t>
+          <t>Marcopolo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RAIL3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11497400</v>
+        <v>13669900</v>
       </c>
     </row>
     <row r="32">
@@ -991,16 +991,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ânima Educação</t>
+          <t>Eletrobras</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ANIM3</t>
+          <t>ELET3</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10993900</v>
+        <v>13541000</v>
       </c>
     </row>
     <row r="33">
@@ -1009,16 +1009,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Siderúrgica Nacional</t>
+          <t>Casas Bahia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10943300</v>
+        <v>12175600</v>
       </c>
     </row>
     <row r="34">
@@ -1027,16 +1027,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gerdau</t>
+          <t>Rumo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GGBR4</t>
+          <t>RAIL3</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9969500</v>
+        <v>12174600</v>
       </c>
     </row>
     <row r="35">
@@ -1045,16 +1045,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Natura</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NTCO3</t>
+          <t>AZZA3</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9539900</v>
+        <v>11682200</v>
       </c>
     </row>
     <row r="36">
@@ -1063,16 +1063,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Petrobras</t>
+          <t>CSN Mineração</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PETR3</t>
+          <t>CMIN3</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9512700</v>
+        <v>11473700</v>
       </c>
     </row>
     <row r="37">
@@ -1081,16 +1081,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Azevedo &amp; Travassos</t>
+          <t>EZTEC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AZEV4</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9354100</v>
+        <v>10777800</v>
       </c>
     </row>
     <row r="38">
@@ -1099,16 +1099,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Grupo CCR</t>
+          <t>MRV</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CCRO3</t>
+          <t>MRVE3</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8762100</v>
+        <v>10477600</v>
       </c>
     </row>
     <row r="39">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8657600</v>
+        <v>10419100</v>
       </c>
     </row>
     <row r="40">
@@ -1135,16 +1135,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PetroRio</t>
+          <t>Banco BTG Pactual</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8474100</v>
+        <v>10124600</v>
       </c>
     </row>
     <row r="41">
@@ -1153,16 +1153,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BRF</t>
+          <t>Banco Bradesco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BRFS3</t>
+          <t>BBDC3</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8322300</v>
+        <v>9505300</v>
       </c>
     </row>
     <row r="42">
@@ -1171,16 +1171,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Equatorial Energia</t>
+          <t>Azul</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EQTL3</t>
+          <t>AZUL4</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8225400</v>
+        <v>9331000</v>
       </c>
     </row>
     <row r="43">
@@ -1189,16 +1189,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cyrela</t>
+          <t>Auren Energia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>AURE3</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7958000</v>
+        <v>9254700</v>
       </c>
     </row>
     <row r="44">
@@ -1207,16 +1207,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marfrig</t>
+          <t>Santos Brasil</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MRFG3</t>
+          <t>STBP3</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>7942800</v>
+        <v>9133000</v>
       </c>
     </row>
     <row r="45">
@@ -1225,16 +1225,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Eletrobras</t>
+          <t>Grupo Pão de Açúcar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ELET3</t>
+          <t>PCAR3</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7677400</v>
+        <v>9053600</v>
       </c>
     </row>
     <row r="46">
@@ -1243,16 +1243,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cemig</t>
+          <t>Ultrapar</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>UGPA3</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>7632900</v>
+        <v>9016300</v>
       </c>
     </row>
     <row r="47">
@@ -1261,16 +1261,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WEG</t>
+          <t>Ânima Educação</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>ANIM3</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>7584000</v>
+        <v>8748200</v>
       </c>
     </row>
     <row r="48">
@@ -1279,16 +1279,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>WEG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7565600</v>
+        <v>8528600</v>
       </c>
     </row>
     <row r="49">
@@ -1297,16 +1297,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hidrovias do Brasil</t>
+          <t>BRF</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HBSA3</t>
+          <t>BRFS3</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>7345300</v>
+        <v>8492900</v>
       </c>
     </row>
     <row r="50">
@@ -1315,16 +1315,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TIM</t>
+          <t>Petrobras</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TIMS3</t>
+          <t>PETR3</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7334400</v>
+        <v>8458900</v>
       </c>
     </row>
     <row r="51">
@@ -1333,16 +1333,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Recrusul</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EMBR3</t>
+          <t>RCSL4</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>7316600</v>
+        <v>8317400</v>
       </c>
     </row>
     <row r="52">
@@ -1351,16 +1351,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Banco BTG Pactual</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BPAC11</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7196000</v>
+        <v>7898800</v>
       </c>
     </row>
     <row r="53">
@@ -1369,16 +1369,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PDG Realty</t>
+          <t>Equatorial Energia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PDGR3</t>
+          <t>EQTL3</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7119000</v>
+        <v>7368700</v>
       </c>
     </row>
     <row r="54">
@@ -1387,16 +1387,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fleury</t>
+          <t>Metalúrgica Gerdau</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FLRY3</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7112600</v>
+        <v>7283100</v>
       </c>
     </row>
     <row r="55">
@@ -1405,16 +1405,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CSN Mineração</t>
+          <t>Eneva</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CMIN3</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6848200</v>
+        <v>7206400</v>
       </c>
     </row>
     <row r="56">
@@ -1423,16 +1423,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ultrapar</t>
+          <t>Petz</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UGPA3</t>
+          <t>PETZ3</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6803200</v>
+        <v>6877700</v>
       </c>
     </row>
     <row r="57">
@@ -1441,16 +1441,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C&amp;A</t>
+          <t>SLC Agrícola</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CEAB3</t>
+          <t>SLCE3</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6657400</v>
+        <v>6845100</v>
       </c>
     </row>
     <row r="58">
@@ -1459,16 +1459,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Grupo Pão de Açúcar</t>
+          <t>Totvs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PCAR3</t>
+          <t>TOTS3</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6405700</v>
+        <v>6714600</v>
       </c>
     </row>
     <row r="59">
@@ -1477,16 +1477,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Simpar</t>
+          <t>Gerdau</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SIMH3</t>
+          <t>GGBR4</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6065200</v>
+        <v>6674200</v>
       </c>
     </row>
     <row r="60">
@@ -1495,16 +1495,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JBS</t>
+          <t>Multiplan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JBSS3</t>
+          <t>MULT3</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6048600</v>
+        <v>6566600</v>
       </c>
     </row>
     <row r="61">
@@ -1513,16 +1513,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Banco Bradesco</t>
+          <t>Suzano</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BBDC3</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6027700</v>
+        <v>6516300</v>
       </c>
     </row>
     <row r="62">
@@ -1531,16 +1531,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eneva</t>
+          <t>3R Petroleum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>BRAV3</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5995200</v>
+        <v>6325800</v>
       </c>
     </row>
     <row r="63">
@@ -1549,16 +1549,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Totvs</t>
+          <t>Carrefour Brasil</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TOTS3</t>
+          <t>CRFB3</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5957100</v>
+        <v>6265800</v>
       </c>
     </row>
     <row r="64">
@@ -1567,16 +1567,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Suzano</t>
+          <t>Intelbras</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>INTB3</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5896900</v>
+        <v>5908300</v>
       </c>
     </row>
     <row r="65">
@@ -1585,16 +1585,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Auren Energia</t>
+          <t>Construtora Tenda</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AURE3</t>
+          <t>TEND3</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5692100</v>
+        <v>5897700</v>
       </c>
     </row>
     <row r="66">
@@ -1603,16 +1603,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Metalúrgica Gerdau</t>
+          <t>Movida</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GOAU4</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5691200</v>
+        <v>5821400</v>
       </c>
     </row>
     <row r="67">
@@ -1621,16 +1621,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Americanas</t>
+          <t>Simpar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AMER3</t>
+          <t>SIMH3</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5639800</v>
+        <v>5803700</v>
       </c>
     </row>
     <row r="68">
@@ -1639,16 +1639,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Movida</t>
+          <t>Copel</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MOVI3</t>
+          <t>CPLE3</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5612400</v>
+        <v>5736600</v>
       </c>
     </row>
     <row r="69">
@@ -1657,16 +1657,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Multiplan</t>
+          <t>Embraer</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MULT3</t>
+          <t>EMBR3</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5448900</v>
+        <v>5653000</v>
       </c>
     </row>
     <row r="70">
@@ -1675,16 +1675,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Rede D'Or</t>
+          <t>Vivara</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RDOR3</t>
+          <t>VIVA3</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5447900</v>
+        <v>5411200</v>
       </c>
     </row>
     <row r="71">
@@ -1693,16 +1693,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JHSF</t>
+          <t>Cyrela</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5305600</v>
+        <v>5257900</v>
       </c>
     </row>
     <row r="72">
@@ -1711,16 +1711,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BB Seguridade</t>
+          <t>Americanas</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BBSE3</t>
+          <t>AMER3</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5292500</v>
+        <v>4929000</v>
       </c>
     </row>
     <row r="73">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Petz</t>
+          <t>Allos</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PETZ3</t>
+          <t>ALOS3</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5142000</v>
+        <v>4896100</v>
       </c>
     </row>
     <row r="74">
@@ -1747,16 +1747,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Copel</t>
+          <t>Qualicorp</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CPLE3</t>
+          <t>QUAL3</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5080500</v>
+        <v>4838200</v>
       </c>
     </row>
     <row r="75">
@@ -1765,16 +1765,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Oncoclínicas</t>
+          <t>EcoRodovias</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ONCO3</t>
+          <t>ECOR3</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5017200</v>
+        <v>4657500</v>
       </c>
     </row>
     <row r="76">
@@ -1783,16 +1783,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Infracommerce</t>
+          <t>JBS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IFCM3</t>
+          <t>JBSS3</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4913400</v>
+        <v>4397200</v>
       </c>
     </row>
     <row r="77">
@@ -1801,16 +1801,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Grupo Mateus</t>
+          <t>Rede D'Or</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GMAT3</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4774600</v>
+        <v>4332000</v>
       </c>
     </row>
     <row r="78">
@@ -1819,16 +1819,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gafisa</t>
+          <t>Marfrig</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GFSA3</t>
+          <t>MRFG3</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4514800</v>
+        <v>4256200</v>
       </c>
     </row>
     <row r="79">
@@ -1837,16 +1837,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Allos</t>
+          <t>Banco Santander</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ALOS3</t>
+          <t>SANB11</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4078700</v>
+        <v>4210500</v>
       </c>
     </row>
     <row r="80">
@@ -1855,16 +1855,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Santos Brasil</t>
+          <t>BB Seguridade</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>STBP3</t>
+          <t>BBSE3</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4073600</v>
+        <v>4159500</v>
       </c>
     </row>
     <row r="81">
@@ -1873,16 +1873,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Vivara</t>
+          <t>Infracommerce</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>VIVA3</t>
+          <t>IFCM3</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3903100</v>
+        <v>3987200</v>
       </c>
     </row>
     <row r="82">
@@ -1891,16 +1891,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SLC Agrícola</t>
+          <t>Sabesp</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SLCE3</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3872500</v>
+        <v>3892100</v>
       </c>
     </row>
     <row r="83">
@@ -1909,16 +1909,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lojas Quero-Quero</t>
+          <t>Serena Energia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LJQQ3</t>
+          <t>SRNA3</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3808800</v>
+        <v>3826700</v>
       </c>
     </row>
     <row r="84">
@@ -1927,16 +1927,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Caixa Seguridade</t>
+          <t>C&amp;A</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CXSE3</t>
+          <t>CEAB3</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3805000</v>
+        <v>3811700</v>
       </c>
     </row>
     <row r="85">
@@ -1945,16 +1945,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Banco Santander</t>
+          <t>Azevedo &amp; Travassos</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SANB11</t>
+          <t>AZEV3</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3706100</v>
+        <v>3777200</v>
       </c>
     </row>
     <row r="86">
@@ -1963,16 +1963,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Méliuz</t>
+          <t>Bradespar</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CASH3</t>
+          <t>BRAP4</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3655600</v>
+        <v>3754000</v>
       </c>
     </row>
     <row r="87">
@@ -1981,16 +1981,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EcoRodovias</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ECOR3</t>
+          <t>CBAV3</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3551800</v>
+        <v>3744600</v>
       </c>
     </row>
     <row r="88">
@@ -1999,16 +1999,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EZTEC</t>
+          <t>JHSF</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EZTC3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3476900</v>
+        <v>3659400</v>
       </c>
     </row>
     <row r="89">
@@ -2017,16 +2017,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GOL</t>
+          <t>Lojas Quero-Quero</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GOLL4</t>
+          <t>LJQQ3</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3425100</v>
+        <v>3640300</v>
       </c>
     </row>
     <row r="90">
@@ -2035,16 +2035,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Klabin</t>
+          <t>Braskem</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>BRKM5</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3410700</v>
+        <v>3531100</v>
       </c>
     </row>
     <row r="91">
@@ -2053,16 +2053,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bradespar</t>
+          <t>Iguatemi</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BRAP4</t>
+          <t>IGTI11</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3340100</v>
+        <v>3442400</v>
       </c>
     </row>
     <row r="92">
@@ -2071,16 +2071,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Vivo</t>
+          <t>Jereissati Participações</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VIVT3</t>
+          <t>IGTI11</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3332600</v>
+        <v>3442400</v>
       </c>
     </row>
     <row r="93">
@@ -2089,16 +2089,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sabesp</t>
+          <t>YDUQS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3290900</v>
+        <v>3397800</v>
       </c>
     </row>
     <row r="94">
@@ -2107,16 +2107,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dexco</t>
+          <t>TIM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DXCO3</t>
+          <t>TIMS3</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3104200</v>
+        <v>3385300</v>
       </c>
     </row>
     <row r="95">
@@ -2125,16 +2125,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Construtora Tenda</t>
+          <t>Caixa Seguridade</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TEND3</t>
+          <t>CXSE3</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3101400</v>
+        <v>3329200</v>
       </c>
     </row>
     <row r="96">
@@ -2143,16 +2143,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Alpargatas</t>
+          <t>Pague Menos</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ALPA4</t>
+          <t>PGMN3</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3048900</v>
+        <v>3284100</v>
       </c>
     </row>
     <row r="97">
@@ -2161,16 +2161,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hypera</t>
+          <t>Even</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>EVEN3</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2999400</v>
+        <v>3149800</v>
       </c>
     </row>
     <row r="98">
@@ -2179,16 +2179,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ClearSale</t>
+          <t>Klabin</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CLSA3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2962800</v>
+        <v>3103700</v>
       </c>
     </row>
     <row r="99">
@@ -2197,16 +2197,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Serena Energia</t>
+          <t>Oncoclínicas</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SRNA3</t>
+          <t>ONCO3</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2918300</v>
+        <v>3056100</v>
       </c>
     </row>
     <row r="100">
@@ -2215,16 +2215,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>Smart Fit</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CBAV3</t>
+          <t>SMFT3</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2903700</v>
+        <v>3017900</v>
       </c>
     </row>
     <row r="101">
@@ -2233,16 +2233,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Randon</t>
+          <t>COPASA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>RAPT4</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2886300</v>
+        <v>2921400</v>
       </c>
     </row>
     <row r="102">
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2816700</v>
+        <v>2901800</v>
       </c>
     </row>
     <row r="103">
@@ -2269,16 +2269,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Braskem</t>
+          <t>Hypera</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BRKM5</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2752500</v>
+        <v>2825500</v>
       </c>
     </row>
     <row r="104">
@@ -2287,16 +2287,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Recrusul</t>
+          <t>Vivo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RCSL4</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2734700</v>
+        <v>2810300</v>
       </c>
     </row>
     <row r="105">
@@ -2305,16 +2305,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Oi</t>
+          <t>ClearSale</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OIBR3</t>
+          <t>CLSA3</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2671800</v>
+        <v>2725300</v>
       </c>
     </row>
     <row r="106">
@@ -2323,16 +2323,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YDUQS</t>
+          <t>GPS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>GGPS3</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2664800</v>
+        <v>2660800</v>
       </c>
     </row>
     <row r="107">
@@ -2341,16 +2341,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Energisa</t>
+          <t>Fleury</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ENGI11</t>
+          <t>FLRY3</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2614000</v>
+        <v>2656800</v>
       </c>
     </row>
     <row r="108">
@@ -2359,16 +2359,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Qualicorp</t>
+          <t>Energisa</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>QUAL3</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2594600</v>
+        <v>2635600</v>
       </c>
     </row>
     <row r="109">
@@ -2377,16 +2377,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kepler Weber</t>
+          <t>Grupo Mateus</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KEPL3</t>
+          <t>GMAT3</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2585400</v>
+        <v>2595300</v>
       </c>
     </row>
     <row r="110">
@@ -2395,16 +2395,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Porto Seguro</t>
+          <t>Alpargatas</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2565400</v>
+        <v>2439300</v>
       </c>
     </row>
     <row r="111">
@@ -2413,16 +2413,16 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>São Martinho</t>
+          <t>Viveo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SMTO3</t>
+          <t>VVEO3</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2403700</v>
+        <v>2407700</v>
       </c>
     </row>
     <row r="112">
@@ -2431,16 +2431,16 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PetroRecôncavo</t>
+          <t>Eletrobras</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RECV3</t>
+          <t>ELET6</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2373700</v>
+        <v>2369500</v>
       </c>
     </row>
     <row r="113">
@@ -2449,16 +2449,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>GOL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>IGTI11</t>
+          <t>GOLL4</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2362800</v>
+        <v>2052800</v>
       </c>
     </row>
     <row r="114">
@@ -2467,16 +2467,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Jereissati Participações</t>
+          <t>Enjoei</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>IGTI11</t>
+          <t>ENJU3</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2362800</v>
+        <v>2007400</v>
       </c>
     </row>
     <row r="115">
@@ -2485,16 +2485,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Intelbras</t>
+          <t>Dexco</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>INTB3</t>
+          <t>DXCO3</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2351100</v>
+        <v>1961200</v>
       </c>
     </row>
     <row r="116">
@@ -2503,16 +2503,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Azevedo &amp; Travassos</t>
+          <t>Hidrovias do Brasil</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AZEV3</t>
+          <t>HBSA3</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2346100</v>
+        <v>1944900</v>
       </c>
     </row>
     <row r="117">
@@ -2521,16 +2521,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Camil Alimentos</t>
+          <t>Kepler Weber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CAML3</t>
+          <t>KEPL3</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2281200</v>
+        <v>1940400</v>
       </c>
     </row>
     <row r="118">
@@ -2539,16 +2539,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Iochpe-Maxion</t>
+          <t>Portobello</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MYPK3</t>
+          <t>PTBL3</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2266500</v>
+        <v>1929800</v>
       </c>
     </row>
     <row r="119">
@@ -2557,16 +2557,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GPS</t>
+          <t>Gafisa</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GGPS3</t>
+          <t>GFSA3</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2254300</v>
+        <v>1915700</v>
       </c>
     </row>
     <row r="120">
@@ -2575,16 +2575,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Smart Fit</t>
+          <t>Grupo SBF</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SMFT3</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2221500</v>
+        <v>1884500</v>
       </c>
     </row>
     <row r="121">
@@ -2593,16 +2593,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Banrisul</t>
+          <t>Randon</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BRSR6</t>
+          <t>RAPT4</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2121100</v>
+        <v>1877300</v>
       </c>
     </row>
     <row r="122">
@@ -2611,16 +2611,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Grupo SBF</t>
+          <t>Iochpe-Maxion</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>MYPK3</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2092300</v>
+        <v>1875800</v>
       </c>
     </row>
     <row r="123">
@@ -2629,16 +2629,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pague Menos</t>
+          <t>Oi</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PGMN3</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2084900</v>
+        <v>1838700</v>
       </c>
     </row>
     <row r="124">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2043400</v>
+        <v>1834700</v>
       </c>
     </row>
     <row r="125">
@@ -2665,16 +2665,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Viveo</t>
+          <t>Taesa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>VVEO3</t>
+          <t>TAEE11</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1971800</v>
+        <v>1794800</v>
       </c>
     </row>
     <row r="126">
@@ -2683,16 +2683,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Klabin</t>
+          <t>Mitre Realty</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KLBN4</t>
+          <t>MTRE3</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1961300</v>
+        <v>1651700</v>
       </c>
     </row>
     <row r="127">
@@ -2701,16 +2701,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Taesa</t>
+          <t>PetroRecôncavo</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TAEE11</t>
+          <t>RECV3</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1893500</v>
+        <v>1612600</v>
       </c>
     </row>
     <row r="128">
@@ -2719,16 +2719,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Alupar</t>
+          <t>Klabin</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ALUP11</t>
+          <t>KLBN4</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1888100</v>
+        <v>1564800</v>
       </c>
     </row>
     <row r="129">
@@ -2737,16 +2737,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Guararapes</t>
+          <t>Banrisul</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GUAR3</t>
+          <t>BRSR6</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1822300</v>
+        <v>1529300</v>
       </c>
     </row>
     <row r="130">
@@ -2755,16 +2755,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Recrusul</t>
+          <t>Direcional</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>RCSL3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1805000</v>
+        <v>1453200</v>
       </c>
     </row>
     <row r="131">
@@ -2773,16 +2773,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Direcional</t>
+          <t>Wilson Sons</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>PORT3</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1797900</v>
+        <v>1440200</v>
       </c>
     </row>
     <row r="132">
@@ -2791,16 +2791,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>COPASA</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CSMG3</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1774000</v>
+        <v>1422200</v>
       </c>
     </row>
     <row r="133">
@@ -2809,16 +2809,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AZZA3</t>
+          <t>JSLG3</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1734900</v>
+        <v>1327200</v>
       </c>
     </row>
     <row r="134">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Engie</t>
+          <t>IRB Brasil RE</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>EGIE3</t>
+          <t>IRBR3</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1660500</v>
+        <v>1295500</v>
       </c>
     </row>
     <row r="135">
@@ -2845,16 +2845,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Grendene</t>
+          <t>Sanepar</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GRND3</t>
+          <t>SAPR4</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1618000</v>
+        <v>1295100</v>
       </c>
     </row>
     <row r="136">
@@ -2863,16 +2863,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sanepar</t>
+          <t>Plano&amp;Plano</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SAPR4</t>
+          <t>PLPL3</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1412500</v>
+        <v>1272200</v>
       </c>
     </row>
     <row r="137">
@@ -2881,16 +2881,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Eletrobras</t>
+          <t>Camil Alimentos</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ELET6</t>
+          <t>CAML3</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1382500</v>
+        <v>1243600</v>
       </c>
     </row>
     <row r="138">
@@ -2899,16 +2899,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Cury</t>
+          <t>Multilaser</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>MLAS3</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1314400</v>
+        <v>1193700</v>
       </c>
     </row>
     <row r="139">
@@ -2917,16 +2917,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Even</t>
+          <t>IMC Alimentação</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>EVEN3</t>
+          <t>MEAL3</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1290200</v>
+        <v>1183600</v>
       </c>
     </row>
     <row r="140">
@@ -2935,16 +2935,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>IRB Brasil RE</t>
+          <t>Alupar</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>IRBR3</t>
+          <t>ALUP11</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1288000</v>
+        <v>1171200</v>
       </c>
     </row>
     <row r="141">
@@ -2953,16 +2953,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Odontoprev</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ODPV3</t>
+          <t>VLID3</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1271900</v>
+        <v>1165700</v>
       </c>
     </row>
     <row r="142">
@@ -2971,16 +2971,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Aeris Energy</t>
+          <t>Cury</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AERI3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1224800</v>
+        <v>1164300</v>
       </c>
     </row>
     <row r="143">
@@ -2989,16 +2989,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Plano&amp;Plano</t>
+          <t>PDG Realty</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PLPL3</t>
+          <t>PDGR3</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1145700</v>
+        <v>1150900</v>
       </c>
     </row>
     <row r="144">
@@ -3007,16 +3007,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sanepar</t>
+          <t>Banco Pan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SAPR11</t>
+          <t>BPAN4</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1040400</v>
+        <v>1142100</v>
       </c>
     </row>
     <row r="145">
@@ -3025,16 +3025,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Marcopolo</t>
+          <t>Grendene</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>POMO3</t>
+          <t>GRND3</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>982000</v>
+        <v>1107600</v>
       </c>
     </row>
     <row r="146">
@@ -3043,16 +3043,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Armac</t>
+          <t>Guararapes</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ARML3</t>
+          <t>GUAR3</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>951500</v>
+        <v>1089600</v>
       </c>
     </row>
     <row r="147">
@@ -3061,16 +3061,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Irani</t>
+          <t>Positivo</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>RANI3</t>
+          <t>POSI3</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>936700</v>
+        <v>1086400</v>
       </c>
     </row>
     <row r="148">
@@ -3079,16 +3079,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Neoenergia</t>
+          <t>Engie</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>NEOE3</t>
+          <t>EGIE3</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>924900</v>
+        <v>1063300</v>
       </c>
     </row>
     <row r="149">
@@ -3097,16 +3097,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Multilaser</t>
+          <t>Dasa</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MLAS3</t>
+          <t>DASA3</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>910200</v>
+        <v>1034200</v>
       </c>
     </row>
     <row r="150">
@@ -3115,16 +3115,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Banco Pan</t>
+          <t>Zamp</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BPAN4</t>
+          <t>ZAMP3</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>908900</v>
+        <v>1032700</v>
       </c>
     </row>
     <row r="151">
@@ -3133,16 +3133,16 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>3tentos</t>
+          <t>Trisul</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TTEN3</t>
+          <t>TRIS3</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>897600</v>
+        <v>1020200</v>
       </c>
     </row>
     <row r="152">
@@ -3151,16 +3151,16 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Jalles Machado</t>
+          <t>Ferbasa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>JALL3</t>
+          <t>FESA4</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>885100</v>
+        <v>983500</v>
       </c>
     </row>
     <row r="153">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>847900</v>
+        <v>969700</v>
       </c>
     </row>
     <row r="154">
@@ -3187,16 +3187,16 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>AgroGalaxy</t>
+          <t>3tentos</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AGXY3</t>
+          <t>TTEN3</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>843100</v>
+        <v>941700</v>
       </c>
     </row>
     <row r="155">
@@ -3205,16 +3205,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>M. Dias Branco</t>
+          <t>Sanepar</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MDIA3</t>
+          <t>SAPR11</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>814400</v>
+        <v>937800</v>
       </c>
     </row>
     <row r="156">
@@ -3223,16 +3223,16 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mills</t>
+          <t>Armac</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MILS3</t>
+          <t>ARML3</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>776400</v>
+        <v>933800</v>
       </c>
     </row>
     <row r="157">
@@ -3241,16 +3241,16 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Banco ABC Brasil</t>
+          <t>São Martinho</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ABCB4</t>
+          <t>SMTO3</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>743100</v>
+        <v>933600</v>
       </c>
     </row>
     <row r="158">
@@ -3259,16 +3259,16 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Zamp</t>
+          <t>Priner</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ZAMP3</t>
+          <t>PRNR3</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>677700</v>
+        <v>903500</v>
       </c>
     </row>
     <row r="159">
@@ -3277,16 +3277,16 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dasa</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DASA3</t>
+          <t>DESK3</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>666400</v>
+        <v>867900</v>
       </c>
     </row>
     <row r="160">
@@ -3295,16 +3295,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mobly</t>
+          <t>Track &amp; Field</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MBLY3</t>
+          <t>TFCO4</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>666300</v>
+        <v>864200</v>
       </c>
     </row>
     <row r="161">
@@ -3313,16 +3313,16 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Sequoia Logística</t>
+          <t>Neoenergia</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SEQL3</t>
+          <t>NEOE3</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>664400</v>
+        <v>851100</v>
       </c>
     </row>
     <row r="162">
@@ -3331,16 +3331,16 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Wilson Sons</t>
+          <t>Vulcabras</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PORT3</t>
+          <t>VULC3</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>629500</v>
+        <v>837500</v>
       </c>
     </row>
     <row r="163">
@@ -3349,16 +3349,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Odontoprev</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>POSI3</t>
+          <t>ODPV3</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>581500</v>
+        <v>837200</v>
       </c>
     </row>
     <row r="164">
@@ -3367,16 +3367,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>Espaçolaser</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>JSLG3</t>
+          <t>ESPA3</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>579700</v>
+        <v>790800</v>
       </c>
     </row>
     <row r="165">
@@ -3385,16 +3385,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SYN</t>
+          <t>Banco ABC Brasil</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SYNE3</t>
+          <t>ABCB4</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>567200</v>
+        <v>761900</v>
       </c>
     </row>
     <row r="166">
@@ -3403,16 +3403,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Mitre Realty</t>
+          <t>Sequoia Logística</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MTRE3</t>
+          <t>SEQL3</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>541600</v>
+        <v>750800</v>
       </c>
     </row>
     <row r="167">
@@ -3421,16 +3421,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tupy</t>
+          <t>Unipar</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TUPY3</t>
+          <t>UNIP6</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>535400</v>
+        <v>712800</v>
       </c>
     </row>
     <row r="168">
@@ -3439,16 +3439,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mahle Metal Leve</t>
+          <t>Recrusul</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LEVE3</t>
+          <t>RCSL3</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>532000</v>
+        <v>674600</v>
       </c>
     </row>
     <row r="169">
@@ -3457,16 +3457,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Espaçolaser</t>
+          <t>Méliuz</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ESPA3</t>
+          <t>CASH3</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>530000</v>
+        <v>641800</v>
       </c>
     </row>
     <row r="170">
@@ -3475,16 +3475,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Vulcabras</t>
+          <t>OceanPact</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>VULC3</t>
+          <t>OPCT3</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>490700</v>
+        <v>633600</v>
       </c>
     </row>
     <row r="171">
@@ -3493,16 +3493,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ser Educacional</t>
+          <t>Mills</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SEER3</t>
+          <t>MILS3</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>484400</v>
+        <v>610400</v>
       </c>
     </row>
     <row r="172">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>483500</v>
+        <v>558000</v>
       </c>
     </row>
     <row r="173">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>461900</v>
+        <v>556400</v>
       </c>
     </row>
     <row r="174">
@@ -3547,16 +3547,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Schulz</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DESK3</t>
+          <t>SHUL4</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>444700</v>
+        <v>526900</v>
       </c>
     </row>
     <row r="175">
@@ -3565,16 +3565,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Renova Energia</t>
+          <t>HBR Realty</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>RNEW4</t>
+          <t>HBRE3</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>440800</v>
+        <v>526400</v>
       </c>
     </row>
     <row r="176">
@@ -3583,16 +3583,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Cruzeiro do Sul Educacional</t>
+          <t>Melnick</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CSED3</t>
+          <t>MELK3</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>420200</v>
+        <v>508600</v>
       </c>
     </row>
     <row r="177">
@@ -3601,16 +3601,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Boa Safra Sementes</t>
+          <t>Mobly</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SOJA3</t>
+          <t>MBLY3</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>410400</v>
+        <v>507900</v>
       </c>
     </row>
     <row r="178">
@@ -3619,16 +3619,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ferbasa</t>
+          <t>Ser Educacional</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>FESA4</t>
+          <t>SEER3</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>407400</v>
+        <v>503800</v>
       </c>
     </row>
     <row r="179">
@@ -3637,16 +3637,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Enjoei</t>
+          <t>Jalles Machado</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ENJU3</t>
+          <t>JALL3</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>404100</v>
+        <v>494700</v>
       </c>
     </row>
     <row r="180">
@@ -3655,16 +3655,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Track &amp; Field</t>
+          <t>Mater Dei</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TFCO4</t>
+          <t>MATD3</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>396600</v>
+        <v>487300</v>
       </c>
     </row>
     <row r="181">
@@ -3673,16 +3673,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Valid</t>
+          <t>Wiz Soluções</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>VLID3</t>
+          <t>WIZC3</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>393600</v>
+        <v>479800</v>
       </c>
     </row>
     <row r="182">
@@ -3691,16 +3691,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Unifique</t>
+          <t>Cruzeiro do Sul Educacional</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>FIQE3</t>
+          <t>CSED3</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>374200</v>
+        <v>469900</v>
       </c>
     </row>
     <row r="183">
@@ -3709,16 +3709,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Wiz Soluções</t>
+          <t>M. Dias Branco</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>WIZC3</t>
+          <t>MDIA3</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>361800</v>
+        <v>447000</v>
       </c>
     </row>
     <row r="184">
@@ -3727,16 +3727,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Fras-le</t>
+          <t>VITRUBREPCOM</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>FRAS3</t>
+          <t>VTRU3</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>355300</v>
+        <v>438500</v>
       </c>
     </row>
     <row r="185">
@@ -3745,16 +3745,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Trisul</t>
+          <t>Helbor</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>TRIS3</t>
+          <t>HBOR3</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>348200</v>
+        <v>420600</v>
       </c>
     </row>
     <row r="186">
@@ -3763,16 +3763,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LOG CP</t>
+          <t>Orizon</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>LOGG3</t>
+          <t>ORVR3</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>330200</v>
+        <v>415600</v>
       </c>
     </row>
     <row r="187">
@@ -3781,16 +3781,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HBR Realty</t>
+          <t>Lojas Marisa</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>HBRE3</t>
+          <t>AMAR3</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>312900</v>
+        <v>405400</v>
       </c>
     </row>
     <row r="188">
@@ -3799,16 +3799,16 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Orizon</t>
+          <t>SYN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ORVR3</t>
+          <t>SYNE3</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>310500</v>
+        <v>404000</v>
       </c>
     </row>
     <row r="189">
@@ -3817,16 +3817,16 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>VITRUBREPCOM</t>
+          <t>Aeris Energy</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>VTRU3</t>
+          <t>AERI3</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>301300</v>
+        <v>399400</v>
       </c>
     </row>
     <row r="190">
@@ -3835,16 +3835,16 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Renova Energia</t>
+          <t>Tupy</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>RNEW3</t>
+          <t>TUPY3</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>299000</v>
+        <v>382700</v>
       </c>
     </row>
     <row r="191">
@@ -3853,16 +3853,16 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>BrasilAgro</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>AGRO3</t>
+          <t>LIGT3</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>294100</v>
+        <v>380200</v>
       </c>
     </row>
     <row r="192">
@@ -3871,16 +3871,16 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>OceanPact</t>
+          <t>Banco BMG</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>OPCT3</t>
+          <t>BMGB4</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>283300</v>
+        <v>367100</v>
       </c>
     </row>
     <row r="193">
@@ -3889,16 +3889,16 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>IMC Alimentação</t>
+          <t>LOG CP</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>MEAL3</t>
+          <t>LOGG3</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>280200</v>
+        <v>359900</v>
       </c>
     </row>
     <row r="194">
@@ -3907,16 +3907,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Banco BMG</t>
+          <t>Cemig</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BMGB4</t>
+          <t>CMIG3</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>272200</v>
+        <v>338200</v>
       </c>
     </row>
     <row r="195">
@@ -3925,16 +3925,16 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Usiminas</t>
+          <t>Fras-le</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USIM3</t>
+          <t>FRAS3</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>267500</v>
+        <v>333300</v>
       </c>
     </row>
     <row r="196">
@@ -3943,16 +3943,16 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Vittia</t>
+          <t>Klabin</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>VITT3</t>
+          <t>KLBN3</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>264600</v>
+        <v>332300</v>
       </c>
     </row>
     <row r="197">
@@ -3961,16 +3961,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Melnick</t>
+          <t>Blau Farmacêutica</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MELK3</t>
+          <t>BLAU3</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>262600</v>
+        <v>318400</v>
       </c>
     </row>
     <row r="198">
@@ -3979,16 +3979,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Bemobi</t>
+          <t>Unifique</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>BMOB3</t>
+          <t>FIQE3</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>251900</v>
+        <v>316400</v>
       </c>
     </row>
     <row r="199">
@@ -3997,16 +3997,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Klabin</t>
+          <t>Irani</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>KLBN3</t>
+          <t>RANI3</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>246700</v>
+        <v>312500</v>
       </c>
     </row>
     <row r="200">
@@ -4015,16 +4015,16 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Portobello</t>
+          <t>Boa Safra Sementes</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PTBL3</t>
+          <t>SOJA3</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>226300</v>
+        <v>304300</v>
       </c>
     </row>
     <row r="201">
@@ -4033,16 +4033,16 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Priner</t>
+          <t>Usiminas</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>PRNR3</t>
+          <t>USIM3</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>225500</v>
+        <v>298500</v>
       </c>
     </row>
     <row r="202">
@@ -4051,16 +4051,16 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Schulz</t>
+          <t>Mahle Metal Leve</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SHUL4</t>
+          <t>LEVE3</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>224400</v>
+        <v>285600</v>
       </c>
     </row>
     <row r="203">
@@ -4069,16 +4069,16 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Paranapanema</t>
+          <t>Vittia</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>PMAM3</t>
+          <t>VITT3</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>220300</v>
+        <v>258000</v>
       </c>
     </row>
     <row r="204">
@@ -4087,16 +4087,16 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Lopes</t>
+          <t>Dimed</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>LPSB3</t>
+          <t>PNVL3</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>218800</v>
+        <v>257400</v>
       </c>
     </row>
     <row r="205">
@@ -4105,16 +4105,16 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Cambuci</t>
+          <t>Banco Santander</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>CAMB3</t>
+          <t>SANB4</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>217400</v>
+        <v>244900</v>
       </c>
     </row>
     <row r="206">
@@ -4123,16 +4123,16 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Lojas Marisa</t>
+          <t>Eletromidia</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AMAR3</t>
+          <t>ELMD3</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>216300</v>
+        <v>238600</v>
       </c>
     </row>
     <row r="207">
@@ -4141,16 +4141,16 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Taurus</t>
+          <t>Banco Santander</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>TASA4</t>
+          <t>SANB3</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>204300</v>
+        <v>230600</v>
       </c>
     </row>
     <row r="208">
@@ -4159,16 +4159,16 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>BR Partners</t>
+          <t>Marcopolo</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>BRBI11</t>
+          <t>POMO3</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>202300</v>
+        <v>227300</v>
       </c>
     </row>
     <row r="209">
@@ -4177,16 +4177,16 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Itaúsa</t>
+          <t>Taurus</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ITSA3</t>
+          <t>TASA4</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>200000</v>
+        <v>221600</v>
       </c>
     </row>
     <row r="210">
@@ -4195,16 +4195,16 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Dimed</t>
+          <t>Cambuci</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>PNVL3</t>
+          <t>CAMB3</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>196400</v>
+        <v>217600</v>
       </c>
     </row>
     <row r="211">
@@ -4213,16 +4213,16 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Banco Santander</t>
+          <t>BR Partners</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>SANB4</t>
+          <t>BRBI11</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>195600</v>
+        <v>205600</v>
       </c>
     </row>
     <row r="212">
@@ -4231,16 +4231,16 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Cemig</t>
+          <t>Bombril</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>CMIG3</t>
+          <t>BOBR4</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>194700</v>
+        <v>204400</v>
       </c>
     </row>
     <row r="213">
@@ -4249,16 +4249,16 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Helbor</t>
+          <t>Bemobi</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>HBOR3</t>
+          <t>BMOB3</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>189000</v>
+        <v>197700</v>
       </c>
     </row>
     <row r="214">
@@ -4267,16 +4267,16 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Lupatech</t>
+          <t>Taesa</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>LUPA3</t>
+          <t>TAEE4</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>186800</v>
+        <v>187400</v>
       </c>
     </row>
     <row r="215">
@@ -4285,16 +4285,16 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Banco Santander</t>
+          <t>Indústrias ROMI</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SANB3</t>
+          <t>ROMI3</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>176000</v>
+        <v>183900</v>
       </c>
     </row>
     <row r="216">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>175000</v>
+        <v>175800</v>
       </c>
     </row>
     <row r="217">
@@ -4321,16 +4321,16 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Banco Pine</t>
+          <t>Coelce</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>PINE4</t>
+          <t>COCE5</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>166900</v>
+        <v>171400</v>
       </c>
     </row>
     <row r="218">
@@ -4339,16 +4339,16 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Sanepar</t>
+          <t>Brisanet</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SAPR3</t>
+          <t>BRST3</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>164000</v>
+        <v>169400</v>
       </c>
     </row>
     <row r="219">
@@ -4357,16 +4357,16 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Taesa</t>
+          <t>Triunfo</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>TAEE4</t>
+          <t>TPIS3</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>162600</v>
+        <v>167200</v>
       </c>
     </row>
     <row r="220">
@@ -4375,16 +4375,16 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Profarma</t>
+          <t>Fictor Alimentos</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>PFRM3</t>
+          <t>FICT3</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>157500</v>
+        <v>162800</v>
       </c>
     </row>
     <row r="221">
@@ -4393,16 +4393,16 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Mater Dei</t>
+          <t>Ambipar</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>MATD3</t>
+          <t>AMBP3</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>147700</v>
+        <v>158100</v>
       </c>
     </row>
     <row r="222">
@@ -4411,16 +4411,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>BrasilAgro</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>LIGT3</t>
+          <t>AGRO3</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>146800</v>
+        <v>155800</v>
       </c>
     </row>
     <row r="223">
@@ -4429,16 +4429,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Brisanet</t>
+          <t>AgroGalaxy</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>BRST3</t>
+          <t>AGXY3</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>146000</v>
+        <v>152600</v>
       </c>
     </row>
     <row r="224">
@@ -4447,16 +4447,16 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Blau Farmacêutica</t>
+          <t>Itaúsa</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>BLAU3</t>
+          <t>ITSA3</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>143600</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="225">
@@ -4465,16 +4465,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Unipar</t>
+          <t>Sanepar</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>UNIP6</t>
+          <t>SAPR3</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>139600</v>
+        <v>122300</v>
       </c>
     </row>
     <row r="226">
@@ -4483,16 +4483,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Time For Fun</t>
+          <t>Banco Pine</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>SHOW3</t>
+          <t>PINE4</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>131000</v>
+        <v>120500</v>
       </c>
     </row>
     <row r="227">
@@ -4501,16 +4501,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>João Fortes</t>
+          <t>São Carlos</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>JFEN3</t>
+          <t>SCAR3</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>130500</v>
+        <v>113700</v>
       </c>
     </row>
     <row r="228">
@@ -4519,16 +4519,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>CSU Cardsystem</t>
+          <t>Profarma</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CSUD3</t>
+          <t>PFRM3</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>125500</v>
+        <v>110200</v>
       </c>
     </row>
     <row r="229">
@@ -4537,16 +4537,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>São Carlos</t>
+          <t>Lopes</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>SCAR3</t>
+          <t>LPSB3</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>111200</v>
+        <v>108800</v>
       </c>
     </row>
     <row r="230">
@@ -4555,16 +4555,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Eternit</t>
+          <t>Paranapanema</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ETER3</t>
+          <t>PMAM3</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>110000</v>
+        <v>107400</v>
       </c>
     </row>
     <row r="231">
@@ -4573,16 +4573,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Kora Saúde</t>
+          <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>KRSA3</t>
+          <t>ATED3</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>104800</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="232">
@@ -4591,16 +4591,16 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>D1000 Varejo Farma</t>
+          <t>Renova Energia</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DMVF3</t>
+          <t>RNEW4</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>94500</v>
+        <v>96900</v>
       </c>
     </row>
     <row r="233">
@@ -4609,16 +4609,16 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Allied</t>
+          <t>Taesa</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ALLD3</t>
+          <t>TAEE3</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>94200</v>
+        <v>89800</v>
       </c>
     </row>
     <row r="234">
@@ -4627,16 +4627,16 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Log-In</t>
+          <t>Unicasa</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>LOGN3</t>
+          <t>UCAS3</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>85000</v>
+        <v>88900</v>
       </c>
     </row>
     <row r="235">
@@ -4645,16 +4645,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Unicasa</t>
+          <t>Eternit</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>UCAS3</t>
+          <t>ETER3</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>84200</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="236">
@@ -4663,16 +4663,16 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Dexxos</t>
+          <t>Electro Aço Altona</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DEXP3</t>
+          <t>EALT4</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>82200</v>
+        <v>73900</v>
       </c>
     </row>
     <row r="237">
@@ -4681,16 +4681,16 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Estapar</t>
+          <t>Renova Energia</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ALPK3</t>
+          <t>RNEW3</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>79300</v>
+        <v>72100</v>
       </c>
     </row>
     <row r="238">
@@ -4699,16 +4699,16 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Ambipar</t>
+          <t>Lupatech</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>AMBP3</t>
+          <t>LUPA3</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>79100</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="239">
@@ -4717,16 +4717,16 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Eletromidia</t>
+          <t>Dexxos</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ELMD3</t>
+          <t>DEXP3</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>76800</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="240">
@@ -4735,16 +4735,16 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Indústrias ROMI</t>
+          <t>Bradespar</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ROMI3</t>
+          <t>BRAP3</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>76500</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="241">
@@ -4753,16 +4753,16 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Viver</t>
+          <t>Jereissati Participações</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>VIVR3</t>
+          <t>IGTI3</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>75800</v>
+        <v>62100</v>
       </c>
     </row>
     <row r="242">
@@ -4771,16 +4771,16 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Technos</t>
+          <t>Iguatemi</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>TECN3</t>
+          <t>IGTI3</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>70700</v>
+        <v>62100</v>
       </c>
     </row>
     <row r="243">
@@ -4789,16 +4789,16 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Bradespar</t>
+          <t>Viver</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>BRAP3</t>
+          <t>VIVR3</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>64100</v>
+        <v>56400</v>
       </c>
     </row>
     <row r="244">
@@ -4807,16 +4807,16 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Taesa</t>
+          <t>Technos</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>TAEE3</t>
+          <t>TECN3</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>58800</v>
+        <v>52700</v>
       </c>
     </row>
     <row r="245">
@@ -4825,16 +4825,16 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Biomm</t>
+          <t>Estapar</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>BIOM3</t>
+          <t>ALPK3</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>50400</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="246">
@@ -4843,16 +4843,16 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>LE LIS BLANC</t>
+          <t>Time For Fun</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>VSTE3</t>
+          <t>SHOW3</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>49700</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="247">
@@ -4861,16 +4861,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Tecnisa</t>
+          <t>CSU Cardsystem</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>TCSA3</t>
+          <t>CSUD3</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>41100</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="248">
@@ -4879,16 +4879,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Neogrid</t>
+          <t>D1000 Varejo Farma</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>NGRD3</t>
+          <t>DMVF3</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>36500</v>
+        <v>47300</v>
       </c>
     </row>
     <row r="249">
@@ -4897,16 +4897,16 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Energisa</t>
+          <t>Log-In</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ENGI4</t>
+          <t>LOGN3</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>32400</v>
+        <v>41100</v>
       </c>
     </row>
     <row r="250">
@@ -4915,16 +4915,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Eucatex</t>
+          <t>Tecnisa</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>EUCA4</t>
+          <t>TCSA3</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>31900</v>
+        <v>39100</v>
       </c>
     </row>
     <row r="251">
@@ -4933,16 +4933,16 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Bombril</t>
+          <t>Metalúrgica Gerdau</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>BOBR4</t>
+          <t>GOAU3</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>31800</v>
+        <v>38900</v>
       </c>
     </row>
     <row r="252">
@@ -4951,16 +4951,16 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Alliança</t>
+          <t>Rossi Residencial</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>AALR3</t>
+          <t>RSID3</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>31300</v>
+        <v>38700</v>
       </c>
     </row>
     <row r="253">
@@ -4969,16 +4969,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>WDC Networks</t>
+          <t>Biomm</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>LVTC3</t>
+          <t>BIOM3</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>29600</v>
+        <v>38600</v>
       </c>
     </row>
     <row r="254">
@@ -4987,16 +4987,16 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Braskem</t>
+          <t>João Fortes</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>BRKM3</t>
+          <t>JFEN3</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>29300</v>
+        <v>28100</v>
       </c>
     </row>
     <row r="255">
@@ -5005,16 +5005,16 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Fertilizantes Heringer</t>
+          <t>WDC Networks</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>FHER3</t>
+          <t>LVTC3</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>28800</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="256">
@@ -5023,16 +5023,16 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Metalúrgica Gerdau</t>
+          <t>Alpargatas</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>GOAU3</t>
+          <t>ALPA3</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>28000</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="257">
@@ -5041,16 +5041,16 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Gerdau</t>
+          <t>Inepar</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>GGBR3</t>
+          <t>INEP3</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>25500</v>
+        <v>25400</v>
       </c>
     </row>
     <row r="258">
@@ -5059,16 +5059,16 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Energisa</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>IGTI3</t>
+          <t>ENGI4</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>24700</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="259">
@@ -5077,16 +5077,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Jereissati Participações</t>
+          <t>Allied</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>IGTI3</t>
+          <t>ALLD3</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>24700</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="260">
@@ -5095,16 +5095,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Randon</t>
+          <t>Kora Saúde</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>RAPT3</t>
+          <t>KRSA3</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>24100</v>
+        <v>20700</v>
       </c>
     </row>
     <row r="261">
@@ -5113,16 +5113,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Sansuy</t>
+          <t>Lojas Marisa</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>SNSY5</t>
+          <t>AMAR11</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>23100</v>
+        <v>20700</v>
       </c>
     </row>
     <row r="262">
@@ -5131,16 +5131,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Fictor Alimentos</t>
+          <t>Haga</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>FICT3</t>
+          <t>HAGA4</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>21600</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="263">
@@ -5149,16 +5149,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Haga</t>
+          <t>Alupar</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>HAGA4</t>
+          <t>ALUP4</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>20700</v>
+        <v>19700</v>
       </c>
     </row>
     <row r="264">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Traders Club</t>
+          <t>Braskem</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>TRAD3</t>
+          <t>BRKM3</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -5185,16 +5185,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Inepar</t>
+          <t>Traders Club</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>INEP3</t>
+          <t>TRAD3</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>18900</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="266">
@@ -5203,16 +5203,16 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Banestes</t>
+          <t>DASA11</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>BEES3</t>
+          <t>DASA11</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>17700</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="267">
@@ -5221,16 +5221,16 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Whirlpool</t>
+          <t>Eucatex</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>WHRL4</t>
+          <t>EUCA4</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>16800</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="268">
@@ -5239,16 +5239,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Dotz</t>
+          <t>Padtec</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>DOTZ3</t>
+          <t>PDTC3</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>16500</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="269">
@@ -5257,16 +5257,16 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Terra Santa</t>
+          <t>Unipar</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>LAND3</t>
+          <t>UNIP3</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>15700</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="270">
@@ -5275,16 +5275,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Atma</t>
+          <t>REAG3</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ATMP3</t>
+          <t>REAG3</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>14800</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="271">
@@ -5293,16 +5293,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Alupar</t>
+          <t>Gerdau</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ALUP4</t>
+          <t>GGBR3</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>13600</v>
+        <v>15800</v>
       </c>
     </row>
     <row r="272">
@@ -5311,16 +5311,16 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Padtec</t>
+          <t>Terra Santa</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>PDTC3</t>
+          <t>LAND3</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>13500</v>
+        <v>15700</v>
       </c>
     </row>
     <row r="273">
@@ -5329,16 +5329,16 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Alupar</t>
+          <t>Fertilizantes Heringer</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ALUP3</t>
+          <t>FHER3</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>12900</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="274">
@@ -5347,16 +5347,16 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>Banco Mercantil do Brasil</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>CEBR6</t>
+          <t>BMEB4</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>12800</v>
+        <v>14800</v>
       </c>
     </row>
     <row r="275">
@@ -5365,16 +5365,16 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Equatorial Energia Pará</t>
+          <t>Randon</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>EQPA3</t>
+          <t>RAPT3</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>12500</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="276">
@@ -5383,16 +5383,16 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Inepar</t>
+          <t>Sansuy</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>INEP4</t>
+          <t>SNSY5</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>11500</v>
+        <v>12700</v>
       </c>
     </row>
     <row r="277">
@@ -5401,16 +5401,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Coelce</t>
+          <t>Neogrid</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>COCE5</t>
+          <t>NGRD3</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>11100</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="278">
@@ -5419,16 +5419,16 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Energisa</t>
+          <t>Dotz</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ENGI3</t>
+          <t>DOTZ3</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>10700</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="279">
@@ -5437,16 +5437,16 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Sansuy</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>SNSY3</t>
+          <t>CEBR6</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>10500</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="280">
@@ -5455,16 +5455,16 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Pettenati</t>
+          <t>Alliança</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>PTNT4</t>
+          <t>AALR3</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>9600</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="281">
@@ -5473,16 +5473,16 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Taurus</t>
+          <t>Banco BTG Pactual</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>TASA3</t>
+          <t>BPAC3</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>9400</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="282">
@@ -5491,16 +5491,16 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Banco Mercantil do Brasil</t>
+          <t>Renova Energia</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>BMEB4</t>
+          <t>RNEW11</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>9300</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="283">
@@ -5509,16 +5509,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
+          <t>Whirlpool</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ATED3</t>
+          <t>WHRL4</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>9100</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="284">
@@ -5527,16 +5527,16 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>REAG3</t>
+          <t>EMAE</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>REAG3</t>
+          <t>EMAE4</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>8800</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="285">
@@ -5545,16 +5545,16 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Oi</t>
+          <t>Inepar</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>OIBR4</t>
+          <t>INEP4</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>8200</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="286">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Electro Aço Altona</t>
+          <t>Banrisul</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>EALT4</t>
+          <t>BRSR3</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -5581,16 +5581,16 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Embpar Participações</t>
+          <t>Santanense</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>EPAR3</t>
+          <t>CTSA4</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>7400</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="288">
@@ -5599,16 +5599,16 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>RNI</t>
+          <t>Azevedo &amp; Travassos</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>RDNI3</t>
+          <t>AZEV11</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>7400</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="289">
@@ -5617,16 +5617,16 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>WLM</t>
+          <t>Grazziotin</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>WLMM4</t>
+          <t>CGRA4</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>7200</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="290">
@@ -5635,16 +5635,16 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Renova Energia</t>
+          <t>Energisa</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>RNEW11</t>
+          <t>ENGI3</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="291">
@@ -5653,16 +5653,16 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Baumer</t>
+          <t>Alupar</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>BALM4</t>
+          <t>ALUP3</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>5700</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="292">
@@ -5671,16 +5671,16 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Azevedo &amp; Travassos</t>
+          <t>Banestes</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>AZEV11</t>
+          <t>BEES3</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>5500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="293">
@@ -5689,16 +5689,16 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Whirlpool</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>WHRL3</t>
+          <t>CEBR3</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>5400</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="294">
@@ -5707,16 +5707,16 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DASA11</t>
+          <t>Banco Pine</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>DASA11</t>
+          <t>PINE3</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>5300</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="295">
@@ -5725,16 +5725,16 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Unipar</t>
+          <t>Banco BTG Pactual</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>UNIP3</t>
+          <t>BPAC5</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>5100</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="296">
@@ -5743,16 +5743,16 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Minupar</t>
+          <t>Metisa</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>MNPR3</t>
+          <t>MTSA4</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>4900</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="297">
@@ -5761,16 +5761,16 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Grazziotin</t>
+          <t>RNI</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>CGRA4</t>
+          <t>RDNI3</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>4900</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="298">
@@ -5779,16 +5779,16 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Celesc</t>
+          <t>Embpar Participações</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>CLSC4</t>
+          <t>EPAR3</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>4400</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="299">
@@ -5797,16 +5797,16 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Alpargatas</t>
+          <t>Grazziotin</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>ALPA3</t>
+          <t>CGRA3</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>3800</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="300">
@@ -5815,16 +5815,16 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Metisa</t>
+          <t>Pettenati</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>MTSA4</t>
+          <t>PTNT4</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>3700</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="301">
@@ -5833,16 +5833,16 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>OSX Brasil</t>
+          <t>Taurus</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>OSXB3</t>
+          <t>TASA3</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>3700</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="302">
@@ -5851,16 +5851,16 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Banco BTG Pactual</t>
+          <t>Metalúrgica Riosulense</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>BPAC5</t>
+          <t>RSUL4</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>3500</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="303">
@@ -5869,16 +5869,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Triunfo</t>
+          <t>Ourofino Saúde Animal</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>TPIS3</t>
+          <t>OFSA3</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>3200</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="304">
@@ -5887,16 +5887,16 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>ISA Energia</t>
+          <t>Banestes</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ISAE3</t>
+          <t>BEES4</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>3100</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="305">
@@ -5905,16 +5905,16 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Westwing</t>
+          <t>Oi</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>WEST3</t>
+          <t>OIBR4</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>3100</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="306">
@@ -5923,16 +5923,16 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Dexxos</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>DEXP4</t>
+          <t>CEBR5</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>2900</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="307">
@@ -5941,16 +5941,16 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Mundial</t>
+          <t>Equatorial Energia Pará</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>MNDL3</t>
+          <t>EQPA3</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>2700</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="308">
@@ -5959,16 +5959,16 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Rede Energia</t>
+          <t>Mercantil do Brasil Financeira</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>REDE3</t>
+          <t>MERC4</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>2700</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="309">
@@ -5977,16 +5977,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Alfa Holdings</t>
+          <t>Telebras</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>RPAD3</t>
+          <t>TELB3</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>2700</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="310">
@@ -5995,16 +5995,16 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Electro Aço Altona</t>
+          <t>Hotéis Othon</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>EALT3</t>
+          <t>HOOT4</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>2600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="311">
@@ -6013,16 +6013,16 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Banco BTG Pactual</t>
+          <t>Celesc</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>BPAC3</t>
+          <t>CLSC4</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>2500</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="312">
@@ -6031,16 +6031,16 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Banestes</t>
+          <t>Banese</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>BEES4</t>
+          <t>BGIP4</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>2500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="313">
@@ -6049,16 +6049,16 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Santanense</t>
+          <t>Banco de Brasília</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>CTSA4</t>
+          <t>BSLI3</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>2500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="314">
@@ -6067,16 +6067,16 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Banco da Amazônia</t>
+          <t>Atma</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>BAZA3</t>
+          <t>ATMP3</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>2400</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="315">
@@ -6085,16 +6085,16 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Telebras</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>AVLL3</t>
+          <t>TELB4</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>2400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="316">
@@ -6103,16 +6103,16 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Telebras</t>
+          <t>Nutriplant</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>TELB4</t>
+          <t>NUTR3</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>2300</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="317">
@@ -6121,16 +6121,16 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Banrisul</t>
+          <t>Rede Energia</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>BRSR3</t>
+          <t>REDE3</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>2200</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="318">
@@ -6139,16 +6139,16 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Banese</t>
+          <t>Unipar</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>BGIP4</t>
+          <t>UNIP5</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>2000</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="319">
@@ -6157,16 +6157,16 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Ourofino Saúde Animal</t>
+          <t>Minupar</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>OFSA3</t>
+          <t>MNPR3</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1900</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="320">
@@ -6175,16 +6175,16 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>Pettenati</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>CEBR3</t>
+          <t>PTNT3</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="321">
@@ -6193,16 +6193,16 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Lojas Marisa</t>
+          <t>Whirlpool</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>AMAR11</t>
+          <t>WHRL3</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="322">
@@ -6211,16 +6211,16 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Refinaria de Manguinhos</t>
+          <t>OSX Brasil</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>RPMG3</t>
+          <t>OSXB3</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="323">
@@ -6229,16 +6229,16 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Rossi Residencial</t>
+          <t>Refinaria de Manguinhos</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>RSID3</t>
+          <t>RPMG3</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="324">
@@ -6247,16 +6247,16 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Bardella</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>BDLL4</t>
+          <t>AVLL3</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="325">
@@ -6265,16 +6265,16 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Banco Pine</t>
+          <t>COELBA</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>PINE3</t>
+          <t>CEEB3</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="326">
@@ -6283,16 +6283,16 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Banco de Brasília</t>
+          <t>Eucatex</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>BSLI3</t>
+          <t>EUCA3</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="327">
@@ -6301,16 +6301,16 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Nutriplant</t>
+          <t>ISA Energia</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>NUTR3</t>
+          <t>ISAE3</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="328">
@@ -6319,16 +6319,16 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Metalúrgica Riosulense</t>
+          <t>Cedro Têxtil</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>RSUL4</t>
+          <t>CEDO4</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>1100</v>
+        <v>700</v>
       </c>
     </row>
     <row r="329">
@@ -6337,16 +6337,16 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>Brasil Brokers</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>CEBR5</t>
+          <t>NEXP3</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>1100</v>
+        <v>700</v>
       </c>
     </row>
     <row r="330">
@@ -6355,16 +6355,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>BIED3</t>
+          <t>Banco da Amazônia</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>BIED3</t>
+          <t>BAZA3</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="331">
@@ -6373,16 +6373,16 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Plascar</t>
+          <t>Elektro</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>PLAS3</t>
+          <t>EKTR4</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="332">
@@ -6391,16 +6391,16 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Alfa Holdings</t>
+          <t>Tronox Pigmentos</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>RPAD5</t>
+          <t>CRPG5</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="333">
@@ -6409,16 +6409,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Comgás</t>
+          <t>Afluente T</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>CGAS5</t>
+          <t>AFLT3</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="334">
@@ -6427,16 +6427,16 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Monteiro Aranha</t>
+          <t>LE LIS BLANC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>MOAR3</t>
+          <t>VSTE3</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="335">
@@ -6445,16 +6445,16 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Tronox Pigmentos</t>
+          <t>Monteiro Aranha</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>CRPG5</t>
+          <t>MOAR3</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row r="336">
@@ -6463,16 +6463,16 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Banco de Brasília</t>
+          <t>Mundial</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>BSLI4</t>
+          <t>MNDL3</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row r="337">
@@ -6481,16 +6481,16 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Haga</t>
+          <t>Habitasul</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>HAGA3</t>
+          <t>HBTS5</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
     </row>
     <row r="338">
@@ -6499,16 +6499,16 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Unipar</t>
+          <t>Copel</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>UNIP5</t>
+          <t>CPLE5</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="339">
@@ -6517,16 +6517,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Grazziotin</t>
+          <t>Comgás</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>CGRA3</t>
+          <t>CGAS5</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
     </row>
     <row r="340">
@@ -6535,16 +6535,16 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Karsten</t>
+          <t>Tekno</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>CTKA4</t>
+          <t>TKNO4</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="341">
@@ -6553,16 +6553,16 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Cedro Têxtil</t>
+          <t>WLM</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>CEDO4</t>
+          <t>WLMM4</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="342">
@@ -6571,16 +6571,16 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Eucatex</t>
+          <t>Electro Aço Altona</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>EUCA3</t>
+          <t>EALT3</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="343">
@@ -6589,16 +6589,16 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Döhler</t>
+          <t>Dexxos</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>DOHL4</t>
+          <t>DEXP4</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="344">
@@ -6607,16 +6607,16 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Alfa Holdings</t>
+          <t>Nordon</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>RPAD6</t>
+          <t>NORD3</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="345">
@@ -6625,16 +6625,16 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Rio Paranapanema Energia</t>
+          <t>Westwing</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>GEPA3</t>
+          <t>WEST3</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="346">
@@ -6643,16 +6643,16 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Equatorial Maranhão</t>
+          <t>Alfa Holdings</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>EQMA3B</t>
+          <t>RPAD6</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="347">
@@ -6661,16 +6661,16 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Telebras</t>
+          <t>PPLA</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>TELB3</t>
+          <t>PPLA11</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>400</v>
+        <v>138</v>
       </c>
     </row>
     <row r="348">
@@ -6679,16 +6679,16 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Equatorial Energia Pará</t>
+          <t>Comgás</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>EQPA5</t>
+          <t>CGAS3</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
     </row>
     <row r="349">
@@ -6697,16 +6697,16 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Brasil Brokers</t>
+          <t>Celesc</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>NEXP3</t>
+          <t>CLSC3</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
     </row>
     <row r="350">
@@ -6715,16 +6715,16 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Eletropar</t>
+          <t>Rio Paranapanema Energia</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>LIPR3</t>
+          <t>GEPA3</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="351">
@@ -6733,16 +6733,16 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PPLA</t>
+          <t>Rio Paranapanema Energia</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>PPLA11</t>
+          <t>GEPA4</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>216</v>
+        <v>100</v>
       </c>
     </row>
     <row r="352">
@@ -6751,16 +6751,16 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Metalfrio</t>
+          <t>Karsten</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>FRIO3</t>
+          <t>CTKA4</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="353">
@@ -6769,16 +6769,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Banco do Nordeste</t>
+          <t>Banco Mercantil de Investimentos</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>BNBR3</t>
+          <t>BMIN4</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="354">
@@ -6787,16 +6787,16 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Bardella</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>BAUH4</t>
+          <t>BDLL3</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="355">
@@ -6805,16 +6805,16 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Wetzel</t>
+          <t>Plascar</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>MWET4</t>
+          <t>PLAS3</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="356">
@@ -6823,16 +6823,16 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Jereissati Participações</t>
+          <t>Döhler</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>IGTI4</t>
+          <t>DOHL3</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="357">
@@ -6841,16 +6841,16 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>BIED3</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>IGTI4</t>
+          <t>BIED3</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="358">
@@ -6859,16 +6859,16 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Comgás</t>
+          <t>Monark</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>CGAS3</t>
+          <t>BMKS3</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="359">
@@ -6877,16 +6877,16 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Celesc</t>
+          <t>Sansuy</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>CLSC3</t>
+          <t>SNSY3</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>100</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="360">
@@ -6895,16 +6895,16 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Elektro</t>
+          <t>Trevisa</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>EKTR4</t>
+          <t>LUXM4</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>100</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="361">
@@ -6913,16 +6913,16 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>COELBA</t>
+          <t>Mangels</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>CEEB3</t>
+          <t>MGEL4</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>100</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="362">
@@ -6936,11 +6936,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>MRSA6B</t>
+          <t>MRSA3B</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="363">
@@ -6949,16 +6949,16 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MRS Logística</t>
+          <t>Participações Aliança da Bahia</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>MRSA5B</t>
+          <t>PEAB3</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="364">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Banese</t>
+          <t>Eletropar</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>BGIP3</t>
+          <t>LIPR3</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Banco Mercantil de Investimentos</t>
+          <t>Karsten</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>BMIN4</t>
+          <t>CTKA3</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Pettenati</t>
+          <t>Ferbasa</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>PTNT3</t>
+          <t>FESA3</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Santanense</t>
+          <t>Cemepe</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>CTSA3</t>
+          <t>MAPT3</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -7039,16 +7039,16 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Monark</t>
+          <t>Cedro Têxtil</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>BMKS3</t>
+          <t>CEDO3</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>32</v>
+        <v>700</v>
       </c>
     </row>
     <row r="369">
@@ -7057,16 +7057,16 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Rio Paranapanema Energia</t>
+          <t>Banco de Brasília</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>GEPA4</t>
+          <t>BSLI4</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>4800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="370">
@@ -7075,16 +7075,16 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>EMAE</t>
+          <t>Döhler</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>EMAE4</t>
+          <t>DOHL4</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>2600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="371">
@@ -7093,16 +7093,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Hotéis Othon</t>
+          <t>Biomm</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>HOOT4</t>
+          <t>BIOM11</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1700</v>
+        <v>300</v>
       </c>
     </row>
     <row r="372">
@@ -7111,16 +7111,16 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>MRS Logística</t>
+          <t>Coelce</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>MRSA3B</t>
+          <t>COCE3</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="373">
@@ -7129,16 +7129,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>São Paulo Turismo</t>
+          <t>Santanense</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>AHEB3</t>
+          <t>CTSA3</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="374">
@@ -7147,16 +7147,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Mangels</t>
+          <t>Energisa MT</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>MGEL4</t>
+          <t>ENMT3</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="375">
@@ -7165,16 +7165,16 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Sondotécnica</t>
+          <t>Banrisul</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>SOND6</t>
+          <t>BRSR5</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="376">
@@ -7183,16 +7183,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Coelce</t>
+          <t>Wetzel</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>COCE3</t>
+          <t>MWET4</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="377">
@@ -7201,16 +7201,16 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Biomm</t>
+          <t>Alfa Holdings</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>BIOM11</t>
+          <t>RPAD3</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="378">
@@ -7219,12 +7219,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>São Paulo Turismo</t>
+          <t>Haga</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>AHEB6</t>
+          <t>HAGA3</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -7237,16 +7237,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Sondotécnica</t>
+          <t>Baumer</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>SOND5</t>
+          <t>BALM4</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="380">
@@ -7255,16 +7255,16 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Banco Mercantil do Brasil</t>
+          <t>Tronox Pigmentos</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>BMEB3</t>
+          <t>CRPG6</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="381">
@@ -7273,16 +7273,16 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>CELGPAR</t>
+          <t>COELBA</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>GPAR3</t>
+          <t>CEEB5</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="382">
@@ -7291,16 +7291,16 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Banrisul</t>
+          <t>Banco Mercantil de Investimentos</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>BRSR5</t>
+          <t>BMIN3</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="383">
@@ -7309,16 +7309,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Copel</t>
+          <t>Sondotécnica</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>CPLE5</t>
+          <t>SOND6</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="384">
@@ -7327,12 +7327,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Afluente T</t>
+          <t>MRS Logística</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>AFLT3</t>
+          <t>MRSA5B</t>
         </is>
       </c>
       <c r="D384" t="n">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Dtcom</t>
+          <t>Panatlântica</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>DTCY3</t>
+          <t>PATI3</t>
         </is>
       </c>
       <c r="D385" t="n">
@@ -7363,16 +7363,16 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Estrela</t>
+          <t>Hercules</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ESTR4</t>
+          <t>HETA4</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="387">
@@ -7381,16 +7381,16 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Fica</t>
+          <t>Metalfrio</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>FIEI3</t>
+          <t>FRIO3</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="388">
@@ -7399,16 +7399,16 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Ferbasa</t>
+          <t>Banco do Nordeste</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>FESA3</t>
+          <t>BNBR3</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="389">
@@ -7417,16 +7417,16 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Nordon</t>
+          <t>Banco Mercantil do Brasil</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>NORD3</t>
+          <t>BMEB3</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="390">
@@ -7435,16 +7435,16 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Tronox Pigmentos</t>
+          <t>MRS Logística</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>CRPG6</t>
+          <t>MRSA6B</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="391">
@@ -7453,16 +7453,16 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Participações Aliança da Bahia</t>
+          <t>Equatorial Maranhão</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>PEAB4</t>
+          <t>EQMA3B</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="392">
@@ -7471,16 +7471,16 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Participações Aliança da Bahia</t>
+          <t>Cemepe</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>PEAB3</t>
+          <t>MAPT4</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
     </row>
     <row r="393">
@@ -7489,16 +7489,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>São Paulo Turismo</t>
+          <t>Bardella</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>AHEB5</t>
+          <t>BDLL4</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="394">
@@ -7507,16 +7507,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Hercules</t>
+          <t>Alfa Holdings</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>HETA4</t>
+          <t>RPAD5</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="395">
@@ -7525,16 +7525,16 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Tekno</t>
+          <t>Equatorial Energia Pará</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>TKNO4</t>
+          <t>EQPA5</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="396">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Bardella</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>BDLL3</t>
+          <t>BAUH4</t>
         </is>
       </c>
       <c r="D396" t="n">
@@ -7561,16 +7561,16 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Energisa MT</t>
+          <t>Jereissati Participações</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>ENMT3</t>
+          <t>IGTI4</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="398">
@@ -7579,16 +7579,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Habitasul</t>
+          <t>Iguatemi</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>HBTS5</t>
+          <t>IGTI4</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="399">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Josapar</t>
+          <t>Banese</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>JOPA3</t>
+          <t>BGIP3</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -7615,16 +7615,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Banco Pine</t>
+          <t>São Paulo Turismo</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>PINE11</t>
+          <t>AHEB3</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="401">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>PORTO VM</t>
+          <t>São Paulo Turismo</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>PSVM11</t>
+          <t>AHEB6</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -7651,16 +7651,16 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Cedro Têxtil</t>
+          <t>Sondotécnica</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>CEDO3</t>
+          <t>SOND5</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="403">
@@ -7669,16 +7669,16 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Braskem</t>
+          <t>CELGPAR</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>BRKM6</t>
+          <t>GPAR3</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="404">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Energisa MT</t>
+          <t>Dtcom</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>ENMT4</t>
+          <t>DTCY3</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -7705,16 +7705,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Metisa</t>
+          <t>Estrela</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>MTSA3</t>
+          <t>ESTR4</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>8000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="406">
@@ -7723,70 +7723,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Panatlântica</t>
+          <t>Fica</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>PATI3</t>
+          <t>FIEI3</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="1" t="n">
-        <v>405</v>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Mercantil do Brasil Financeira</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>MERC4</t>
-        </is>
-      </c>
-      <c r="D407" t="n">
         <v>500</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="1" t="n">
-        <v>406</v>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>WLM</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>WLMM3</t>
-        </is>
-      </c>
-      <c r="D408" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="1" t="n">
-        <v>407</v>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Baumer</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>BALM3</t>
-        </is>
-      </c>
-      <c r="D409" t="n">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Bases/Lista de ações.xlsx
+++ b/Bases/Lista de ações.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D406"/>
+  <dimension ref="A1:D403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Volume no último dia útil (lido em 15/03/2025)</t>
+          <t>Volume no último dia útil (lido em 16/03/2025)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42086800</v>
+        <v>42077200</v>
       </c>
     </row>
     <row r="8">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26742900</v>
+        <v>26742800</v>
       </c>
     </row>
     <row r="18">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>22864500</v>
+        <v>22864700</v>
       </c>
     </row>
     <row r="21">
@@ -2067,4084 +2067,4084 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jereissati Participações</t>
+          <t>YDUQS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IGTI11</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3442400</v>
+        <v>3397800</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YDUQS</t>
+          <t>TIM</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>TIMS3</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3397800</v>
+        <v>3385300</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TIM</t>
+          <t>Caixa Seguridade</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TIMS3</t>
+          <t>CXSE3</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3385300</v>
+        <v>3329200</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Caixa Seguridade</t>
+          <t>Pague Menos</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CXSE3</t>
+          <t>PGMN3</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3329200</v>
+        <v>3284100</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pague Menos</t>
+          <t>Even</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PGMN3</t>
+          <t>EVEN3</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3284100</v>
+        <v>3149800</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Even</t>
+          <t>Klabin</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EVEN3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3149800</v>
+        <v>3103700</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Klabin</t>
+          <t>Oncoclínicas</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>ONCO3</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3103700</v>
+        <v>3056100</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Oncoclínicas</t>
+          <t>Smart Fit</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ONCO3</t>
+          <t>SMFT3</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3056100</v>
+        <v>3017900</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Smart Fit</t>
+          <t>COPASA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SMFT3</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3017900</v>
+        <v>2921400</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COPASA</t>
+          <t>CPFL Energia</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CSMG3</t>
+          <t>CPFE3</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2921400</v>
+        <v>2901800</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CPFL Energia</t>
+          <t>Hypera</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CPFE3</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2901800</v>
+        <v>2825500</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hypera</t>
+          <t>Vivo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2825500</v>
+        <v>2810300</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Vivo</t>
+          <t>ClearSale</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VIVT3</t>
+          <t>CLSA3</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2810300</v>
+        <v>2725300</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ClearSale</t>
+          <t>GPS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CLSA3</t>
+          <t>GGPS3</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2725300</v>
+        <v>2660800</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GPS</t>
+          <t>Fleury</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GGPS3</t>
+          <t>FLRY3</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2660800</v>
+        <v>2656800</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Fleury</t>
+          <t>Energisa</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FLRY3</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2656800</v>
+        <v>2635600</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Energisa</t>
+          <t>Grupo Mateus</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ENGI11</t>
+          <t>GMAT3</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2635600</v>
+        <v>2595300</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Grupo Mateus</t>
+          <t>Alpargatas</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GMAT3</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2595300</v>
+        <v>2439400</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Alpargatas</t>
+          <t>Viveo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ALPA4</t>
+          <t>VVEO3</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2439300</v>
+        <v>2407700</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Viveo</t>
+          <t>Eletrobras</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VVEO3</t>
+          <t>ELET6</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2407700</v>
+        <v>2369500</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Eletrobras</t>
+          <t>GOL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ELET6</t>
+          <t>GOLL4</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2369500</v>
+        <v>2052800</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GOL</t>
+          <t>Enjoei</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GOLL4</t>
+          <t>ENJU3</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2052800</v>
+        <v>2007400</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Enjoei</t>
+          <t>Dexco</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ENJU3</t>
+          <t>DXCO3</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2007400</v>
+        <v>1961200</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Dexco</t>
+          <t>Hidrovias do Brasil</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DXCO3</t>
+          <t>HBSA3</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1961200</v>
+        <v>1944900</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hidrovias do Brasil</t>
+          <t>Kepler Weber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HBSA3</t>
+          <t>KEPL3</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1944900</v>
+        <v>1940400</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Kepler Weber</t>
+          <t>Portobello</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KEPL3</t>
+          <t>PTBL3</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1940400</v>
+        <v>1929800</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Portobello</t>
+          <t>Gafisa</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PTBL3</t>
+          <t>GFSA3</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1929800</v>
+        <v>1915700</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Gafisa</t>
+          <t>Grupo SBF</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GFSA3</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1915700</v>
+        <v>1884500</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Grupo SBF</t>
+          <t>Randon</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>RAPT4</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1884500</v>
+        <v>1877300</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Randon</t>
+          <t>Iochpe-Maxion</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>RAPT4</t>
+          <t>MYPK3</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1877300</v>
+        <v>1875800</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Iochpe-Maxion</t>
+          <t>Oi</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MYPK3</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1875800</v>
+        <v>1838700</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Oi</t>
+          <t>ISA Energia</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>OIBR3</t>
+          <t>ISAE4</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1838700</v>
+        <v>1834700</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ISA Energia</t>
+          <t>Taesa</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ISAE4</t>
+          <t>TAEE11</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1834700</v>
+        <v>1794800</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Taesa</t>
+          <t>Mitre Realty</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TAEE11</t>
+          <t>MTRE3</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1794800</v>
+        <v>1651700</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mitre Realty</t>
+          <t>PetroRecôncavo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MTRE3</t>
+          <t>RECV3</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1651700</v>
+        <v>1612600</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PetroRecôncavo</t>
+          <t>Klabin</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>RECV3</t>
+          <t>KLBN4</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1612600</v>
+        <v>1564800</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Klabin</t>
+          <t>Banrisul</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KLBN4</t>
+          <t>BRSR6</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1564800</v>
+        <v>1529300</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Banrisul</t>
+          <t>Direcional</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BRSR6</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1529300</v>
+        <v>1453200</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Direcional</t>
+          <t>Wilson Sons</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>PORT3</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1453200</v>
+        <v>1440200</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Wilson Sons</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PORT3</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1440200</v>
+        <v>1422200</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Porto Seguro</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>JSLG3</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1422200</v>
+        <v>1327200</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>IRB Brasil RE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>JSLG3</t>
+          <t>IRBR3</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1327200</v>
+        <v>1295500</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>IRB Brasil RE</t>
+          <t>Sanepar</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>IRBR3</t>
+          <t>SAPR4</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1295500</v>
+        <v>1295100</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sanepar</t>
+          <t>Plano&amp;Plano</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SAPR4</t>
+          <t>PLPL3</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1295100</v>
+        <v>1272200</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Plano&amp;Plano</t>
+          <t>Camil Alimentos</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PLPL3</t>
+          <t>CAML3</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1272200</v>
+        <v>1243600</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Camil Alimentos</t>
+          <t>Multilaser</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CAML3</t>
+          <t>MLAS3</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1243600</v>
+        <v>1193700</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Multilaser</t>
+          <t>IMC Alimentação</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MLAS3</t>
+          <t>MEAL3</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1193700</v>
+        <v>1183600</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IMC Alimentação</t>
+          <t>Alupar</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MEAL3</t>
+          <t>ALUP11</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1183600</v>
+        <v>1171200</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Alupar</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ALUP11</t>
+          <t>VLID3</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1171200</v>
+        <v>1165700</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Valid</t>
+          <t>Cury</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>VLID3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1165700</v>
+        <v>1164300</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cury</t>
+          <t>PDG Realty</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>PDGR3</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1164300</v>
+        <v>1150900</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PDG Realty</t>
+          <t>Banco Pan</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PDGR3</t>
+          <t>BPAN4</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1150900</v>
+        <v>1142100</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Banco Pan</t>
+          <t>Grendene</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BPAN4</t>
+          <t>GRND3</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1142100</v>
+        <v>1107600</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Grendene</t>
+          <t>Guararapes</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GRND3</t>
+          <t>GUAR3</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1107600</v>
+        <v>1089600</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Guararapes</t>
+          <t>Positivo</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>GUAR3</t>
+          <t>POSI3</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1089600</v>
+        <v>1086400</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Engie</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>POSI3</t>
+          <t>EGIE3</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1086400</v>
+        <v>1063300</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Engie</t>
+          <t>Dasa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>EGIE3</t>
+          <t>DASA3</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1063300</v>
+        <v>1034200</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dasa</t>
+          <t>Zamp</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DASA3</t>
+          <t>ZAMP3</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1034200</v>
+        <v>1032700</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Zamp</t>
+          <t>Trisul</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ZAMP3</t>
+          <t>TRIS3</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1032700</v>
+        <v>1020200</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Trisul</t>
+          <t>Ferbasa</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TRIS3</t>
+          <t>FESA4</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1020200</v>
+        <v>983500</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ferbasa</t>
+          <t>Itaú Unibanco</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FESA4</t>
+          <t>ITUB3</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>983500</v>
+        <v>969700</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Itaú Unibanco</t>
+          <t>3tentos</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ITUB3</t>
+          <t>TTEN3</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>969700</v>
+        <v>941700</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3tentos</t>
+          <t>Sanepar</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TTEN3</t>
+          <t>SAPR11</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>941700</v>
+        <v>937800</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Sanepar</t>
+          <t>Armac</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SAPR11</t>
+          <t>ARML3</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>937800</v>
+        <v>933800</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Armac</t>
+          <t>São Martinho</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ARML3</t>
+          <t>SMTO3</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>933800</v>
+        <v>933600</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>São Martinho</t>
+          <t>Priner</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SMTO3</t>
+          <t>PRNR3</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>933600</v>
+        <v>903500</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Priner</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PRNR3</t>
+          <t>DESK3</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>903500</v>
+        <v>867900</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Track &amp; Field</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DESK3</t>
+          <t>TFCO4</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>867900</v>
+        <v>864200</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Track &amp; Field</t>
+          <t>Neoenergia</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>TFCO4</t>
+          <t>NEOE3</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>864200</v>
+        <v>851100</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Neoenergia</t>
+          <t>Vulcabras</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NEOE3</t>
+          <t>VULC3</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>851100</v>
+        <v>837500</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Vulcabras</t>
+          <t>Odontoprev</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>VULC3</t>
+          <t>ODPV3</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>837500</v>
+        <v>837200</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Odontoprev</t>
+          <t>Espaçolaser</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ODPV3</t>
+          <t>ESPA3</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>837200</v>
+        <v>790800</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Espaçolaser</t>
+          <t>Banco ABC Brasil</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ESPA3</t>
+          <t>ABCB4</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>790800</v>
+        <v>761900</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Banco ABC Brasil</t>
+          <t>Sequoia Logística</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ABCB4</t>
+          <t>SEQL3</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>761900</v>
+        <v>750800</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Sequoia Logística</t>
+          <t>Unipar</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SEQL3</t>
+          <t>UNIP6</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>750800</v>
+        <v>712800</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Unipar</t>
+          <t>Recrusul</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>UNIP6</t>
+          <t>RCSL3</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>712800</v>
+        <v>674600</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Recrusul</t>
+          <t>Méliuz</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>RCSL3</t>
+          <t>CASH3</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>674600</v>
+        <v>641800</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Méliuz</t>
+          <t>OceanPact</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CASH3</t>
+          <t>OPCT3</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>641800</v>
+        <v>633600</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>OceanPact</t>
+          <t>Mills</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>OPCT3</t>
+          <t>MILS3</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>633600</v>
+        <v>610400</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mills</t>
+          <t>Lavvi Incorporadora</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MILS3</t>
+          <t>LAVV3</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>610400</v>
+        <v>558000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Lavvi Incorporadora</t>
+          <t>Moura Dubeux</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>LAVV3</t>
+          <t>MDNE3</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>558000</v>
+        <v>556400</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Moura Dubeux</t>
+          <t>Schulz</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MDNE3</t>
+          <t>SHUL4</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>556400</v>
+        <v>526900</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Schulz</t>
+          <t>HBR Realty</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SHUL4</t>
+          <t>HBRE3</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>526900</v>
+        <v>526400</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HBR Realty</t>
+          <t>Melnick</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>HBRE3</t>
+          <t>MELK3</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>526400</v>
+        <v>508600</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Melnick</t>
+          <t>Mobly</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>MELK3</t>
+          <t>MBLY3</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>508600</v>
+        <v>507900</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mobly</t>
+          <t>Ser Educacional</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MBLY3</t>
+          <t>SEER3</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>507900</v>
+        <v>503800</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ser Educacional</t>
+          <t>Jalles Machado</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SEER3</t>
+          <t>JALL3</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>503800</v>
+        <v>494700</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jalles Machado</t>
+          <t>Mater Dei</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>JALL3</t>
+          <t>MATD3</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>494700</v>
+        <v>487300</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mater Dei</t>
+          <t>Wiz Soluções</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>MATD3</t>
+          <t>WIZC3</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>487300</v>
+        <v>479800</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Wiz Soluções</t>
+          <t>Cruzeiro do Sul Educacional</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>WIZC3</t>
+          <t>CSED3</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>479800</v>
+        <v>469900</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Cruzeiro do Sul Educacional</t>
+          <t>M. Dias Branco</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CSED3</t>
+          <t>MDIA3</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>469900</v>
+        <v>447000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>M. Dias Branco</t>
+          <t>VITRUBREPCOM</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MDIA3</t>
+          <t>VTRU3</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>447000</v>
+        <v>438500</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>VITRUBREPCOM</t>
+          <t>Helbor</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>VTRU3</t>
+          <t>HBOR3</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>438500</v>
+        <v>420600</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Helbor</t>
+          <t>Orizon</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>HBOR3</t>
+          <t>ORVR3</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>420600</v>
+        <v>415600</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Orizon</t>
+          <t>Lojas Marisa</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ORVR3</t>
+          <t>AMAR3</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>415600</v>
+        <v>405400</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Lojas Marisa</t>
+          <t>SYN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>AMAR3</t>
+          <t>SYNE3</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>405400</v>
+        <v>404000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SYN</t>
+          <t>Aeris Energy</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SYNE3</t>
+          <t>AERI3</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>404000</v>
+        <v>399400</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Aeris Energy</t>
+          <t>Tupy</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>AERI3</t>
+          <t>TUPY3</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>399400</v>
+        <v>382700</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Tupy</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>TUPY3</t>
+          <t>LIGT3</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>382700</v>
+        <v>380200</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Banco BMG</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>LIGT3</t>
+          <t>BMGB4</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>380200</v>
+        <v>367100</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Banco BMG</t>
+          <t>LOG CP</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>BMGB4</t>
+          <t>LOGG3</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>367100</v>
+        <v>359900</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>LOG CP</t>
+          <t>Cemig</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>LOGG3</t>
+          <t>CMIG3</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>359900</v>
+        <v>338200</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Cemig</t>
+          <t>Fras-le</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>CMIG3</t>
+          <t>FRAS3</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>338200</v>
+        <v>333300</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Fras-le</t>
+          <t>Klabin</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>FRAS3</t>
+          <t>KLBN3</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>333300</v>
+        <v>332300</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Klabin</t>
+          <t>Blau Farmacêutica</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>KLBN3</t>
+          <t>BLAU3</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>332300</v>
+        <v>318400</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Blau Farmacêutica</t>
+          <t>Unifique</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>BLAU3</t>
+          <t>FIQE3</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>318400</v>
+        <v>316400</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Unifique</t>
+          <t>Irani</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>FIQE3</t>
+          <t>RANI3</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>316400</v>
+        <v>312500</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Irani</t>
+          <t>Boa Safra Sementes</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>RANI3</t>
+          <t>SOJA3</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>312500</v>
+        <v>304300</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Boa Safra Sementes</t>
+          <t>Usiminas</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SOJA3</t>
+          <t>USIM3</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>304300</v>
+        <v>298500</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Usiminas</t>
+          <t>Mahle Metal Leve</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USIM3</t>
+          <t>LEVE3</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>298500</v>
+        <v>285600</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Mahle Metal Leve</t>
+          <t>Vittia</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>LEVE3</t>
+          <t>VITT3</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>285600</v>
+        <v>258000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Vittia</t>
+          <t>Dimed</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>VITT3</t>
+          <t>PNVL3</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>258000</v>
+        <v>257400</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Dimed</t>
+          <t>Banco Santander</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PNVL3</t>
+          <t>SANB4</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>257400</v>
+        <v>244900</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Banco Santander</t>
+          <t>Eletromidia</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>SANB4</t>
+          <t>ELMD3</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>244900</v>
+        <v>238600</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Eletromidia</t>
+          <t>Banco Santander</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ELMD3</t>
+          <t>SANB3</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>238600</v>
+        <v>230600</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Banco Santander</t>
+          <t>Marcopolo</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SANB3</t>
+          <t>POMO3</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>230600</v>
+        <v>227300</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Marcopolo</t>
+          <t>Taurus</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>POMO3</t>
+          <t>TASA4</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>227300</v>
+        <v>221600</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Taurus</t>
+          <t>Cambuci</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>TASA4</t>
+          <t>CAMB3</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>221600</v>
+        <v>217600</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Cambuci</t>
+          <t>BR Partners</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>CAMB3</t>
+          <t>BRBI11</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>217600</v>
+        <v>205600</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>BR Partners</t>
+          <t>Bombril</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>BRBI11</t>
+          <t>BOBR4</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>205600</v>
+        <v>204400</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Bombril</t>
+          <t>Bemobi</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>BOBR4</t>
+          <t>BMOB3</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>204400</v>
+        <v>197700</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Bemobi</t>
+          <t>Taesa</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BMOB3</t>
+          <t>TAEE4</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>197700</v>
+        <v>187400</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Taesa</t>
+          <t>Indústrias ROMI</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>TAEE4</t>
+          <t>ROMI3</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>187400</v>
+        <v>183900</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Indústrias ROMI</t>
+          <t>Tegma</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ROMI3</t>
+          <t>TGMA3</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>183900</v>
+        <v>175800</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tegma</t>
+          <t>Coelce</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>TGMA3</t>
+          <t>COCE5</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>175800</v>
+        <v>171400</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Coelce</t>
+          <t>Brisanet</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>COCE5</t>
+          <t>BRST3</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>171400</v>
+        <v>169400</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Brisanet</t>
+          <t>Triunfo</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>BRST3</t>
+          <t>TPIS3</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>169400</v>
+        <v>167200</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Triunfo</t>
+          <t>Fictor Alimentos</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>TPIS3</t>
+          <t>FICT3</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>167200</v>
+        <v>162800</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Fictor Alimentos</t>
+          <t>Ambipar</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FICT3</t>
+          <t>AMBP3</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>162800</v>
+        <v>158100</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Ambipar</t>
+          <t>BrasilAgro</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>AMBP3</t>
+          <t>AGRO3</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>158100</v>
+        <v>155800</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>BrasilAgro</t>
+          <t>AgroGalaxy</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>AGRO3</t>
+          <t>AGXY3</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>155800</v>
+        <v>152600</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>AgroGalaxy</t>
+          <t>Itaúsa</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>AGXY3</t>
+          <t>ITSA3</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>152600</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Itaúsa</t>
+          <t>Sanepar</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ITSA3</t>
+          <t>SAPR3</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>137500</v>
+        <v>122300</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Sanepar</t>
+          <t>Banco Pine</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SAPR3</t>
+          <t>PINE4</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>122300</v>
+        <v>120500</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Banco Pine</t>
+          <t>São Carlos</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>PINE4</t>
+          <t>SCAR3</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>120500</v>
+        <v>113700</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>São Carlos</t>
+          <t>Profarma</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SCAR3</t>
+          <t>PFRM3</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>113700</v>
+        <v>110200</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Profarma</t>
+          <t>Lopes</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>PFRM3</t>
+          <t>LPSB3</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>110200</v>
+        <v>108800</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Lopes</t>
+          <t>Paranapanema</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>LPSB3</t>
+          <t>PMAM3</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>108800</v>
+        <v>107400</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Paranapanema</t>
+          <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>PMAM3</t>
+          <t>ATED3</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>107400</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
+          <t>Renova Energia</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ATED3</t>
+          <t>RNEW4</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>97500</v>
+        <v>96900</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Renova Energia</t>
+          <t>Taesa</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>RNEW4</t>
+          <t>TAEE3</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>96900</v>
+        <v>89800</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Taesa</t>
+          <t>Unicasa</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>TAEE3</t>
+          <t>UCAS3</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>89800</v>
+        <v>88900</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Unicasa</t>
+          <t>Eternit</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>UCAS3</t>
+          <t>ETER3</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>88900</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Eternit</t>
+          <t>Electro Aço Altona</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ETER3</t>
+          <t>EALT4</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>74200</v>
+        <v>73900</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Electro Aço Altona</t>
+          <t>Renova Energia</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>EALT4</t>
+          <t>RNEW3</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>73900</v>
+        <v>72100</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Renova Energia</t>
+          <t>Lupatech</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>RNEW3</t>
+          <t>LUPA3</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>72100</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Lupatech</t>
+          <t>Dexxos</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>LUPA3</t>
+          <t>DEXP3</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>71400</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Dexxos</t>
+          <t>Bradespar</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>DEXP3</t>
+          <t>BRAP3</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>66300</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Bradespar</t>
+          <t>Jereissati Participações</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>BRAP3</t>
+          <t>IGTI3</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>62700</v>
+        <v>62100</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Jereissati Participações</t>
+          <t>Viver</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>IGTI3</t>
+          <t>VIVR3</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>62100</v>
+        <v>56400</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Technos</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>IGTI3</t>
+          <t>TECN3</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>62100</v>
+        <v>52700</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Viver</t>
+          <t>Estapar</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>VIVR3</t>
+          <t>ALPK3</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>56400</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Technos</t>
+          <t>Time For Fun</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>TECN3</t>
+          <t>SHOW3</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>52700</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Estapar</t>
+          <t>CSU Cardsystem</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ALPK3</t>
+          <t>CSUD3</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>49600</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Time For Fun</t>
+          <t>D1000 Varejo Farma</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>SHOW3</t>
+          <t>DMVF3</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>49600</v>
+        <v>47300</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>CSU Cardsystem</t>
+          <t>Log-In</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>CSUD3</t>
+          <t>LOGN3</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>47600</v>
+        <v>41100</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>D1000 Varejo Farma</t>
+          <t>Tecnisa</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DMVF3</t>
+          <t>TCSA3</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>47300</v>
+        <v>39100</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Log-In</t>
+          <t>Metalúrgica Gerdau</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>LOGN3</t>
+          <t>GOAU3</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>41100</v>
+        <v>38900</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Tecnisa</t>
+          <t>Rossi Residencial</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>TCSA3</t>
+          <t>RSID3</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>39100</v>
+        <v>38700</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Metalúrgica Gerdau</t>
+          <t>Biomm</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>GOAU3</t>
+          <t>BIOM3</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>38900</v>
+        <v>38600</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Rossi Residencial</t>
+          <t>João Fortes</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>RSID3</t>
+          <t>JFEN3</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>38700</v>
+        <v>28100</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Biomm</t>
+          <t>WDC Networks</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>BIOM3</t>
+          <t>LVTC3</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>38600</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>João Fortes</t>
+          <t>Alpargatas</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>JFEN3</t>
+          <t>ALPA3</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>28100</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>WDC Networks</t>
+          <t>Inepar</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>LVTC3</t>
+          <t>INEP3</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>26100</v>
+        <v>25400</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Alpargatas</t>
+          <t>Energisa</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ALPA3</t>
+          <t>ENGI4</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>25500</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Inepar</t>
+          <t>Allied</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>INEP3</t>
+          <t>ALLD3</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>25400</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Energisa</t>
+          <t>Kora Saúde</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ENGI4</t>
+          <t>KRSA3</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>24400</v>
+        <v>20700</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Allied</t>
+          <t>Lojas Marisa</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ALLD3</t>
+          <t>AMAR11</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>23200</v>
+        <v>20700</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Kora Saúde</t>
+          <t>Haga</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>KRSA3</t>
+          <t>HAGA4</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>20700</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Lojas Marisa</t>
+          <t>Alupar</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>AMAR11</t>
+          <t>ALUP4</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>20700</v>
+        <v>19700</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Haga</t>
+          <t>Braskem</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>HAGA4</t>
+          <t>BRKM3</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>20500</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Alupar</t>
+          <t>Traders Club</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ALUP4</t>
+          <t>TRAD3</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>19700</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Braskem</t>
+          <t>DASA11</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>BRKM3</t>
+          <t>DASA11</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>19500</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Traders Club</t>
+          <t>Eucatex</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>TRAD3</t>
+          <t>EUCA4</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>19500</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DASA11</t>
+          <t>Padtec</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DASA11</t>
+          <t>PDTC3</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>18500</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Eucatex</t>
+          <t>Unipar</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>EUCA4</t>
+          <t>UNIP3</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>18200</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Padtec</t>
+          <t>REAG3</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>PDTC3</t>
+          <t>REAG3</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>17500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Unipar</t>
+          <t>Gerdau</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>UNIP3</t>
+          <t>GGBR3</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>17100</v>
+        <v>15800</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>REAG3</t>
+          <t>Terra Santa</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>REAG3</t>
+          <t>LAND3</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>16500</v>
+        <v>15700</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Gerdau</t>
+          <t>Fertilizantes Heringer</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>GGBR3</t>
+          <t>FHER3</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>15800</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Terra Santa</t>
+          <t>Banco Mercantil do Brasil</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>LAND3</t>
+          <t>BMEB4</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>15700</v>
+        <v>14800</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Fertilizantes Heringer</t>
+          <t>Randon</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>FHER3</t>
+          <t>RAPT3</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>15600</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Banco Mercantil do Brasil</t>
+          <t>Sansuy</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>BMEB4</t>
+          <t>SNSY5</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>14800</v>
+        <v>12700</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Randon</t>
+          <t>Neogrid</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>RAPT3</t>
+          <t>NGRD3</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>13100</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Sansuy</t>
+          <t>Dotz</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>SNSY5</t>
+          <t>DOTZ3</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>12700</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Neogrid</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>NGRD3</t>
+          <t>CEBR6</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>12200</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Dotz</t>
+          <t>Alliança</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>DOTZ3</t>
+          <t>AALR3</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>11900</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>Banco BTG Pactual</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>CEBR6</t>
+          <t>BPAC3</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>11800</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Alliança</t>
+          <t>Renova Energia</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>AALR3</t>
+          <t>RNEW11</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>11500</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Banco BTG Pactual</t>
+          <t>Whirlpool</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>BPAC3</t>
+          <t>WHRL4</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>9000</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Renova Energia</t>
+          <t>EMAE</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>RNEW11</t>
+          <t>EMAE4</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>8900</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Whirlpool</t>
+          <t>Inepar</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>WHRL4</t>
+          <t>INEP4</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>8600</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>EMAE</t>
+          <t>Banrisul</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>EMAE4</t>
+          <t>BRSR3</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>8500</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Inepar</t>
+          <t>Santanense</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>INEP4</t>
+          <t>CTSA4</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>8000</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Banrisul</t>
+          <t>Azevedo &amp; Travassos</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>BRSR3</t>
+          <t>AZEV11</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>7800</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Santanense</t>
+          <t>Grazziotin</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>CTSA4</t>
+          <t>CGRA4</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>7600</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Azevedo &amp; Travassos</t>
+          <t>Energisa</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>AZEV11</t>
+          <t>ENGI3</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>7600</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Grazziotin</t>
+          <t>Alupar</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>CGRA4</t>
+          <t>ALUP3</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>7100</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Energisa</t>
+          <t>Banestes</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ENGI3</t>
+          <t>BEES3</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>7000</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Alupar</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ALUP3</t>
+          <t>CEBR3</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>7000</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Banestes</t>
+          <t>Banco Pine</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>BEES3</t>
+          <t>PINE3</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>6600</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>Banco BTG Pactual</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>CEBR3</t>
+          <t>BPAC5</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>6400</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Banco Pine</t>
+          <t>Metisa</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>PINE3</t>
+          <t>MTSA4</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>6400</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Banco BTG Pactual</t>
+          <t>RNI</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>BPAC5</t>
+          <t>RDNI3</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>5600</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Metisa</t>
+          <t>Embpar Participações</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>MTSA4</t>
+          <t>EPAR3</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>5300</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>RNI</t>
+          <t>Grazziotin</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>RDNI3</t>
+          <t>CGRA3</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>5300</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Embpar Participações</t>
+          <t>Pettenati</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>EPAR3</t>
+          <t>PTNT4</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>5000</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Grazziotin</t>
+          <t>Taurus</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>CGRA3</t>
+          <t>TASA3</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>4900</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Pettenati</t>
+          <t>Metalúrgica Riosulense</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>PTNT4</t>
+          <t>RSUL4</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>4700</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Taurus</t>
+          <t>Ourofino Saúde Animal</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>TASA3</t>
+          <t>OFSA3</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>4600</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Metalúrgica Riosulense</t>
+          <t>Banestes</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>RSUL4</t>
+          <t>BEES4</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>4200</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Ourofino Saúde Animal</t>
+          <t>Oi</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>OFSA3</t>
+          <t>OIBR4</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>4200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Banestes</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>BEES4</t>
+          <t>CEBR5</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>4100</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Oi</t>
+          <t>Equatorial Energia Pará</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>OIBR4</t>
+          <t>EQPA3</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>Mercantil do Brasil Financeira</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>CEBR5</t>
+          <t>MERC4</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>3400</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Equatorial Energia Pará</t>
+          <t>Telebras</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>EQPA3</t>
+          <t>TELB3</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>3000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Mercantil do Brasil Financeira</t>
+          <t>Hotéis Othon</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>MERC4</t>
+          <t>HOOT4</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>2800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Telebras</t>
+          <t>Celesc</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>TELB3</t>
+          <t>CLSC4</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>2200</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Hotéis Othon</t>
+          <t>Banese</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>HOOT4</t>
+          <t>BGIP4</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Celesc</t>
+          <t>Banco de Brasília</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>CLSC4</t>
+          <t>BSLI3</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1900</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Banese</t>
+          <t>Atma</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>BGIP4</t>
+          <t>ATMP3</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Banco de Brasília</t>
+          <t>Telebras</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>BSLI3</t>
+          <t>TELB4</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Atma</t>
+          <t>Nutriplant</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>ATMP3</t>
+          <t>NUTR3</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Telebras</t>
+          <t>Rede Energia</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>TELB4</t>
+          <t>REDE3</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1600</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Nutriplant</t>
+          <t>Unipar</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>NUTR3</t>
+          <t>UNIP5</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Rede Energia</t>
+          <t>Minupar</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>REDE3</t>
+          <t>MNPR3</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Unipar</t>
+          <t>Pettenati</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>UNIP5</t>
+          <t>PTNT3</t>
         </is>
       </c>
       <c r="D318" t="n">
@@ -6153,52 +6153,52 @@
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Minupar</t>
+          <t>Whirlpool</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>MNPR3</t>
+          <t>WHRL3</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pettenati</t>
+          <t>OSX Brasil</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>PTNT3</t>
+          <t>OSXB3</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Whirlpool</t>
+          <t>Refinaria de Manguinhos</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>WHRL3</t>
+          <t>RPMG3</t>
         </is>
       </c>
       <c r="D321" t="n">
@@ -6207,16 +6207,16 @@
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>OSX Brasil</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>OSXB3</t>
+          <t>AVLL3</t>
         </is>
       </c>
       <c r="D322" t="n">
@@ -6225,142 +6225,142 @@
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Refinaria de Manguinhos</t>
+          <t>COELBA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>RPMG3</t>
+          <t>CEEB3</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Eucatex</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>AVLL3</t>
+          <t>EUCA3</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>COELBA</t>
+          <t>ISA Energia</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>CEEB3</t>
+          <t>ISAE3</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Eucatex</t>
+          <t>Cedro Têxtil</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>EUCA3</t>
+          <t>CEDO4</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>ISA Energia</t>
+          <t>Brasil Brokers</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>ISAE3</t>
+          <t>NEXP3</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Cedro Têxtil</t>
+          <t>Banco da Amazônia</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>CEDO4</t>
+          <t>BAZA3</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Brasil Brokers</t>
+          <t>Elektro</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>NEXP3</t>
+          <t>EKTR4</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Banco da Amazônia</t>
+          <t>Tronox Pigmentos</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>BAZA3</t>
+          <t>CRPG5</t>
         </is>
       </c>
       <c r="D330" t="n">
@@ -6369,16 +6369,16 @@
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Elektro</t>
+          <t>Afluente T</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>EKTR4</t>
+          <t>AFLT3</t>
         </is>
       </c>
       <c r="D331" t="n">
@@ -6387,16 +6387,16 @@
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Tronox Pigmentos</t>
+          <t>LE LIS BLANC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>CRPG5</t>
+          <t>VSTE3</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -6405,124 +6405,124 @@
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Afluente T</t>
+          <t>Monteiro Aranha</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>AFLT3</t>
+          <t>MOAR3</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>LE LIS BLANC</t>
+          <t>Mundial</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>VSTE3</t>
+          <t>MNDL3</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Monteiro Aranha</t>
+          <t>Habitasul</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>MOAR3</t>
+          <t>HBTS5</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Mundial</t>
+          <t>Copel</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>MNDL3</t>
+          <t>CPLE5</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Habitasul</t>
+          <t>Comgás</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>HBTS5</t>
+          <t>CGAS5</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Copel</t>
+          <t>Tekno</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>CPLE5</t>
+          <t>TKNO4</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Comgás</t>
+          <t>WLM</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>CGAS5</t>
+          <t>WLMM4</t>
         </is>
       </c>
       <c r="D339" t="n">
@@ -6531,16 +6531,16 @@
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Tekno</t>
+          <t>Electro Aço Altona</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>TKNO4</t>
+          <t>EALT3</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -6549,16 +6549,16 @@
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>WLM</t>
+          <t>Dexxos</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>WLMM4</t>
+          <t>DEXP4</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -6567,16 +6567,16 @@
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Electro Aço Altona</t>
+          <t>Nordon</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>EALT3</t>
+          <t>NORD3</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -6585,16 +6585,16 @@
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Dexxos</t>
+          <t>Westwing</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>DEXP4</t>
+          <t>WEST3</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -6603,16 +6603,16 @@
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Nordon</t>
+          <t>Alfa Holdings</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>NORD3</t>
+          <t>RPAD6</t>
         </is>
       </c>
       <c r="D344" t="n">
@@ -6621,70 +6621,70 @@
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Westwing</t>
+          <t>PPLA</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>WEST3</t>
+          <t>PPLA11</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>200</v>
+        <v>138</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Alfa Holdings</t>
+          <t>Comgás</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>RPAD6</t>
+          <t>CGAS3</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PPLA</t>
+          <t>Celesc</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>PPLA11</t>
+          <t>CLSC3</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>138</v>
+        <v>100</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Comgás</t>
+          <t>Rio Paranapanema Energia</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>CGAS3</t>
+          <t>GEPA3</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -6693,16 +6693,16 @@
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Celesc</t>
+          <t>Rio Paranapanema Energia</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>CLSC3</t>
+          <t>GEPA4</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -6711,16 +6711,16 @@
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Rio Paranapanema Energia</t>
+          <t>Karsten</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>GEPA3</t>
+          <t>CTKA4</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -6729,16 +6729,16 @@
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Rio Paranapanema Energia</t>
+          <t>Banco Mercantil de Investimentos</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>GEPA4</t>
+          <t>BMIN4</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -6747,16 +6747,16 @@
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Karsten</t>
+          <t>Bardella</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>CTKA4</t>
+          <t>BDLL3</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -6765,16 +6765,16 @@
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Banco Mercantil de Investimentos</t>
+          <t>Plascar</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>BMIN4</t>
+          <t>PLAS3</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -6783,16 +6783,16 @@
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Bardella</t>
+          <t>Döhler</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>BDLL3</t>
+          <t>DOHL3</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -6801,16 +6801,16 @@
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Plascar</t>
+          <t>BIED3</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>PLAS3</t>
+          <t>BIED3</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -6819,160 +6819,160 @@
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Döhler</t>
+          <t>Monark</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>DOHL3</t>
+          <t>BMKS3</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>BIED3</t>
+          <t>Sansuy</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>BIED3</t>
+          <t>SNSY3</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>100</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Monark</t>
+          <t>Trevisa</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>BMKS3</t>
+          <t>LUXM4</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>32</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Sansuy</t>
+          <t>Mangels</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>SNSY3</t>
+          <t>MGEL4</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>9200</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Trevisa</t>
+          <t>MRS Logística</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>LUXM4</t>
+          <t>MRSA3B</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>4600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Mangels</t>
+          <t>Participações Aliança da Bahia</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>MGEL4</t>
+          <t>PEAB3</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>MRS Logística</t>
+          <t>Eletropar</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>MRSA3B</t>
+          <t>LIPR3</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Participações Aliança da Bahia</t>
+          <t>Karsten</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>PEAB3</t>
+          <t>CTKA3</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Eletropar</t>
+          <t>Ferbasa</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>LIPR3</t>
+          <t>FESA3</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -6981,16 +6981,16 @@
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Karsten</t>
+          <t>Cemepe</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>CTKA3</t>
+          <t>MAPT3</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -6999,160 +6999,160 @@
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Ferbasa</t>
+          <t>Cedro Têxtil</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>FESA3</t>
+          <t>CEDO3</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Cemepe</t>
+          <t>Banco de Brasília</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>MAPT3</t>
+          <t>BSLI4</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Cedro Têxtil</t>
+          <t>Döhler</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>CEDO3</t>
+          <t>DOHL4</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Banco de Brasília</t>
+          <t>Biomm</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>BSLI4</t>
+          <t>BIOM11</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Döhler</t>
+          <t>Coelce</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>DOHL4</t>
+          <t>COCE3</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Biomm</t>
+          <t>Santanense</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>BIOM11</t>
+          <t>CTSA3</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Coelce</t>
+          <t>Energisa MT</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>COCE3</t>
+          <t>ENMT3</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Santanense</t>
+          <t>Banrisul</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>CTSA3</t>
+          <t>BRSR5</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Energisa MT</t>
+          <t>Wetzel</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>ENMT3</t>
+          <t>MWET4</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -7161,16 +7161,16 @@
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Banrisul</t>
+          <t>Alfa Holdings</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>BRSR5</t>
+          <t>RPAD3</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -7179,16 +7179,16 @@
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Wetzel</t>
+          <t>Haga</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>MWET4</t>
+          <t>HAGA3</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -7197,232 +7197,232 @@
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Alfa Holdings</t>
+          <t>Baumer</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>RPAD3</t>
+          <t>BALM4</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Haga</t>
+          <t>Tronox Pigmentos</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>HAGA3</t>
+          <t>CRPG6</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Baumer</t>
+          <t>COELBA</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>BALM4</t>
+          <t>CEEB5</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Tronox Pigmentos</t>
+          <t>Banco Mercantil de Investimentos</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>CRPG6</t>
+          <t>BMIN3</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>COELBA</t>
+          <t>Sondotécnica</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>CEEB5</t>
+          <t>SOND6</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Banco Mercantil de Investimentos</t>
+          <t>MRS Logística</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>BMIN3</t>
+          <t>MRSA5B</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Sondotécnica</t>
+          <t>Panatlântica</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>SOND6</t>
+          <t>PATI3</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>MRS Logística</t>
+          <t>Hercules</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>MRSA5B</t>
+          <t>HETA4</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Panatlântica</t>
+          <t>Metalfrio</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>PATI3</t>
+          <t>FRIO3</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Hercules</t>
+          <t>Banco do Nordeste</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>HETA4</t>
+          <t>BNBR3</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Metalfrio</t>
+          <t>Banco Mercantil do Brasil</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>FRIO3</t>
+          <t>BMEB3</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Banco do Nordeste</t>
+          <t>MRS Logística</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>BNBR3</t>
+          <t>MRSA6B</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Banco Mercantil do Brasil</t>
+          <t>Equatorial Maranhão</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>BMEB3</t>
+          <t>EQMA3B</t>
         </is>
       </c>
       <c r="D389" t="n">
@@ -7431,16 +7431,16 @@
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>MRS Logística</t>
+          <t>Cemepe</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>MRSA6B</t>
+          <t>MAPT4</t>
         </is>
       </c>
       <c r="D390" t="n">
@@ -7449,160 +7449,160 @@
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Equatorial Maranhão</t>
+          <t>Bardella</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>EQMA3B</t>
+          <t>BDLL4</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Cemepe</t>
+          <t>Alfa Holdings</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>MAPT4</t>
+          <t>RPAD5</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Bardella</t>
+          <t>Equatorial Energia Pará</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>BDLL4</t>
+          <t>EQPA5</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1400</v>
+        <v>400</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Alfa Holdings</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>RPAD5</t>
+          <t>BAUH4</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Equatorial Energia Pará</t>
+          <t>Jereissati Participações</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>EQPA5</t>
+          <t>IGTI4</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Banese</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>BAUH4</t>
+          <t>BGIP3</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Jereissati Participações</t>
+          <t>São Paulo Turismo</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>IGTI4</t>
+          <t>AHEB3</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>São Paulo Turismo</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>IGTI4</t>
+          <t>AHEB6</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Banese</t>
+          <t>Sondotécnica</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>BGIP3</t>
+          <t>SOND5</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -7611,34 +7611,34 @@
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>São Paulo Turismo</t>
+          <t>CELGPAR</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>AHEB3</t>
+          <t>GPAR3</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>São Paulo Turismo</t>
+          <t>Dtcom</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>AHEB6</t>
+          <t>DTCY3</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -7647,16 +7647,16 @@
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Sondotécnica</t>
+          <t>Estrela</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>SOND5</t>
+          <t>ESTR4</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -7665,73 +7665,19 @@
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>CELGPAR</t>
+          <t>Fica</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>GPAR3</t>
+          <t>FIEI3</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="1" t="n">
-        <v>402</v>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Dtcom</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>DTCY3</t>
-        </is>
-      </c>
-      <c r="D404" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="1" t="n">
-        <v>403</v>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Estrela</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>ESTR4</t>
-        </is>
-      </c>
-      <c r="D405" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="1" t="n">
-        <v>404</v>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Fica</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>FIEI3</t>
-        </is>
-      </c>
-      <c r="D406" t="n">
         <v>500</v>
       </c>
     </row>

--- a/Bases/Lista de ações.xlsx
+++ b/Bases/Lista de ações.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="728">
   <si>
     <t>Nome da Empresa</t>
   </si>
@@ -22,2158 +22,2182 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>Volume no último dia útil (lido em 30/03/2025)</t>
+    <t>Volume no último dia útil (lido em 12/04/2025)</t>
+  </si>
+  <si>
+    <t>Petrobras</t>
+  </si>
+  <si>
+    <t>Cogna</t>
+  </si>
+  <si>
+    <t>Hapvida</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>Oi</t>
+  </si>
+  <si>
+    <t>Itaúsa</t>
+  </si>
+  <si>
+    <t>Ambev</t>
+  </si>
+  <si>
+    <t>Grupo Pão de Açúcar</t>
+  </si>
+  <si>
+    <t>Banco Bradesco</t>
+  </si>
+  <si>
+    <t>Itaú Unibanco</t>
+  </si>
+  <si>
+    <t>Magazine Luiza</t>
+  </si>
+  <si>
+    <t>Carrefour Brasil</t>
+  </si>
+  <si>
+    <t>Vale</t>
+  </si>
+  <si>
+    <t>Grupo CCR</t>
+  </si>
+  <si>
+    <t>Marcopolo</t>
+  </si>
+  <si>
+    <t>CVC</t>
+  </si>
+  <si>
+    <t>Grupo Vamos</t>
+  </si>
+  <si>
+    <t>Cosan</t>
+  </si>
+  <si>
+    <t>Metalúrgica Gerdau</t>
+  </si>
+  <si>
+    <t>PetroRio</t>
+  </si>
+  <si>
+    <t>3R Petroleum</t>
+  </si>
+  <si>
+    <t>Lojas Renner</t>
+  </si>
+  <si>
+    <t>Banco do Brasil</t>
+  </si>
+  <si>
+    <t>Rumo</t>
+  </si>
+  <si>
+    <t>Minerva</t>
+  </si>
+  <si>
+    <t>Cemig</t>
+  </si>
+  <si>
+    <t>Localiza</t>
+  </si>
+  <si>
+    <t>Automob</t>
+  </si>
+  <si>
+    <t>Gerdau</t>
+  </si>
+  <si>
+    <t>Copel</t>
+  </si>
+  <si>
+    <t>Ânima Educação</t>
+  </si>
+  <si>
+    <t>Assaí</t>
+  </si>
+  <si>
+    <t>Azul</t>
+  </si>
+  <si>
+    <t>Randon</t>
+  </si>
+  <si>
+    <t>Raízen</t>
+  </si>
+  <si>
+    <t>Locaweb</t>
+  </si>
+  <si>
+    <t>RaiaDrogasil</t>
+  </si>
+  <si>
+    <t>Usiminas</t>
+  </si>
+  <si>
+    <t>Vibra Energia</t>
+  </si>
+  <si>
+    <t>MRV</t>
+  </si>
+  <si>
+    <t>Eneva</t>
+  </si>
+  <si>
+    <t>Siderúrgica Nacional</t>
+  </si>
+  <si>
+    <t>Serena Energia</t>
+  </si>
+  <si>
+    <t>Banco BTG Pactual</t>
+  </si>
+  <si>
+    <t>Natura</t>
+  </si>
+  <si>
+    <t>Cyrela</t>
+  </si>
+  <si>
+    <t>Movida</t>
   </si>
   <si>
     <t>Infracommerce</t>
   </si>
   <si>
-    <t>Hapvida</t>
-  </si>
-  <si>
-    <t>Cogna</t>
-  </si>
-  <si>
-    <t>CVC</t>
-  </si>
-  <si>
-    <t>Itaúsa</t>
-  </si>
-  <si>
-    <t>Ambev</t>
-  </si>
-  <si>
-    <t>Grupo Vamos</t>
-  </si>
-  <si>
-    <t>Vale</t>
-  </si>
-  <si>
-    <t>Magazine Luiza</t>
+    <t>CBA</t>
+  </si>
+  <si>
+    <t>Casas Bahia</t>
+  </si>
+  <si>
+    <t>Simpar</t>
+  </si>
+  <si>
+    <t>Grupo Mateus</t>
+  </si>
+  <si>
+    <t>Klabin</t>
   </si>
   <si>
     <t>Gafisa</t>
   </si>
   <si>
-    <t>Banco Bradesco</t>
-  </si>
-  <si>
-    <t>Itaú Unibanco</t>
-  </si>
-  <si>
-    <t>Petrobras</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>Marcopolo</t>
-  </si>
-  <si>
-    <t>Lojas Renner</t>
-  </si>
-  <si>
-    <t>Usiminas</t>
-  </si>
-  <si>
-    <t>Natura</t>
-  </si>
-  <si>
-    <t>Assaí</t>
+    <t>Equatorial Energia</t>
+  </si>
+  <si>
+    <t>Rede D'Or</t>
+  </si>
+  <si>
+    <t>Eletrobras</t>
+  </si>
+  <si>
+    <t>Suzano</t>
+  </si>
+  <si>
+    <t>Marfrig</t>
+  </si>
+  <si>
+    <t>CSN Mineração</t>
+  </si>
+  <si>
+    <t>Banco Santander</t>
+  </si>
+  <si>
+    <t>PetroRecôncavo</t>
+  </si>
+  <si>
+    <t>Multiplan</t>
+  </si>
+  <si>
+    <t>TIM</t>
+  </si>
+  <si>
+    <t>SLC Agrícola</t>
+  </si>
+  <si>
+    <t>EcoRodovias</t>
   </si>
   <si>
     <t>Petz</t>
   </si>
   <si>
-    <t>Banco do Brasil</t>
-  </si>
-  <si>
-    <t>Casas Bahia</t>
-  </si>
-  <si>
-    <t>Raízen</t>
-  </si>
-  <si>
-    <t>Ânima Educação</t>
-  </si>
-  <si>
-    <t>Grupo CCR</t>
-  </si>
-  <si>
-    <t>Rumo</t>
-  </si>
-  <si>
-    <t>Cemig</t>
-  </si>
-  <si>
-    <t>Eletrobras</t>
-  </si>
-  <si>
-    <t>Azul</t>
+    <t>Azevedo &amp; Travassos</t>
+  </si>
+  <si>
+    <t>BRF</t>
+  </si>
+  <si>
+    <t>Wilson Sons</t>
+  </si>
+  <si>
+    <t>Ultrapar</t>
+  </si>
+  <si>
+    <t>Smart Fit</t>
+  </si>
+  <si>
+    <t>Recrusul</t>
+  </si>
+  <si>
+    <t>Banco Pan</t>
+  </si>
+  <si>
+    <t>Americanas</t>
+  </si>
+  <si>
+    <t>Auren Energia</t>
+  </si>
+  <si>
+    <t>Enjoei</t>
+  </si>
+  <si>
+    <t>JBS</t>
+  </si>
+  <si>
+    <t>C&amp;A</t>
+  </si>
+  <si>
+    <t>Bradespar</t>
+  </si>
+  <si>
+    <t>Embraer</t>
+  </si>
+  <si>
+    <t>Intelbras</t>
+  </si>
+  <si>
+    <t>Sabesp</t>
+  </si>
+  <si>
+    <t>Allos</t>
+  </si>
+  <si>
+    <t>WEG</t>
+  </si>
+  <si>
+    <t>YDUQS</t>
+  </si>
+  <si>
+    <t>Vivara</t>
+  </si>
+  <si>
+    <t>BB Seguridade</t>
+  </si>
+  <si>
+    <t>São Martinho</t>
+  </si>
+  <si>
+    <t>Lojas Quero-Quero</t>
+  </si>
+  <si>
+    <t>Direcional</t>
+  </si>
+  <si>
+    <t>Totvs</t>
+  </si>
+  <si>
+    <t>IRB Brasil RE</t>
+  </si>
+  <si>
+    <t>EZTEC</t>
+  </si>
+  <si>
+    <t>Cury</t>
+  </si>
+  <si>
+    <t>Braskem</t>
+  </si>
+  <si>
+    <t>Qualicorp</t>
+  </si>
+  <si>
+    <t>GPS</t>
   </si>
   <si>
     <t>JHSF</t>
   </si>
   <si>
-    <t>MRV</t>
-  </si>
-  <si>
-    <t>Locaweb</t>
-  </si>
-  <si>
-    <t>Automob</t>
-  </si>
-  <si>
-    <t>Americanas</t>
-  </si>
-  <si>
-    <t>Siderúrgica Nacional</t>
-  </si>
-  <si>
-    <t>Simpar</t>
-  </si>
-  <si>
-    <t>Cosan</t>
-  </si>
-  <si>
-    <t>Vibra Energia</t>
-  </si>
-  <si>
-    <t>Gerdau</t>
-  </si>
-  <si>
-    <t>Minerva</t>
-  </si>
-  <si>
-    <t>CBA</t>
-  </si>
-  <si>
-    <t>RaiaDrogasil</t>
-  </si>
-  <si>
-    <t>Carrefour Brasil</t>
-  </si>
-  <si>
-    <t>Copel</t>
-  </si>
-  <si>
-    <t>Grupo Pão de Açúcar</t>
-  </si>
-  <si>
-    <t>Banco BTG Pactual</t>
-  </si>
-  <si>
-    <t>Equatorial Energia</t>
-  </si>
-  <si>
-    <t>Metalúrgica Gerdau</t>
-  </si>
-  <si>
-    <t>EcoRodovias</t>
-  </si>
-  <si>
-    <t>BRF</t>
-  </si>
-  <si>
-    <t>Localiza</t>
-  </si>
-  <si>
-    <t>TIM</t>
-  </si>
-  <si>
-    <t>Lojas Quero-Quero</t>
-  </si>
-  <si>
-    <t>3R Petroleum</t>
-  </si>
-  <si>
-    <t>Recrusul</t>
-  </si>
-  <si>
-    <t>Oi</t>
-  </si>
-  <si>
-    <t>JBS</t>
-  </si>
-  <si>
-    <t>Movida</t>
-  </si>
-  <si>
-    <t>Grupo Mateus</t>
-  </si>
-  <si>
-    <t>Cyrela</t>
-  </si>
-  <si>
-    <t>CSN Mineração</t>
-  </si>
-  <si>
-    <t>YDUQS</t>
-  </si>
-  <si>
-    <t>Suzano</t>
+    <t>Dexco</t>
+  </si>
+  <si>
+    <t>Iguatemi</t>
+  </si>
+  <si>
+    <t>Arezzo</t>
+  </si>
+  <si>
+    <t>Santos Brasil</t>
+  </si>
+  <si>
+    <t>Caixa Seguridade</t>
+  </si>
+  <si>
+    <t>Fleury</t>
+  </si>
+  <si>
+    <t>CPFL Energia</t>
+  </si>
+  <si>
+    <t>Cruzeiro do Sul Educacional</t>
+  </si>
+  <si>
+    <t>GOL</t>
+  </si>
+  <si>
+    <t>Boa Safra Sementes</t>
+  </si>
+  <si>
+    <t>Energisa</t>
+  </si>
+  <si>
+    <t>Lavvi Incorporadora</t>
+  </si>
+  <si>
+    <t>COPASA</t>
+  </si>
+  <si>
+    <t>Camil Alimentos</t>
+  </si>
+  <si>
+    <t>Grendene</t>
+  </si>
+  <si>
+    <t>Guararapes</t>
+  </si>
+  <si>
+    <t>Kepler Weber</t>
+  </si>
+  <si>
+    <t>Méliuz</t>
+  </si>
+  <si>
+    <t>Paranapanema</t>
+  </si>
+  <si>
+    <t>Hypera</t>
+  </si>
+  <si>
+    <t>Neoenergia</t>
+  </si>
+  <si>
+    <t>Oncoclínicas</t>
+  </si>
+  <si>
+    <t>Construtora Tenda</t>
+  </si>
+  <si>
+    <t>Odontoprev</t>
   </si>
   <si>
     <t>Armac</t>
   </si>
   <si>
-    <t>Klabin</t>
-  </si>
-  <si>
-    <t>Auren Energia</t>
-  </si>
-  <si>
-    <t>Smart Fit</t>
-  </si>
-  <si>
-    <t>Randon</t>
-  </si>
-  <si>
-    <t>Embraer</t>
-  </si>
-  <si>
-    <t>GOL</t>
-  </si>
-  <si>
-    <t>Eneva</t>
-  </si>
-  <si>
-    <t>Azevedo &amp; Travassos</t>
-  </si>
-  <si>
-    <t>Marfrig</t>
-  </si>
-  <si>
-    <t>Oncoclínicas</t>
+    <t>Engie</t>
+  </si>
+  <si>
+    <t>Vivo</t>
+  </si>
+  <si>
+    <t>Hidrovias do Brasil</t>
+  </si>
+  <si>
+    <t>Grupo SBF</t>
+  </si>
+  <si>
+    <t>Porto Seguro</t>
+  </si>
+  <si>
+    <t>Tupy</t>
+  </si>
+  <si>
+    <t>Taesa</t>
+  </si>
+  <si>
+    <t>Light</t>
+  </si>
+  <si>
+    <t>Iochpe-Maxion</t>
+  </si>
+  <si>
+    <t>Even</t>
+  </si>
+  <si>
+    <t>Alpargatas</t>
+  </si>
+  <si>
+    <t>Positivo</t>
+  </si>
+  <si>
+    <t>3tentos</t>
+  </si>
+  <si>
+    <t>Unifique</t>
+  </si>
+  <si>
+    <t>Dasa</t>
+  </si>
+  <si>
+    <t>ISA Energia</t>
+  </si>
+  <si>
+    <t>Banrisul</t>
+  </si>
+  <si>
+    <t>JSL</t>
+  </si>
+  <si>
+    <t>Mills</t>
+  </si>
+  <si>
+    <t>Ser Educacional</t>
+  </si>
+  <si>
+    <t>Multilaser</t>
+  </si>
+  <si>
+    <t>Sanepar</t>
+  </si>
+  <si>
+    <t>Helbor</t>
+  </si>
+  <si>
+    <t>Alupar</t>
+  </si>
+  <si>
+    <t>Alliança</t>
+  </si>
+  <si>
+    <t>Bemobi</t>
+  </si>
+  <si>
+    <t>Pague Menos</t>
   </si>
   <si>
     <t>Viveo</t>
   </si>
   <si>
-    <t>WEG</t>
-  </si>
-  <si>
-    <t>PetroRio</t>
-  </si>
-  <si>
-    <t>Braskem</t>
-  </si>
-  <si>
-    <t>Santos Brasil</t>
-  </si>
-  <si>
-    <t>Caixa Seguridade</t>
-  </si>
-  <si>
-    <t>Allos</t>
-  </si>
-  <si>
-    <t>Multiplan</t>
-  </si>
-  <si>
-    <t>Fleury</t>
+    <t>Vulcabras</t>
+  </si>
+  <si>
+    <t>HBR Realty</t>
+  </si>
+  <si>
+    <t>Melnick</t>
+  </si>
+  <si>
+    <t>Blau Farmacêutica</t>
+  </si>
+  <si>
+    <t>Banco ABC Brasil</t>
+  </si>
+  <si>
+    <t>Plano&amp;Plano</t>
+  </si>
+  <si>
+    <t>Dimed</t>
+  </si>
+  <si>
+    <t>VITRUBREPCOM</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
+    <t>Zamp</t>
+  </si>
+  <si>
+    <t>Banco BMG</t>
+  </si>
+  <si>
+    <t>Irani</t>
+  </si>
+  <si>
+    <t>Mitre Realty</t>
+  </si>
+  <si>
+    <t>AgroGalaxy</t>
+  </si>
+  <si>
+    <t>Portobello</t>
+  </si>
+  <si>
+    <t>SYN</t>
+  </si>
+  <si>
+    <t>Profarma</t>
+  </si>
+  <si>
+    <t>Espaçolaser</t>
+  </si>
+  <si>
+    <t>Banco Pine</t>
+  </si>
+  <si>
+    <t>Schulz</t>
+  </si>
+  <si>
+    <t>M. Dias Branco</t>
+  </si>
+  <si>
+    <t>Ferbasa</t>
+  </si>
+  <si>
+    <t>Eletromidia</t>
+  </si>
+  <si>
+    <t>Moura Dubeux</t>
+  </si>
+  <si>
+    <t>BR Partners</t>
+  </si>
+  <si>
+    <t>IMC Alimentação</t>
+  </si>
+  <si>
+    <t>Renova Energia</t>
+  </si>
+  <si>
+    <t>Vittia</t>
+  </si>
+  <si>
+    <t>OceanPact</t>
+  </si>
+  <si>
+    <t>BrasilAgro</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve</t>
+  </si>
+  <si>
+    <t>LOG CP</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Wiz Soluções</t>
+  </si>
+  <si>
+    <t>Fras-le</t>
+  </si>
+  <si>
+    <t>Sequoia Logística</t>
+  </si>
+  <si>
+    <t>Mater Dei</t>
+  </si>
+  <si>
+    <t>Mobly</t>
+  </si>
+  <si>
+    <t>Trisul</t>
+  </si>
+  <si>
+    <t>Jalles Machado</t>
+  </si>
+  <si>
+    <t>Track &amp; Field</t>
+  </si>
+  <si>
+    <t>Aeris Energy</t>
+  </si>
+  <si>
+    <t>Taurus</t>
+  </si>
+  <si>
+    <t>Orizon</t>
+  </si>
+  <si>
+    <t>PDG Realty</t>
+  </si>
+  <si>
+    <t>Brisanet</t>
+  </si>
+  <si>
+    <t>Priner</t>
+  </si>
+  <si>
+    <t>Lojas Marisa</t>
+  </si>
+  <si>
+    <t>Time For Fun</t>
+  </si>
+  <si>
+    <t>Unipar</t>
+  </si>
+  <si>
+    <t>Tegma</t>
+  </si>
+  <si>
+    <t>Estapar</t>
+  </si>
+  <si>
+    <t>D1000 Varejo Farma</t>
+  </si>
+  <si>
+    <t>Rossi Residencial</t>
+  </si>
+  <si>
+    <t>Eternit</t>
+  </si>
+  <si>
+    <t>Indústrias ROMI</t>
+  </si>
+  <si>
+    <t>Technos</t>
+  </si>
+  <si>
+    <t>WDC Networks</t>
   </si>
   <si>
     <t>Jereissati Participações</t>
   </si>
   <si>
-    <t>Ultrapar</t>
-  </si>
-  <si>
-    <t>GPS</t>
-  </si>
-  <si>
-    <t>Hypera</t>
-  </si>
-  <si>
-    <t>Rede D'Or</t>
-  </si>
-  <si>
-    <t>Vivara</t>
-  </si>
-  <si>
-    <t>Ser Educacional</t>
-  </si>
-  <si>
-    <t>Sanepar</t>
-  </si>
-  <si>
-    <t>Light</t>
-  </si>
-  <si>
-    <t>BB Seguridade</t>
-  </si>
-  <si>
-    <t>Bradespar</t>
-  </si>
-  <si>
-    <t>Intelbras</t>
-  </si>
-  <si>
-    <t>Banco Santander</t>
-  </si>
-  <si>
-    <t>C&amp;A</t>
-  </si>
-  <si>
-    <t>Serena Energia</t>
-  </si>
-  <si>
-    <t>Iochpe-Maxion</t>
-  </si>
-  <si>
-    <t>Hidrovias do Brasil</t>
-  </si>
-  <si>
-    <t>Arezzo</t>
-  </si>
-  <si>
-    <t>COPASA</t>
-  </si>
-  <si>
-    <t>Porto Seguro</t>
-  </si>
-  <si>
-    <t>Totvs</t>
-  </si>
-  <si>
-    <t>Tupy</t>
-  </si>
-  <si>
-    <t>Energisa</t>
-  </si>
-  <si>
-    <t>Banco BMG</t>
+    <t>Fertilizantes Heringer</t>
+  </si>
+  <si>
+    <t>Dexxos</t>
+  </si>
+  <si>
+    <t>São Carlos</t>
+  </si>
+  <si>
+    <t>Eucatex</t>
+  </si>
+  <si>
+    <t>Ambipar</t>
+  </si>
+  <si>
+    <t>Lopes</t>
+  </si>
+  <si>
+    <t>Terra Santa</t>
+  </si>
+  <si>
+    <t>Inepar</t>
+  </si>
+  <si>
+    <t>Viver</t>
+  </si>
+  <si>
+    <t>Traders Club</t>
+  </si>
+  <si>
+    <t>DASA11</t>
+  </si>
+  <si>
+    <t>Lupatech</t>
+  </si>
+  <si>
+    <t>CSU Cardsystem</t>
+  </si>
+  <si>
+    <t>Padtec</t>
+  </si>
+  <si>
+    <t>Cambuci</t>
+  </si>
+  <si>
+    <t>Bombril</t>
+  </si>
+  <si>
+    <t>Neogrid</t>
+  </si>
+  <si>
+    <t>Allied</t>
+  </si>
+  <si>
+    <t>Unicasa</t>
+  </si>
+  <si>
+    <t>Tecnisa</t>
+  </si>
+  <si>
+    <t>Fictor Alimentos</t>
+  </si>
+  <si>
+    <t>Banestes</t>
+  </si>
+  <si>
+    <t>CEB</t>
+  </si>
+  <si>
+    <t>RNI</t>
+  </si>
+  <si>
+    <t>REAG3</t>
+  </si>
+  <si>
+    <t>Banco Mercantil do Brasil</t>
+  </si>
+  <si>
+    <t>Dotz</t>
+  </si>
+  <si>
+    <t>Banco de Brasília</t>
+  </si>
+  <si>
+    <t>Pettenati</t>
+  </si>
+  <si>
+    <t>Whirlpool</t>
+  </si>
+  <si>
+    <t>Equatorial Energia Pará</t>
+  </si>
+  <si>
+    <t>Log-In</t>
+  </si>
+  <si>
+    <t>João Fortes</t>
+  </si>
+  <si>
+    <t>Telebras</t>
+  </si>
+  <si>
+    <t>Westwing</t>
+  </si>
+  <si>
+    <t>Triunfo</t>
+  </si>
+  <si>
+    <t>Embpar Participações</t>
+  </si>
+  <si>
+    <t>Electro Aço Altona</t>
+  </si>
+  <si>
+    <t>Biomm</t>
+  </si>
+  <si>
+    <t>OSX Brasil</t>
+  </si>
+  <si>
+    <t>Alphaville</t>
+  </si>
+  <si>
+    <t>Banco da Amazônia</t>
+  </si>
+  <si>
+    <t>Nutriplant</t>
+  </si>
+  <si>
+    <t>LE LIS BLANC</t>
+  </si>
+  <si>
+    <t>Cedro Têxtil</t>
+  </si>
+  <si>
+    <t>Celesc</t>
+  </si>
+  <si>
+    <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
+  </si>
+  <si>
+    <t>Panatlântica</t>
+  </si>
+  <si>
+    <t>Ourofino Saúde Animal</t>
+  </si>
+  <si>
+    <t>Sansuy</t>
+  </si>
+  <si>
+    <t>Hotéis Othon</t>
+  </si>
+  <si>
+    <t>Minupar</t>
+  </si>
+  <si>
+    <t>Döhler</t>
+  </si>
+  <si>
+    <t>Equatorial Maranhão</t>
+  </si>
+  <si>
+    <t>Alfa Holdings</t>
+  </si>
+  <si>
+    <t>Brasil Brokers</t>
+  </si>
+  <si>
+    <t>Mundial</t>
+  </si>
+  <si>
+    <t>Kora Saúde</t>
+  </si>
+  <si>
+    <t>WLM</t>
+  </si>
+  <si>
+    <t>Coelce</t>
+  </si>
+  <si>
+    <t>Plascar</t>
+  </si>
+  <si>
+    <t>Haga</t>
+  </si>
+  <si>
+    <t>EMAE</t>
+  </si>
+  <si>
+    <t>Banese</t>
+  </si>
+  <si>
+    <t>Santanense</t>
+  </si>
+  <si>
+    <t>Nordon</t>
+  </si>
+  <si>
+    <t>Tronox Pigmentos</t>
+  </si>
+  <si>
+    <t>Grazziotin</t>
+  </si>
+  <si>
+    <t>Rede Energia</t>
+  </si>
+  <si>
+    <t>Mangels</t>
+  </si>
+  <si>
+    <t>Karsten</t>
+  </si>
+  <si>
+    <t>Metisa</t>
+  </si>
+  <si>
+    <t>Rio Paranapanema Energia</t>
+  </si>
+  <si>
+    <t>Fica</t>
+  </si>
+  <si>
+    <t>Metalúrgica Riosulense</t>
+  </si>
+  <si>
+    <t>Dtcom</t>
+  </si>
+  <si>
+    <t>Energisa MT</t>
+  </si>
+  <si>
+    <t>MRS Logística</t>
+  </si>
+  <si>
+    <t>Josapar</t>
+  </si>
+  <si>
+    <t>Banco Mercantil de Investimentos</t>
+  </si>
+  <si>
+    <t>BIED3</t>
+  </si>
+  <si>
+    <t>Atma</t>
+  </si>
+  <si>
+    <t>Naturgy (CEG)</t>
+  </si>
+  <si>
+    <t>Baumer</t>
+  </si>
+  <si>
+    <t>Monark</t>
+  </si>
+  <si>
+    <t>Refinaria de Manguinhos</t>
+  </si>
+  <si>
+    <t>Monteiro Aranha</t>
+  </si>
+  <si>
+    <t>Comgás</t>
+  </si>
+  <si>
+    <t>Banco do Nordeste</t>
+  </si>
+  <si>
+    <t>COELBA</t>
+  </si>
+  <si>
+    <t>Trevisa</t>
+  </si>
+  <si>
+    <t>Tekno</t>
+  </si>
+  <si>
+    <t>Elektro</t>
+  </si>
+  <si>
+    <t>PPLA</t>
+  </si>
+  <si>
+    <t>São Paulo Turismo</t>
+  </si>
+  <si>
+    <t>Habitasul</t>
+  </si>
+  <si>
+    <t>Estrela</t>
+  </si>
+  <si>
+    <t>CELGPAR</t>
+  </si>
+  <si>
+    <t>CEEE D</t>
+  </si>
+  <si>
+    <t>PORTO VM</t>
+  </si>
+  <si>
+    <t>Sondotécnica</t>
+  </si>
+  <si>
+    <t>Eletropar</t>
+  </si>
+  <si>
+    <t>Bardella</t>
+  </si>
+  <si>
+    <t>Participações Aliança da Bahia</t>
+  </si>
+  <si>
+    <t>Mercantil do Brasil Financeira</t>
+  </si>
+  <si>
+    <t>Hercules</t>
+  </si>
+  <si>
+    <t>Afluente T</t>
+  </si>
+  <si>
+    <t>Metalfrio</t>
+  </si>
+  <si>
+    <t>Excelsior</t>
+  </si>
+  <si>
+    <t>Wetzel</t>
   </si>
   <si>
     <t>ClearSale</t>
   </si>
   <si>
-    <t>Sabesp</t>
-  </si>
-  <si>
-    <t>Grendene</t>
-  </si>
-  <si>
-    <t>Dexco</t>
-  </si>
-  <si>
-    <t>Zamp</t>
-  </si>
-  <si>
-    <t>Engie</t>
-  </si>
-  <si>
-    <t>Vivo</t>
-  </si>
-  <si>
-    <t>Kepler Weber</t>
-  </si>
-  <si>
-    <t>Construtora Tenda</t>
-  </si>
-  <si>
-    <t>Odontoprev</t>
-  </si>
-  <si>
-    <t>ISA Energia</t>
-  </si>
-  <si>
-    <t>Qualicorp</t>
-  </si>
-  <si>
-    <t>Wilson Sons</t>
-  </si>
-  <si>
-    <t>Even</t>
-  </si>
-  <si>
-    <t>Grupo SBF</t>
-  </si>
-  <si>
-    <t>Cury</t>
-  </si>
-  <si>
-    <t>Guararapes</t>
-  </si>
-  <si>
-    <t>Pague Menos</t>
-  </si>
-  <si>
-    <t>Melnick</t>
-  </si>
-  <si>
-    <t>Boa Safra Sementes</t>
-  </si>
-  <si>
-    <t>Dasa</t>
-  </si>
-  <si>
-    <t>Alpargatas</t>
-  </si>
-  <si>
-    <t>SYN</t>
-  </si>
-  <si>
-    <t>VITRUBREPCOM</t>
-  </si>
-  <si>
-    <t>Multilaser</t>
-  </si>
-  <si>
-    <t>Camil Alimentos</t>
-  </si>
-  <si>
-    <t>São Martinho</t>
-  </si>
-  <si>
-    <t>SLC Agrícola</t>
-  </si>
-  <si>
-    <t>Mitre Realty</t>
-  </si>
-  <si>
-    <t>IMC Alimentação</t>
-  </si>
-  <si>
-    <t>Banco Pan</t>
-  </si>
-  <si>
-    <t>Enjoei</t>
-  </si>
-  <si>
-    <t>PetroRecôncavo</t>
-  </si>
-  <si>
-    <t>Taesa</t>
-  </si>
-  <si>
-    <t>Alupar</t>
-  </si>
-  <si>
-    <t>Mills</t>
-  </si>
-  <si>
-    <t>EZTEC</t>
-  </si>
-  <si>
-    <t>Direcional</t>
-  </si>
-  <si>
-    <t>M. Dias Branco</t>
-  </si>
-  <si>
-    <t>Positivo</t>
-  </si>
-  <si>
-    <t>Méliuz</t>
-  </si>
-  <si>
-    <t>CPFL Energia</t>
-  </si>
-  <si>
-    <t>Banrisul</t>
-  </si>
-  <si>
-    <t>Trisul</t>
-  </si>
-  <si>
-    <t>Banco ABC Brasil</t>
-  </si>
-  <si>
-    <t>Tegma</t>
-  </si>
-  <si>
-    <t>3tentos</t>
-  </si>
-  <si>
-    <t>JSL</t>
-  </si>
-  <si>
-    <t>IRB Brasil RE</t>
-  </si>
-  <si>
-    <t>Ferbasa</t>
-  </si>
-  <si>
-    <t>Helbor</t>
-  </si>
-  <si>
-    <t>Mater Dei</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve</t>
-  </si>
-  <si>
-    <t>Paranapanema</t>
-  </si>
-  <si>
-    <t>Moura Dubeux</t>
-  </si>
-  <si>
-    <t>Dimed</t>
-  </si>
-  <si>
-    <t>PDG Realty</t>
-  </si>
-  <si>
-    <t>Neoenergia</t>
-  </si>
-  <si>
-    <t>Vulcabras</t>
-  </si>
-  <si>
-    <t>Unifique</t>
-  </si>
-  <si>
-    <t>Irani</t>
-  </si>
-  <si>
-    <t>Biomm</t>
-  </si>
-  <si>
-    <t>Wiz Soluções</t>
-  </si>
-  <si>
-    <t>Plano&amp;Plano</t>
-  </si>
-  <si>
-    <t>BR Partners</t>
-  </si>
-  <si>
-    <t>Aeris Energy</t>
-  </si>
-  <si>
-    <t>Lavvi Incorporadora</t>
-  </si>
-  <si>
-    <t>Fras-le</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>Jalles Machado</t>
-  </si>
-  <si>
-    <t>HBR Realty</t>
-  </si>
-  <si>
-    <t>Bemobi</t>
-  </si>
-  <si>
-    <t>Blau Farmacêutica</t>
-  </si>
-  <si>
-    <t>Schulz</t>
-  </si>
-  <si>
-    <t>Alliança</t>
-  </si>
-  <si>
-    <t>AgroGalaxy</t>
-  </si>
-  <si>
-    <t>Eletromidia</t>
-  </si>
-  <si>
-    <t>Mobly</t>
-  </si>
-  <si>
-    <t>Profarma</t>
-  </si>
-  <si>
-    <t>OceanPact</t>
-  </si>
-  <si>
-    <t>Sequoia Logística</t>
-  </si>
-  <si>
-    <t>Lojas Marisa</t>
-  </si>
-  <si>
-    <t>Orizon</t>
-  </si>
-  <si>
-    <t>Valid</t>
-  </si>
-  <si>
-    <t>Taurus</t>
-  </si>
-  <si>
-    <t>Track &amp; Field</t>
-  </si>
-  <si>
-    <t>São Carlos</t>
-  </si>
-  <si>
-    <t>Priner</t>
-  </si>
-  <si>
-    <t>LOG CP</t>
-  </si>
-  <si>
-    <t>Vittia</t>
-  </si>
-  <si>
-    <t>Cruzeiro do Sul Educacional</t>
-  </si>
-  <si>
-    <t>Lupatech</t>
-  </si>
-  <si>
-    <t>Portobello</t>
-  </si>
-  <si>
-    <t>Time For Fun</t>
-  </si>
-  <si>
-    <t>Inepar</t>
-  </si>
-  <si>
-    <t>Eucatex</t>
-  </si>
-  <si>
-    <t>Espaçolaser</t>
-  </si>
-  <si>
-    <t>Unipar</t>
-  </si>
-  <si>
-    <t>Dexxos</t>
-  </si>
-  <si>
-    <t>Brisanet</t>
-  </si>
-  <si>
-    <t>Eternit</t>
-  </si>
-  <si>
-    <t>Unicasa</t>
-  </si>
-  <si>
-    <t>Allied</t>
-  </si>
-  <si>
-    <t>Indústrias ROMI</t>
-  </si>
-  <si>
-    <t>Triunfo</t>
-  </si>
-  <si>
-    <t>BrasilAgro</t>
-  </si>
-  <si>
-    <t>Estapar</t>
-  </si>
-  <si>
-    <t>Viver</t>
-  </si>
-  <si>
-    <t>Technos</t>
-  </si>
-  <si>
-    <t>Atma</t>
-  </si>
-  <si>
-    <t>Renova Energia</t>
-  </si>
-  <si>
-    <t>Fictor Alimentos</t>
-  </si>
-  <si>
-    <t>Banco Pine</t>
-  </si>
-  <si>
-    <t>WDC Networks</t>
-  </si>
-  <si>
-    <t>Ambipar</t>
-  </si>
-  <si>
-    <t>Lopes</t>
-  </si>
-  <si>
-    <t>Electro Aço Altona</t>
-  </si>
-  <si>
-    <t>D1000 Varejo Farma</t>
-  </si>
-  <si>
-    <t>Traders Club</t>
-  </si>
-  <si>
-    <t>RNI</t>
-  </si>
-  <si>
-    <t>Padtec</t>
-  </si>
-  <si>
-    <t>Tecnisa</t>
-  </si>
-  <si>
-    <t>CSU Cardsystem</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer</t>
-  </si>
-  <si>
-    <t>Bombril</t>
-  </si>
-  <si>
-    <t>Hotéis Othon</t>
-  </si>
-  <si>
-    <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
-  </si>
-  <si>
-    <t>Log-In</t>
-  </si>
-  <si>
-    <t>Neogrid</t>
-  </si>
-  <si>
-    <t>João Fortes</t>
-  </si>
-  <si>
-    <t>Whirlpool</t>
-  </si>
-  <si>
-    <t>Rossi Residencial</t>
-  </si>
-  <si>
-    <t>Dotz</t>
-  </si>
-  <si>
-    <t>Cambuci</t>
-  </si>
-  <si>
-    <t>LE LIS BLANC</t>
-  </si>
-  <si>
-    <t>Banestes</t>
-  </si>
-  <si>
-    <t>Terra Santa</t>
-  </si>
-  <si>
-    <t>Banco Mercantil do Brasil</t>
-  </si>
-  <si>
-    <t>Embpar Participações</t>
-  </si>
-  <si>
-    <t>Equatorial Energia Pará</t>
-  </si>
-  <si>
-    <t>Nutriplant</t>
-  </si>
-  <si>
-    <t>Westwing</t>
-  </si>
-  <si>
-    <t>Banco da Amazônia</t>
-  </si>
-  <si>
-    <t>EMAE</t>
-  </si>
-  <si>
-    <t>Coelce</t>
-  </si>
-  <si>
-    <t>CEB</t>
-  </si>
-  <si>
-    <t>Sansuy</t>
-  </si>
-  <si>
-    <t>OSX Brasil</t>
-  </si>
-  <si>
-    <t>Pettenati</t>
-  </si>
-  <si>
-    <t>Ourofino Saúde Animal</t>
-  </si>
-  <si>
-    <t>Panatlântica</t>
-  </si>
-  <si>
-    <t>BIED3</t>
-  </si>
-  <si>
-    <t>REAG3</t>
-  </si>
-  <si>
-    <t>Banese</t>
-  </si>
-  <si>
-    <t>Mangels</t>
-  </si>
-  <si>
-    <t>Grazziotin</t>
-  </si>
-  <si>
-    <t>Banco de Brasília</t>
-  </si>
-  <si>
-    <t>Tekno</t>
-  </si>
-  <si>
-    <t>Celesc</t>
-  </si>
-  <si>
-    <t>Döhler</t>
-  </si>
-  <si>
-    <t>Haga</t>
-  </si>
-  <si>
-    <t>Metalúrgica Riosulense</t>
-  </si>
-  <si>
-    <t>DASA11</t>
-  </si>
-  <si>
-    <t>Cedro Têxtil</t>
-  </si>
-  <si>
-    <t>Tronox Pigmentos</t>
-  </si>
-  <si>
-    <t>Metisa</t>
-  </si>
-  <si>
-    <t>WLM</t>
-  </si>
-  <si>
-    <t>Telebras</t>
-  </si>
-  <si>
-    <t>Kora Saúde</t>
-  </si>
-  <si>
-    <t>Fica</t>
-  </si>
-  <si>
-    <t>Refinaria de Manguinhos</t>
-  </si>
-  <si>
-    <t>PPLA</t>
-  </si>
-  <si>
-    <t>Metalfrio</t>
-  </si>
-  <si>
-    <t>Elektro</t>
-  </si>
-  <si>
-    <t>Monteiro Aranha</t>
-  </si>
-  <si>
-    <t>Rio Paranapanema Energia</t>
-  </si>
-  <si>
-    <t>Minupar</t>
-  </si>
-  <si>
-    <t>Banco Mercantil de Investimentos</t>
-  </si>
-  <si>
-    <t>Afluente T</t>
-  </si>
-  <si>
-    <t>Rede Energia</t>
-  </si>
-  <si>
-    <t>Equatorial Maranhão</t>
-  </si>
-  <si>
-    <t>Participações Aliança da Bahia</t>
-  </si>
-  <si>
-    <t>COELBA</t>
-  </si>
-  <si>
-    <t>Karsten</t>
-  </si>
-  <si>
-    <t>Santanense</t>
-  </si>
-  <si>
-    <t>Banco do Nordeste</t>
-  </si>
-  <si>
-    <t>Josapar</t>
-  </si>
-  <si>
-    <t>Mundial</t>
-  </si>
-  <si>
-    <t>Wetzel</t>
-  </si>
-  <si>
-    <t>Bardella</t>
-  </si>
-  <si>
-    <t>Brasil Brokers</t>
-  </si>
-  <si>
-    <t>Sondotécnica</t>
-  </si>
-  <si>
-    <t>Baumer</t>
-  </si>
-  <si>
-    <t>Monark</t>
-  </si>
-  <si>
-    <t>Alphaville</t>
-  </si>
-  <si>
-    <t>Dtcom</t>
-  </si>
-  <si>
-    <t>Comgás</t>
-  </si>
-  <si>
-    <t>São Paulo Turismo</t>
-  </si>
-  <si>
-    <t>Habitasul</t>
-  </si>
-  <si>
-    <t>Alfa Holdings</t>
-  </si>
-  <si>
-    <t>Plascar</t>
-  </si>
-  <si>
-    <t>Nordon</t>
-  </si>
-  <si>
-    <t>Hercules</t>
-  </si>
-  <si>
-    <t>PORTO VM</t>
-  </si>
-  <si>
-    <t>Cemepe</t>
-  </si>
-  <si>
-    <t>Trevisa</t>
-  </si>
-  <si>
-    <t>Ampla Energia</t>
-  </si>
-  <si>
-    <t>Energisa MT</t>
-  </si>
-  <si>
-    <t>Eletropar</t>
-  </si>
-  <si>
-    <t>Mercantil do Brasil Financeira</t>
-  </si>
-  <si>
-    <t>MRS Logística</t>
-  </si>
-  <si>
-    <t>Estrela</t>
+    <t>PETR4</t>
+  </si>
+  <si>
+    <t>COGN3</t>
+  </si>
+  <si>
+    <t>HAPV3</t>
+  </si>
+  <si>
+    <t>B3SA3</t>
+  </si>
+  <si>
+    <t>OIBR3</t>
+  </si>
+  <si>
+    <t>ITSA4</t>
+  </si>
+  <si>
+    <t>ABEV3</t>
+  </si>
+  <si>
+    <t>PCAR3</t>
+  </si>
+  <si>
+    <t>BBDC4</t>
+  </si>
+  <si>
+    <t>ITUB4</t>
+  </si>
+  <si>
+    <t>MGLU3</t>
+  </si>
+  <si>
+    <t>CRFB3</t>
+  </si>
+  <si>
+    <t>VALE3</t>
+  </si>
+  <si>
+    <t>PETR3</t>
+  </si>
+  <si>
+    <t>CCRO3</t>
+  </si>
+  <si>
+    <t>POMO4</t>
+  </si>
+  <si>
+    <t>CVCB3</t>
+  </si>
+  <si>
+    <t>VAMO3</t>
+  </si>
+  <si>
+    <t>CSAN3</t>
+  </si>
+  <si>
+    <t>GOAU4</t>
+  </si>
+  <si>
+    <t>PRIO3</t>
+  </si>
+  <si>
+    <t>BRAV3</t>
+  </si>
+  <si>
+    <t>LREN3</t>
+  </si>
+  <si>
+    <t>BBAS3</t>
+  </si>
+  <si>
+    <t>RAIL3</t>
+  </si>
+  <si>
+    <t>BEEF3</t>
+  </si>
+  <si>
+    <t>CMIG4</t>
+  </si>
+  <si>
+    <t>RENT3</t>
+  </si>
+  <si>
+    <t>AMOB3</t>
+  </si>
+  <si>
+    <t>GGBR4</t>
+  </si>
+  <si>
+    <t>CPLE6</t>
+  </si>
+  <si>
+    <t>ANIM3</t>
+  </si>
+  <si>
+    <t>ASAI3</t>
+  </si>
+  <si>
+    <t>AZUL4</t>
+  </si>
+  <si>
+    <t>RAPT4</t>
+  </si>
+  <si>
+    <t>RAIZ4</t>
+  </si>
+  <si>
+    <t>LWSA3</t>
+  </si>
+  <si>
+    <t>RADL3</t>
+  </si>
+  <si>
+    <t>CPLE3</t>
+  </si>
+  <si>
+    <t>USIM5</t>
+  </si>
+  <si>
+    <t>VBBR3</t>
+  </si>
+  <si>
+    <t>MRVE3</t>
+  </si>
+  <si>
+    <t>ENEV3</t>
+  </si>
+  <si>
+    <t>CSNA3</t>
+  </si>
+  <si>
+    <t>SRNA3</t>
+  </si>
+  <si>
+    <t>BPAC11</t>
+  </si>
+  <si>
+    <t>NTCO3</t>
+  </si>
+  <si>
+    <t>CYRE3</t>
+  </si>
+  <si>
+    <t>MOVI3</t>
   </si>
   <si>
     <t>IFCM3</t>
   </si>
   <si>
-    <t>HAPV3</t>
-  </si>
-  <si>
-    <t>COGN3</t>
-  </si>
-  <si>
-    <t>CVCB3</t>
-  </si>
-  <si>
-    <t>ITSA4</t>
-  </si>
-  <si>
-    <t>ABEV3</t>
-  </si>
-  <si>
-    <t>VAMO3</t>
-  </si>
-  <si>
-    <t>VALE3</t>
-  </si>
-  <si>
-    <t>MGLU3</t>
+    <t>CBAV3</t>
+  </si>
+  <si>
+    <t>BHIA3</t>
+  </si>
+  <si>
+    <t>SIMH3</t>
+  </si>
+  <si>
+    <t>GMAT3</t>
+  </si>
+  <si>
+    <t>KLBN11</t>
   </si>
   <si>
     <t>GFSA3</t>
   </si>
   <si>
-    <t>BBDC4</t>
-  </si>
-  <si>
-    <t>ITUB4</t>
-  </si>
-  <si>
-    <t>PETR4</t>
-  </si>
-  <si>
-    <t>B3SA3</t>
-  </si>
-  <si>
-    <t>POMO4</t>
-  </si>
-  <si>
-    <t>LREN3</t>
-  </si>
-  <si>
-    <t>USIM5</t>
-  </si>
-  <si>
-    <t>NTCO3</t>
-  </si>
-  <si>
-    <t>ASAI3</t>
+    <t>EQTL3</t>
+  </si>
+  <si>
+    <t>RDOR3</t>
+  </si>
+  <si>
+    <t>BBDC3</t>
+  </si>
+  <si>
+    <t>ELET3</t>
+  </si>
+  <si>
+    <t>SUZB3</t>
+  </si>
+  <si>
+    <t>MRFG3</t>
+  </si>
+  <si>
+    <t>CMIN3</t>
+  </si>
+  <si>
+    <t>SANB11</t>
+  </si>
+  <si>
+    <t>RECV3</t>
+  </si>
+  <si>
+    <t>MULT3</t>
+  </si>
+  <si>
+    <t>TIMS3</t>
+  </si>
+  <si>
+    <t>SLCE3</t>
+  </si>
+  <si>
+    <t>ECOR3</t>
   </si>
   <si>
     <t>PETZ3</t>
   </si>
   <si>
-    <t>BBAS3</t>
-  </si>
-  <si>
-    <t>BHIA3</t>
-  </si>
-  <si>
-    <t>RAIZ4</t>
-  </si>
-  <si>
-    <t>ANIM3</t>
-  </si>
-  <si>
-    <t>CCRO3</t>
-  </si>
-  <si>
-    <t>RAIL3</t>
-  </si>
-  <si>
-    <t>CMIG4</t>
-  </si>
-  <si>
-    <t>ELET3</t>
-  </si>
-  <si>
-    <t>AZUL4</t>
+    <t>AZEV4</t>
+  </si>
+  <si>
+    <t>BRFS3</t>
+  </si>
+  <si>
+    <t>PORT3</t>
+  </si>
+  <si>
+    <t>UGPA3</t>
+  </si>
+  <si>
+    <t>SMFT3</t>
+  </si>
+  <si>
+    <t>RCSL4</t>
+  </si>
+  <si>
+    <t>BPAN4</t>
+  </si>
+  <si>
+    <t>AMER3</t>
+  </si>
+  <si>
+    <t>AURE3</t>
+  </si>
+  <si>
+    <t>ENJU3</t>
+  </si>
+  <si>
+    <t>JBSS3</t>
+  </si>
+  <si>
+    <t>CEAB3</t>
+  </si>
+  <si>
+    <t>KLBN4</t>
+  </si>
+  <si>
+    <t>BRAP4</t>
+  </si>
+  <si>
+    <t>EMBR3</t>
+  </si>
+  <si>
+    <t>INTB3</t>
+  </si>
+  <si>
+    <t>SBSP3</t>
+  </si>
+  <si>
+    <t>ALOS3</t>
+  </si>
+  <si>
+    <t>WEGE3</t>
+  </si>
+  <si>
+    <t>YDUQ3</t>
+  </si>
+  <si>
+    <t>VIVA3</t>
+  </si>
+  <si>
+    <t>BBSE3</t>
+  </si>
+  <si>
+    <t>SMTO3</t>
+  </si>
+  <si>
+    <t>LJQQ3</t>
+  </si>
+  <si>
+    <t>DIRR3</t>
+  </si>
+  <si>
+    <t>TOTS3</t>
+  </si>
+  <si>
+    <t>IRBR3</t>
+  </si>
+  <si>
+    <t>EZTC3</t>
+  </si>
+  <si>
+    <t>CURY3</t>
+  </si>
+  <si>
+    <t>BRKM5</t>
+  </si>
+  <si>
+    <t>QUAL3</t>
+  </si>
+  <si>
+    <t>GGPS3</t>
   </si>
   <si>
     <t>JHSF3</t>
   </si>
   <si>
-    <t>MRVE3</t>
-  </si>
-  <si>
-    <t>LWSA3</t>
-  </si>
-  <si>
-    <t>AMOB3</t>
-  </si>
-  <si>
-    <t>AMER3</t>
-  </si>
-  <si>
-    <t>CSNA3</t>
-  </si>
-  <si>
-    <t>SIMH3</t>
-  </si>
-  <si>
-    <t>CSAN3</t>
-  </si>
-  <si>
-    <t>VBBR3</t>
-  </si>
-  <si>
-    <t>GGBR4</t>
-  </si>
-  <si>
-    <t>BEEF3</t>
-  </si>
-  <si>
-    <t>CBAV3</t>
-  </si>
-  <si>
-    <t>RADL3</t>
-  </si>
-  <si>
-    <t>CRFB3</t>
-  </si>
-  <si>
-    <t>CPLE6</t>
-  </si>
-  <si>
-    <t>PCAR3</t>
-  </si>
-  <si>
-    <t>BPAC11</t>
-  </si>
-  <si>
-    <t>EQTL3</t>
-  </si>
-  <si>
-    <t>GOAU4</t>
-  </si>
-  <si>
-    <t>ECOR3</t>
-  </si>
-  <si>
-    <t>BRFS3</t>
-  </si>
-  <si>
-    <t>RENT3</t>
-  </si>
-  <si>
-    <t>TIMS3</t>
-  </si>
-  <si>
-    <t>LJQQ3</t>
-  </si>
-  <si>
-    <t>BRAV3</t>
-  </si>
-  <si>
-    <t>PETR3</t>
-  </si>
-  <si>
-    <t>RCSL4</t>
-  </si>
-  <si>
-    <t>OIBR3</t>
-  </si>
-  <si>
-    <t>JBSS3</t>
-  </si>
-  <si>
-    <t>MOVI3</t>
-  </si>
-  <si>
-    <t>GMAT3</t>
-  </si>
-  <si>
-    <t>BBDC3</t>
-  </si>
-  <si>
-    <t>CYRE3</t>
-  </si>
-  <si>
-    <t>CMIN3</t>
-  </si>
-  <si>
-    <t>YDUQ3</t>
-  </si>
-  <si>
-    <t>SUZB3</t>
+    <t>DXCO3</t>
+  </si>
+  <si>
+    <t>IGTI11</t>
+  </si>
+  <si>
+    <t>AZZA3</t>
+  </si>
+  <si>
+    <t>STBP3</t>
+  </si>
+  <si>
+    <t>CXSE3</t>
+  </si>
+  <si>
+    <t>AZEV3</t>
+  </si>
+  <si>
+    <t>ELET6</t>
+  </si>
+  <si>
+    <t>FLRY3</t>
+  </si>
+  <si>
+    <t>CPFE3</t>
+  </si>
+  <si>
+    <t>CSED3</t>
+  </si>
+  <si>
+    <t>GOLL4</t>
+  </si>
+  <si>
+    <t>SOJA3</t>
+  </si>
+  <si>
+    <t>ENGI11</t>
+  </si>
+  <si>
+    <t>LAVV3</t>
+  </si>
+  <si>
+    <t>CSMG3</t>
+  </si>
+  <si>
+    <t>CAML3</t>
+  </si>
+  <si>
+    <t>GRND3</t>
+  </si>
+  <si>
+    <t>GUAR3</t>
+  </si>
+  <si>
+    <t>KEPL3</t>
+  </si>
+  <si>
+    <t>CASH3</t>
+  </si>
+  <si>
+    <t>PMAM3</t>
+  </si>
+  <si>
+    <t>HYPE3</t>
+  </si>
+  <si>
+    <t>NEOE3</t>
+  </si>
+  <si>
+    <t>ONCO3</t>
+  </si>
+  <si>
+    <t>TEND3</t>
+  </si>
+  <si>
+    <t>ODPV3</t>
   </si>
   <si>
     <t>ARML3</t>
   </si>
   <si>
-    <t>KLBN11</t>
-  </si>
-  <si>
-    <t>AURE3</t>
-  </si>
-  <si>
-    <t>SMFT3</t>
-  </si>
-  <si>
-    <t>RAPT4</t>
-  </si>
-  <si>
-    <t>EMBR3</t>
-  </si>
-  <si>
-    <t>GOLL4</t>
-  </si>
-  <si>
-    <t>ENEV3</t>
-  </si>
-  <si>
-    <t>AZEV4</t>
-  </si>
-  <si>
-    <t>MRFG3</t>
-  </si>
-  <si>
-    <t>CPLE3</t>
-  </si>
-  <si>
-    <t>ONCO3</t>
+    <t>EGIE3</t>
+  </si>
+  <si>
+    <t>VIVT3</t>
+  </si>
+  <si>
+    <t>HBSA3</t>
+  </si>
+  <si>
+    <t>SBFG3</t>
+  </si>
+  <si>
+    <t>PSSA3</t>
+  </si>
+  <si>
+    <t>TUPY3</t>
+  </si>
+  <si>
+    <t>TAEE11</t>
+  </si>
+  <si>
+    <t>LIGT3</t>
+  </si>
+  <si>
+    <t>MYPK3</t>
+  </si>
+  <si>
+    <t>KLBN3</t>
+  </si>
+  <si>
+    <t>EVEN3</t>
+  </si>
+  <si>
+    <t>RCSL3</t>
+  </si>
+  <si>
+    <t>ALPA4</t>
+  </si>
+  <si>
+    <t>POSI3</t>
+  </si>
+  <si>
+    <t>TTEN3</t>
+  </si>
+  <si>
+    <t>FIQE3</t>
+  </si>
+  <si>
+    <t>DASA3</t>
+  </si>
+  <si>
+    <t>ISAE4</t>
+  </si>
+  <si>
+    <t>BRSR6</t>
+  </si>
+  <si>
+    <t>JSLG3</t>
+  </si>
+  <si>
+    <t>MILS3</t>
+  </si>
+  <si>
+    <t>SEER3</t>
+  </si>
+  <si>
+    <t>MLAS3</t>
+  </si>
+  <si>
+    <t>SAPR4</t>
+  </si>
+  <si>
+    <t>HBOR3</t>
+  </si>
+  <si>
+    <t>ALUP11</t>
+  </si>
+  <si>
+    <t>AALR3</t>
+  </si>
+  <si>
+    <t>BMOB3</t>
+  </si>
+  <si>
+    <t>PGMN3</t>
   </si>
   <si>
     <t>VVEO3</t>
   </si>
   <si>
-    <t>WEGE3</t>
-  </si>
-  <si>
-    <t>PRIO3</t>
-  </si>
-  <si>
-    <t>BRKM5</t>
-  </si>
-  <si>
-    <t>STBP3</t>
-  </si>
-  <si>
-    <t>CXSE3</t>
-  </si>
-  <si>
-    <t>ALOS3</t>
-  </si>
-  <si>
-    <t>MULT3</t>
-  </si>
-  <si>
-    <t>FLRY3</t>
-  </si>
-  <si>
-    <t>IGTI11</t>
-  </si>
-  <si>
-    <t>UGPA3</t>
-  </si>
-  <si>
-    <t>GGPS3</t>
-  </si>
-  <si>
-    <t>HYPE3</t>
-  </si>
-  <si>
-    <t>RDOR3</t>
-  </si>
-  <si>
-    <t>VIVA3</t>
-  </si>
-  <si>
-    <t>SEER3</t>
-  </si>
-  <si>
-    <t>SAPR4</t>
-  </si>
-  <si>
-    <t>LIGT3</t>
-  </si>
-  <si>
-    <t>BBSE3</t>
-  </si>
-  <si>
-    <t>BRAP4</t>
-  </si>
-  <si>
-    <t>INTB3</t>
-  </si>
-  <si>
-    <t>KLBN4</t>
-  </si>
-  <si>
-    <t>SANB11</t>
-  </si>
-  <si>
-    <t>CEAB3</t>
-  </si>
-  <si>
-    <t>SRNA3</t>
-  </si>
-  <si>
-    <t>ELET6</t>
-  </si>
-  <si>
-    <t>MYPK3</t>
-  </si>
-  <si>
-    <t>HBSA3</t>
-  </si>
-  <si>
-    <t>AZZA3</t>
-  </si>
-  <si>
-    <t>CSMG3</t>
-  </si>
-  <si>
-    <t>PSSA3</t>
-  </si>
-  <si>
-    <t>TOTS3</t>
-  </si>
-  <si>
-    <t>RCSL3</t>
-  </si>
-  <si>
-    <t>TUPY3</t>
-  </si>
-  <si>
-    <t>ENGI11</t>
+    <t>VULC3</t>
+  </si>
+  <si>
+    <t>HBRE3</t>
+  </si>
+  <si>
+    <t>MELK3</t>
+  </si>
+  <si>
+    <t>BLAU3</t>
+  </si>
+  <si>
+    <t>ABCB4</t>
+  </si>
+  <si>
+    <t>PLPL3</t>
+  </si>
+  <si>
+    <t>PNVL3</t>
+  </si>
+  <si>
+    <t>VTRU3</t>
+  </si>
+  <si>
+    <t>ITUB3</t>
+  </si>
+  <si>
+    <t>VLID3</t>
+  </si>
+  <si>
+    <t>ZAMP3</t>
   </si>
   <si>
     <t>BMGB4</t>
   </si>
   <si>
+    <t>RANI3</t>
+  </si>
+  <si>
+    <t>MTRE3</t>
+  </si>
+  <si>
+    <t>AGXY3</t>
+  </si>
+  <si>
+    <t>PTBL3</t>
+  </si>
+  <si>
+    <t>SYNE3</t>
+  </si>
+  <si>
+    <t>PFRM3</t>
+  </si>
+  <si>
+    <t>ESPA3</t>
+  </si>
+  <si>
+    <t>SAPR11</t>
+  </si>
+  <si>
+    <t>PINE4</t>
+  </si>
+  <si>
+    <t>SHUL4</t>
+  </si>
+  <si>
+    <t>MDIA3</t>
+  </si>
+  <si>
+    <t>FESA4</t>
+  </si>
+  <si>
+    <t>ELMD3</t>
+  </si>
+  <si>
+    <t>POMO3</t>
+  </si>
+  <si>
+    <t>MDNE3</t>
+  </si>
+  <si>
+    <t>BRBI11</t>
+  </si>
+  <si>
+    <t>MEAL3</t>
+  </si>
+  <si>
+    <t>RNEW4</t>
+  </si>
+  <si>
+    <t>VITT3</t>
+  </si>
+  <si>
+    <t>OPCT3</t>
+  </si>
+  <si>
+    <t>USIM3</t>
+  </si>
+  <si>
+    <t>AGRO3</t>
+  </si>
+  <si>
+    <t>LEVE3</t>
+  </si>
+  <si>
+    <t>RNEW3</t>
+  </si>
+  <si>
+    <t>LOGG3</t>
+  </si>
+  <si>
+    <t>DESK3</t>
+  </si>
+  <si>
+    <t>WIZC3</t>
+  </si>
+  <si>
+    <t>FRAS3</t>
+  </si>
+  <si>
+    <t>SEQL3</t>
+  </si>
+  <si>
+    <t>MATD3</t>
+  </si>
+  <si>
+    <t>MBLY3</t>
+  </si>
+  <si>
+    <t>TRIS3</t>
+  </si>
+  <si>
+    <t>JALL3</t>
+  </si>
+  <si>
+    <t>TFCO4</t>
+  </si>
+  <si>
+    <t>AERI3</t>
+  </si>
+  <si>
+    <t>TASA4</t>
+  </si>
+  <si>
+    <t>ORVR3</t>
+  </si>
+  <si>
+    <t>PDGR3</t>
+  </si>
+  <si>
+    <t>TAEE4</t>
+  </si>
+  <si>
+    <t>BRST3</t>
+  </si>
+  <si>
+    <t>PRNR3</t>
+  </si>
+  <si>
+    <t>AMAR3</t>
+  </si>
+  <si>
+    <t>ITSA3</t>
+  </si>
+  <si>
+    <t>SAPR3</t>
+  </si>
+  <si>
+    <t>SHOW3</t>
+  </si>
+  <si>
+    <t>UNIP6</t>
+  </si>
+  <si>
+    <t>TGMA3</t>
+  </si>
+  <si>
+    <t>ALPK3</t>
+  </si>
+  <si>
+    <t>DMVF3</t>
+  </si>
+  <si>
+    <t>RSID3</t>
+  </si>
+  <si>
+    <t>ETER3</t>
+  </si>
+  <si>
+    <t>ROMI3</t>
+  </si>
+  <si>
+    <t>TECN3</t>
+  </si>
+  <si>
+    <t>SANB4</t>
+  </si>
+  <si>
+    <t>LVTC3</t>
+  </si>
+  <si>
+    <t>SANB3</t>
+  </si>
+  <si>
+    <t>CMIG3</t>
+  </si>
+  <si>
+    <t>IGTI3</t>
+  </si>
+  <si>
+    <t>FHER3</t>
+  </si>
+  <si>
+    <t>DEXP3</t>
+  </si>
+  <si>
+    <t>TAEE3</t>
+  </si>
+  <si>
+    <t>SCAR3</t>
+  </si>
+  <si>
+    <t>BRAP3</t>
+  </si>
+  <si>
+    <t>EUCA4</t>
+  </si>
+  <si>
+    <t>RAPT3</t>
+  </si>
+  <si>
+    <t>AMBP3</t>
+  </si>
+  <si>
+    <t>LPSB3</t>
+  </si>
+  <si>
+    <t>LAND3</t>
+  </si>
+  <si>
+    <t>GOAU3</t>
+  </si>
+  <si>
+    <t>INEP3</t>
+  </si>
+  <si>
+    <t>VIVR3</t>
+  </si>
+  <si>
+    <t>OIBR4</t>
+  </si>
+  <si>
+    <t>TRAD3</t>
+  </si>
+  <si>
+    <t>GGBR3</t>
+  </si>
+  <si>
+    <t>ALUP4</t>
+  </si>
+  <si>
+    <t>LUPA3</t>
+  </si>
+  <si>
+    <t>CSUD3</t>
+  </si>
+  <si>
+    <t>PDTC3</t>
+  </si>
+  <si>
+    <t>CAMB3</t>
+  </si>
+  <si>
+    <t>BOBR4</t>
+  </si>
+  <si>
+    <t>NGRD3</t>
+  </si>
+  <si>
+    <t>ALLD3</t>
+  </si>
+  <si>
+    <t>UCAS3</t>
+  </si>
+  <si>
+    <t>TCSA3</t>
+  </si>
+  <si>
+    <t>FICT3</t>
+  </si>
+  <si>
+    <t>BEES3</t>
+  </si>
+  <si>
+    <t>CEBR6</t>
+  </si>
+  <si>
+    <t>PINE3</t>
+  </si>
+  <si>
+    <t>RDNI3</t>
+  </si>
+  <si>
+    <t>BMEB4</t>
+  </si>
+  <si>
+    <t>DOTZ3</t>
+  </si>
+  <si>
+    <t>ALUP3</t>
+  </si>
+  <si>
+    <t>BSLI3</t>
+  </si>
+  <si>
+    <t>BPAC5</t>
+  </si>
+  <si>
+    <t>INEP4</t>
+  </si>
+  <si>
+    <t>PTNT4</t>
+  </si>
+  <si>
+    <t>WHRL3</t>
+  </si>
+  <si>
+    <t>EQPA3</t>
+  </si>
+  <si>
+    <t>ENGI4</t>
+  </si>
+  <si>
+    <t>LOGN3</t>
+  </si>
+  <si>
+    <t>JFEN3</t>
+  </si>
+  <si>
+    <t>BSLI4</t>
+  </si>
+  <si>
+    <t>TELB4</t>
+  </si>
+  <si>
+    <t>WEST3</t>
+  </si>
+  <si>
+    <t>ALPA3</t>
+  </si>
+  <si>
+    <t>TPIS3</t>
+  </si>
+  <si>
+    <t>BRKM3</t>
+  </si>
+  <si>
+    <t>EPAR3</t>
+  </si>
+  <si>
+    <t>EALT4</t>
+  </si>
+  <si>
+    <t>CEBR3</t>
+  </si>
+  <si>
+    <t>UNIP3</t>
+  </si>
+  <si>
+    <t>WHRL4</t>
+  </si>
+  <si>
+    <t>BPAC3</t>
+  </si>
+  <si>
+    <t>BIOM3</t>
+  </si>
+  <si>
+    <t>OSXB3</t>
+  </si>
+  <si>
+    <t>TASA3</t>
+  </si>
+  <si>
+    <t>AVLL3</t>
+  </si>
+  <si>
+    <t>BAZA3</t>
+  </si>
+  <si>
+    <t>BRSR3</t>
+  </si>
+  <si>
+    <t>NUTR3</t>
+  </si>
+  <si>
+    <t>VSTE3</t>
+  </si>
+  <si>
+    <t>CEDO3</t>
+  </si>
+  <si>
+    <t>BEES4</t>
+  </si>
+  <si>
+    <t>CLSC4</t>
+  </si>
+  <si>
+    <t>ATED3</t>
+  </si>
+  <si>
+    <t>ENGI3</t>
+  </si>
+  <si>
+    <t>PATI3</t>
+  </si>
+  <si>
+    <t>OFSA3</t>
+  </si>
+  <si>
+    <t>TELB3</t>
+  </si>
+  <si>
+    <t>SNSY5</t>
+  </si>
+  <si>
+    <t>RNEW11</t>
+  </si>
+  <si>
+    <t>HOOT4</t>
+  </si>
+  <si>
+    <t>MNPR3</t>
+  </si>
+  <si>
+    <t>DEXP4</t>
+  </si>
+  <si>
+    <t>DOHL4</t>
+  </si>
+  <si>
+    <t>ISAE3</t>
+  </si>
+  <si>
+    <t>EQMA3B</t>
+  </si>
+  <si>
+    <t>RPAD6</t>
+  </si>
+  <si>
+    <t>NEXP3</t>
+  </si>
+  <si>
+    <t>MNDL3</t>
+  </si>
+  <si>
+    <t>KRSA3</t>
+  </si>
+  <si>
+    <t>WLMM4</t>
+  </si>
+  <si>
+    <t>COCE5</t>
+  </si>
+  <si>
+    <t>PLAS3</t>
+  </si>
+  <si>
+    <t>HAGA4</t>
+  </si>
+  <si>
+    <t>EMAE4</t>
+  </si>
+  <si>
+    <t>BGIP4</t>
+  </si>
+  <si>
+    <t>CEBR5</t>
+  </si>
+  <si>
+    <t>CTSA4</t>
+  </si>
+  <si>
+    <t>NORD3</t>
+  </si>
+  <si>
+    <t>CTSA3</t>
+  </si>
+  <si>
+    <t>CRPG5</t>
+  </si>
+  <si>
+    <t>BMEB3</t>
+  </si>
+  <si>
+    <t>CGRA4</t>
+  </si>
+  <si>
+    <t>REDE3</t>
+  </si>
+  <si>
+    <t>AMAR11</t>
+  </si>
+  <si>
+    <t>MGEL4</t>
+  </si>
+  <si>
+    <t>CTKA4</t>
+  </si>
+  <si>
+    <t>AZEV11</t>
+  </si>
+  <si>
+    <t>MTSA4</t>
+  </si>
+  <si>
+    <t>GEPA4</t>
+  </si>
+  <si>
+    <t>FIEI3</t>
+  </si>
+  <si>
+    <t>RSUL4</t>
+  </si>
+  <si>
+    <t>EALT3</t>
+  </si>
+  <si>
+    <t>RPAD3</t>
+  </si>
+  <si>
+    <t>DTCY3</t>
+  </si>
+  <si>
+    <t>ENMT3</t>
+  </si>
+  <si>
+    <t>MRSA6B</t>
+  </si>
+  <si>
+    <t>JOPA3</t>
+  </si>
+  <si>
+    <t>CEDO4</t>
+  </si>
+  <si>
+    <t>BMIN4</t>
+  </si>
+  <si>
+    <t>SNSY3</t>
+  </si>
+  <si>
+    <t>ATMP3</t>
+  </si>
+  <si>
+    <t>CEGR3</t>
+  </si>
+  <si>
+    <t>MRSA3B</t>
+  </si>
+  <si>
+    <t>BALM4</t>
+  </si>
+  <si>
+    <t>HAGA3</t>
+  </si>
+  <si>
+    <t>BMKS3</t>
+  </si>
+  <si>
+    <t>RPMG3</t>
+  </si>
+  <si>
+    <t>MOAR3</t>
+  </si>
+  <si>
+    <t>CGRA3</t>
+  </si>
+  <si>
+    <t>CRPG6</t>
+  </si>
+  <si>
+    <t>CPLE5</t>
+  </si>
+  <si>
+    <t>CGAS5</t>
+  </si>
+  <si>
+    <t>CGAS3</t>
+  </si>
+  <si>
+    <t>BNBR3</t>
+  </si>
+  <si>
+    <t>CEEB3</t>
+  </si>
+  <si>
+    <t>GEPA3</t>
+  </si>
+  <si>
+    <t>EUCA3</t>
+  </si>
+  <si>
+    <t>LUXM4</t>
+  </si>
+  <si>
+    <t>TKNO4</t>
+  </si>
+  <si>
+    <t>EKTR4</t>
+  </si>
+  <si>
+    <t>FESA3</t>
+  </si>
+  <si>
+    <t>IGTI4</t>
+  </si>
+  <si>
+    <t>PPLA11</t>
+  </si>
+  <si>
+    <t>AHEB3</t>
+  </si>
+  <si>
+    <t>PTNT3</t>
+  </si>
+  <si>
+    <t>HBTS5</t>
+  </si>
+  <si>
+    <t>ESTR4</t>
+  </si>
+  <si>
+    <t>UNIP5</t>
+  </si>
+  <si>
+    <t>GPAR3</t>
+  </si>
+  <si>
+    <t>BRKM6</t>
+  </si>
+  <si>
+    <t>RPAD5</t>
+  </si>
+  <si>
+    <t>CEED3</t>
+  </si>
+  <si>
+    <t>PSVM11</t>
+  </si>
+  <si>
+    <t>BRSR5</t>
+  </si>
+  <si>
+    <t>SOND5</t>
+  </si>
+  <si>
+    <t>LIPR3</t>
+  </si>
+  <si>
+    <t>BGIP3</t>
+  </si>
+  <si>
+    <t>BMIN3</t>
+  </si>
+  <si>
+    <t>BDLL3</t>
+  </si>
+  <si>
+    <t>PEAB3</t>
+  </si>
+  <si>
+    <t>EQPA5</t>
+  </si>
+  <si>
+    <t>MERC4</t>
+  </si>
+  <si>
+    <t>EQPA7</t>
+  </si>
+  <si>
+    <t>CLSC3</t>
+  </si>
+  <si>
+    <t>DOHL3</t>
+  </si>
+  <si>
+    <t>HETA4</t>
+  </si>
+  <si>
+    <t>PEAB4</t>
+  </si>
+  <si>
+    <t>WLMM3</t>
+  </si>
+  <si>
+    <t>AFLT3</t>
+  </si>
+  <si>
+    <t>FRIO3</t>
+  </si>
+  <si>
+    <t>COCE3</t>
+  </si>
+  <si>
+    <t>BALM3</t>
+  </si>
+  <si>
+    <t>BAUH4</t>
+  </si>
+  <si>
+    <t>MWET4</t>
+  </si>
+  <si>
+    <t>PATI4</t>
+  </si>
+  <si>
     <t>CLSA3</t>
   </si>
   <si>
-    <t>SBSP3</t>
-  </si>
-  <si>
-    <t>GRND3</t>
-  </si>
-  <si>
-    <t>DXCO3</t>
-  </si>
-  <si>
-    <t>ZAMP3</t>
-  </si>
-  <si>
-    <t>EGIE3</t>
-  </si>
-  <si>
-    <t>VIVT3</t>
-  </si>
-  <si>
-    <t>KEPL3</t>
-  </si>
-  <si>
-    <t>TEND3</t>
-  </si>
-  <si>
-    <t>ODPV3</t>
-  </si>
-  <si>
-    <t>ISAE4</t>
-  </si>
-  <si>
-    <t>QUAL3</t>
-  </si>
-  <si>
-    <t>PORT3</t>
-  </si>
-  <si>
-    <t>EVEN3</t>
-  </si>
-  <si>
-    <t>SBFG3</t>
-  </si>
-  <si>
-    <t>CURY3</t>
-  </si>
-  <si>
-    <t>GUAR3</t>
-  </si>
-  <si>
-    <t>PGMN3</t>
-  </si>
-  <si>
-    <t>MELK3</t>
-  </si>
-  <si>
-    <t>SOJA3</t>
-  </si>
-  <si>
-    <t>DASA3</t>
-  </si>
-  <si>
-    <t>ALPA4</t>
-  </si>
-  <si>
-    <t>SYNE3</t>
-  </si>
-  <si>
-    <t>VTRU3</t>
-  </si>
-  <si>
-    <t>MLAS3</t>
-  </si>
-  <si>
-    <t>CAML3</t>
-  </si>
-  <si>
-    <t>SMTO3</t>
-  </si>
-  <si>
-    <t>SLCE3</t>
-  </si>
-  <si>
-    <t>MTRE3</t>
-  </si>
-  <si>
-    <t>MEAL3</t>
-  </si>
-  <si>
-    <t>BPAN4</t>
-  </si>
-  <si>
-    <t>ENJU3</t>
-  </si>
-  <si>
-    <t>RECV3</t>
-  </si>
-  <si>
-    <t>TAEE11</t>
-  </si>
-  <si>
-    <t>ALUP11</t>
-  </si>
-  <si>
-    <t>MILS3</t>
-  </si>
-  <si>
-    <t>EZTC3</t>
-  </si>
-  <si>
-    <t>DIRR3</t>
-  </si>
-  <si>
-    <t>AZEV3</t>
-  </si>
-  <si>
-    <t>MDIA3</t>
-  </si>
-  <si>
-    <t>POSI3</t>
-  </si>
-  <si>
-    <t>CASH3</t>
-  </si>
-  <si>
-    <t>CPFE3</t>
-  </si>
-  <si>
-    <t>BRSR6</t>
-  </si>
-  <si>
-    <t>TRIS3</t>
-  </si>
-  <si>
-    <t>ABCB4</t>
-  </si>
-  <si>
-    <t>TGMA3</t>
-  </si>
-  <si>
-    <t>POMO3</t>
-  </si>
-  <si>
-    <t>TTEN3</t>
-  </si>
-  <si>
-    <t>JSLG3</t>
-  </si>
-  <si>
-    <t>IRBR3</t>
-  </si>
-  <si>
-    <t>FESA4</t>
-  </si>
-  <si>
-    <t>HBOR3</t>
-  </si>
-  <si>
-    <t>ITUB3</t>
-  </si>
-  <si>
-    <t>MATD3</t>
-  </si>
-  <si>
-    <t>SAPR11</t>
-  </si>
-  <si>
-    <t>LEVE3</t>
-  </si>
-  <si>
-    <t>PMAM3</t>
-  </si>
-  <si>
-    <t>MDNE3</t>
-  </si>
-  <si>
-    <t>KLBN3</t>
-  </si>
-  <si>
-    <t>PNVL3</t>
-  </si>
-  <si>
-    <t>PDGR3</t>
-  </si>
-  <si>
-    <t>NEOE3</t>
-  </si>
-  <si>
-    <t>SAPR3</t>
-  </si>
-  <si>
-    <t>VULC3</t>
-  </si>
-  <si>
-    <t>FIQE3</t>
-  </si>
-  <si>
-    <t>RANI3</t>
-  </si>
-  <si>
-    <t>BIOM3</t>
-  </si>
-  <si>
-    <t>WIZC3</t>
-  </si>
-  <si>
-    <t>PLPL3</t>
-  </si>
-  <si>
-    <t>BRBI11</t>
-  </si>
-  <si>
-    <t>AERI3</t>
-  </si>
-  <si>
-    <t>LAVV3</t>
-  </si>
-  <si>
-    <t>FRAS3</t>
-  </si>
-  <si>
-    <t>DESK3</t>
-  </si>
-  <si>
-    <t>JALL3</t>
-  </si>
-  <si>
-    <t>HBRE3</t>
-  </si>
-  <si>
-    <t>BMOB3</t>
-  </si>
-  <si>
-    <t>BLAU3</t>
-  </si>
-  <si>
-    <t>SHUL4</t>
-  </si>
-  <si>
-    <t>AALR3</t>
-  </si>
-  <si>
-    <t>AGXY3</t>
-  </si>
-  <si>
-    <t>ELMD3</t>
-  </si>
-  <si>
-    <t>USIM3</t>
-  </si>
-  <si>
-    <t>CMIG3</t>
-  </si>
-  <si>
-    <t>MBLY3</t>
-  </si>
-  <si>
-    <t>PFRM3</t>
-  </si>
-  <si>
-    <t>OPCT3</t>
-  </si>
-  <si>
-    <t>SEQL3</t>
-  </si>
-  <si>
-    <t>AMAR3</t>
-  </si>
-  <si>
-    <t>ORVR3</t>
-  </si>
-  <si>
-    <t>VLID3</t>
-  </si>
-  <si>
-    <t>TASA4</t>
-  </si>
-  <si>
-    <t>TFCO4</t>
-  </si>
-  <si>
-    <t>SCAR3</t>
-  </si>
-  <si>
-    <t>PRNR3</t>
-  </si>
-  <si>
-    <t>LOGG3</t>
-  </si>
-  <si>
-    <t>VITT3</t>
-  </si>
-  <si>
-    <t>CSED3</t>
-  </si>
-  <si>
-    <t>ITSA3</t>
-  </si>
-  <si>
-    <t>LUPA3</t>
-  </si>
-  <si>
-    <t>PTBL3</t>
-  </si>
-  <si>
-    <t>SHOW3</t>
-  </si>
-  <si>
-    <t>INEP3</t>
-  </si>
-  <si>
-    <t>EUCA4</t>
-  </si>
-  <si>
-    <t>ESPA3</t>
-  </si>
-  <si>
-    <t>UNIP6</t>
-  </si>
-  <si>
-    <t>DEXP3</t>
-  </si>
-  <si>
-    <t>TAEE4</t>
-  </si>
-  <si>
-    <t>BRST3</t>
-  </si>
-  <si>
-    <t>ETER3</t>
-  </si>
-  <si>
-    <t>UCAS3</t>
-  </si>
-  <si>
-    <t>ALLD3</t>
-  </si>
-  <si>
-    <t>ROMI3</t>
-  </si>
-  <si>
-    <t>SANB4</t>
-  </si>
-  <si>
-    <t>TPIS3</t>
-  </si>
-  <si>
-    <t>AGRO3</t>
-  </si>
-  <si>
-    <t>SANB3</t>
-  </si>
-  <si>
-    <t>ALPK3</t>
-  </si>
-  <si>
-    <t>VIVR3</t>
-  </si>
-  <si>
-    <t>TECN3</t>
-  </si>
-  <si>
-    <t>ATMP3</t>
-  </si>
-  <si>
-    <t>RNEW4</t>
-  </si>
-  <si>
-    <t>FICT3</t>
-  </si>
-  <si>
-    <t>PINE4</t>
-  </si>
-  <si>
-    <t>IGTI3</t>
-  </si>
-  <si>
-    <t>LVTC3</t>
-  </si>
-  <si>
-    <t>AMBP3</t>
-  </si>
-  <si>
-    <t>LPSB3</t>
-  </si>
-  <si>
-    <t>EALT4</t>
-  </si>
-  <si>
-    <t>DMVF3</t>
-  </si>
-  <si>
-    <t>TAEE3</t>
-  </si>
-  <si>
-    <t>TRAD3</t>
-  </si>
-  <si>
-    <t>GOAU3</t>
-  </si>
-  <si>
-    <t>RDNI3</t>
-  </si>
-  <si>
-    <t>PDTC3</t>
-  </si>
-  <si>
-    <t>BRAP3</t>
-  </si>
-  <si>
-    <t>RNEW3</t>
-  </si>
-  <si>
-    <t>TCSA3</t>
-  </si>
-  <si>
-    <t>CSUD3</t>
-  </si>
-  <si>
-    <t>FHER3</t>
-  </si>
-  <si>
-    <t>BOBR4</t>
-  </si>
-  <si>
-    <t>RAPT3</t>
-  </si>
-  <si>
-    <t>HOOT4</t>
-  </si>
-  <si>
-    <t>OIBR4</t>
-  </si>
-  <si>
-    <t>ATED3</t>
-  </si>
-  <si>
-    <t>LOGN3</t>
-  </si>
-  <si>
-    <t>NGRD3</t>
-  </si>
-  <si>
-    <t>JFEN3</t>
-  </si>
-  <si>
-    <t>GGBR3</t>
-  </si>
-  <si>
-    <t>BRKM3</t>
-  </si>
-  <si>
-    <t>WHRL4</t>
-  </si>
-  <si>
-    <t>RSID3</t>
-  </si>
-  <si>
-    <t>DOTZ3</t>
-  </si>
-  <si>
-    <t>AZEV11</t>
-  </si>
-  <si>
-    <t>CAMB3</t>
-  </si>
-  <si>
-    <t>VSTE3</t>
-  </si>
-  <si>
-    <t>TASA3</t>
-  </si>
-  <si>
-    <t>BEES3</t>
-  </si>
-  <si>
-    <t>ENGI4</t>
-  </si>
-  <si>
-    <t>LAND3</t>
-  </si>
-  <si>
-    <t>INEP4</t>
-  </si>
-  <si>
-    <t>BMEB4</t>
-  </si>
-  <si>
-    <t>EPAR3</t>
-  </si>
-  <si>
-    <t>EALT3</t>
-  </si>
-  <si>
-    <t>RNEW11</t>
-  </si>
-  <si>
-    <t>ENGI3</t>
-  </si>
-  <si>
-    <t>EQPA3</t>
-  </si>
-  <si>
-    <t>NUTR3</t>
-  </si>
-  <si>
-    <t>WEST3</t>
-  </si>
-  <si>
-    <t>BAZA3</t>
-  </si>
-  <si>
-    <t>ALUP4</t>
-  </si>
-  <si>
-    <t>ALPA3</t>
-  </si>
-  <si>
-    <t>EMAE4</t>
-  </si>
-  <si>
-    <t>COCE5</t>
-  </si>
-  <si>
-    <t>UNIP3</t>
-  </si>
-  <si>
-    <t>CEBR5</t>
-  </si>
-  <si>
-    <t>SNSY5</t>
-  </si>
-  <si>
-    <t>OSXB3</t>
-  </si>
-  <si>
-    <t>PTNT4</t>
-  </si>
-  <si>
-    <t>OFSA3</t>
-  </si>
-  <si>
-    <t>PATI3</t>
-  </si>
-  <si>
-    <t>CEBR6</t>
-  </si>
-  <si>
-    <t>ISAE3</t>
-  </si>
-  <si>
-    <t>BGIP4</t>
-  </si>
-  <si>
-    <t>BEES4</t>
-  </si>
-  <si>
-    <t>MGEL4</t>
-  </si>
-  <si>
-    <t>PINE3</t>
-  </si>
-  <si>
-    <t>CGRA4</t>
-  </si>
-  <si>
-    <t>BSLI4</t>
-  </si>
-  <si>
-    <t>WHRL3</t>
-  </si>
-  <si>
-    <t>TKNO4</t>
-  </si>
-  <si>
-    <t>CLSC4</t>
-  </si>
-  <si>
-    <t>DOHL4</t>
-  </si>
-  <si>
-    <t>HAGA4</t>
-  </si>
-  <si>
-    <t>BRSR3</t>
-  </si>
-  <si>
-    <t>RSUL4</t>
-  </si>
-  <si>
-    <t>BPAC3</t>
-  </si>
-  <si>
-    <t>CEDO4</t>
-  </si>
-  <si>
-    <t>CRPG6</t>
-  </si>
-  <si>
-    <t>MTSA4</t>
-  </si>
-  <si>
-    <t>WLMM4</t>
-  </si>
-  <si>
-    <t>TELB4</t>
-  </si>
-  <si>
-    <t>CEBR3</t>
-  </si>
-  <si>
-    <t>FESA3</t>
-  </si>
-  <si>
-    <t>ALUP3</t>
-  </si>
-  <si>
-    <t>DEXP4</t>
-  </si>
-  <si>
-    <t>CRPG5</t>
-  </si>
-  <si>
-    <t>KRSA3</t>
-  </si>
-  <si>
-    <t>PATI4</t>
-  </si>
-  <si>
-    <t>BPAC5</t>
-  </si>
-  <si>
-    <t>BSLI3</t>
-  </si>
-  <si>
-    <t>FIEI3</t>
-  </si>
-  <si>
-    <t>RPMG3</t>
-  </si>
-  <si>
-    <t>PPLA11</t>
-  </si>
-  <si>
-    <t>SNSY3</t>
-  </si>
-  <si>
-    <t>HAGA3</t>
-  </si>
-  <si>
-    <t>AMAR11</t>
-  </si>
-  <si>
-    <t>TELB3</t>
-  </si>
-  <si>
-    <t>FRIO3</t>
-  </si>
-  <si>
-    <t>EKTR4</t>
-  </si>
-  <si>
-    <t>MOAR3</t>
-  </si>
-  <si>
-    <t>GEPA4</t>
-  </si>
-  <si>
-    <t>GEPA3</t>
-  </si>
-  <si>
-    <t>MNPR3</t>
-  </si>
-  <si>
-    <t>BMIN4</t>
-  </si>
-  <si>
-    <t>AFLT3</t>
-  </si>
-  <si>
-    <t>REDE3</t>
-  </si>
-  <si>
-    <t>EQMA3B</t>
-  </si>
-  <si>
-    <t>UNIP5</t>
-  </si>
-  <si>
-    <t>PEAB3</t>
-  </si>
-  <si>
-    <t>CEEB3</t>
-  </si>
-  <si>
-    <t>CTKA4</t>
-  </si>
-  <si>
-    <t>CTSA4</t>
-  </si>
-  <si>
-    <t>BNBR3</t>
-  </si>
-  <si>
-    <t>CGRA3</t>
-  </si>
-  <si>
-    <t>JOPA3</t>
-  </si>
-  <si>
-    <t>MNDL3</t>
-  </si>
-  <si>
-    <t>BMIN3</t>
-  </si>
-  <si>
-    <t>MWET4</t>
-  </si>
-  <si>
-    <t>BDLL4</t>
-  </si>
-  <si>
-    <t>NEXP3</t>
-  </si>
-  <si>
-    <t>SOND5</t>
-  </si>
-  <si>
-    <t>BGIP3</t>
-  </si>
-  <si>
-    <t>EUCA3</t>
-  </si>
-  <si>
-    <t>BALM4</t>
-  </si>
-  <si>
-    <t>BMKS3</t>
-  </si>
-  <si>
-    <t>AVLL3</t>
-  </si>
-  <si>
-    <t>DTCY3</t>
-  </si>
-  <si>
-    <t>PEAB4</t>
-  </si>
-  <si>
-    <t>PTNT3</t>
-  </si>
-  <si>
-    <t>CEDO3</t>
-  </si>
-  <si>
-    <t>CTSA3</t>
-  </si>
-  <si>
-    <t>CGAS3</t>
-  </si>
-  <si>
-    <t>AHEB6</t>
-  </si>
-  <si>
-    <t>BMEB3</t>
-  </si>
-  <si>
-    <t>HBTS5</t>
-  </si>
-  <si>
-    <t>BDLL3</t>
-  </si>
-  <si>
-    <t>PINE11</t>
-  </si>
-  <si>
-    <t>RPAD5</t>
-  </si>
-  <si>
-    <t>DOHL3</t>
-  </si>
-  <si>
-    <t>PLAS3</t>
-  </si>
-  <si>
-    <t>RPAD6</t>
-  </si>
-  <si>
-    <t>CGAS5</t>
-  </si>
-  <si>
-    <t>CPLE5</t>
-  </si>
-  <si>
-    <t>NORD3</t>
-  </si>
-  <si>
-    <t>BALM3</t>
-  </si>
-  <si>
-    <t>IGTI4</t>
-  </si>
-  <si>
-    <t>HETA4</t>
-  </si>
-  <si>
-    <t>PSVM11</t>
-  </si>
-  <si>
-    <t>RPAD3</t>
-  </si>
-  <si>
-    <t>MAPT4</t>
-  </si>
-  <si>
-    <t>LUXM4</t>
-  </si>
-  <si>
-    <t>USIM6</t>
-  </si>
-  <si>
-    <t>CBEE3</t>
-  </si>
-  <si>
-    <t>ENMT4</t>
-  </si>
-  <si>
-    <t>BRSR5</t>
-  </si>
-  <si>
-    <t>MWET3</t>
-  </si>
-  <si>
-    <t>MAPT3</t>
-  </si>
-  <si>
-    <t>LIPR3</t>
-  </si>
-  <si>
-    <t>CLSC3</t>
-  </si>
-  <si>
-    <t>MERC4</t>
-  </si>
-  <si>
-    <t>ENMT3</t>
-  </si>
-  <si>
-    <t>MRSA3B</t>
-  </si>
-  <si>
-    <t>ESTR4</t>
+    <t>CTKA3</t>
+  </si>
+  <si>
+    <t>ESTR3</t>
+  </si>
+  <si>
+    <t>MRSA5B</t>
   </si>
 </sst>
 </file>
@@ -2531,7 +2555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C402"/>
+  <dimension ref="A1:C407"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2550,10 +2574,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C2">
-        <v>131606600</v>
+        <v>65323100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2561,10 +2585,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C3">
-        <v>68474600</v>
+        <v>57266800</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2572,10 +2596,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C4">
-        <v>63030500</v>
+        <v>46935100</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2583,10 +2607,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C5">
-        <v>43117200</v>
+        <v>46094000</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2594,10 +2618,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C6">
-        <v>40890700</v>
+        <v>40969000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2605,10 +2629,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C7">
-        <v>37767300</v>
+        <v>37812200</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2616,10 +2640,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C8">
-        <v>34339000</v>
+        <v>35635500</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2627,10 +2651,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C9">
-        <v>31137900</v>
+        <v>28362200</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2638,10 +2662,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C10">
-        <v>30844000</v>
+        <v>28170600</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2649,10 +2673,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C11">
-        <v>28297400</v>
+        <v>27525100</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2660,10 +2684,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C12">
-        <v>25971500</v>
+        <v>27424500</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2671,10 +2695,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C13">
-        <v>22271400</v>
+        <v>24230800</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2682,703 +2706,703 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C14">
-        <v>22057700</v>
+        <v>22129400</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C15">
-        <v>20197500</v>
+        <v>19003500</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C16">
-        <v>19533800</v>
+        <v>17300200</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C17">
-        <v>18815900</v>
+        <v>17242200</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C18">
-        <v>15263300</v>
+        <v>17226900</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C19">
-        <v>13333100</v>
+        <v>16814400</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C20">
-        <v>12889700</v>
+        <v>16628200</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C21">
-        <v>12803100</v>
+        <v>16423100</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C22">
-        <v>12444500</v>
+        <v>16036900</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C23">
-        <v>12163800</v>
+        <v>15566500</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C24">
-        <v>11955800</v>
+        <v>15531100</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C25">
-        <v>11420300</v>
+        <v>14792900</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C26">
-        <v>10586000</v>
+        <v>14529200</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C27">
-        <v>10512600</v>
+        <v>14188700</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C28">
-        <v>10400000</v>
+        <v>13846300</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C29">
-        <v>10262600</v>
+        <v>13520200</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C30">
-        <v>10210100</v>
+        <v>13017900</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C31">
-        <v>10186200</v>
+        <v>12951000</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C32">
-        <v>10047700</v>
+        <v>12342000</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C33">
-        <v>9606800</v>
+        <v>12055900</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C34">
-        <v>9573500</v>
+        <v>11854100</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C35">
-        <v>9171200</v>
+        <v>11681600</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C36">
-        <v>9124000</v>
+        <v>10906700</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C37">
-        <v>8963300</v>
+        <v>10450200</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C38">
-        <v>8867800</v>
+        <v>10289700</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C39">
-        <v>8307200</v>
+        <v>10223600</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C40">
-        <v>8220600</v>
+        <v>9894400</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C41">
-        <v>8027000</v>
+        <v>9590200</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C42">
-        <v>7884600</v>
+        <v>9389600</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C43">
-        <v>7835600</v>
+        <v>9275100</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C44">
-        <v>7707000</v>
+        <v>9079600</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C45">
-        <v>7695500</v>
+        <v>9047700</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C46">
-        <v>7441700</v>
+        <v>8789800</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C47">
-        <v>7314100</v>
+        <v>8776900</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C48">
-        <v>6903700</v>
+        <v>7983300</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C49">
-        <v>6743300</v>
+        <v>7901500</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C50">
-        <v>6304500</v>
+        <v>7855200</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C51">
-        <v>6184600</v>
+        <v>7709800</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C52">
-        <v>6140800</v>
+        <v>7512500</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C53">
-        <v>6113300</v>
+        <v>7494800</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C54">
-        <v>6090100</v>
+        <v>7185500</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C55">
-        <v>6051800</v>
+        <v>7086800</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C56">
-        <v>6023900</v>
+        <v>6872000</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C57">
-        <v>5931000</v>
+        <v>6722700</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C58">
-        <v>5698500</v>
+        <v>6674900</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C59">
-        <v>5414600</v>
+        <v>6658900</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C60">
-        <v>5368500</v>
+        <v>6381400</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C61">
-        <v>5313800</v>
+        <v>6319300</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C62">
-        <v>5302900</v>
+        <v>6029100</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C63">
-        <v>5201900</v>
+        <v>5672700</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C64">
-        <v>5193300</v>
+        <v>5390600</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C65">
-        <v>5071500</v>
+        <v>5358300</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C66">
-        <v>4908700</v>
+        <v>5272400</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C67">
-        <v>4873100</v>
+        <v>5227400</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C68">
-        <v>4856800</v>
+        <v>5216100</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C69">
-        <v>4838200</v>
+        <v>5086700</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C70">
-        <v>4761400</v>
+        <v>5083800</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C71">
-        <v>4629800</v>
+        <v>5012700</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C72">
-        <v>4505500</v>
+        <v>4975400</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C73">
-        <v>4474400</v>
+        <v>4927800</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C74">
-        <v>4396100</v>
+        <v>4669200</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C75">
-        <v>4314500</v>
+        <v>4508600</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C76">
-        <v>4282000</v>
+        <v>4486600</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C77">
-        <v>4182600</v>
+        <v>4418200</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -3386,10 +3410,10 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C78">
-        <v>4022900</v>
+        <v>4313300</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -3397,10 +3421,10 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C79">
-        <v>3934500</v>
+        <v>4300500</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -3408,10 +3432,10 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C80">
-        <v>3862100</v>
+        <v>4186600</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -3419,10 +3443,10 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C81">
-        <v>3759600</v>
+        <v>4102600</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -3430,10 +3454,10 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C82">
-        <v>3742100</v>
+        <v>4056700</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -3441,197 +3465,197 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C83">
-        <v>3705100</v>
+        <v>4056000</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C84">
-        <v>3675600</v>
+        <v>4055300</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B85" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C85">
-        <v>3476900</v>
+        <v>4019900</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B86" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C86">
-        <v>3475000</v>
+        <v>3994100</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B87" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C87">
-        <v>3462600</v>
+        <v>3752600</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B88" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C88">
-        <v>3393400</v>
+        <v>3714300</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B89" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C89">
-        <v>3318100</v>
+        <v>3495400</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B90" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C90">
-        <v>3294800</v>
+        <v>3282800</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B91" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C91">
-        <v>3102800</v>
+        <v>3179500</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B92" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C92">
-        <v>3025400</v>
+        <v>3178300</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B93" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C93">
-        <v>2893500</v>
+        <v>3159800</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B94" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C94">
-        <v>2885000</v>
+        <v>3128800</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B95" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C95">
-        <v>2865100</v>
+        <v>3066700</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B96" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C96">
-        <v>2763300</v>
+        <v>2925000</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B97" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C97">
-        <v>2745300</v>
+        <v>2769800</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B98" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C98">
-        <v>2703100</v>
+        <v>2769600</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B99" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C99">
-        <v>2578600</v>
+        <v>2753100</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B100" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C100">
-        <v>2502400</v>
+        <v>2740500</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -3639,10 +3663,10 @@
         <v>98</v>
       </c>
       <c r="B101" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C101">
-        <v>2452500</v>
+        <v>2739500</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -3650,10 +3674,10 @@
         <v>99</v>
       </c>
       <c r="B102" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C102">
-        <v>2413100</v>
+        <v>2702900</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -3661,98 +3685,98 @@
         <v>100</v>
       </c>
       <c r="B103" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C103">
-        <v>2391100</v>
+        <v>2624400</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="B104" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C104">
-        <v>2363600</v>
+        <v>2451300</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C105">
-        <v>2322300</v>
+        <v>2374000</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C106">
-        <v>2285100</v>
+        <v>2297200</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C107">
-        <v>2258800</v>
+        <v>2167800</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B108" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C108">
-        <v>2240700</v>
+        <v>2073600</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B109" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C109">
-        <v>2056400</v>
+        <v>2017800</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="B110" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C110">
-        <v>2052500</v>
+        <v>1984900</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B111" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C111">
-        <v>2033700</v>
+        <v>1966200</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -3760,10 +3784,10 @@
         <v>107</v>
       </c>
       <c r="B112" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C112">
-        <v>1990800</v>
+        <v>1955700</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -3771,10 +3795,10 @@
         <v>108</v>
       </c>
       <c r="B113" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C113">
-        <v>1934300</v>
+        <v>1929900</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -3782,10 +3806,10 @@
         <v>109</v>
       </c>
       <c r="B114" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C114">
-        <v>1885200</v>
+        <v>1817100</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -3793,10 +3817,10 @@
         <v>110</v>
       </c>
       <c r="B115" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C115">
-        <v>1868200</v>
+        <v>1796000</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -3804,10 +3828,10 @@
         <v>111</v>
       </c>
       <c r="B116" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C116">
-        <v>1862700</v>
+        <v>1717900</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -3815,10 +3839,10 @@
         <v>112</v>
       </c>
       <c r="B117" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C117">
-        <v>1789900</v>
+        <v>1600700</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -3826,10 +3850,10 @@
         <v>113</v>
       </c>
       <c r="B118" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C118">
-        <v>1685400</v>
+        <v>1576300</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -3837,10 +3861,10 @@
         <v>114</v>
       </c>
       <c r="B119" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C119">
-        <v>1640200</v>
+        <v>1546700</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -3848,10 +3872,10 @@
         <v>115</v>
       </c>
       <c r="B120" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C120">
-        <v>1637800</v>
+        <v>1540600</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -3859,10 +3883,10 @@
         <v>116</v>
       </c>
       <c r="B121" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C121">
-        <v>1514100</v>
+        <v>1502100</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -3870,10 +3894,10 @@
         <v>117</v>
       </c>
       <c r="B122" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C122">
-        <v>1463500</v>
+        <v>1491200</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -3881,10 +3905,10 @@
         <v>118</v>
       </c>
       <c r="B123" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C123">
-        <v>1437000</v>
+        <v>1486500</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -3892,10 +3916,10 @@
         <v>119</v>
       </c>
       <c r="B124" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C124">
-        <v>1407500</v>
+        <v>1455000</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -3903,10 +3927,10 @@
         <v>120</v>
       </c>
       <c r="B125" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C125">
-        <v>1400400</v>
+        <v>1429400</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -3914,10 +3938,10 @@
         <v>121</v>
       </c>
       <c r="B126" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C126">
-        <v>1379900</v>
+        <v>1413000</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -3925,10 +3949,10 @@
         <v>122</v>
       </c>
       <c r="B127" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C127">
-        <v>1361500</v>
+        <v>1397000</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -3936,10 +3960,10 @@
         <v>123</v>
       </c>
       <c r="B128" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C128">
-        <v>1330700</v>
+        <v>1393300</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -3947,10 +3971,10 @@
         <v>124</v>
       </c>
       <c r="B129" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C129">
-        <v>1317000</v>
+        <v>1368700</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -3958,10 +3982,10 @@
         <v>125</v>
       </c>
       <c r="B130" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C130">
-        <v>1308400</v>
+        <v>1336600</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -3969,10 +3993,10 @@
         <v>126</v>
       </c>
       <c r="B131" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C131">
-        <v>1273200</v>
+        <v>1326800</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -3980,10 +4004,10 @@
         <v>127</v>
       </c>
       <c r="B132" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C132">
-        <v>1229400</v>
+        <v>1288300</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -3991,10 +4015,10 @@
         <v>128</v>
       </c>
       <c r="B133" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C133">
-        <v>1213700</v>
+        <v>1257700</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -4002,10 +4026,10 @@
         <v>129</v>
       </c>
       <c r="B134" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C134">
-        <v>1197800</v>
+        <v>1209200</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -4013,10 +4037,10 @@
         <v>130</v>
       </c>
       <c r="B135" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C135">
-        <v>1195600</v>
+        <v>1208600</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -4024,10 +4048,10 @@
         <v>131</v>
       </c>
       <c r="B136" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C136">
-        <v>1181700</v>
+        <v>1182800</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -4035,10 +4059,10 @@
         <v>132</v>
       </c>
       <c r="B137" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C137">
-        <v>1179900</v>
+        <v>1161900</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -4046,10 +4070,10 @@
         <v>133</v>
       </c>
       <c r="B138" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C138">
-        <v>1152000</v>
+        <v>1140200</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -4057,10 +4081,10 @@
         <v>134</v>
       </c>
       <c r="B139" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C139">
-        <v>1151400</v>
+        <v>1071700</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -4068,252 +4092,252 @@
         <v>135</v>
       </c>
       <c r="B140" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C140">
-        <v>1093700</v>
+        <v>998100</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="B141" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C141">
-        <v>1077600</v>
+        <v>982800</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B142" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C142">
-        <v>1062800</v>
+        <v>977800</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="B143" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C143">
-        <v>1056000</v>
+        <v>962200</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B144" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C144">
-        <v>1032100</v>
+        <v>914300</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B145" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C145">
-        <v>1016900</v>
+        <v>902000</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B146" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C146">
-        <v>963700</v>
+        <v>874400</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B147" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C147">
-        <v>962800</v>
+        <v>870400</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B148" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C148">
-        <v>957900</v>
+        <v>864100</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B149" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C149">
-        <v>883400</v>
+        <v>855800</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B150" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C150">
-        <v>876300</v>
+        <v>823000</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B151" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C151">
-        <v>859400</v>
+        <v>751700</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B152" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C152">
-        <v>845300</v>
+        <v>748000</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="B153" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C153">
-        <v>840300</v>
+        <v>719100</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B154" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C154">
-        <v>830100</v>
+        <v>718300</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B155" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C155">
-        <v>794800</v>
+        <v>711200</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B156" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C156">
-        <v>770100</v>
+        <v>684500</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B157" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C157">
-        <v>743700</v>
+        <v>669600</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B158" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C158">
-        <v>741300</v>
+        <v>611400</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B159" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C159">
-        <v>735600</v>
+        <v>604800</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B160" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C160">
-        <v>729500</v>
+        <v>590000</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B161" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C161">
-        <v>711400</v>
+        <v>551600</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="B162" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C162">
-        <v>704900</v>
+        <v>520500</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -4321,10 +4345,10 @@
         <v>156</v>
       </c>
       <c r="B163" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C163">
-        <v>692500</v>
+        <v>512200</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -4332,10 +4356,10 @@
         <v>157</v>
       </c>
       <c r="B164" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C164">
-        <v>645000</v>
+        <v>465700</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -4343,10 +4367,10 @@
         <v>158</v>
       </c>
       <c r="B165" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C165">
-        <v>642100</v>
+        <v>433800</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -4354,10 +4378,10 @@
         <v>159</v>
       </c>
       <c r="B166" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C166">
-        <v>631700</v>
+        <v>409000</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -4365,307 +4389,307 @@
         <v>160</v>
       </c>
       <c r="B167" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C167">
-        <v>624600</v>
+        <v>402400</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="B168" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C168">
-        <v>606300</v>
+        <v>399600</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B169" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C169">
-        <v>605400</v>
+        <v>397400</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C170">
-        <v>591000</v>
+        <v>376900</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B171" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C171">
-        <v>582700</v>
+        <v>368000</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B172" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C172">
-        <v>577200</v>
+        <v>364000</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B173" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C173">
-        <v>529600</v>
+        <v>359500</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>67</v>
+        <v>166</v>
       </c>
       <c r="B174" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C174">
-        <v>527400</v>
+        <v>357500</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B175" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C175">
-        <v>512900</v>
+        <v>356200</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B176" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C176">
-        <v>505000</v>
+        <v>355900</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B177" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C177">
-        <v>474500</v>
+        <v>340100</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="B178" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C178">
-        <v>466700</v>
+        <v>339900</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B179" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C179">
-        <v>465100</v>
+        <v>338300</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B180" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C180">
-        <v>465100</v>
+        <v>316400</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="B181" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C181">
-        <v>457700</v>
+        <v>316100</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B182" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C182">
-        <v>456800</v>
+        <v>316100</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B183" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C183">
-        <v>443800</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B184" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C184">
-        <v>440700</v>
+        <v>310700</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B185" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C185">
-        <v>414700</v>
+        <v>310500</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B186" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C186">
-        <v>386500</v>
+        <v>308900</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>176</v>
+        <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C187">
-        <v>371600</v>
+        <v>292800</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B188" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C188">
-        <v>364400</v>
+        <v>289700</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B189" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C189">
-        <v>357400</v>
+        <v>280900</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B190" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C190">
-        <v>348000</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B191" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C191">
-        <v>340600</v>
+        <v>251900</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B192" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C192">
-        <v>339600</v>
+        <v>242200</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B193" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C193">
-        <v>336800</v>
+        <v>236000</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>183</v>
+        <v>40</v>
       </c>
       <c r="B194" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C194">
-        <v>319000</v>
+        <v>233900</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -4673,10 +4697,10 @@
         <v>184</v>
       </c>
       <c r="B195" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C195">
-        <v>303700</v>
+        <v>221800</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -4684,186 +4708,186 @@
         <v>185</v>
       </c>
       <c r="B196" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C196">
-        <v>269800</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B197" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C197">
-        <v>266100</v>
+        <v>216300</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
       <c r="B198" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C198">
-        <v>266000</v>
+        <v>212400</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>29</v>
+        <v>187</v>
       </c>
       <c r="B199" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C199">
-        <v>240300</v>
+        <v>211400</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B200" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C200">
-        <v>239900</v>
+        <v>206400</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B201" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C201">
-        <v>228900</v>
+        <v>201300</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B202" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C202">
-        <v>228600</v>
+        <v>196400</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B203" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C203">
-        <v>224600</v>
+        <v>195300</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B204" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C204">
-        <v>224000</v>
+        <v>194600</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B205" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C205">
-        <v>218700</v>
+        <v>192100</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B206" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C206">
-        <v>214500</v>
+        <v>191800</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B207" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C207">
-        <v>179200</v>
+        <v>186600</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B208" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C208">
-        <v>173100</v>
+        <v>178500</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B209" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C209">
-        <v>172600</v>
+        <v>169600</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B210" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C210">
-        <v>172600</v>
+        <v>166800</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B211" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C211">
-        <v>167800</v>
+        <v>165700</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="B212" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C212">
-        <v>165600</v>
+        <v>158200</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -4871,120 +4895,120 @@
         <v>200</v>
       </c>
       <c r="B213" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C213">
-        <v>163200</v>
+        <v>155100</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>7</v>
+        <v>201</v>
       </c>
       <c r="B214" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C214">
-        <v>160300</v>
+        <v>146300</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B215" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C215">
-        <v>159500</v>
+        <v>143600</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>202</v>
+        <v>8</v>
       </c>
       <c r="B216" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C216">
-        <v>159200</v>
+        <v>139700</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>203</v>
+        <v>148</v>
       </c>
       <c r="B217" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C217">
-        <v>156800</v>
+        <v>122900</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B218" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C218">
-        <v>146100</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B219" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C219">
-        <v>136800</v>
+        <v>119200</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B220" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C220">
-        <v>135900</v>
+        <v>105100</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B221" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C221">
-        <v>130800</v>
+        <v>104600</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B222" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C222">
-        <v>122100</v>
+        <v>94000</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="B223" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C223">
-        <v>118500</v>
+        <v>92500</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -4992,10 +5016,10 @@
         <v>209</v>
       </c>
       <c r="B224" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C224">
-        <v>117800</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -5003,10 +5027,10 @@
         <v>210</v>
       </c>
       <c r="B225" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C225">
-        <v>106600</v>
+        <v>78300</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -5014,439 +5038,439 @@
         <v>211</v>
       </c>
       <c r="B226" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C226">
-        <v>100000</v>
+        <v>76500</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="B227" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C227">
-        <v>93400</v>
+        <v>74700</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B228" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C228">
-        <v>92200</v>
+        <v>72500</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="B229" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C229">
-        <v>91900</v>
+        <v>70100</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>214</v>
+        <v>28</v>
       </c>
       <c r="B230" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C230">
-        <v>91200</v>
+        <v>66500</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B231" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C231">
-        <v>89200</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="B232" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C232">
-        <v>81800</v>
+        <v>58400</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B233" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C233">
-        <v>81400</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>217</v>
+        <v>133</v>
       </c>
       <c r="B234" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C234">
-        <v>81200</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B235" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C235">
-        <v>78900</v>
+        <v>48900</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="B236" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C236">
-        <v>67600</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B237" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C237">
-        <v>59700</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>221</v>
+        <v>36</v>
       </c>
       <c r="B238" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C238">
-        <v>58100</v>
+        <v>44400</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B239" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C239">
-        <v>53400</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>86</v>
+        <v>219</v>
       </c>
       <c r="B240" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C240">
-        <v>52400</v>
+        <v>42200</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B241" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C241">
-        <v>50400</v>
+        <v>42100</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="B242" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C242">
-        <v>48000</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B243" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C243">
-        <v>47100</v>
+        <v>34900</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B244" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C244">
-        <v>47000</v>
+        <v>34300</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>227</v>
+        <v>7</v>
       </c>
       <c r="B245" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C245">
-        <v>47000</v>
+        <v>31300</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="B246" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C246">
-        <v>45000</v>
+        <v>30300</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B247" t="s">
-        <v>567</v>
+        <v>224</v>
       </c>
       <c r="C247">
-        <v>41300</v>
+        <v>29400</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B248" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C248">
-        <v>40800</v>
+        <v>28700</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>229</v>
+        <v>150</v>
       </c>
       <c r="B249" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C249">
-        <v>39600</v>
+        <v>28700</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B250" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C250">
-        <v>37500</v>
+        <v>28700</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="B251" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C251">
-        <v>35300</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B252" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C252">
-        <v>33700</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B253" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C253">
-        <v>32300</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B254" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C254">
-        <v>31400</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B255" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C255">
-        <v>29100</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B256" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C256">
-        <v>29000</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>70</v>
+        <v>232</v>
       </c>
       <c r="B257" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C257">
-        <v>27700</v>
+        <v>20600</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B258" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C258">
-        <v>27400</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>58</v>
+        <v>234</v>
       </c>
       <c r="B259" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C259">
-        <v>26900</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B260" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C260">
-        <v>25500</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B261" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C261">
-        <v>24900</v>
+        <v>15100</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="B262" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C262">
-        <v>24600</v>
+        <v>15100</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B263" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C263">
-        <v>21400</v>
+        <v>15100</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="B264" t="s">
-        <v>584</v>
+        <v>238</v>
       </c>
       <c r="C264">
-        <v>19100</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="B265" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C265">
-        <v>17100</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -5454,186 +5478,186 @@
         <v>240</v>
       </c>
       <c r="B266" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C266">
-        <v>16500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>241</v>
+        <v>150</v>
       </c>
       <c r="B267" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C267">
-        <v>16500</v>
+        <v>13800</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B268" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C268">
-        <v>15700</v>
+        <v>13300</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="B269" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C269">
-        <v>15600</v>
+        <v>13300</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="B270" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C270">
-        <v>14500</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B271" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C271">
-        <v>14000</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>194</v>
+        <v>243</v>
       </c>
       <c r="B272" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C272">
-        <v>13800</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B273" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C273">
-        <v>13200</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B274" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C274">
-        <v>12900</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B275" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C275">
-        <v>11200</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="B276" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C276">
-        <v>10600</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B277" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C277">
-        <v>10500</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B278" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C278">
-        <v>10500</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="B279" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C279">
-        <v>9500</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="B280" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C280">
-        <v>8500</v>
+        <v>7400</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="B281" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C281">
-        <v>8300</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="B282" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C282">
-        <v>8100</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -5641,10 +5665,10 @@
         <v>250</v>
       </c>
       <c r="B283" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C283">
-        <v>7700</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -5652,18 +5676,18 @@
         <v>251</v>
       </c>
       <c r="B284" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C284">
-        <v>7600</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="B285" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C285">
         <v>5800</v>
@@ -5671,54 +5695,54 @@
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="B286" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C286">
-        <v>5800</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="B287" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C287">
-        <v>4800</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>253</v>
+        <v>46</v>
       </c>
       <c r="B288" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C288">
-        <v>4700</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B289" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C289">
-        <v>4700</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>207</v>
+        <v>253</v>
       </c>
       <c r="B290" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C290">
         <v>4100</v>
@@ -5726,43 +5750,43 @@
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="B291" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C291">
-        <v>4100</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B292" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C292">
-        <v>4100</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B293" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C293">
-        <v>3900</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>258</v>
+        <v>143</v>
       </c>
       <c r="B294" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C294">
         <v>3800</v>
@@ -5770,343 +5794,343 @@
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B295" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C295">
-        <v>3500</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B296" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C296">
-        <v>3400</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B297" t="s">
-        <v>261</v>
+        <v>618</v>
       </c>
       <c r="C297">
-        <v>3400</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B298" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C298">
-        <v>3100</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B299" t="s">
-        <v>262</v>
+        <v>620</v>
       </c>
       <c r="C299">
-        <v>3100</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="B300" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C300">
-        <v>3000</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>263</v>
+        <v>112</v>
       </c>
       <c r="B301" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C301">
-        <v>2900</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B302" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C302">
-        <v>2900</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B303" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C303">
-        <v>2700</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="B304" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C304">
-        <v>2700</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B305" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C305">
-        <v>2600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>266</v>
+        <v>181</v>
       </c>
       <c r="B306" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C306">
-        <v>2500</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="B307" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C307">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B308" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C308">
-        <v>2400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="B309" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C309">
-        <v>2400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B310" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C310">
-        <v>2300</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>270</v>
+        <v>142</v>
       </c>
       <c r="B311" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C311">
-        <v>2200</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>152</v>
+        <v>267</v>
       </c>
       <c r="B312" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C312">
-        <v>2100</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B313" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C313">
-        <v>2000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>48</v>
+        <v>269</v>
       </c>
       <c r="B314" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C314">
-        <v>2000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B315" t="s">
-        <v>272</v>
+        <v>636</v>
       </c>
       <c r="C315">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B316" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C316">
-        <v>1900</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B317" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C317">
-        <v>1900</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B318" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C318">
-        <v>1800</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B319" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C319">
-        <v>1800</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B320" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C320">
-        <v>1700</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="B321" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C321">
-        <v>1600</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>159</v>
+        <v>277</v>
       </c>
       <c r="B322" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C322">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>144</v>
+        <v>236</v>
       </c>
       <c r="B323" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C323">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="B324" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C324">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B325" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C325">
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -6114,373 +6138,373 @@
         <v>278</v>
       </c>
       <c r="B326" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C326">
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="B327" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C327">
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>48</v>
+        <v>239</v>
       </c>
       <c r="B328" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C328">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B329" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C329">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B330" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C330">
-        <v>1100</v>
+        <v>800</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>280</v>
+        <v>202</v>
       </c>
       <c r="B331" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C331">
-        <v>1100</v>
+        <v>800</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B332" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C332">
-        <v>1007</v>
+        <v>600</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="B333" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C333">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>270</v>
+        <v>70</v>
       </c>
       <c r="B334" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C334">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>191</v>
+        <v>285</v>
       </c>
       <c r="B335" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C335">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B336" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C336">
-        <v>900</v>
+        <v>400</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B337" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C337">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B338" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C338">
-        <v>700</v>
+        <v>300</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="B339" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C339">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B340" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C340">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B341" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C341">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B342" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C342">
-        <v>600</v>
+        <v>200</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B343" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C343">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B344" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C344">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="B345" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C345">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B346" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C346">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>207</v>
+        <v>263</v>
       </c>
       <c r="B347" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C347">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B348" t="s">
-        <v>665</v>
+        <v>294</v>
       </c>
       <c r="C348">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B349" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C349">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B350" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C350">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B351" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C351">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B352" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C352">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B353" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C353">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B354" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C354">
-        <v>200</v>
+        <v>99</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B355" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C355">
-        <v>200</v>
+        <v>15700</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="B356" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C356">
-        <v>200</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="B357" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C357">
-        <v>200</v>
+        <v>700</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="B358" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C358">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
+        <v>32</v>
+      </c>
+      <c r="B359" t="s">
+        <v>679</v>
+      </c>
+      <c r="C359">
         <v>300</v>
-      </c>
-      <c r="B359" t="s">
-        <v>676</v>
-      </c>
-      <c r="C359">
-        <v>200</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -6488,194 +6512,194 @@
         <v>301</v>
       </c>
       <c r="B360" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C360">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="B361" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C361">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>205</v>
+        <v>302</v>
       </c>
       <c r="B362" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C362">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B363" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C363">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="B364" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C364">
-        <v>9</v>
+        <v>200</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>304</v>
+        <v>217</v>
       </c>
       <c r="B365" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C365">
-        <v>10700</v>
+        <v>200</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B366" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C366">
-        <v>1300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B367" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C367">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>258</v>
+        <v>306</v>
       </c>
       <c r="B368" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C368">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>273</v>
+        <v>176</v>
       </c>
       <c r="B369" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C369">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>294</v>
+        <v>213</v>
       </c>
       <c r="B370" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C370">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B371" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C371">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B372" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C372">
-        <v>100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B373" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C373">
-        <v>100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B374" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C374">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B375" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C375">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="B376" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C376">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B377" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C377">
         <v>100</v>
@@ -6683,10 +6707,10 @@
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>269</v>
+        <v>98</v>
       </c>
       <c r="B378" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C378">
         <v>100</v>
@@ -6694,65 +6718,65 @@
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="B379" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C379">
-        <v>3500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B380" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C380">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B381" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C381">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="B382" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C382">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B383" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C383">
-        <v>400</v>
+        <v>100</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="B384" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C384">
         <v>100</v>
@@ -6760,10 +6784,10 @@
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>86</v>
+        <v>277</v>
       </c>
       <c r="B385" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C385">
         <v>100</v>
@@ -6771,10 +6795,10 @@
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="B386" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C386">
         <v>100</v>
@@ -6782,10 +6806,10 @@
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B387" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C387">
         <v>100</v>
@@ -6793,76 +6817,76 @@
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B388" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C388">
-        <v>100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>314</v>
+        <v>244</v>
       </c>
       <c r="B389" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C389">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B390" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C390">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="B391" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C391">
-        <v>100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>316</v>
+        <v>259</v>
       </c>
       <c r="B392" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C392">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="B393" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C393">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>152</v>
+        <v>319</v>
       </c>
       <c r="B394" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C394">
         <v>100</v>
@@ -6870,43 +6894,43 @@
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="B395" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C395">
-        <v>200</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>314</v>
+        <v>272</v>
       </c>
       <c r="B396" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C396">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B397" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C397">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="B398" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C398">
         <v>100</v>
@@ -6914,10 +6938,10 @@
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
       <c r="B399" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C399">
         <v>100</v>
@@ -6925,35 +6949,90 @@
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="B400" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C400">
-        <v>400</v>
+        <v>100</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B401" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C401">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B402" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C402">
-        <v>1500</v>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403" t="s">
+        <v>261</v>
+      </c>
+      <c r="B403" t="s">
+        <v>723</v>
+      </c>
+      <c r="C403">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3">
+      <c r="A404" t="s">
+        <v>324</v>
+      </c>
+      <c r="B404" t="s">
+        <v>724</v>
+      </c>
+      <c r="C404">
+        <v>5513000</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3">
+      <c r="A405" t="s">
+        <v>284</v>
+      </c>
+      <c r="B405" t="s">
+        <v>725</v>
+      </c>
+      <c r="C405">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406" t="s">
+        <v>310</v>
+      </c>
+      <c r="B406" t="s">
+        <v>726</v>
+      </c>
+      <c r="C406">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3">
+      <c r="A407" t="s">
+        <v>291</v>
+      </c>
+      <c r="B407" t="s">
+        <v>727</v>
+      </c>
+      <c r="C407">
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/Bases/Lista de ações.xlsx
+++ b/Bases/Lista de ações.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="725">
   <si>
     <t>Nome da Empresa</t>
   </si>
@@ -22,936 +22,954 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>Volume no último dia útil (lido em 12/04/2025)</t>
+    <t>Volume no último dia útil (lido em 19/04/2025)</t>
+  </si>
+  <si>
+    <t>Cogna</t>
   </si>
   <si>
     <t>Petrobras</t>
   </si>
   <si>
-    <t>Cogna</t>
-  </si>
-  <si>
     <t>Hapvida</t>
   </si>
   <si>
+    <t>Ambev</t>
+  </si>
+  <si>
+    <t>Magazine Luiza</t>
+  </si>
+  <si>
+    <t>Locaweb</t>
+  </si>
+  <si>
+    <t>Itaúsa</t>
+  </si>
+  <si>
+    <t>Banco Bradesco</t>
+  </si>
+  <si>
+    <t>Ânima Educação</t>
+  </si>
+  <si>
+    <t>Grupo Pão de Açúcar</t>
+  </si>
+  <si>
+    <t>Vale</t>
+  </si>
+  <si>
+    <t>MRV</t>
+  </si>
+  <si>
+    <t>Hidrovias do Brasil</t>
+  </si>
+  <si>
+    <t>Cosan</t>
+  </si>
+  <si>
+    <t>Itaú Unibanco</t>
+  </si>
+  <si>
+    <t>Banco do Brasil</t>
+  </si>
+  <si>
+    <t>CVC</t>
+  </si>
+  <si>
     <t>B3</t>
   </si>
   <si>
+    <t>Minerva</t>
+  </si>
+  <si>
+    <t>YDUQS</t>
+  </si>
+  <si>
+    <t>Carrefour Brasil</t>
+  </si>
+  <si>
+    <t>Lojas Renner</t>
+  </si>
+  <si>
+    <t>Vibra Energia</t>
+  </si>
+  <si>
+    <t>Azul</t>
+  </si>
+  <si>
+    <t>Cemig</t>
+  </si>
+  <si>
+    <t>Metalúrgica Gerdau</t>
+  </si>
+  <si>
+    <t>Assaí</t>
+  </si>
+  <si>
+    <t>Eletrobras</t>
+  </si>
+  <si>
+    <t>Rumo</t>
+  </si>
+  <si>
+    <t>Natura</t>
+  </si>
+  <si>
+    <t>Copel</t>
+  </si>
+  <si>
+    <t>PetroRio</t>
+  </si>
+  <si>
+    <t>Marcopolo</t>
+  </si>
+  <si>
+    <t>Usiminas</t>
+  </si>
+  <si>
+    <t>3R Petroleum</t>
+  </si>
+  <si>
+    <t>RaiaDrogasil</t>
+  </si>
+  <si>
+    <t>Gerdau</t>
+  </si>
+  <si>
+    <t>Localiza</t>
+  </si>
+  <si>
+    <t>Raízen</t>
+  </si>
+  <si>
+    <t>BRF</t>
+  </si>
+  <si>
+    <t>Siderúrgica Nacional</t>
+  </si>
+  <si>
+    <t>Grupo CCR</t>
+  </si>
+  <si>
+    <t>EcoRodovias</t>
+  </si>
+  <si>
+    <t>CSN Mineração</t>
+  </si>
+  <si>
+    <t>Infracommerce</t>
+  </si>
+  <si>
+    <t>Equatorial Energia</t>
+  </si>
+  <si>
+    <t>Klabin</t>
+  </si>
+  <si>
+    <t>Automob</t>
+  </si>
+  <si>
+    <t>Banco BTG Pactual</t>
+  </si>
+  <si>
+    <t>Grupo Vamos</t>
+  </si>
+  <si>
+    <t>Ultrapar</t>
+  </si>
+  <si>
+    <t>Eneva</t>
+  </si>
+  <si>
+    <t>Simpar</t>
+  </si>
+  <si>
+    <t>CBA</t>
+  </si>
+  <si>
+    <t>JHSF</t>
+  </si>
+  <si>
+    <t>Movida</t>
+  </si>
+  <si>
+    <t>Casas Bahia</t>
+  </si>
+  <si>
+    <t>Bradespar</t>
+  </si>
+  <si>
+    <t>Gafisa</t>
+  </si>
+  <si>
+    <t>Multiplan</t>
+  </si>
+  <si>
+    <t>Petz</t>
+  </si>
+  <si>
+    <t>Marfrig</t>
+  </si>
+  <si>
+    <t>Embraer</t>
+  </si>
+  <si>
+    <t>Dexco</t>
+  </si>
+  <si>
+    <t>Recrusul</t>
+  </si>
+  <si>
+    <t>JBS</t>
+  </si>
+  <si>
+    <t>Santos Brasil</t>
+  </si>
+  <si>
+    <t>Grupo Mateus</t>
+  </si>
+  <si>
+    <t>Serena Energia</t>
+  </si>
+  <si>
+    <t>Allos</t>
+  </si>
+  <si>
+    <t>Auren Energia</t>
+  </si>
+  <si>
+    <t>Vivo</t>
+  </si>
+  <si>
+    <t>Cyrela</t>
+  </si>
+  <si>
+    <t>Suzano</t>
+  </si>
+  <si>
+    <t>Energisa</t>
+  </si>
+  <si>
+    <t>Caixa Seguridade</t>
+  </si>
+  <si>
+    <t>Banco Santander</t>
+  </si>
+  <si>
+    <t>WEG</t>
+  </si>
+  <si>
+    <t>Qualicorp</t>
+  </si>
+  <si>
+    <t>Totvs</t>
+  </si>
+  <si>
+    <t>Randon</t>
+  </si>
+  <si>
+    <t>GOL</t>
+  </si>
+  <si>
+    <t>Smart Fit</t>
+  </si>
+  <si>
     <t>Oi</t>
   </si>
   <si>
-    <t>Itaúsa</t>
-  </si>
-  <si>
-    <t>Ambev</t>
-  </si>
-  <si>
-    <t>Grupo Pão de Açúcar</t>
-  </si>
-  <si>
-    <t>Banco Bradesco</t>
-  </si>
-  <si>
-    <t>Itaú Unibanco</t>
-  </si>
-  <si>
-    <t>Magazine Luiza</t>
-  </si>
-  <si>
-    <t>Carrefour Brasil</t>
-  </si>
-  <si>
-    <t>Vale</t>
-  </si>
-  <si>
-    <t>Grupo CCR</t>
-  </si>
-  <si>
-    <t>Marcopolo</t>
-  </si>
-  <si>
-    <t>CVC</t>
-  </si>
-  <si>
-    <t>Grupo Vamos</t>
-  </si>
-  <si>
-    <t>Cosan</t>
-  </si>
-  <si>
-    <t>Metalúrgica Gerdau</t>
-  </si>
-  <si>
-    <t>PetroRio</t>
-  </si>
-  <si>
-    <t>3R Petroleum</t>
-  </si>
-  <si>
-    <t>Lojas Renner</t>
-  </si>
-  <si>
-    <t>Banco do Brasil</t>
-  </si>
-  <si>
-    <t>Rumo</t>
-  </si>
-  <si>
-    <t>Minerva</t>
-  </si>
-  <si>
-    <t>Cemig</t>
-  </si>
-  <si>
-    <t>Localiza</t>
-  </si>
-  <si>
-    <t>Automob</t>
-  </si>
-  <si>
-    <t>Gerdau</t>
-  </si>
-  <si>
-    <t>Copel</t>
-  </si>
-  <si>
-    <t>Ânima Educação</t>
-  </si>
-  <si>
-    <t>Assaí</t>
-  </si>
-  <si>
-    <t>Azul</t>
-  </si>
-  <si>
-    <t>Randon</t>
-  </si>
-  <si>
-    <t>Raízen</t>
-  </si>
-  <si>
-    <t>Locaweb</t>
-  </si>
-  <si>
-    <t>RaiaDrogasil</t>
-  </si>
-  <si>
-    <t>Usiminas</t>
-  </si>
-  <si>
-    <t>Vibra Energia</t>
-  </si>
-  <si>
-    <t>MRV</t>
-  </si>
-  <si>
-    <t>Eneva</t>
-  </si>
-  <si>
-    <t>Siderúrgica Nacional</t>
-  </si>
-  <si>
-    <t>Serena Energia</t>
-  </si>
-  <si>
-    <t>Banco BTG Pactual</t>
-  </si>
-  <si>
-    <t>Natura</t>
-  </si>
-  <si>
-    <t>Cyrela</t>
-  </si>
-  <si>
-    <t>Movida</t>
-  </si>
-  <si>
-    <t>Infracommerce</t>
-  </si>
-  <si>
-    <t>CBA</t>
-  </si>
-  <si>
-    <t>Casas Bahia</t>
-  </si>
-  <si>
-    <t>Simpar</t>
-  </si>
-  <si>
-    <t>Grupo Mateus</t>
-  </si>
-  <si>
-    <t>Klabin</t>
-  </si>
-  <si>
-    <t>Gafisa</t>
-  </si>
-  <si>
-    <t>Equatorial Energia</t>
+    <t>Fleury</t>
+  </si>
+  <si>
+    <t>TIM</t>
+  </si>
+  <si>
+    <t>C&amp;A</t>
   </si>
   <si>
     <t>Rede D'Or</t>
   </si>
   <si>
-    <t>Eletrobras</t>
-  </si>
-  <si>
-    <t>Suzano</t>
-  </si>
-  <si>
-    <t>Marfrig</t>
-  </si>
-  <si>
-    <t>CSN Mineração</t>
-  </si>
-  <si>
-    <t>Banco Santander</t>
+    <t>Jereissati Participações</t>
+  </si>
+  <si>
+    <t>Enjoei</t>
   </si>
   <si>
     <t>PetroRecôncavo</t>
   </si>
   <si>
-    <t>Multiplan</t>
-  </si>
-  <si>
-    <t>TIM</t>
+    <t>Braskem</t>
+  </si>
+  <si>
+    <t>Hypera</t>
+  </si>
+  <si>
+    <t>Banrisul</t>
+  </si>
+  <si>
+    <t>Odontoprev</t>
+  </si>
+  <si>
+    <t>Vivara</t>
+  </si>
+  <si>
+    <t>Sabesp</t>
+  </si>
+  <si>
+    <t>Grendene</t>
+  </si>
+  <si>
+    <t>São Martinho</t>
+  </si>
+  <si>
+    <t>Lojas Quero-Quero</t>
+  </si>
+  <si>
+    <t>BB Seguridade</t>
+  </si>
+  <si>
+    <t>Méliuz</t>
+  </si>
+  <si>
+    <t>Arezzo</t>
+  </si>
+  <si>
+    <t>Construtora Tenda</t>
+  </si>
+  <si>
+    <t>EZTEC</t>
   </si>
   <si>
     <t>SLC Agrícola</t>
   </si>
   <si>
-    <t>EcoRodovias</t>
-  </si>
-  <si>
-    <t>Petz</t>
+    <t>Tupy</t>
+  </si>
+  <si>
+    <t>Viveo</t>
+  </si>
+  <si>
+    <t>CPFL Energia</t>
+  </si>
+  <si>
+    <t>Positivo</t>
+  </si>
+  <si>
+    <t>Camil Alimentos</t>
+  </si>
+  <si>
+    <t>Ser Educacional</t>
+  </si>
+  <si>
+    <t>Americanas</t>
+  </si>
+  <si>
+    <t>Helbor</t>
   </si>
   <si>
     <t>Azevedo &amp; Travassos</t>
   </si>
   <si>
-    <t>BRF</t>
+    <t>Direcional</t>
+  </si>
+  <si>
+    <t>Porto Seguro</t>
+  </si>
+  <si>
+    <t>Kepler Weber</t>
+  </si>
+  <si>
+    <t>Multilaser</t>
+  </si>
+  <si>
+    <t>COPASA</t>
+  </si>
+  <si>
+    <t>Armac</t>
+  </si>
+  <si>
+    <t>Intelbras</t>
+  </si>
+  <si>
+    <t>Alpargatas</t>
+  </si>
+  <si>
+    <t>GPS</t>
+  </si>
+  <si>
+    <t>Guararapes</t>
+  </si>
+  <si>
+    <t>Even</t>
+  </si>
+  <si>
+    <t>Cury</t>
+  </si>
+  <si>
+    <t>Oncoclínicas</t>
+  </si>
+  <si>
+    <t>Engie</t>
+  </si>
+  <si>
+    <t>ISA Energia</t>
+  </si>
+  <si>
+    <t>Grupo SBF</t>
+  </si>
+  <si>
+    <t>Taesa</t>
+  </si>
+  <si>
+    <t>3tentos</t>
+  </si>
+  <si>
+    <t>Iochpe-Maxion</t>
+  </si>
+  <si>
+    <t>Banco Pan</t>
+  </si>
+  <si>
+    <t>Neoenergia</t>
+  </si>
+  <si>
+    <t>Sanepar</t>
+  </si>
+  <si>
+    <t>IMC Alimentação</t>
+  </si>
+  <si>
+    <t>Cruzeiro do Sul Educacional</t>
+  </si>
+  <si>
+    <t>Mobly</t>
+  </si>
+  <si>
+    <t>Boa Safra Sementes</t>
+  </si>
+  <si>
+    <t>Alupar</t>
+  </si>
+  <si>
+    <t>Ferbasa</t>
+  </si>
+  <si>
+    <t>PDG Realty</t>
   </si>
   <si>
     <t>Wilson Sons</t>
   </si>
   <si>
-    <t>Ultrapar</t>
-  </si>
-  <si>
-    <t>Smart Fit</t>
-  </si>
-  <si>
-    <t>Recrusul</t>
-  </si>
-  <si>
-    <t>Banco Pan</t>
-  </si>
-  <si>
-    <t>Americanas</t>
-  </si>
-  <si>
-    <t>Auren Energia</t>
-  </si>
-  <si>
-    <t>Enjoei</t>
-  </si>
-  <si>
-    <t>JBS</t>
-  </si>
-  <si>
-    <t>C&amp;A</t>
-  </si>
-  <si>
-    <t>Bradespar</t>
-  </si>
-  <si>
-    <t>Embraer</t>
-  </si>
-  <si>
-    <t>Intelbras</t>
-  </si>
-  <si>
-    <t>Sabesp</t>
-  </si>
-  <si>
-    <t>Allos</t>
-  </si>
-  <si>
-    <t>WEG</t>
-  </si>
-  <si>
-    <t>YDUQS</t>
-  </si>
-  <si>
-    <t>Vivara</t>
-  </si>
-  <si>
-    <t>BB Seguridade</t>
-  </si>
-  <si>
-    <t>São Martinho</t>
-  </si>
-  <si>
-    <t>Lojas Quero-Quero</t>
-  </si>
-  <si>
-    <t>Direcional</t>
-  </si>
-  <si>
-    <t>Totvs</t>
+    <t>Vulcabras</t>
+  </si>
+  <si>
+    <t>Lavvi Incorporadora</t>
+  </si>
+  <si>
+    <t>Paranapanema</t>
+  </si>
+  <si>
+    <t>M. Dias Branco</t>
+  </si>
+  <si>
+    <t>Plano&amp;Plano</t>
+  </si>
+  <si>
+    <t>Blau Farmacêutica</t>
+  </si>
+  <si>
+    <t>JSL</t>
+  </si>
+  <si>
+    <t>Zamp</t>
   </si>
   <si>
     <t>IRB Brasil RE</t>
   </si>
   <si>
-    <t>EZTEC</t>
-  </si>
-  <si>
-    <t>Cury</t>
-  </si>
-  <si>
-    <t>Braskem</t>
-  </si>
-  <si>
-    <t>Qualicorp</t>
-  </si>
-  <si>
-    <t>GPS</t>
-  </si>
-  <si>
-    <t>JHSF</t>
-  </si>
-  <si>
-    <t>Dexco</t>
-  </si>
-  <si>
-    <t>Iguatemi</t>
-  </si>
-  <si>
-    <t>Arezzo</t>
-  </si>
-  <si>
-    <t>Santos Brasil</t>
-  </si>
-  <si>
-    <t>Caixa Seguridade</t>
-  </si>
-  <si>
-    <t>Fleury</t>
-  </si>
-  <si>
-    <t>CPFL Energia</t>
-  </si>
-  <si>
-    <t>Cruzeiro do Sul Educacional</t>
-  </si>
-  <si>
-    <t>GOL</t>
-  </si>
-  <si>
-    <t>Boa Safra Sementes</t>
-  </si>
-  <si>
-    <t>Energisa</t>
-  </si>
-  <si>
-    <t>Lavvi Incorporadora</t>
-  </si>
-  <si>
-    <t>COPASA</t>
-  </si>
-  <si>
-    <t>Camil Alimentos</t>
-  </si>
-  <si>
-    <t>Grendene</t>
-  </si>
-  <si>
-    <t>Guararapes</t>
-  </si>
-  <si>
-    <t>Kepler Weber</t>
-  </si>
-  <si>
-    <t>Méliuz</t>
-  </si>
-  <si>
-    <t>Paranapanema</t>
-  </si>
-  <si>
-    <t>Hypera</t>
-  </si>
-  <si>
-    <t>Neoenergia</t>
-  </si>
-  <si>
-    <t>Oncoclínicas</t>
-  </si>
-  <si>
-    <t>Construtora Tenda</t>
-  </si>
-  <si>
-    <t>Odontoprev</t>
-  </si>
-  <si>
-    <t>Armac</t>
-  </si>
-  <si>
-    <t>Engie</t>
-  </si>
-  <si>
-    <t>Vivo</t>
-  </si>
-  <si>
-    <t>Hidrovias do Brasil</t>
-  </si>
-  <si>
-    <t>Grupo SBF</t>
-  </si>
-  <si>
-    <t>Porto Seguro</t>
-  </si>
-  <si>
-    <t>Tupy</t>
-  </si>
-  <si>
-    <t>Taesa</t>
+    <t>Melnick</t>
+  </si>
+  <si>
+    <t>Priner</t>
+  </si>
+  <si>
+    <t>Schulz</t>
+  </si>
+  <si>
+    <t>Pague Menos</t>
+  </si>
+  <si>
+    <t>Mater Dei</t>
+  </si>
+  <si>
+    <t>Unifique</t>
+  </si>
+  <si>
+    <t>Banco ABC Brasil</t>
+  </si>
+  <si>
+    <t>BrasilAgro</t>
+  </si>
+  <si>
+    <t>Trisul</t>
+  </si>
+  <si>
+    <t>Profarma</t>
+  </si>
+  <si>
+    <t>SYN</t>
+  </si>
+  <si>
+    <t>OceanPact</t>
   </si>
   <si>
     <t>Light</t>
   </si>
   <si>
-    <t>Iochpe-Maxion</t>
-  </si>
-  <si>
-    <t>Even</t>
-  </si>
-  <si>
-    <t>Alpargatas</t>
-  </si>
-  <si>
-    <t>Positivo</t>
-  </si>
-  <si>
-    <t>3tentos</t>
-  </si>
-  <si>
-    <t>Unifique</t>
+    <t>Mitre Realty</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve</t>
+  </si>
+  <si>
+    <t>VITRUBREPCOM</t>
+  </si>
+  <si>
+    <t>Jalles Machado</t>
+  </si>
+  <si>
+    <t>Espaçolaser</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
+    <t>Orizon</t>
+  </si>
+  <si>
+    <t>AgroGalaxy</t>
+  </si>
+  <si>
+    <t>Bemobi</t>
+  </si>
+  <si>
+    <t>Portobello</t>
+  </si>
+  <si>
+    <t>Moura Dubeux</t>
+  </si>
+  <si>
+    <t>Banco BMG</t>
+  </si>
+  <si>
+    <t>Irani</t>
+  </si>
+  <si>
+    <t>Taurus</t>
+  </si>
+  <si>
+    <t>BR Partners</t>
+  </si>
+  <si>
+    <t>Technos</t>
+  </si>
+  <si>
+    <t>Track &amp; Field</t>
+  </si>
+  <si>
+    <t>Sequoia Logística</t>
   </si>
   <si>
     <t>Dasa</t>
   </si>
   <si>
-    <t>ISA Energia</t>
-  </si>
-  <si>
-    <t>Banrisul</t>
-  </si>
-  <si>
-    <t>JSL</t>
+    <t>Lojas Marisa</t>
+  </si>
+  <si>
+    <t>Wiz Soluções</t>
+  </si>
+  <si>
+    <t>Aeris Energy</t>
+  </si>
+  <si>
+    <t>Banco Pine</t>
   </si>
   <si>
     <t>Mills</t>
   </si>
   <si>
-    <t>Ser Educacional</t>
-  </si>
-  <si>
-    <t>Multilaser</t>
-  </si>
-  <si>
-    <t>Sanepar</t>
-  </si>
-  <si>
-    <t>Helbor</t>
-  </si>
-  <si>
-    <t>Alupar</t>
+    <t>Brisanet</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>HBR Realty</t>
+  </si>
+  <si>
+    <t>Dimed</t>
   </si>
   <si>
     <t>Alliança</t>
   </si>
   <si>
-    <t>Bemobi</t>
-  </si>
-  <si>
-    <t>Pague Menos</t>
-  </si>
-  <si>
-    <t>Viveo</t>
-  </si>
-  <si>
-    <t>Vulcabras</t>
-  </si>
-  <si>
-    <t>HBR Realty</t>
-  </si>
-  <si>
-    <t>Melnick</t>
-  </si>
-  <si>
-    <t>Blau Farmacêutica</t>
-  </si>
-  <si>
-    <t>Banco ABC Brasil</t>
-  </si>
-  <si>
-    <t>Plano&amp;Plano</t>
-  </si>
-  <si>
-    <t>Dimed</t>
-  </si>
-  <si>
-    <t>VITRUBREPCOM</t>
-  </si>
-  <si>
-    <t>Valid</t>
-  </si>
-  <si>
-    <t>Zamp</t>
-  </si>
-  <si>
-    <t>Banco BMG</t>
-  </si>
-  <si>
-    <t>Irani</t>
-  </si>
-  <si>
-    <t>Mitre Realty</t>
-  </si>
-  <si>
-    <t>AgroGalaxy</t>
-  </si>
-  <si>
-    <t>Portobello</t>
-  </si>
-  <si>
-    <t>SYN</t>
-  </si>
-  <si>
-    <t>Profarma</t>
-  </si>
-  <si>
-    <t>Espaçolaser</t>
-  </si>
-  <si>
-    <t>Banco Pine</t>
-  </si>
-  <si>
-    <t>Schulz</t>
-  </si>
-  <si>
-    <t>M. Dias Branco</t>
-  </si>
-  <si>
-    <t>Ferbasa</t>
+    <t>LOG CP</t>
+  </si>
+  <si>
+    <t>D1000 Varejo Farma</t>
+  </si>
+  <si>
+    <t>Vittia</t>
+  </si>
+  <si>
+    <t>Ambipar</t>
+  </si>
+  <si>
+    <t>Tegma</t>
+  </si>
+  <si>
+    <t>Fras-le</t>
   </si>
   <si>
     <t>Eletromidia</t>
   </si>
   <si>
-    <t>Moura Dubeux</t>
-  </si>
-  <si>
-    <t>BR Partners</t>
-  </si>
-  <si>
-    <t>IMC Alimentação</t>
+    <t>Unipar</t>
+  </si>
+  <si>
+    <t>Dexxos</t>
+  </si>
+  <si>
+    <t>Indústrias ROMI</t>
+  </si>
+  <si>
+    <t>CSU Cardsystem</t>
+  </si>
+  <si>
+    <t>Eucatex</t>
+  </si>
+  <si>
+    <t>Lopes</t>
+  </si>
+  <si>
+    <t>Inepar</t>
+  </si>
+  <si>
+    <t>Rossi Residencial</t>
+  </si>
+  <si>
+    <t>Viver</t>
+  </si>
+  <si>
+    <t>Estapar</t>
+  </si>
+  <si>
+    <t>Unicasa</t>
+  </si>
+  <si>
+    <t>Lupatech</t>
   </si>
   <si>
     <t>Renova Energia</t>
   </si>
   <si>
-    <t>Vittia</t>
-  </si>
-  <si>
-    <t>OceanPact</t>
-  </si>
-  <si>
-    <t>BrasilAgro</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve</t>
-  </si>
-  <si>
-    <t>LOG CP</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>Wiz Soluções</t>
-  </si>
-  <si>
-    <t>Fras-le</t>
-  </si>
-  <si>
-    <t>Sequoia Logística</t>
-  </si>
-  <si>
-    <t>Mater Dei</t>
-  </si>
-  <si>
-    <t>Mobly</t>
-  </si>
-  <si>
-    <t>Trisul</t>
-  </si>
-  <si>
-    <t>Jalles Machado</t>
-  </si>
-  <si>
-    <t>Track &amp; Field</t>
-  </si>
-  <si>
-    <t>Aeris Energy</t>
-  </si>
-  <si>
-    <t>Taurus</t>
-  </si>
-  <si>
-    <t>Orizon</t>
-  </si>
-  <si>
-    <t>PDG Realty</t>
-  </si>
-  <si>
-    <t>Brisanet</t>
-  </si>
-  <si>
-    <t>Priner</t>
-  </si>
-  <si>
-    <t>Lojas Marisa</t>
+    <t>Terra Santa</t>
+  </si>
+  <si>
+    <t>Fictor Alimentos</t>
+  </si>
+  <si>
+    <t>São Carlos</t>
+  </si>
+  <si>
+    <t>Eternit</t>
+  </si>
+  <si>
+    <t>Padtec</t>
+  </si>
+  <si>
+    <t>Traders Club</t>
+  </si>
+  <si>
+    <t>Allied</t>
+  </si>
+  <si>
+    <t>Tecnisa</t>
+  </si>
+  <si>
+    <t>Log-In</t>
+  </si>
+  <si>
+    <t>Biomm</t>
   </si>
   <si>
     <t>Time For Fun</t>
   </si>
   <si>
-    <t>Unipar</t>
-  </si>
-  <si>
-    <t>Tegma</t>
-  </si>
-  <si>
-    <t>Estapar</t>
-  </si>
-  <si>
-    <t>D1000 Varejo Farma</t>
-  </si>
-  <si>
-    <t>Rossi Residencial</t>
-  </si>
-  <si>
-    <t>Eternit</t>
-  </si>
-  <si>
-    <t>Indústrias ROMI</t>
-  </si>
-  <si>
-    <t>Technos</t>
+    <t>Pettenati</t>
+  </si>
+  <si>
+    <t>João Fortes</t>
+  </si>
+  <si>
+    <t>Dotz</t>
+  </si>
+  <si>
+    <t>Bombril</t>
+  </si>
+  <si>
+    <t>DASA11</t>
+  </si>
+  <si>
+    <t>REAG3</t>
+  </si>
+  <si>
+    <t>Banestes</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer</t>
   </si>
   <si>
     <t>WDC Networks</t>
   </si>
   <si>
-    <t>Jereissati Participações</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer</t>
-  </si>
-  <si>
-    <t>Dexxos</t>
-  </si>
-  <si>
-    <t>São Carlos</t>
-  </si>
-  <si>
-    <t>Eucatex</t>
-  </si>
-  <si>
-    <t>Ambipar</t>
-  </si>
-  <si>
-    <t>Lopes</t>
-  </si>
-  <si>
-    <t>Terra Santa</t>
-  </si>
-  <si>
-    <t>Inepar</t>
-  </si>
-  <si>
-    <t>Viver</t>
-  </si>
-  <si>
-    <t>Traders Club</t>
-  </si>
-  <si>
-    <t>DASA11</t>
-  </si>
-  <si>
-    <t>Lupatech</t>
-  </si>
-  <si>
-    <t>CSU Cardsystem</t>
-  </si>
-  <si>
-    <t>Padtec</t>
+    <t>Hotéis Othon</t>
+  </si>
+  <si>
+    <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
+  </si>
+  <si>
+    <t>Banco de Brasília</t>
+  </si>
+  <si>
+    <t>Santanense</t>
+  </si>
+  <si>
+    <t>Banco Mercantil do Brasil</t>
+  </si>
+  <si>
+    <t>Electro Aço Altona</t>
+  </si>
+  <si>
+    <t>CEB</t>
   </si>
   <si>
     <t>Cambuci</t>
   </si>
   <si>
-    <t>Bombril</t>
+    <t>Equatorial Energia Pará</t>
+  </si>
+  <si>
+    <t>BIED3</t>
+  </si>
+  <si>
+    <t>Triunfo</t>
+  </si>
+  <si>
+    <t>Embpar Participações</t>
+  </si>
+  <si>
+    <t>Atma</t>
+  </si>
+  <si>
+    <t>Refinaria de Manguinhos</t>
+  </si>
+  <si>
+    <t>LE LIS BLANC</t>
+  </si>
+  <si>
+    <t>Coelce</t>
+  </si>
+  <si>
+    <t>Minupar</t>
   </si>
   <si>
     <t>Neogrid</t>
   </si>
   <si>
-    <t>Allied</t>
-  </si>
-  <si>
-    <t>Unicasa</t>
-  </si>
-  <si>
-    <t>Tecnisa</t>
-  </si>
-  <si>
-    <t>Fictor Alimentos</t>
-  </si>
-  <si>
-    <t>Banestes</t>
-  </si>
-  <si>
-    <t>CEB</t>
+    <t>Nutriplant</t>
+  </si>
+  <si>
+    <t>Banco da Amazônia</t>
   </si>
   <si>
     <t>RNI</t>
   </si>
   <si>
-    <t>REAG3</t>
-  </si>
-  <si>
-    <t>Banco Mercantil do Brasil</t>
-  </si>
-  <si>
-    <t>Dotz</t>
-  </si>
-  <si>
-    <t>Banco de Brasília</t>
-  </si>
-  <si>
-    <t>Pettenati</t>
+    <t>Mangels</t>
+  </si>
+  <si>
+    <t>Sansuy</t>
+  </si>
+  <si>
+    <t>Celesc</t>
+  </si>
+  <si>
+    <t>Alphaville</t>
   </si>
   <si>
     <t>Whirlpool</t>
   </si>
   <si>
-    <t>Equatorial Energia Pará</t>
-  </si>
-  <si>
-    <t>Log-In</t>
-  </si>
-  <si>
-    <t>João Fortes</t>
+    <t>Grazziotin</t>
   </si>
   <si>
     <t>Telebras</t>
   </si>
   <si>
+    <t>Haga</t>
+  </si>
+  <si>
+    <t>Comgás</t>
+  </si>
+  <si>
+    <t>OSX Brasil</t>
+  </si>
+  <si>
+    <t>Mundial</t>
+  </si>
+  <si>
+    <t>Tronox Pigmentos</t>
+  </si>
+  <si>
+    <t>PPLA</t>
+  </si>
+  <si>
+    <t>Metisa</t>
+  </si>
+  <si>
+    <t>WLM</t>
+  </si>
+  <si>
+    <t>Panatlântica</t>
+  </si>
+  <si>
+    <t>Banese</t>
+  </si>
+  <si>
+    <t>Ourofino Saúde Animal</t>
+  </si>
+  <si>
+    <t>EMAE</t>
+  </si>
+  <si>
+    <t>Rio Paranapanema Energia</t>
+  </si>
+  <si>
+    <t>Brasil Brokers</t>
+  </si>
+  <si>
+    <t>Metalúrgica Riosulense</t>
+  </si>
+  <si>
+    <t>Karsten</t>
+  </si>
+  <si>
+    <t>Rede Energia</t>
+  </si>
+  <si>
+    <t>COELBA</t>
+  </si>
+  <si>
+    <t>Nordon</t>
+  </si>
+  <si>
     <t>Westwing</t>
   </si>
   <si>
-    <t>Triunfo</t>
-  </si>
-  <si>
-    <t>Embpar Participações</t>
-  </si>
-  <si>
-    <t>Electro Aço Altona</t>
-  </si>
-  <si>
-    <t>Biomm</t>
-  </si>
-  <si>
-    <t>OSX Brasil</t>
-  </si>
-  <si>
-    <t>Alphaville</t>
-  </si>
-  <si>
-    <t>Banco da Amazônia</t>
-  </si>
-  <si>
-    <t>Nutriplant</t>
-  </si>
-  <si>
-    <t>LE LIS BLANC</t>
+    <t>Banco do Nordeste</t>
+  </si>
+  <si>
+    <t>Energisa MT</t>
+  </si>
+  <si>
+    <t>Elektro</t>
+  </si>
+  <si>
+    <t>MRS Logística</t>
+  </si>
+  <si>
+    <t>Equatorial Maranhão</t>
+  </si>
+  <si>
+    <t>Baumer</t>
+  </si>
+  <si>
+    <t>Cemepe</t>
+  </si>
+  <si>
+    <t>Döhler</t>
+  </si>
+  <si>
+    <t>São Paulo Turismo</t>
+  </si>
+  <si>
+    <t>Habitasul</t>
   </si>
   <si>
     <t>Cedro Têxtil</t>
   </si>
   <si>
-    <t>Celesc</t>
-  </si>
-  <si>
-    <t>ATOM EDUCAÇÃO E EDITORA S.A.</t>
-  </si>
-  <si>
-    <t>Panatlântica</t>
-  </si>
-  <si>
-    <t>Ourofino Saúde Animal</t>
-  </si>
-  <si>
-    <t>Sansuy</t>
-  </si>
-  <si>
-    <t>Hotéis Othon</t>
-  </si>
-  <si>
-    <t>Minupar</t>
-  </si>
-  <si>
-    <t>Döhler</t>
-  </si>
-  <si>
-    <t>Equatorial Maranhão</t>
+    <t>Banco Mercantil de Investimentos</t>
+  </si>
+  <si>
+    <t>Bardella</t>
+  </si>
+  <si>
+    <t>Monark</t>
+  </si>
+  <si>
+    <t>Wetzel</t>
+  </si>
+  <si>
+    <t>Plascar</t>
+  </si>
+  <si>
+    <t>Tekno</t>
+  </si>
+  <si>
+    <t>CELGPAR</t>
+  </si>
+  <si>
+    <t>Josapar</t>
+  </si>
+  <si>
+    <t>Participações Aliança da Bahia</t>
+  </si>
+  <si>
+    <t>Trevisa</t>
+  </si>
+  <si>
+    <t>Dtcom</t>
+  </si>
+  <si>
+    <t>Kora Saúde</t>
+  </si>
+  <si>
+    <t>Afluente T</t>
+  </si>
+  <si>
+    <t>Excelsior</t>
+  </si>
+  <si>
+    <t>Mercantil do Brasil Financeira</t>
   </si>
   <si>
     <t>Alfa Holdings</t>
   </si>
   <si>
-    <t>Brasil Brokers</t>
-  </si>
-  <si>
-    <t>Mundial</t>
-  </si>
-  <si>
-    <t>Kora Saúde</t>
-  </si>
-  <si>
-    <t>WLM</t>
-  </si>
-  <si>
-    <t>Coelce</t>
-  </si>
-  <si>
-    <t>Plascar</t>
-  </si>
-  <si>
-    <t>Haga</t>
-  </si>
-  <si>
-    <t>EMAE</t>
-  </si>
-  <si>
-    <t>Banese</t>
-  </si>
-  <si>
-    <t>Santanense</t>
-  </si>
-  <si>
-    <t>Nordon</t>
-  </si>
-  <si>
-    <t>Tronox Pigmentos</t>
-  </si>
-  <si>
-    <t>Grazziotin</t>
-  </si>
-  <si>
-    <t>Rede Energia</t>
-  </si>
-  <si>
-    <t>Mangels</t>
-  </si>
-  <si>
-    <t>Karsten</t>
-  </si>
-  <si>
-    <t>Metisa</t>
-  </si>
-  <si>
-    <t>Rio Paranapanema Energia</t>
-  </si>
-  <si>
     <t>Fica</t>
   </si>
   <si>
-    <t>Metalúrgica Riosulense</t>
-  </si>
-  <si>
-    <t>Dtcom</t>
-  </si>
-  <si>
-    <t>Energisa MT</t>
-  </si>
-  <si>
-    <t>MRS Logística</t>
-  </si>
-  <si>
-    <t>Josapar</t>
-  </si>
-  <si>
-    <t>Banco Mercantil de Investimentos</t>
-  </si>
-  <si>
-    <t>BIED3</t>
-  </si>
-  <si>
-    <t>Atma</t>
-  </si>
-  <si>
     <t>Naturgy (CEG)</t>
   </si>
   <si>
-    <t>Baumer</t>
-  </si>
-  <si>
-    <t>Monark</t>
-  </si>
-  <si>
-    <t>Refinaria de Manguinhos</t>
-  </si>
-  <si>
     <t>Monteiro Aranha</t>
   </si>
   <si>
-    <t>Comgás</t>
-  </si>
-  <si>
-    <t>Banco do Nordeste</t>
-  </si>
-  <si>
-    <t>COELBA</t>
-  </si>
-  <si>
-    <t>Trevisa</t>
-  </si>
-  <si>
-    <t>Tekno</t>
-  </si>
-  <si>
-    <t>Elektro</t>
-  </si>
-  <si>
-    <t>PPLA</t>
-  </si>
-  <si>
-    <t>São Paulo Turismo</t>
-  </si>
-  <si>
-    <t>Habitasul</t>
-  </si>
-  <si>
     <t>Estrela</t>
   </si>
   <si>
-    <t>CELGPAR</t>
-  </si>
-  <si>
     <t>CEEE D</t>
   </si>
   <si>
@@ -964,1152 +982,1176 @@
     <t>Eletropar</t>
   </si>
   <si>
-    <t>Bardella</t>
-  </si>
-  <si>
-    <t>Participações Aliança da Bahia</t>
-  </si>
-  <si>
-    <t>Mercantil do Brasil Financeira</t>
-  </si>
-  <si>
     <t>Hercules</t>
   </si>
   <si>
-    <t>Afluente T</t>
-  </si>
-  <si>
-    <t>Metalfrio</t>
-  </si>
-  <si>
-    <t>Excelsior</t>
-  </si>
-  <si>
-    <t>Wetzel</t>
-  </si>
-  <si>
-    <t>ClearSale</t>
+    <t>COGN3</t>
   </si>
   <si>
     <t>PETR4</t>
   </si>
   <si>
-    <t>COGN3</t>
-  </si>
-  <si>
     <t>HAPV3</t>
   </si>
   <si>
+    <t>ABEV3</t>
+  </si>
+  <si>
+    <t>MGLU3</t>
+  </si>
+  <si>
+    <t>LWSA3</t>
+  </si>
+  <si>
+    <t>ITSA4</t>
+  </si>
+  <si>
+    <t>BBDC4</t>
+  </si>
+  <si>
+    <t>ANIM3</t>
+  </si>
+  <si>
+    <t>PCAR3</t>
+  </si>
+  <si>
+    <t>VALE3</t>
+  </si>
+  <si>
+    <t>MRVE3</t>
+  </si>
+  <si>
+    <t>HBSA3</t>
+  </si>
+  <si>
+    <t>CSAN3</t>
+  </si>
+  <si>
+    <t>ITUB4</t>
+  </si>
+  <si>
+    <t>BBAS3</t>
+  </si>
+  <si>
+    <t>CVCB3</t>
+  </si>
+  <si>
     <t>B3SA3</t>
   </si>
   <si>
+    <t>BEEF3</t>
+  </si>
+  <si>
+    <t>YDUQ3</t>
+  </si>
+  <si>
+    <t>CRFB3</t>
+  </si>
+  <si>
+    <t>LREN3</t>
+  </si>
+  <si>
+    <t>PETR3</t>
+  </si>
+  <si>
+    <t>VBBR3</t>
+  </si>
+  <si>
+    <t>AZUL4</t>
+  </si>
+  <si>
+    <t>CMIG4</t>
+  </si>
+  <si>
+    <t>GOAU4</t>
+  </si>
+  <si>
+    <t>ASAI3</t>
+  </si>
+  <si>
+    <t>ELET3</t>
+  </si>
+  <si>
+    <t>RAIL3</t>
+  </si>
+  <si>
+    <t>NTCO3</t>
+  </si>
+  <si>
+    <t>CPLE6</t>
+  </si>
+  <si>
+    <t>PRIO3</t>
+  </si>
+  <si>
+    <t>POMO4</t>
+  </si>
+  <si>
+    <t>USIM5</t>
+  </si>
+  <si>
+    <t>BRAV3</t>
+  </si>
+  <si>
+    <t>RADL3</t>
+  </si>
+  <si>
+    <t>GGBR4</t>
+  </si>
+  <si>
+    <t>RENT3</t>
+  </si>
+  <si>
+    <t>RAIZ4</t>
+  </si>
+  <si>
+    <t>BRFS3</t>
+  </si>
+  <si>
+    <t>CSNA3</t>
+  </si>
+  <si>
+    <t>CCRO3</t>
+  </si>
+  <si>
+    <t>BBDC3</t>
+  </si>
+  <si>
+    <t>ECOR3</t>
+  </si>
+  <si>
+    <t>CMIN3</t>
+  </si>
+  <si>
+    <t>IFCM3</t>
+  </si>
+  <si>
+    <t>EQTL3</t>
+  </si>
+  <si>
+    <t>KLBN11</t>
+  </si>
+  <si>
+    <t>AMOB3</t>
+  </si>
+  <si>
+    <t>BPAC11</t>
+  </si>
+  <si>
+    <t>VAMO3</t>
+  </si>
+  <si>
+    <t>UGPA3</t>
+  </si>
+  <si>
+    <t>ENEV3</t>
+  </si>
+  <si>
+    <t>SIMH3</t>
+  </si>
+  <si>
+    <t>CBAV3</t>
+  </si>
+  <si>
+    <t>JHSF3</t>
+  </si>
+  <si>
+    <t>MOVI3</t>
+  </si>
+  <si>
+    <t>BHIA3</t>
+  </si>
+  <si>
+    <t>BRAP4</t>
+  </si>
+  <si>
+    <t>GFSA3</t>
+  </si>
+  <si>
+    <t>MULT3</t>
+  </si>
+  <si>
+    <t>PETZ3</t>
+  </si>
+  <si>
+    <t>MRFG3</t>
+  </si>
+  <si>
+    <t>EMBR3</t>
+  </si>
+  <si>
+    <t>DXCO3</t>
+  </si>
+  <si>
+    <t>RCSL4</t>
+  </si>
+  <si>
+    <t>JBSS3</t>
+  </si>
+  <si>
+    <t>STBP3</t>
+  </si>
+  <si>
+    <t>GMAT3</t>
+  </si>
+  <si>
+    <t>SRNA3</t>
+  </si>
+  <si>
+    <t>ALOS3</t>
+  </si>
+  <si>
+    <t>AURE3</t>
+  </si>
+  <si>
+    <t>VIVT3</t>
+  </si>
+  <si>
+    <t>CYRE3</t>
+  </si>
+  <si>
+    <t>SUZB3</t>
+  </si>
+  <si>
+    <t>ENGI11</t>
+  </si>
+  <si>
+    <t>CPLE3</t>
+  </si>
+  <si>
+    <t>CXSE3</t>
+  </si>
+  <si>
+    <t>SANB11</t>
+  </si>
+  <si>
+    <t>WEGE3</t>
+  </si>
+  <si>
+    <t>QUAL3</t>
+  </si>
+  <si>
+    <t>TOTS3</t>
+  </si>
+  <si>
+    <t>RAPT4</t>
+  </si>
+  <si>
+    <t>GOLL4</t>
+  </si>
+  <si>
+    <t>SMFT3</t>
+  </si>
+  <si>
     <t>OIBR3</t>
   </si>
   <si>
-    <t>ITSA4</t>
-  </si>
-  <si>
-    <t>ABEV3</t>
-  </si>
-  <si>
-    <t>PCAR3</t>
-  </si>
-  <si>
-    <t>BBDC4</t>
-  </si>
-  <si>
-    <t>ITUB4</t>
-  </si>
-  <si>
-    <t>MGLU3</t>
-  </si>
-  <si>
-    <t>CRFB3</t>
-  </si>
-  <si>
-    <t>VALE3</t>
-  </si>
-  <si>
-    <t>PETR3</t>
-  </si>
-  <si>
-    <t>CCRO3</t>
-  </si>
-  <si>
-    <t>POMO4</t>
-  </si>
-  <si>
-    <t>CVCB3</t>
-  </si>
-  <si>
-    <t>VAMO3</t>
-  </si>
-  <si>
-    <t>CSAN3</t>
-  </si>
-  <si>
-    <t>GOAU4</t>
-  </si>
-  <si>
-    <t>PRIO3</t>
-  </si>
-  <si>
-    <t>BRAV3</t>
-  </si>
-  <si>
-    <t>LREN3</t>
-  </si>
-  <si>
-    <t>BBAS3</t>
-  </si>
-  <si>
-    <t>RAIL3</t>
-  </si>
-  <si>
-    <t>BEEF3</t>
-  </si>
-  <si>
-    <t>CMIG4</t>
-  </si>
-  <si>
-    <t>RENT3</t>
-  </si>
-  <si>
-    <t>AMOB3</t>
-  </si>
-  <si>
-    <t>GGBR4</t>
-  </si>
-  <si>
-    <t>CPLE6</t>
-  </si>
-  <si>
-    <t>ANIM3</t>
-  </si>
-  <si>
-    <t>ASAI3</t>
-  </si>
-  <si>
-    <t>AZUL4</t>
-  </si>
-  <si>
-    <t>RAPT4</t>
-  </si>
-  <si>
-    <t>RAIZ4</t>
-  </si>
-  <si>
-    <t>LWSA3</t>
-  </si>
-  <si>
-    <t>RADL3</t>
-  </si>
-  <si>
-    <t>CPLE3</t>
-  </si>
-  <si>
-    <t>USIM5</t>
-  </si>
-  <si>
-    <t>VBBR3</t>
-  </si>
-  <si>
-    <t>MRVE3</t>
-  </si>
-  <si>
-    <t>ENEV3</t>
-  </si>
-  <si>
-    <t>CSNA3</t>
-  </si>
-  <si>
-    <t>SRNA3</t>
-  </si>
-  <si>
-    <t>BPAC11</t>
-  </si>
-  <si>
-    <t>NTCO3</t>
-  </si>
-  <si>
-    <t>CYRE3</t>
-  </si>
-  <si>
-    <t>MOVI3</t>
-  </si>
-  <si>
-    <t>IFCM3</t>
-  </si>
-  <si>
-    <t>CBAV3</t>
-  </si>
-  <si>
-    <t>BHIA3</t>
-  </si>
-  <si>
-    <t>SIMH3</t>
-  </si>
-  <si>
-    <t>GMAT3</t>
-  </si>
-  <si>
-    <t>KLBN11</t>
-  </si>
-  <si>
-    <t>GFSA3</t>
-  </si>
-  <si>
-    <t>EQTL3</t>
+    <t>FLRY3</t>
+  </si>
+  <si>
+    <t>TIMS3</t>
+  </si>
+  <si>
+    <t>CEAB3</t>
   </si>
   <si>
     <t>RDOR3</t>
   </si>
   <si>
-    <t>BBDC3</t>
-  </si>
-  <si>
-    <t>ELET3</t>
-  </si>
-  <si>
-    <t>SUZB3</t>
-  </si>
-  <si>
-    <t>MRFG3</t>
-  </si>
-  <si>
-    <t>CMIN3</t>
-  </si>
-  <si>
-    <t>SANB11</t>
+    <t>IGTI11</t>
+  </si>
+  <si>
+    <t>ENJU3</t>
   </si>
   <si>
     <t>RECV3</t>
   </si>
   <si>
-    <t>MULT3</t>
-  </si>
-  <si>
-    <t>TIMS3</t>
+    <t>BRKM5</t>
+  </si>
+  <si>
+    <t>HYPE3</t>
+  </si>
+  <si>
+    <t>BRSR6</t>
+  </si>
+  <si>
+    <t>ODPV3</t>
+  </si>
+  <si>
+    <t>VIVA3</t>
+  </si>
+  <si>
+    <t>SBSP3</t>
+  </si>
+  <si>
+    <t>GRND3</t>
+  </si>
+  <si>
+    <t>SMTO3</t>
+  </si>
+  <si>
+    <t>LJQQ3</t>
+  </si>
+  <si>
+    <t>BBSE3</t>
+  </si>
+  <si>
+    <t>CASH3</t>
+  </si>
+  <si>
+    <t>AZZA3</t>
+  </si>
+  <si>
+    <t>TEND3</t>
+  </si>
+  <si>
+    <t>EZTC3</t>
   </si>
   <si>
     <t>SLCE3</t>
   </si>
   <si>
-    <t>ECOR3</t>
-  </si>
-  <si>
-    <t>PETZ3</t>
+    <t>TUPY3</t>
+  </si>
+  <si>
+    <t>VVEO3</t>
+  </si>
+  <si>
+    <t>CPFE3</t>
+  </si>
+  <si>
+    <t>POSI3</t>
+  </si>
+  <si>
+    <t>CAML3</t>
+  </si>
+  <si>
+    <t>SEER3</t>
+  </si>
+  <si>
+    <t>AMER3</t>
+  </si>
+  <si>
+    <t>HBOR3</t>
   </si>
   <si>
     <t>AZEV4</t>
   </si>
   <si>
-    <t>BRFS3</t>
+    <t>ELET6</t>
+  </si>
+  <si>
+    <t>KLBN4</t>
+  </si>
+  <si>
+    <t>DIRR3</t>
+  </si>
+  <si>
+    <t>PSSA3</t>
+  </si>
+  <si>
+    <t>KEPL3</t>
+  </si>
+  <si>
+    <t>MLAS3</t>
+  </si>
+  <si>
+    <t>CSMG3</t>
+  </si>
+  <si>
+    <t>ARML3</t>
+  </si>
+  <si>
+    <t>INTB3</t>
+  </si>
+  <si>
+    <t>ALPA4</t>
+  </si>
+  <si>
+    <t>GGPS3</t>
+  </si>
+  <si>
+    <t>GUAR3</t>
+  </si>
+  <si>
+    <t>EVEN3</t>
+  </si>
+  <si>
+    <t>CURY3</t>
+  </si>
+  <si>
+    <t>AZEV3</t>
+  </si>
+  <si>
+    <t>ONCO3</t>
+  </si>
+  <si>
+    <t>EGIE3</t>
+  </si>
+  <si>
+    <t>ISAE4</t>
+  </si>
+  <si>
+    <t>SBFG3</t>
+  </si>
+  <si>
+    <t>TAEE11</t>
+  </si>
+  <si>
+    <t>TTEN3</t>
+  </si>
+  <si>
+    <t>MYPK3</t>
+  </si>
+  <si>
+    <t>BPAN4</t>
+  </si>
+  <si>
+    <t>NEOE3</t>
+  </si>
+  <si>
+    <t>SAPR4</t>
+  </si>
+  <si>
+    <t>MEAL3</t>
+  </si>
+  <si>
+    <t>CSED3</t>
+  </si>
+  <si>
+    <t>MBLY3</t>
+  </si>
+  <si>
+    <t>SOJA3</t>
+  </si>
+  <si>
+    <t>ALUP11</t>
+  </si>
+  <si>
+    <t>FESA4</t>
+  </si>
+  <si>
+    <t>SAPR11</t>
+  </si>
+  <si>
+    <t>PDGR3</t>
+  </si>
+  <si>
+    <t>RCSL3</t>
   </si>
   <si>
     <t>PORT3</t>
   </si>
   <si>
-    <t>UGPA3</t>
-  </si>
-  <si>
-    <t>SMFT3</t>
-  </si>
-  <si>
-    <t>RCSL4</t>
-  </si>
-  <si>
-    <t>BPAN4</t>
-  </si>
-  <si>
-    <t>AMER3</t>
-  </si>
-  <si>
-    <t>AURE3</t>
-  </si>
-  <si>
-    <t>ENJU3</t>
-  </si>
-  <si>
-    <t>JBSS3</t>
-  </si>
-  <si>
-    <t>CEAB3</t>
-  </si>
-  <si>
-    <t>KLBN4</t>
-  </si>
-  <si>
-    <t>BRAP4</t>
-  </si>
-  <si>
-    <t>EMBR3</t>
-  </si>
-  <si>
-    <t>INTB3</t>
-  </si>
-  <si>
-    <t>SBSP3</t>
-  </si>
-  <si>
-    <t>ALOS3</t>
-  </si>
-  <si>
-    <t>WEGE3</t>
-  </si>
-  <si>
-    <t>YDUQ3</t>
-  </si>
-  <si>
-    <t>VIVA3</t>
-  </si>
-  <si>
-    <t>BBSE3</t>
-  </si>
-  <si>
-    <t>SMTO3</t>
-  </si>
-  <si>
-    <t>LJQQ3</t>
-  </si>
-  <si>
-    <t>DIRR3</t>
-  </si>
-  <si>
-    <t>TOTS3</t>
+    <t>VULC3</t>
+  </si>
+  <si>
+    <t>LAVV3</t>
+  </si>
+  <si>
+    <t>PMAM3</t>
+  </si>
+  <si>
+    <t>MDIA3</t>
+  </si>
+  <si>
+    <t>PLPL3</t>
+  </si>
+  <si>
+    <t>BLAU3</t>
+  </si>
+  <si>
+    <t>JSLG3</t>
+  </si>
+  <si>
+    <t>ZAMP3</t>
   </si>
   <si>
     <t>IRBR3</t>
   </si>
   <si>
-    <t>EZTC3</t>
-  </si>
-  <si>
-    <t>CURY3</t>
-  </si>
-  <si>
-    <t>BRKM5</t>
-  </si>
-  <si>
-    <t>QUAL3</t>
-  </si>
-  <si>
-    <t>GGPS3</t>
-  </si>
-  <si>
-    <t>JHSF3</t>
-  </si>
-  <si>
-    <t>DXCO3</t>
-  </si>
-  <si>
-    <t>IGTI11</t>
-  </si>
-  <si>
-    <t>AZZA3</t>
-  </si>
-  <si>
-    <t>STBP3</t>
-  </si>
-  <si>
-    <t>CXSE3</t>
-  </si>
-  <si>
-    <t>AZEV3</t>
-  </si>
-  <si>
-    <t>ELET6</t>
-  </si>
-  <si>
-    <t>FLRY3</t>
-  </si>
-  <si>
-    <t>CPFE3</t>
-  </si>
-  <si>
-    <t>CSED3</t>
-  </si>
-  <si>
-    <t>GOLL4</t>
-  </si>
-  <si>
-    <t>SOJA3</t>
-  </si>
-  <si>
-    <t>ENGI11</t>
-  </si>
-  <si>
-    <t>LAVV3</t>
-  </si>
-  <si>
-    <t>CSMG3</t>
-  </si>
-  <si>
-    <t>CAML3</t>
-  </si>
-  <si>
-    <t>GRND3</t>
-  </si>
-  <si>
-    <t>GUAR3</t>
-  </si>
-  <si>
-    <t>KEPL3</t>
-  </si>
-  <si>
-    <t>CASH3</t>
-  </si>
-  <si>
-    <t>PMAM3</t>
-  </si>
-  <si>
-    <t>HYPE3</t>
-  </si>
-  <si>
-    <t>NEOE3</t>
-  </si>
-  <si>
-    <t>ONCO3</t>
-  </si>
-  <si>
-    <t>TEND3</t>
-  </si>
-  <si>
-    <t>ODPV3</t>
-  </si>
-  <si>
-    <t>ARML3</t>
-  </si>
-  <si>
-    <t>EGIE3</t>
-  </si>
-  <si>
-    <t>VIVT3</t>
-  </si>
-  <si>
-    <t>HBSA3</t>
-  </si>
-  <si>
-    <t>SBFG3</t>
-  </si>
-  <si>
-    <t>PSSA3</t>
-  </si>
-  <si>
-    <t>TUPY3</t>
-  </si>
-  <si>
-    <t>TAEE11</t>
+    <t>MELK3</t>
+  </si>
+  <si>
+    <t>PRNR3</t>
+  </si>
+  <si>
+    <t>SHUL4</t>
+  </si>
+  <si>
+    <t>PGMN3</t>
+  </si>
+  <si>
+    <t>MATD3</t>
+  </si>
+  <si>
+    <t>FIQE3</t>
+  </si>
+  <si>
+    <t>ABCB4</t>
+  </si>
+  <si>
+    <t>AGRO3</t>
+  </si>
+  <si>
+    <t>TRIS3</t>
+  </si>
+  <si>
+    <t>PFRM3</t>
+  </si>
+  <si>
+    <t>SYNE3</t>
+  </si>
+  <si>
+    <t>OPCT3</t>
   </si>
   <si>
     <t>LIGT3</t>
   </si>
   <si>
-    <t>MYPK3</t>
+    <t>MTRE3</t>
+  </si>
+  <si>
+    <t>LEVE3</t>
+  </si>
+  <si>
+    <t>VTRU3</t>
+  </si>
+  <si>
+    <t>JALL3</t>
+  </si>
+  <si>
+    <t>ITUB3</t>
+  </si>
+  <si>
+    <t>ESPA3</t>
   </si>
   <si>
     <t>KLBN3</t>
   </si>
   <si>
-    <t>EVEN3</t>
-  </si>
-  <si>
-    <t>RCSL3</t>
-  </si>
-  <si>
-    <t>ALPA4</t>
-  </si>
-  <si>
-    <t>POSI3</t>
-  </si>
-  <si>
-    <t>TTEN3</t>
-  </si>
-  <si>
-    <t>FIQE3</t>
+    <t>VLID3</t>
+  </si>
+  <si>
+    <t>ORVR3</t>
+  </si>
+  <si>
+    <t>AGXY3</t>
+  </si>
+  <si>
+    <t>BMOB3</t>
+  </si>
+  <si>
+    <t>PTBL3</t>
+  </si>
+  <si>
+    <t>MDNE3</t>
+  </si>
+  <si>
+    <t>BMGB4</t>
+  </si>
+  <si>
+    <t>RANI3</t>
+  </si>
+  <si>
+    <t>POMO3</t>
+  </si>
+  <si>
+    <t>TASA4</t>
+  </si>
+  <si>
+    <t>BRBI11</t>
+  </si>
+  <si>
+    <t>TECN3</t>
+  </si>
+  <si>
+    <t>TFCO4</t>
+  </si>
+  <si>
+    <t>SEQL3</t>
   </si>
   <si>
     <t>DASA3</t>
   </si>
   <si>
-    <t>ISAE4</t>
-  </si>
-  <si>
-    <t>BRSR6</t>
-  </si>
-  <si>
-    <t>JSLG3</t>
+    <t>AMAR3</t>
+  </si>
+  <si>
+    <t>WIZC3</t>
+  </si>
+  <si>
+    <t>AERI3</t>
+  </si>
+  <si>
+    <t>PINE4</t>
   </si>
   <si>
     <t>MILS3</t>
   </si>
   <si>
-    <t>SEER3</t>
-  </si>
-  <si>
-    <t>MLAS3</t>
-  </si>
-  <si>
-    <t>SAPR4</t>
-  </si>
-  <si>
-    <t>HBOR3</t>
-  </si>
-  <si>
-    <t>ALUP11</t>
+    <t>BRST3</t>
+  </si>
+  <si>
+    <t>DESK3</t>
+  </si>
+  <si>
+    <t>HBRE3</t>
+  </si>
+  <si>
+    <t>PNVL3</t>
   </si>
   <si>
     <t>AALR3</t>
   </si>
   <si>
-    <t>BMOB3</t>
-  </si>
-  <si>
-    <t>PGMN3</t>
-  </si>
-  <si>
-    <t>VVEO3</t>
-  </si>
-  <si>
-    <t>VULC3</t>
-  </si>
-  <si>
-    <t>HBRE3</t>
-  </si>
-  <si>
-    <t>MELK3</t>
-  </si>
-  <si>
-    <t>BLAU3</t>
-  </si>
-  <si>
-    <t>ABCB4</t>
-  </si>
-  <si>
-    <t>PLPL3</t>
-  </si>
-  <si>
-    <t>PNVL3</t>
-  </si>
-  <si>
-    <t>VTRU3</t>
-  </si>
-  <si>
-    <t>ITUB3</t>
-  </si>
-  <si>
-    <t>VLID3</t>
-  </si>
-  <si>
-    <t>ZAMP3</t>
-  </si>
-  <si>
-    <t>BMGB4</t>
-  </si>
-  <si>
-    <t>RANI3</t>
-  </si>
-  <si>
-    <t>MTRE3</t>
-  </si>
-  <si>
-    <t>AGXY3</t>
-  </si>
-  <si>
-    <t>PTBL3</t>
-  </si>
-  <si>
-    <t>SYNE3</t>
-  </si>
-  <si>
-    <t>PFRM3</t>
-  </si>
-  <si>
-    <t>ESPA3</t>
-  </si>
-  <si>
-    <t>SAPR11</t>
-  </si>
-  <si>
-    <t>PINE4</t>
-  </si>
-  <si>
-    <t>SHUL4</t>
-  </si>
-  <si>
-    <t>MDIA3</t>
-  </si>
-  <si>
-    <t>FESA4</t>
+    <t>LOGG3</t>
+  </si>
+  <si>
+    <t>DMVF3</t>
+  </si>
+  <si>
+    <t>USIM3</t>
+  </si>
+  <si>
+    <t>CMIG3</t>
+  </si>
+  <si>
+    <t>SAPR3</t>
+  </si>
+  <si>
+    <t>VITT3</t>
+  </si>
+  <si>
+    <t>ITSA3</t>
+  </si>
+  <si>
+    <t>AMBP3</t>
+  </si>
+  <si>
+    <t>TGMA3</t>
+  </si>
+  <si>
+    <t>FRAS3</t>
+  </si>
+  <si>
+    <t>TAEE4</t>
   </si>
   <si>
     <t>ELMD3</t>
   </si>
   <si>
-    <t>POMO3</t>
-  </si>
-  <si>
-    <t>MDNE3</t>
-  </si>
-  <si>
-    <t>BRBI11</t>
-  </si>
-  <si>
-    <t>MEAL3</t>
+    <t>SANB3</t>
+  </si>
+  <si>
+    <t>UNIP6</t>
+  </si>
+  <si>
+    <t>DEXP3</t>
+  </si>
+  <si>
+    <t>ROMI3</t>
+  </si>
+  <si>
+    <t>BRAP3</t>
+  </si>
+  <si>
+    <t>CSUD3</t>
+  </si>
+  <si>
+    <t>EUCA4</t>
+  </si>
+  <si>
+    <t>SANB4</t>
+  </si>
+  <si>
+    <t>LPSB3</t>
+  </si>
+  <si>
+    <t>INEP4</t>
+  </si>
+  <si>
+    <t>INEP3</t>
+  </si>
+  <si>
+    <t>TAEE3</t>
+  </si>
+  <si>
+    <t>IGTI3</t>
+  </si>
+  <si>
+    <t>RSID3</t>
+  </si>
+  <si>
+    <t>VIVR3</t>
+  </si>
+  <si>
+    <t>ALPK3</t>
+  </si>
+  <si>
+    <t>UCAS3</t>
+  </si>
+  <si>
+    <t>LUPA3</t>
+  </si>
+  <si>
+    <t>OIBR4</t>
   </si>
   <si>
     <t>RNEW4</t>
   </si>
   <si>
-    <t>VITT3</t>
-  </si>
-  <si>
-    <t>OPCT3</t>
-  </si>
-  <si>
-    <t>USIM3</t>
-  </si>
-  <si>
-    <t>AGRO3</t>
-  </si>
-  <si>
-    <t>LEVE3</t>
+    <t>LAND3</t>
+  </si>
+  <si>
+    <t>FICT3</t>
+  </si>
+  <si>
+    <t>SCAR3</t>
+  </si>
+  <si>
+    <t>ETER3</t>
   </si>
   <si>
     <t>RNEW3</t>
   </si>
   <si>
-    <t>LOGG3</t>
-  </si>
-  <si>
-    <t>DESK3</t>
-  </si>
-  <si>
-    <t>WIZC3</t>
-  </si>
-  <si>
-    <t>FRAS3</t>
-  </si>
-  <si>
-    <t>SEQL3</t>
-  </si>
-  <si>
-    <t>MATD3</t>
-  </si>
-  <si>
-    <t>MBLY3</t>
-  </si>
-  <si>
-    <t>TRIS3</t>
-  </si>
-  <si>
-    <t>JALL3</t>
-  </si>
-  <si>
-    <t>TFCO4</t>
-  </si>
-  <si>
-    <t>AERI3</t>
-  </si>
-  <si>
-    <t>TASA4</t>
-  </si>
-  <si>
-    <t>ORVR3</t>
-  </si>
-  <si>
-    <t>PDGR3</t>
-  </si>
-  <si>
-    <t>TAEE4</t>
-  </si>
-  <si>
-    <t>BRST3</t>
-  </si>
-  <si>
-    <t>PRNR3</t>
-  </si>
-  <si>
-    <t>AMAR3</t>
-  </si>
-  <si>
-    <t>ITSA3</t>
-  </si>
-  <si>
-    <t>SAPR3</t>
+    <t>PDTC3</t>
+  </si>
+  <si>
+    <t>TRAD3</t>
+  </si>
+  <si>
+    <t>ALLD3</t>
+  </si>
+  <si>
+    <t>TCSA3</t>
+  </si>
+  <si>
+    <t>TASA3</t>
+  </si>
+  <si>
+    <t>LOGN3</t>
+  </si>
+  <si>
+    <t>BIOM3</t>
   </si>
   <si>
     <t>SHOW3</t>
   </si>
   <si>
-    <t>UNIP6</t>
-  </si>
-  <si>
-    <t>TGMA3</t>
-  </si>
-  <si>
-    <t>ALPK3</t>
-  </si>
-  <si>
-    <t>DMVF3</t>
-  </si>
-  <si>
-    <t>RSID3</t>
-  </si>
-  <si>
-    <t>ETER3</t>
-  </si>
-  <si>
-    <t>ROMI3</t>
-  </si>
-  <si>
-    <t>TECN3</t>
-  </si>
-  <si>
-    <t>SANB4</t>
+    <t>PTNT4</t>
+  </si>
+  <si>
+    <t>JFEN3</t>
+  </si>
+  <si>
+    <t>ALUP4</t>
+  </si>
+  <si>
+    <t>DOTZ3</t>
+  </si>
+  <si>
+    <t>PINE3</t>
+  </si>
+  <si>
+    <t>BOBR4</t>
+  </si>
+  <si>
+    <t>GOAU3</t>
+  </si>
+  <si>
+    <t>GGBR3</t>
+  </si>
+  <si>
+    <t>ALUP3</t>
+  </si>
+  <si>
+    <t>BEES3</t>
+  </si>
+  <si>
+    <t>FHER3</t>
   </si>
   <si>
     <t>LVTC3</t>
   </si>
   <si>
-    <t>SANB3</t>
-  </si>
-  <si>
-    <t>CMIG3</t>
-  </si>
-  <si>
-    <t>IGTI3</t>
-  </si>
-  <si>
-    <t>FHER3</t>
-  </si>
-  <si>
-    <t>DEXP3</t>
-  </si>
-  <si>
-    <t>TAEE3</t>
-  </si>
-  <si>
-    <t>SCAR3</t>
-  </si>
-  <si>
-    <t>BRAP3</t>
-  </si>
-  <si>
-    <t>EUCA4</t>
+    <t>HOOT4</t>
+  </si>
+  <si>
+    <t>ATED3</t>
+  </si>
+  <si>
+    <t>BSLI4</t>
+  </si>
+  <si>
+    <t>BSLI3</t>
+  </si>
+  <si>
+    <t>BRKM3</t>
   </si>
   <si>
     <t>RAPT3</t>
   </si>
   <si>
-    <t>AMBP3</t>
-  </si>
-  <si>
-    <t>LPSB3</t>
-  </si>
-  <si>
-    <t>LAND3</t>
-  </si>
-  <si>
-    <t>GOAU3</t>
-  </si>
-  <si>
-    <t>INEP3</t>
-  </si>
-  <si>
-    <t>VIVR3</t>
-  </si>
-  <si>
-    <t>OIBR4</t>
-  </si>
-  <si>
-    <t>TRAD3</t>
-  </si>
-  <si>
-    <t>GGBR3</t>
-  </si>
-  <si>
-    <t>ALUP4</t>
-  </si>
-  <si>
-    <t>LUPA3</t>
-  </si>
-  <si>
-    <t>CSUD3</t>
-  </si>
-  <si>
-    <t>PDTC3</t>
+    <t>CTSA4</t>
+  </si>
+  <si>
+    <t>BMEB4</t>
+  </si>
+  <si>
+    <t>EALT4</t>
+  </si>
+  <si>
+    <t>CEBR3</t>
   </si>
   <si>
     <t>CAMB3</t>
   </si>
   <si>
-    <t>BOBR4</t>
+    <t>BPAC5</t>
+  </si>
+  <si>
+    <t>ENGI4</t>
+  </si>
+  <si>
+    <t>EQPA3</t>
+  </si>
+  <si>
+    <t>TPIS3</t>
+  </si>
+  <si>
+    <t>EPAR3</t>
+  </si>
+  <si>
+    <t>BPAC3</t>
+  </si>
+  <si>
+    <t>ATMP3</t>
+  </si>
+  <si>
+    <t>RPMG3</t>
+  </si>
+  <si>
+    <t>VSTE3</t>
+  </si>
+  <si>
+    <t>COCE5</t>
+  </si>
+  <si>
+    <t>CEBR6</t>
+  </si>
+  <si>
+    <t>ENGI3</t>
+  </si>
+  <si>
+    <t>MNPR3</t>
+  </si>
+  <si>
+    <t>UNIP3</t>
   </si>
   <si>
     <t>NGRD3</t>
   </si>
   <si>
-    <t>ALLD3</t>
-  </si>
-  <si>
-    <t>UCAS3</t>
-  </si>
-  <si>
-    <t>TCSA3</t>
-  </si>
-  <si>
-    <t>FICT3</t>
-  </si>
-  <si>
-    <t>BEES3</t>
-  </si>
-  <si>
-    <t>CEBR6</t>
-  </si>
-  <si>
-    <t>PINE3</t>
+    <t>DEXP4</t>
+  </si>
+  <si>
+    <t>NUTR3</t>
+  </si>
+  <si>
+    <t>BAZA3</t>
+  </si>
+  <si>
+    <t>CEBR5</t>
+  </si>
+  <si>
+    <t>ALPA3</t>
+  </si>
+  <si>
+    <t>RNEW11</t>
+  </si>
+  <si>
+    <t>BRSR3</t>
   </si>
   <si>
     <t>RDNI3</t>
   </si>
   <si>
-    <t>BMEB4</t>
-  </si>
-  <si>
-    <t>DOTZ3</t>
-  </si>
-  <si>
-    <t>ALUP3</t>
-  </si>
-  <si>
-    <t>BSLI3</t>
-  </si>
-  <si>
-    <t>BPAC5</t>
-  </si>
-  <si>
-    <t>INEP4</t>
-  </si>
-  <si>
-    <t>PTNT4</t>
+    <t>BEES4</t>
+  </si>
+  <si>
+    <t>MGEL4</t>
+  </si>
+  <si>
+    <t>SNSY5</t>
+  </si>
+  <si>
+    <t>CLSC4</t>
+  </si>
+  <si>
+    <t>EUCA3</t>
+  </si>
+  <si>
+    <t>AVLL3</t>
+  </si>
+  <si>
+    <t>WHRL4</t>
+  </si>
+  <si>
+    <t>CGRA4</t>
+  </si>
+  <si>
+    <t>TELB4</t>
+  </si>
+  <si>
+    <t>ISAE3</t>
+  </si>
+  <si>
+    <t>HAGA4</t>
+  </si>
+  <si>
+    <t>CGAS5</t>
+  </si>
+  <si>
+    <t>OSXB3</t>
+  </si>
+  <si>
+    <t>MNDL3</t>
+  </si>
+  <si>
+    <t>CGRA3</t>
+  </si>
+  <si>
+    <t>AMAR11</t>
+  </si>
+  <si>
+    <t>CRPG5</t>
+  </si>
+  <si>
+    <t>PPLA11</t>
+  </si>
+  <si>
+    <t>MTSA4</t>
   </si>
   <si>
     <t>WHRL3</t>
   </si>
   <si>
-    <t>EQPA3</t>
-  </si>
-  <si>
-    <t>ENGI4</t>
-  </si>
-  <si>
-    <t>LOGN3</t>
-  </si>
-  <si>
-    <t>JFEN3</t>
-  </si>
-  <si>
-    <t>BSLI4</t>
-  </si>
-  <si>
-    <t>TELB4</t>
+    <t>WLMM4</t>
+  </si>
+  <si>
+    <t>PATI3</t>
+  </si>
+  <si>
+    <t>BGIP4</t>
+  </si>
+  <si>
+    <t>OFSA3</t>
+  </si>
+  <si>
+    <t>EMAE4</t>
+  </si>
+  <si>
+    <t>PTNT3</t>
+  </si>
+  <si>
+    <t>GEPA4</t>
+  </si>
+  <si>
+    <t>AZEV11</t>
+  </si>
+  <si>
+    <t>NEXP3</t>
+  </si>
+  <si>
+    <t>RSUL4</t>
+  </si>
+  <si>
+    <t>CTKA4</t>
+  </si>
+  <si>
+    <t>TELB3</t>
+  </si>
+  <si>
+    <t>FESA3</t>
+  </si>
+  <si>
+    <t>REDE3</t>
+  </si>
+  <si>
+    <t>CEEB3</t>
+  </si>
+  <si>
+    <t>GEPA3</t>
+  </si>
+  <si>
+    <t>NORD3</t>
   </si>
   <si>
     <t>WEST3</t>
   </si>
   <si>
-    <t>ALPA3</t>
-  </si>
-  <si>
-    <t>TPIS3</t>
-  </si>
-  <si>
-    <t>BRKM3</t>
-  </si>
-  <si>
-    <t>EPAR3</t>
-  </si>
-  <si>
-    <t>EALT4</t>
-  </si>
-  <si>
-    <t>CEBR3</t>
-  </si>
-  <si>
-    <t>UNIP3</t>
-  </si>
-  <si>
-    <t>WHRL4</t>
-  </si>
-  <si>
-    <t>BPAC3</t>
-  </si>
-  <si>
-    <t>BIOM3</t>
-  </si>
-  <si>
-    <t>OSXB3</t>
-  </si>
-  <si>
-    <t>TASA3</t>
-  </si>
-  <si>
-    <t>AVLL3</t>
-  </si>
-  <si>
-    <t>BAZA3</t>
-  </si>
-  <si>
-    <t>BRSR3</t>
-  </si>
-  <si>
-    <t>NUTR3</t>
-  </si>
-  <si>
-    <t>VSTE3</t>
+    <t>BNBR3</t>
+  </si>
+  <si>
+    <t>ENMT4</t>
+  </si>
+  <si>
+    <t>ENMT3</t>
+  </si>
+  <si>
+    <t>EKTR4</t>
+  </si>
+  <si>
+    <t>MRSA5B</t>
+  </si>
+  <si>
+    <t>EQMA3B</t>
+  </si>
+  <si>
+    <t>BALM4</t>
+  </si>
+  <si>
+    <t>CPLE5</t>
+  </si>
+  <si>
+    <t>MAPT4</t>
+  </si>
+  <si>
+    <t>DOHL4</t>
+  </si>
+  <si>
+    <t>HAGA3</t>
+  </si>
+  <si>
+    <t>AHEB3</t>
+  </si>
+  <si>
+    <t>HBTS5</t>
+  </si>
+  <si>
+    <t>BMEB3</t>
+  </si>
+  <si>
+    <t>COCE3</t>
+  </si>
+  <si>
+    <t>CEDO4</t>
+  </si>
+  <si>
+    <t>CRPG6</t>
+  </si>
+  <si>
+    <t>BMIN4</t>
+  </si>
+  <si>
+    <t>BRSR5</t>
+  </si>
+  <si>
+    <t>BDLL4</t>
+  </si>
+  <si>
+    <t>USIM6</t>
+  </si>
+  <si>
+    <t>MAPT3</t>
+  </si>
+  <si>
+    <t>CTSA3</t>
+  </si>
+  <si>
+    <t>BMKS3</t>
+  </si>
+  <si>
+    <t>EALT3</t>
+  </si>
+  <si>
+    <t>PATI4</t>
+  </si>
+  <si>
+    <t>MWET4</t>
+  </si>
+  <si>
+    <t>PLAS3</t>
+  </si>
+  <si>
+    <t>TKNO4</t>
+  </si>
+  <si>
+    <t>UNIP5</t>
   </si>
   <si>
     <t>CEDO3</t>
   </si>
   <si>
-    <t>BEES4</t>
-  </si>
-  <si>
-    <t>CLSC4</t>
-  </si>
-  <si>
-    <t>ATED3</t>
-  </si>
-  <si>
-    <t>ENGI3</t>
-  </si>
-  <si>
-    <t>PATI3</t>
-  </si>
-  <si>
-    <t>OFSA3</t>
-  </si>
-  <si>
-    <t>TELB3</t>
-  </si>
-  <si>
-    <t>SNSY5</t>
-  </si>
-  <si>
-    <t>RNEW11</t>
-  </si>
-  <si>
-    <t>HOOT4</t>
-  </si>
-  <si>
-    <t>MNPR3</t>
-  </si>
-  <si>
-    <t>DEXP4</t>
-  </si>
-  <si>
-    <t>DOHL4</t>
-  </si>
-  <si>
-    <t>ISAE3</t>
-  </si>
-  <si>
-    <t>EQMA3B</t>
+    <t>GPAR3</t>
+  </si>
+  <si>
+    <t>JOPA3</t>
+  </si>
+  <si>
+    <t>CGAS3</t>
+  </si>
+  <si>
+    <t>AHEB6</t>
+  </si>
+  <si>
+    <t>PEAB3</t>
+  </si>
+  <si>
+    <t>LUXM4</t>
+  </si>
+  <si>
+    <t>BDLL3</t>
+  </si>
+  <si>
+    <t>DTCY3</t>
+  </si>
+  <si>
+    <t>KRSA3</t>
+  </si>
+  <si>
+    <t>AFLT3</t>
+  </si>
+  <si>
+    <t>SNSY3</t>
+  </si>
+  <si>
+    <t>BAUH4</t>
+  </si>
+  <si>
+    <t>MERC4</t>
   </si>
   <si>
     <t>RPAD6</t>
   </si>
   <si>
-    <t>NEXP3</t>
-  </si>
-  <si>
-    <t>MNDL3</t>
-  </si>
-  <si>
-    <t>KRSA3</t>
-  </si>
-  <si>
-    <t>WLMM4</t>
-  </si>
-  <si>
-    <t>COCE5</t>
-  </si>
-  <si>
-    <t>PLAS3</t>
-  </si>
-  <si>
-    <t>HAGA4</t>
-  </si>
-  <si>
-    <t>EMAE4</t>
-  </si>
-  <si>
-    <t>BGIP4</t>
-  </si>
-  <si>
-    <t>CEBR5</t>
-  </si>
-  <si>
-    <t>CTSA4</t>
-  </si>
-  <si>
-    <t>NORD3</t>
-  </si>
-  <si>
-    <t>CTSA3</t>
-  </si>
-  <si>
-    <t>CRPG5</t>
-  </si>
-  <si>
-    <t>BMEB3</t>
-  </si>
-  <si>
-    <t>CGRA4</t>
-  </si>
-  <si>
-    <t>REDE3</t>
-  </si>
-  <si>
-    <t>AMAR11</t>
-  </si>
-  <si>
-    <t>MGEL4</t>
-  </si>
-  <si>
-    <t>CTKA4</t>
-  </si>
-  <si>
-    <t>AZEV11</t>
-  </si>
-  <si>
-    <t>MTSA4</t>
-  </si>
-  <si>
-    <t>GEPA4</t>
-  </si>
-  <si>
     <t>FIEI3</t>
   </si>
   <si>
-    <t>RSUL4</t>
-  </si>
-  <si>
-    <t>EALT3</t>
-  </si>
-  <si>
     <t>RPAD3</t>
   </si>
   <si>
-    <t>DTCY3</t>
-  </si>
-  <si>
-    <t>ENMT3</t>
-  </si>
-  <si>
     <t>MRSA6B</t>
   </si>
   <si>
-    <t>JOPA3</t>
-  </si>
-  <si>
-    <t>CEDO4</t>
-  </si>
-  <si>
-    <t>BMIN4</t>
-  </si>
-  <si>
-    <t>SNSY3</t>
-  </si>
-  <si>
-    <t>ATMP3</t>
-  </si>
-  <si>
     <t>CEGR3</t>
   </si>
   <si>
     <t>MRSA3B</t>
   </si>
   <si>
-    <t>BALM4</t>
-  </si>
-  <si>
-    <t>HAGA3</t>
-  </si>
-  <si>
-    <t>BMKS3</t>
-  </si>
-  <si>
-    <t>RPMG3</t>
-  </si>
-  <si>
     <t>MOAR3</t>
   </si>
   <si>
-    <t>CGRA3</t>
-  </si>
-  <si>
-    <t>CRPG6</t>
-  </si>
-  <si>
-    <t>CPLE5</t>
-  </si>
-  <si>
-    <t>CGAS5</t>
-  </si>
-  <si>
-    <t>CGAS3</t>
-  </si>
-  <si>
-    <t>BNBR3</t>
-  </si>
-  <si>
-    <t>CEEB3</t>
-  </si>
-  <si>
-    <t>GEPA3</t>
-  </si>
-  <si>
-    <t>EUCA3</t>
-  </si>
-  <si>
-    <t>LUXM4</t>
-  </si>
-  <si>
-    <t>TKNO4</t>
-  </si>
-  <si>
-    <t>EKTR4</t>
-  </si>
-  <si>
-    <t>FESA3</t>
-  </si>
-  <si>
     <t>IGTI4</t>
   </si>
   <si>
-    <t>PPLA11</t>
-  </si>
-  <si>
-    <t>AHEB3</t>
-  </si>
-  <si>
-    <t>PTNT3</t>
-  </si>
-  <si>
-    <t>HBTS5</t>
-  </si>
-  <si>
     <t>ESTR4</t>
   </si>
   <si>
-    <t>UNIP5</t>
-  </si>
-  <si>
-    <t>GPAR3</t>
-  </si>
-  <si>
     <t>BRKM6</t>
   </si>
   <si>
@@ -2122,9 +2164,6 @@
     <t>PSVM11</t>
   </si>
   <si>
-    <t>BRSR5</t>
-  </si>
-  <si>
     <t>SOND5</t>
   </si>
   <si>
@@ -2137,18 +2176,9 @@
     <t>BMIN3</t>
   </si>
   <si>
-    <t>BDLL3</t>
-  </si>
-  <si>
-    <t>PEAB3</t>
-  </si>
-  <si>
     <t>EQPA5</t>
   </si>
   <si>
-    <t>MERC4</t>
-  </si>
-  <si>
     <t>EQPA7</t>
   </si>
   <si>
@@ -2159,45 +2189,6 @@
   </si>
   <si>
     <t>HETA4</t>
-  </si>
-  <si>
-    <t>PEAB4</t>
-  </si>
-  <si>
-    <t>WLMM3</t>
-  </si>
-  <si>
-    <t>AFLT3</t>
-  </si>
-  <si>
-    <t>FRIO3</t>
-  </si>
-  <si>
-    <t>COCE3</t>
-  </si>
-  <si>
-    <t>BALM3</t>
-  </si>
-  <si>
-    <t>BAUH4</t>
-  </si>
-  <si>
-    <t>MWET4</t>
-  </si>
-  <si>
-    <t>PATI4</t>
-  </si>
-  <si>
-    <t>CLSA3</t>
-  </si>
-  <si>
-    <t>CTKA3</t>
-  </si>
-  <si>
-    <t>ESTR3</t>
-  </si>
-  <si>
-    <t>MRSA5B</t>
   </si>
 </sst>
 </file>
@@ -2555,7 +2546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C407"/>
+  <dimension ref="A1:C406"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2574,10 +2565,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C2">
-        <v>65323100</v>
+        <v>111753600</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2585,10 +2576,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C3">
-        <v>57266800</v>
+        <v>65752700</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2596,10 +2587,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C4">
-        <v>46935100</v>
+        <v>57331500</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2607,10 +2598,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C5">
-        <v>46094000</v>
+        <v>56058800</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2618,10 +2609,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C6">
-        <v>40969000</v>
+        <v>26837300</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2629,10 +2620,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C7">
-        <v>37812200</v>
+        <v>26722600</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2640,10 +2631,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C8">
-        <v>35635500</v>
+        <v>26349700</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2651,10 +2642,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C9">
-        <v>28362200</v>
+        <v>26315900</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2662,10 +2653,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C10">
-        <v>28170600</v>
+        <v>25618200</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2673,10 +2664,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C11">
-        <v>27525100</v>
+        <v>24249700</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2684,10 +2675,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C12">
-        <v>27424500</v>
+        <v>23172400</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2695,10 +2686,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C13">
-        <v>24230800</v>
+        <v>22614000</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2706,120 +2697,120 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C14">
-        <v>22129400</v>
+        <v>21338500</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C15">
-        <v>19003500</v>
+        <v>20096100</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C16">
-        <v>17300200</v>
+        <v>19903500</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C17">
-        <v>17242200</v>
+        <v>17336900</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C18">
-        <v>17226900</v>
+        <v>16902200</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C19">
-        <v>16814400</v>
+        <v>16597800</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C20">
-        <v>16628200</v>
+        <v>16395400</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C21">
-        <v>16423100</v>
+        <v>16381600</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C22">
-        <v>16036900</v>
+        <v>16095900</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C23">
-        <v>15566500</v>
+        <v>14522900</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C24">
-        <v>15531100</v>
+        <v>14425100</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2827,10 +2818,10 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C25">
-        <v>14792900</v>
+        <v>13245000</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2838,10 +2829,10 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C26">
-        <v>14529200</v>
+        <v>12511200</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2849,10 +2840,10 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C27">
-        <v>14188700</v>
+        <v>11870700</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2860,10 +2851,10 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C28">
-        <v>13846300</v>
+        <v>11578600</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2871,10 +2862,10 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C29">
-        <v>13520200</v>
+        <v>11134800</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2882,10 +2873,10 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C30">
-        <v>13017900</v>
+        <v>11111400</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2893,10 +2884,10 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C31">
-        <v>12951000</v>
+        <v>10802500</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2904,10 +2895,10 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C32">
-        <v>12342000</v>
+        <v>10678300</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2915,10 +2906,10 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C33">
-        <v>12055900</v>
+        <v>10075900</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2926,10 +2917,10 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C34">
-        <v>11854100</v>
+        <v>9855200</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2937,10 +2928,10 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C35">
-        <v>11681600</v>
+        <v>9256400</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2948,10 +2939,10 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C36">
-        <v>10906700</v>
+        <v>9102900</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2959,10 +2950,10 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C37">
-        <v>10450200</v>
+        <v>9063700</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2970,10 +2961,10 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C38">
-        <v>10289700</v>
+        <v>8647600</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2981,76 +2972,76 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C39">
-        <v>10223600</v>
+        <v>8357300</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C40">
-        <v>9894400</v>
+        <v>7870500</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C41">
-        <v>9590200</v>
+        <v>7761300</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C42">
-        <v>9389600</v>
+        <v>7675800</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C43">
-        <v>9275100</v>
+        <v>7347200</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C44">
-        <v>9079600</v>
+        <v>7065100</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C45">
-        <v>9047700</v>
+        <v>6993800</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -3058,10 +3049,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C46">
-        <v>8789800</v>
+        <v>6977400</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -3069,10 +3060,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C47">
-        <v>8776900</v>
+        <v>6838400</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -3080,10 +3071,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C48">
-        <v>7983300</v>
+        <v>6824800</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -3091,10 +3082,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C49">
-        <v>7901500</v>
+        <v>6538800</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -3102,10 +3093,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C50">
-        <v>7855200</v>
+        <v>6493600</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -3113,10 +3104,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C51">
-        <v>7709800</v>
+        <v>6333100</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -3124,10 +3115,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C52">
-        <v>7512500</v>
+        <v>6115400</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -3135,10 +3126,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C53">
-        <v>7494800</v>
+        <v>6084100</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -3146,10 +3137,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C54">
-        <v>7185500</v>
+        <v>6002400</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -3157,10 +3148,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C55">
-        <v>7086800</v>
+        <v>5843600</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -3168,10 +3159,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C56">
-        <v>6872000</v>
+        <v>5800700</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -3179,10 +3170,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C57">
-        <v>6722700</v>
+        <v>5667200</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -3190,10 +3181,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C58">
-        <v>6674900</v>
+        <v>5458800</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -3201,230 +3192,230 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C59">
-        <v>6658900</v>
+        <v>5338100</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C60">
-        <v>6381400</v>
+        <v>5307200</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C61">
-        <v>6319300</v>
+        <v>5175800</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C62">
-        <v>6029100</v>
+        <v>5165000</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C63">
-        <v>5672700</v>
+        <v>5062300</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C64">
-        <v>5390600</v>
+        <v>4975800</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C65">
-        <v>5358300</v>
+        <v>4749500</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C66">
-        <v>5272400</v>
+        <v>4717400</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C67">
-        <v>5227400</v>
+        <v>4611400</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C68">
-        <v>5216100</v>
+        <v>4574800</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C69">
-        <v>5086700</v>
+        <v>4557600</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C70">
-        <v>5083800</v>
+        <v>4486900</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C71">
-        <v>5012700</v>
+        <v>4380300</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C72">
-        <v>4975400</v>
+        <v>4349200</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C73">
-        <v>4927800</v>
+        <v>4088000</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C74">
-        <v>4669200</v>
+        <v>4087500</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C75">
-        <v>4508600</v>
+        <v>3996100</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C76">
-        <v>4486600</v>
+        <v>3817900</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C77">
-        <v>4418200</v>
+        <v>3815100</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C78">
-        <v>4313300</v>
+        <v>3744400</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C79">
-        <v>4300500</v>
+        <v>3720200</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -3432,10 +3423,10 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C80">
-        <v>4186600</v>
+        <v>3707900</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -3443,10 +3434,10 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C81">
-        <v>4102600</v>
+        <v>3672500</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -3454,10 +3445,10 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C82">
-        <v>4056700</v>
+        <v>3543500</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -3465,571 +3456,571 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C83">
-        <v>4056000</v>
+        <v>3515200</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C84">
-        <v>4055300</v>
+        <v>3375400</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C85">
-        <v>4019900</v>
+        <v>3276800</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C86">
-        <v>3994100</v>
+        <v>3233400</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C87">
-        <v>3752600</v>
+        <v>3187700</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C88">
-        <v>3714300</v>
+        <v>3135100</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C89">
-        <v>3495400</v>
+        <v>3057600</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C90">
-        <v>3282800</v>
+        <v>2882700</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C91">
-        <v>3179500</v>
+        <v>2834400</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C92">
-        <v>3178300</v>
+        <v>2790100</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C93">
-        <v>3159800</v>
+        <v>2766100</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C94">
-        <v>3128800</v>
+        <v>2680700</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C95">
-        <v>3066700</v>
+        <v>2634600</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C96">
-        <v>2925000</v>
+        <v>2574400</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C97">
-        <v>2769800</v>
+        <v>2559200</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C98">
-        <v>2769600</v>
+        <v>2484300</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C99">
-        <v>2753100</v>
+        <v>2321300</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C100">
-        <v>2740500</v>
+        <v>2305500</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C101">
-        <v>2739500</v>
+        <v>2245100</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C102">
-        <v>2702900</v>
+        <v>2194500</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C103">
-        <v>2624400</v>
+        <v>2159400</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C104">
-        <v>2451300</v>
+        <v>2125300</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C105">
-        <v>2374000</v>
+        <v>2090700</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C106">
-        <v>2297200</v>
+        <v>2086800</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C107">
-        <v>2167800</v>
+        <v>2002600</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C108">
-        <v>2073600</v>
+        <v>1993800</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C109">
-        <v>2017800</v>
+        <v>1954700</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C110">
-        <v>1984900</v>
+        <v>1920200</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C111">
-        <v>1966200</v>
+        <v>1898100</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C112">
-        <v>1955700</v>
+        <v>1862900</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C113">
-        <v>1929900</v>
+        <v>1800700</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C114">
-        <v>1817100</v>
+        <v>1795600</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C115">
-        <v>1796000</v>
+        <v>1788600</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C116">
-        <v>1717900</v>
+        <v>1739500</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C117">
-        <v>1600700</v>
+        <v>1716200</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C118">
-        <v>1576300</v>
+        <v>1673800</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C119">
-        <v>1546700</v>
+        <v>1669200</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="B120" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C120">
-        <v>1540600</v>
+        <v>1520100</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="B121" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C121">
-        <v>1502100</v>
+        <v>1512900</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C122">
-        <v>1491200</v>
+        <v>1511000</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C123">
-        <v>1486500</v>
+        <v>1497500</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C124">
-        <v>1455000</v>
+        <v>1485800</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C125">
-        <v>1429400</v>
+        <v>1484300</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C126">
-        <v>1413000</v>
+        <v>1439500</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C127">
-        <v>1397000</v>
+        <v>1414500</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C128">
-        <v>1393300</v>
+        <v>1407700</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C129">
-        <v>1368700</v>
+        <v>1401300</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C130">
-        <v>1336600</v>
+        <v>1348400</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C131">
-        <v>1326800</v>
+        <v>1336200</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C132">
-        <v>1288300</v>
+        <v>1288600</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C133">
-        <v>1257700</v>
+        <v>1198900</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B134" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C134">
-        <v>1209200</v>
+        <v>1195500</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -4037,10 +4028,10 @@
         <v>130</v>
       </c>
       <c r="B135" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C135">
-        <v>1208600</v>
+        <v>1168500</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -4048,10 +4039,10 @@
         <v>131</v>
       </c>
       <c r="B136" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C136">
-        <v>1182800</v>
+        <v>1165000</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -4059,10 +4050,10 @@
         <v>132</v>
       </c>
       <c r="B137" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C137">
-        <v>1161900</v>
+        <v>1153000</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -4070,10 +4061,10 @@
         <v>133</v>
       </c>
       <c r="B138" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C138">
-        <v>1140200</v>
+        <v>1096100</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -4081,10 +4072,10 @@
         <v>134</v>
       </c>
       <c r="B139" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C139">
-        <v>1071700</v>
+        <v>1091500</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -4092,153 +4083,153 @@
         <v>135</v>
       </c>
       <c r="B140" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C140">
-        <v>998100</v>
+        <v>1082400</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="B141" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C141">
-        <v>982800</v>
+        <v>1051500</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B142" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C142">
-        <v>977800</v>
+        <v>992000</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="B143" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C143">
-        <v>962200</v>
+        <v>989800</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B144" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C144">
-        <v>914300</v>
+        <v>953600</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B145" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C145">
-        <v>902000</v>
+        <v>898500</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B146" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C146">
-        <v>874400</v>
+        <v>877000</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B147" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C147">
-        <v>870400</v>
+        <v>856000</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B148" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C148">
-        <v>864100</v>
+        <v>843000</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B149" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C149">
-        <v>855800</v>
+        <v>821200</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B150" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C150">
-        <v>823000</v>
+        <v>795700</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B151" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C151">
-        <v>751700</v>
+        <v>742800</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B152" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C152">
-        <v>748000</v>
+        <v>723700</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="B153" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C153">
-        <v>719100</v>
+        <v>688100</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -4246,10 +4237,10 @@
         <v>147</v>
       </c>
       <c r="B154" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C154">
-        <v>718300</v>
+        <v>687900</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -4257,10 +4248,10 @@
         <v>148</v>
       </c>
       <c r="B155" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C155">
-        <v>711200</v>
+        <v>640800</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -4268,10 +4259,10 @@
         <v>149</v>
       </c>
       <c r="B156" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C156">
-        <v>684500</v>
+        <v>622300</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -4279,10 +4270,10 @@
         <v>150</v>
       </c>
       <c r="B157" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C157">
-        <v>669600</v>
+        <v>605100</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -4290,10 +4281,10 @@
         <v>151</v>
       </c>
       <c r="B158" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C158">
-        <v>611400</v>
+        <v>598000</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -4301,10 +4292,10 @@
         <v>152</v>
       </c>
       <c r="B159" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C159">
-        <v>604800</v>
+        <v>590100</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -4312,10 +4303,10 @@
         <v>153</v>
       </c>
       <c r="B160" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C160">
-        <v>590000</v>
+        <v>586100</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -4323,10 +4314,10 @@
         <v>154</v>
       </c>
       <c r="B161" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C161">
-        <v>551600</v>
+        <v>586000</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -4334,10 +4325,10 @@
         <v>155</v>
       </c>
       <c r="B162" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C162">
-        <v>520500</v>
+        <v>513800</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -4345,10 +4336,10 @@
         <v>156</v>
       </c>
       <c r="B163" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C163">
-        <v>512200</v>
+        <v>488400</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -4356,10 +4347,10 @@
         <v>157</v>
       </c>
       <c r="B164" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C164">
-        <v>465700</v>
+        <v>487800</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -4367,10 +4358,10 @@
         <v>158</v>
       </c>
       <c r="B165" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C165">
-        <v>433800</v>
+        <v>480100</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -4378,10 +4369,10 @@
         <v>159</v>
       </c>
       <c r="B166" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C166">
-        <v>409000</v>
+        <v>464400</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -4389,10 +4380,10 @@
         <v>160</v>
       </c>
       <c r="B167" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C167">
-        <v>402400</v>
+        <v>430600</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -4400,10 +4391,10 @@
         <v>161</v>
       </c>
       <c r="B168" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C168">
-        <v>399600</v>
+        <v>430000</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -4411,164 +4402,164 @@
         <v>162</v>
       </c>
       <c r="B169" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C169">
-        <v>397400</v>
+        <v>424900</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="B170" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C170">
-        <v>376900</v>
+        <v>419600</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B171" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C171">
-        <v>368000</v>
+        <v>408300</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B172" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C172">
-        <v>364000</v>
+        <v>404800</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B173" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C173">
-        <v>359500</v>
+        <v>396300</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B174" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C174">
-        <v>357500</v>
+        <v>393800</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B175" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C175">
-        <v>356200</v>
+        <v>393500</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B176" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C176">
-        <v>355900</v>
+        <v>393100</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B177" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C177">
-        <v>340100</v>
+        <v>391400</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B178" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C178">
-        <v>339900</v>
+        <v>370800</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B179" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C179">
-        <v>338300</v>
+        <v>344900</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B180" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C180">
-        <v>316400</v>
+        <v>339700</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C181">
-        <v>316100</v>
+        <v>328200</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B182" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C182">
-        <v>316100</v>
+        <v>318800</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="B183" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C183">
-        <v>312000</v>
+        <v>315200</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -4576,10 +4567,10 @@
         <v>175</v>
       </c>
       <c r="B184" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C184">
-        <v>310700</v>
+        <v>307500</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -4587,10 +4578,10 @@
         <v>176</v>
       </c>
       <c r="B185" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C185">
-        <v>310500</v>
+        <v>301800</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -4598,76 +4589,76 @@
         <v>177</v>
       </c>
       <c r="B186" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C186">
-        <v>308900</v>
+        <v>294800</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="B187" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C187">
-        <v>292800</v>
+        <v>293200</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B188" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C188">
-        <v>289700</v>
+        <v>292800</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B189" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C189">
-        <v>280900</v>
+        <v>282100</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B190" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C190">
-        <v>259000</v>
+        <v>274500</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B191" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C191">
-        <v>251900</v>
+        <v>270600</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>182</v>
+        <v>35</v>
       </c>
       <c r="B192" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C192">
-        <v>242200</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -4675,230 +4666,230 @@
         <v>183</v>
       </c>
       <c r="B193" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C193">
-        <v>236000</v>
+        <v>267100</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="B194" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C194">
-        <v>233900</v>
+        <v>256200</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B195" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C195">
-        <v>221800</v>
+        <v>249900</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B196" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C196">
-        <v>217000</v>
+        <v>246600</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B197" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C197">
-        <v>216300</v>
+        <v>229600</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B198" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C198">
-        <v>212400</v>
+        <v>228100</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B199" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C199">
-        <v>211400</v>
+        <v>222400</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B200" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C200">
-        <v>206400</v>
+        <v>219500</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B201" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C201">
-        <v>201300</v>
+        <v>212100</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B202" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C202">
-        <v>196400</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B203" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C203">
-        <v>195300</v>
+        <v>202900</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B204" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C204">
-        <v>194600</v>
+        <v>193700</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B205" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C205">
-        <v>192100</v>
+        <v>182500</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B206" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C206">
-        <v>191800</v>
+        <v>182200</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B207" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C207">
-        <v>186600</v>
+        <v>175100</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B208" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C208">
-        <v>178500</v>
+        <v>166800</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B209" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C209">
-        <v>169600</v>
+        <v>165700</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B210" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C210">
-        <v>166800</v>
+        <v>162400</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>199</v>
+        <v>36</v>
       </c>
       <c r="B211" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C211">
-        <v>165700</v>
+        <v>149500</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="B212" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C212">
-        <v>158200</v>
+        <v>145400</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>200</v>
+        <v>139</v>
       </c>
       <c r="B213" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C213">
-        <v>155100</v>
+        <v>128400</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -4906,65 +4897,65 @@
         <v>201</v>
       </c>
       <c r="B214" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C214">
-        <v>146300</v>
+        <v>128300</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="B215" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C215">
-        <v>143600</v>
+        <v>124200</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>8</v>
+        <v>202</v>
       </c>
       <c r="B216" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C216">
-        <v>139700</v>
+        <v>123400</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="B217" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C217">
-        <v>122900</v>
+        <v>114100</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B218" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C218">
-        <v>120000</v>
+        <v>112400</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>204</v>
+        <v>134</v>
       </c>
       <c r="B219" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C219">
-        <v>119200</v>
+        <v>102400</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -4972,252 +4963,252 @@
         <v>205</v>
       </c>
       <c r="B220" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C220">
-        <v>105100</v>
+        <v>96800</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="B221" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C221">
-        <v>104600</v>
+        <v>96800</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B222" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C222">
-        <v>94000</v>
+        <v>94300</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B223" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C223">
-        <v>92500</v>
+        <v>87500</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B224" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C224">
-        <v>81200</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="B225" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C225">
-        <v>78300</v>
+        <v>81500</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B226" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C226">
-        <v>76500</v>
+        <v>79000</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>63</v>
+        <v>210</v>
       </c>
       <c r="B227" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C227">
-        <v>74700</v>
+        <v>76100</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>212</v>
+        <v>79</v>
       </c>
       <c r="B228" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C228">
-        <v>72500</v>
+        <v>69200</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>63</v>
+        <v>211</v>
       </c>
       <c r="B229" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C229">
-        <v>70100</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>28</v>
+        <v>212</v>
       </c>
       <c r="B230" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C230">
-        <v>66500</v>
+        <v>68700</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B231" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C231">
-        <v>59000</v>
+        <v>66800</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>214</v>
+        <v>134</v>
       </c>
       <c r="B232" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C232">
-        <v>58400</v>
+        <v>61300</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>215</v>
+        <v>91</v>
       </c>
       <c r="B233" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C233">
-        <v>52400</v>
+        <v>61200</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
       <c r="B234" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C234">
-        <v>49600</v>
+        <v>56500</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B235" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C235">
-        <v>48900</v>
+        <v>55100</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="B236" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C236">
-        <v>47700</v>
+        <v>52100</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B237" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C237">
-        <v>45200</v>
+        <v>50700</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>36</v>
+        <v>217</v>
       </c>
       <c r="B238" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C238">
-        <v>44400</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="B239" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C239">
-        <v>42500</v>
+        <v>45100</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B240" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C240">
-        <v>42200</v>
+        <v>43600</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B241" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C241">
-        <v>42100</v>
+        <v>41900</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="B242" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C242">
-        <v>35400</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -5225,10 +5216,10 @@
         <v>221</v>
       </c>
       <c r="B243" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C243">
-        <v>34900</v>
+        <v>36100</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -5236,21 +5227,21 @@
         <v>222</v>
       </c>
       <c r="B244" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C244">
-        <v>34300</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>7</v>
+        <v>218</v>
       </c>
       <c r="B245" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C245">
-        <v>31300</v>
+        <v>33300</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -5258,10 +5249,10 @@
         <v>223</v>
       </c>
       <c r="B246" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C246">
-        <v>30300</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -5269,109 +5260,109 @@
         <v>224</v>
       </c>
       <c r="B247" t="s">
-        <v>224</v>
+        <v>568</v>
       </c>
       <c r="C247">
-        <v>29400</v>
+        <v>32400</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="B248" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C248">
-        <v>28700</v>
+        <v>31300</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="B249" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C249">
-        <v>28700</v>
+        <v>31100</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="B250" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C250">
-        <v>28700</v>
+        <v>26300</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B251" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C251">
-        <v>26200</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B252" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C252">
-        <v>26200</v>
+        <v>23700</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B253" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C253">
-        <v>25500</v>
+        <v>21800</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B254" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C254">
-        <v>24300</v>
+        <v>21300</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B255" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C255">
-        <v>23200</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>231</v>
+        <v>144</v>
       </c>
       <c r="B256" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C256">
-        <v>21600</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -5379,381 +5370,381 @@
         <v>232</v>
       </c>
       <c r="B257" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C257">
-        <v>20600</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="B258" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C258">
-        <v>19600</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B259" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C259">
-        <v>15900</v>
+        <v>16300</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>235</v>
+        <v>28</v>
       </c>
       <c r="B260" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C260">
-        <v>15400</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>236</v>
+        <v>39</v>
       </c>
       <c r="B261" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C261">
-        <v>15100</v>
+        <v>14600</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>173</v>
+        <v>234</v>
       </c>
       <c r="B262" t="s">
-        <v>584</v>
+        <v>234</v>
       </c>
       <c r="C262">
-        <v>15100</v>
+        <v>14200</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B263" t="s">
-        <v>585</v>
+        <v>235</v>
       </c>
       <c r="C263">
-        <v>15100</v>
+        <v>13700</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>238</v>
+        <v>144</v>
       </c>
       <c r="B264" t="s">
-        <v>238</v>
+        <v>583</v>
       </c>
       <c r="C264">
-        <v>15000</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B265" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C265">
-        <v>14300</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B266" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C266">
-        <v>14000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="B267" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C267">
-        <v>13800</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B268" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C268">
-        <v>13300</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="B269" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C269">
-        <v>13300</v>
+        <v>12800</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="B270" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C270">
-        <v>13200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B271" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C271">
-        <v>12600</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>243</v>
+        <v>94</v>
       </c>
       <c r="B272" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C272">
-        <v>11800</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>244</v>
+        <v>83</v>
       </c>
       <c r="B273" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C273">
-        <v>11200</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="B274" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C274">
-        <v>9800</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B275" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C275">
-        <v>8900</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B276" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C276">
-        <v>8800</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B277" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C277">
-        <v>8100</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B278" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C278">
-        <v>7500</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>248</v>
+        <v>51</v>
       </c>
       <c r="B279" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C279">
-        <v>7500</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="B280" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C280">
-        <v>7400</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B281" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C281">
-        <v>6900</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>98</v>
+        <v>248</v>
       </c>
       <c r="B282" t="s">
-        <v>603</v>
+        <v>248</v>
       </c>
       <c r="C282">
-        <v>6700</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B283" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C283">
-        <v>6500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B284" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C284">
-        <v>5900</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>236</v>
+        <v>51</v>
       </c>
       <c r="B285" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C285">
-        <v>5800</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="B286" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C286">
-        <v>5500</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B287" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C287">
-        <v>5400</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>46</v>
+        <v>253</v>
       </c>
       <c r="B288" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C288">
-        <v>4900</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B289" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C289">
-        <v>4200</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B290" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C290">
-        <v>4100</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="B291" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C291">
         <v>4000</v>
@@ -5761,10 +5752,10 @@
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B292" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C292">
         <v>3900</v>
@@ -5772,35 +5763,35 @@
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="B293" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C293">
-        <v>3800</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>143</v>
+        <v>256</v>
       </c>
       <c r="B294" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C294">
-        <v>3800</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="B295" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C295">
-        <v>3100</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -5808,10 +5799,10 @@
         <v>257</v>
       </c>
       <c r="B296" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C296">
-        <v>2900</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -5819,161 +5810,161 @@
         <v>258</v>
       </c>
       <c r="B297" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C297">
-        <v>2800</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B298" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C298">
-        <v>2800</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>259</v>
+        <v>125</v>
       </c>
       <c r="B299" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C299">
-        <v>2700</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B300" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C300">
-        <v>2700</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B301" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C301">
-        <v>2500</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B302" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C302">
-        <v>2300</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="B303" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C303">
-        <v>2200</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B304" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C304">
-        <v>2200</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B305" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C305">
-        <v>2200</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>181</v>
+        <v>262</v>
       </c>
       <c r="B306" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C306">
-        <v>2200</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>264</v>
+        <v>210</v>
       </c>
       <c r="B307" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C307">
-        <v>2000</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B308" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C308">
-        <v>1800</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="B309" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C309">
-        <v>1800</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B310" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C310">
-        <v>1800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>142</v>
+        <v>266</v>
       </c>
       <c r="B311" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C311">
         <v>1700</v>
@@ -5981,263 +5972,263 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>267</v>
+        <v>132</v>
       </c>
       <c r="B312" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C312">
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B313" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C313">
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B314" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C314">
-        <v>1700</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B315" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C315">
-        <v>1600</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B316" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C316">
-        <v>1500</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B317" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C317">
-        <v>1300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>273</v>
+        <v>189</v>
       </c>
       <c r="B318" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C318">
-        <v>1300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B319" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C319">
-        <v>1300</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B320" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C320">
-        <v>1300</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B321" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C321">
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B322" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C322">
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="B323" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C323">
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B324" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C324">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B325" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C325">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B326" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C326">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B327" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C327">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="B328" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C328">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B329" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C329">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>282</v>
+        <v>117</v>
       </c>
       <c r="B330" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C330">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>202</v>
+        <v>280</v>
       </c>
       <c r="B331" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C331">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B332" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C332">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B333" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C333">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>70</v>
+        <v>266</v>
       </c>
       <c r="B334" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C334">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>285</v>
+        <v>145</v>
       </c>
       <c r="B335" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C335">
         <v>400</v>
@@ -6245,10 +6236,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B336" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C336">
         <v>400</v>
@@ -6256,21 +6247,21 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B337" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C337">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B338" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C338">
         <v>300</v>
@@ -6278,10 +6269,10 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="B339" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C339">
         <v>300</v>
@@ -6289,10 +6280,10 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B340" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C340">
         <v>300</v>
@@ -6300,21 +6291,21 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B341" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C341">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B342" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C342">
         <v>200</v>
@@ -6322,10 +6313,10 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B343" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C343">
         <v>200</v>
@@ -6333,10 +6324,10 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B344" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C344">
         <v>200</v>
@@ -6344,10 +6335,10 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="B345" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C345">
         <v>200</v>
@@ -6355,10 +6346,10 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B346" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C346">
         <v>200</v>
@@ -6366,10 +6357,10 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="B347" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C347">
         <v>200</v>
@@ -6377,10 +6368,10 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>294</v>
+        <v>33</v>
       </c>
       <c r="B348" t="s">
-        <v>294</v>
+        <v>666</v>
       </c>
       <c r="C348">
         <v>200</v>
@@ -6388,10 +6379,10 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B349" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C349">
         <v>200</v>
@@ -6399,32 +6390,32 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B350" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C350">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="B351" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C351">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B352" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C352">
         <v>100</v>
@@ -6432,10 +6423,10 @@
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="B353" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C353">
         <v>100</v>
@@ -6443,175 +6434,175 @@
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
-        <v>298</v>
+        <v>243</v>
       </c>
       <c r="B354" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C354">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
       <c r="B355" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C355">
-        <v>15700</v>
+        <v>100</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B356" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C356">
-        <v>2200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B357" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C357">
-        <v>700</v>
+        <v>100</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="B358" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C358">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="B359" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C359">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B360" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C360">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>301</v>
+        <v>36</v>
       </c>
       <c r="B361" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C361">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B362" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C362">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="B363" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C363">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B364" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C364">
-        <v>200</v>
+        <v>88</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="B365" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C365">
-        <v>200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="B366" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C366">
-        <v>200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B367" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C367">
-        <v>100</v>
+        <v>700</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B368" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C368">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>176</v>
+        <v>303</v>
       </c>
       <c r="B369" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C369">
         <v>100</v>
@@ -6619,10 +6610,10 @@
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B370" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C370">
         <v>100</v>
@@ -6630,76 +6621,76 @@
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B371" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C371">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B372" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C372">
-        <v>900</v>
+        <v>100</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>242</v>
+        <v>305</v>
       </c>
       <c r="B373" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C373">
-        <v>900</v>
+        <v>100</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="B374" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C374">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="B375" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C375">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>204</v>
+        <v>306</v>
       </c>
       <c r="B376" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C376">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B377" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C377">
         <v>100</v>
@@ -6707,10 +6698,10 @@
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>98</v>
+        <v>299</v>
       </c>
       <c r="B378" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C378">
         <v>100</v>
@@ -6718,10 +6709,10 @@
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B379" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C379">
         <v>100</v>
@@ -6729,43 +6720,43 @@
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B380" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C380">
-        <v>500</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B381" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C381">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>143</v>
+        <v>261</v>
       </c>
       <c r="B382" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C382">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B383" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C383">
         <v>100</v>
@@ -6773,10 +6764,10 @@
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B384" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C384">
         <v>100</v>
@@ -6784,109 +6775,109 @@
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="B385" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C385">
-        <v>100</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="B386" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C386">
-        <v>100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B387" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C387">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>317</v>
+        <v>290</v>
       </c>
       <c r="B388" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C388">
-        <v>1400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>244</v>
+        <v>315</v>
       </c>
       <c r="B389" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C389">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="B390" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C390">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="B391" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C391">
-        <v>400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>259</v>
+        <v>91</v>
       </c>
       <c r="B392" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C392">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="B393" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C393">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>319</v>
+        <v>94</v>
       </c>
       <c r="B394" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C394">
         <v>100</v>
@@ -6894,32 +6885,32 @@
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B395" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C395">
-        <v>3000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="B396" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C396">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B397" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C397">
         <v>500</v>
@@ -6927,10 +6918,10 @@
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B398" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C398">
         <v>100</v>
@@ -6938,10 +6929,10 @@
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="B399" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C399">
         <v>100</v>
@@ -6949,10 +6940,10 @@
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="B400" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C400">
         <v>100</v>
@@ -6960,54 +6951,54 @@
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="B401" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C401">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c r="B402" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C402">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B403" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C403">
-        <v>100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="B404" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C404">
-        <v>5513000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B405" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C405">
         <v>100</v>
@@ -7015,24 +7006,13 @@
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B406" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C406">
         <v>100</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3">
-      <c r="A407" t="s">
-        <v>291</v>
-      </c>
-      <c r="B407" t="s">
-        <v>727</v>
-      </c>
-      <c r="C407">
-        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/Bases/Lista de ações.xlsx
+++ b/Bases/Lista de ações.xlsx
@@ -319,15 +319,15 @@
     <t>Sanepar</t>
   </si>
   <si>
+    <t>Banco Santander</t>
+  </si>
+  <si>
+    <t>Randon</t>
+  </si>
+  <si>
     <t>Recrusul</t>
   </si>
   <si>
-    <t>Banco Santander</t>
-  </si>
-  <si>
-    <t>Randon</t>
-  </si>
-  <si>
     <t>Fleury</t>
   </si>
   <si>
@@ -1288,13 +1288,13 @@
     <t>SAPR4</t>
   </si>
   <si>
+    <t>SANB11</t>
+  </si>
+  <si>
+    <t>RAPT4</t>
+  </si>
+  <si>
     <t>RCSL4</t>
-  </si>
-  <si>
-    <t>SANB11</t>
-  </si>
-  <si>
-    <t>RAPT4</t>
   </si>
   <si>
     <t>FLRY3</t>
@@ -2575,7 +2575,7 @@
         <v>282174900</v>
       </c>
       <c r="D2" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2589,7 +2589,7 @@
         <v>65204900</v>
       </c>
       <c r="D3" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2603,7 +2603,7 @@
         <v>64731600</v>
       </c>
       <c r="D4" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2617,7 +2617,7 @@
         <v>37935400</v>
       </c>
       <c r="D5" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2631,7 +2631,7 @@
         <v>37609700</v>
       </c>
       <c r="D6" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2642,10 +2642,10 @@
         <v>329</v>
       </c>
       <c r="C7">
-        <v>35795000</v>
+        <v>35795300</v>
       </c>
       <c r="D7" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2659,7 +2659,7 @@
         <v>35579100</v>
       </c>
       <c r="D8" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2673,7 +2673,7 @@
         <v>31760000</v>
       </c>
       <c r="D9" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2687,7 +2687,7 @@
         <v>29781400</v>
       </c>
       <c r="D10" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2701,7 +2701,7 @@
         <v>26227400</v>
       </c>
       <c r="D11" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2715,7 +2715,7 @@
         <v>26162200</v>
       </c>
       <c r="D12" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2726,10 +2726,10 @@
         <v>335</v>
       </c>
       <c r="C13">
-        <v>24978800</v>
+        <v>24980100</v>
       </c>
       <c r="D13" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2743,7 +2743,7 @@
         <v>24151500</v>
       </c>
       <c r="D14" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2757,7 +2757,7 @@
         <v>19383700</v>
       </c>
       <c r="D15" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2768,10 +2768,10 @@
         <v>338</v>
       </c>
       <c r="C16">
-        <v>19134800</v>
+        <v>19129400</v>
       </c>
       <c r="D16" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2785,7 +2785,7 @@
         <v>17884400</v>
       </c>
       <c r="D17" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2799,7 +2799,7 @@
         <v>17748600</v>
       </c>
       <c r="D18" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2813,7 +2813,7 @@
         <v>16986500</v>
       </c>
       <c r="D19" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2827,7 +2827,7 @@
         <v>15879100</v>
       </c>
       <c r="D20" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2841,7 +2841,7 @@
         <v>15628900</v>
       </c>
       <c r="D21" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2855,7 +2855,7 @@
         <v>14692000</v>
       </c>
       <c r="D22" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2869,7 +2869,7 @@
         <v>13749000</v>
       </c>
       <c r="D23" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2883,7 +2883,7 @@
         <v>13331400</v>
       </c>
       <c r="D24" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2897,7 +2897,7 @@
         <v>12487200</v>
       </c>
       <c r="D25" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2911,7 +2911,7 @@
         <v>12271300</v>
       </c>
       <c r="D26" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2925,7 +2925,7 @@
         <v>12026500</v>
       </c>
       <c r="D27" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2939,7 +2939,7 @@
         <v>11836900</v>
       </c>
       <c r="D28" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2953,7 +2953,7 @@
         <v>11655000</v>
       </c>
       <c r="D29" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2967,7 +2967,7 @@
         <v>11649400</v>
       </c>
       <c r="D30" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2981,7 +2981,7 @@
         <v>11489500</v>
       </c>
       <c r="D31" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2995,7 +2995,7 @@
         <v>11241600</v>
       </c>
       <c r="D32" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -3009,7 +3009,7 @@
         <v>10892500</v>
       </c>
       <c r="D33" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -3020,10 +3020,10 @@
         <v>356</v>
       </c>
       <c r="C34">
-        <v>10867400</v>
+        <v>10867300</v>
       </c>
       <c r="D34" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3037,7 +3037,7 @@
         <v>10623500</v>
       </c>
       <c r="D35" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3051,7 +3051,7 @@
         <v>10483000</v>
       </c>
       <c r="D36" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3065,7 +3065,7 @@
         <v>10397200</v>
       </c>
       <c r="D37" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3079,7 +3079,7 @@
         <v>10363400</v>
       </c>
       <c r="D38" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3090,10 +3090,10 @@
         <v>361</v>
       </c>
       <c r="C39">
-        <v>10241400</v>
+        <v>10241800</v>
       </c>
       <c r="D39" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3107,7 +3107,7 @@
         <v>10032300</v>
       </c>
       <c r="D40" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3121,7 +3121,7 @@
         <v>9985000</v>
       </c>
       <c r="D41" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3132,10 +3132,10 @@
         <v>364</v>
       </c>
       <c r="C42">
-        <v>9898800</v>
+        <v>9900100</v>
       </c>
       <c r="D42" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3149,7 +3149,7 @@
         <v>9629400</v>
       </c>
       <c r="D43" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3160,10 +3160,10 @@
         <v>366</v>
       </c>
       <c r="C44">
-        <v>9537800</v>
+        <v>9538800</v>
       </c>
       <c r="D44" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3177,7 +3177,7 @@
         <v>9144900</v>
       </c>
       <c r="D45" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3188,10 +3188,10 @@
         <v>368</v>
       </c>
       <c r="C46">
-        <v>9077700</v>
+        <v>9070500</v>
       </c>
       <c r="D46" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3205,7 +3205,7 @@
         <v>8816200</v>
       </c>
       <c r="D47" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3219,7 +3219,7 @@
         <v>8768100</v>
       </c>
       <c r="D48" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3230,10 +3230,10 @@
         <v>371</v>
       </c>
       <c r="C49">
-        <v>8555400</v>
+        <v>8556400</v>
       </c>
       <c r="D49" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3247,7 +3247,7 @@
         <v>8418600</v>
       </c>
       <c r="D50" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3261,7 +3261,7 @@
         <v>8327900</v>
       </c>
       <c r="D51" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3275,7 +3275,7 @@
         <v>8269500</v>
       </c>
       <c r="D52" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3289,7 +3289,7 @@
         <v>7971200</v>
       </c>
       <c r="D53" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3303,7 +3303,7 @@
         <v>7962500</v>
       </c>
       <c r="D54" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3317,7 +3317,7 @@
         <v>7926500</v>
       </c>
       <c r="D55" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3331,7 +3331,7 @@
         <v>7878300</v>
       </c>
       <c r="D56" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3342,10 +3342,10 @@
         <v>379</v>
       </c>
       <c r="C57">
-        <v>7618000</v>
+        <v>7620300</v>
       </c>
       <c r="D57" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3359,7 +3359,7 @@
         <v>7437100</v>
       </c>
       <c r="D58" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3370,10 +3370,10 @@
         <v>381</v>
       </c>
       <c r="C59">
-        <v>7158000</v>
+        <v>7129200</v>
       </c>
       <c r="D59" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3387,7 +3387,7 @@
         <v>7115300</v>
       </c>
       <c r="D60" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3401,7 +3401,7 @@
         <v>6961800</v>
       </c>
       <c r="D61" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3415,7 +3415,7 @@
         <v>6715200</v>
       </c>
       <c r="D62" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3429,7 +3429,7 @@
         <v>6563400</v>
       </c>
       <c r="D63" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3443,7 +3443,7 @@
         <v>6212800</v>
       </c>
       <c r="D64" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3457,7 +3457,7 @@
         <v>6092500</v>
       </c>
       <c r="D65" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3471,7 +3471,7 @@
         <v>6043800</v>
       </c>
       <c r="D66" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3485,7 +3485,7 @@
         <v>5957500</v>
       </c>
       <c r="D67" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3499,7 +3499,7 @@
         <v>5928000</v>
       </c>
       <c r="D68" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3513,7 +3513,7 @@
         <v>5707400</v>
       </c>
       <c r="D69" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3527,7 +3527,7 @@
         <v>5601000</v>
       </c>
       <c r="D70" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3538,10 +3538,10 @@
         <v>393</v>
       </c>
       <c r="C71">
-        <v>5484100</v>
+        <v>5485300</v>
       </c>
       <c r="D71" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3555,7 +3555,7 @@
         <v>5424000</v>
       </c>
       <c r="D72" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3569,7 +3569,7 @@
         <v>5128600</v>
       </c>
       <c r="D73" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3583,7 +3583,7 @@
         <v>4929000</v>
       </c>
       <c r="D74" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3597,7 +3597,7 @@
         <v>4899000</v>
       </c>
       <c r="D75" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3608,10 +3608,10 @@
         <v>398</v>
       </c>
       <c r="C76">
-        <v>4671300</v>
+        <v>4671200</v>
       </c>
       <c r="D76" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3625,7 +3625,7 @@
         <v>4611500</v>
       </c>
       <c r="D77" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3639,7 +3639,7 @@
         <v>4551600</v>
       </c>
       <c r="D78" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3653,7 +3653,7 @@
         <v>4547900</v>
       </c>
       <c r="D79" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3667,7 +3667,7 @@
         <v>4513400</v>
       </c>
       <c r="D80" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3681,7 +3681,7 @@
         <v>4379000</v>
       </c>
       <c r="D81" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3692,10 +3692,10 @@
         <v>404</v>
       </c>
       <c r="C82">
-        <v>4202700</v>
+        <v>4202800</v>
       </c>
       <c r="D82" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3709,7 +3709,7 @@
         <v>4195500</v>
       </c>
       <c r="D83" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3723,7 +3723,7 @@
         <v>4070400</v>
       </c>
       <c r="D84" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3737,7 +3737,7 @@
         <v>3959800</v>
       </c>
       <c r="D85" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3751,7 +3751,7 @@
         <v>3739800</v>
       </c>
       <c r="D86" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3765,7 +3765,7 @@
         <v>3705800</v>
       </c>
       <c r="D87" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3779,7 +3779,7 @@
         <v>3641600</v>
       </c>
       <c r="D88" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3793,7 +3793,7 @@
         <v>3588800</v>
       </c>
       <c r="D89" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3807,7 +3807,7 @@
         <v>2971200</v>
       </c>
       <c r="D90" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3821,7 +3821,7 @@
         <v>2840700</v>
       </c>
       <c r="D91" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3835,7 +3835,7 @@
         <v>2827600</v>
       </c>
       <c r="D92" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3849,7 +3849,7 @@
         <v>2826600</v>
       </c>
       <c r="D93" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3863,7 +3863,7 @@
         <v>2763900</v>
       </c>
       <c r="D94" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3877,7 +3877,7 @@
         <v>2718300</v>
       </c>
       <c r="D95" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3888,10 +3888,10 @@
         <v>418</v>
       </c>
       <c r="C96">
-        <v>2652600</v>
+        <v>2652700</v>
       </c>
       <c r="D96" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3905,7 +3905,7 @@
         <v>2650700</v>
       </c>
       <c r="D97" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3919,7 +3919,7 @@
         <v>2614400</v>
       </c>
       <c r="D98" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3933,7 +3933,7 @@
         <v>2449700</v>
       </c>
       <c r="D99" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3947,7 +3947,7 @@
         <v>2445600</v>
       </c>
       <c r="D100" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3961,7 +3961,7 @@
         <v>2411100</v>
       </c>
       <c r="D101" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3972,10 +3972,10 @@
         <v>424</v>
       </c>
       <c r="C102">
-        <v>2328400</v>
+        <v>2324000</v>
       </c>
       <c r="D102" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3986,10 +3986,10 @@
         <v>425</v>
       </c>
       <c r="C103">
-        <v>2324000</v>
+        <v>2302500</v>
       </c>
       <c r="D103" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -4000,10 +4000,10 @@
         <v>426</v>
       </c>
       <c r="C104">
-        <v>2302500</v>
+        <v>2298100</v>
       </c>
       <c r="D104" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -4017,7 +4017,7 @@
         <v>2274200</v>
       </c>
       <c r="D105" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -4031,7 +4031,7 @@
         <v>2271800</v>
       </c>
       <c r="D106" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -4045,7 +4045,7 @@
         <v>2127600</v>
       </c>
       <c r="D107" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -4059,7 +4059,7 @@
         <v>2098300</v>
       </c>
       <c r="D108" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4073,7 +4073,7 @@
         <v>2083300</v>
       </c>
       <c r="D109" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4087,7 +4087,7 @@
         <v>1993800</v>
       </c>
       <c r="D110" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4101,7 +4101,7 @@
         <v>1977400</v>
       </c>
       <c r="D111" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4112,10 +4112,10 @@
         <v>434</v>
       </c>
       <c r="C112">
-        <v>1954100</v>
+        <v>1952200</v>
       </c>
       <c r="D112" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4126,10 +4126,10 @@
         <v>435</v>
       </c>
       <c r="C113">
-        <v>1939300</v>
+        <v>1939600</v>
       </c>
       <c r="D113" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4143,7 +4143,7 @@
         <v>1920800</v>
       </c>
       <c r="D114" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4157,7 +4157,7 @@
         <v>1885400</v>
       </c>
       <c r="D115" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4171,7 +4171,7 @@
         <v>1844800</v>
       </c>
       <c r="D116" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4185,7 +4185,7 @@
         <v>1835800</v>
       </c>
       <c r="D117" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4199,7 +4199,7 @@
         <v>1817500</v>
       </c>
       <c r="D118" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4213,7 +4213,7 @@
         <v>1810900</v>
       </c>
       <c r="D119" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4227,7 +4227,7 @@
         <v>1808000</v>
       </c>
       <c r="D120" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4241,7 +4241,7 @@
         <v>1795400</v>
       </c>
       <c r="D121" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4255,7 +4255,7 @@
         <v>1724300</v>
       </c>
       <c r="D122" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4269,7 +4269,7 @@
         <v>1676200</v>
       </c>
       <c r="D123" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4283,7 +4283,7 @@
         <v>1602700</v>
       </c>
       <c r="D124" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4297,7 +4297,7 @@
         <v>1587900</v>
       </c>
       <c r="D125" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4311,7 +4311,7 @@
         <v>1587600</v>
       </c>
       <c r="D126" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4325,7 +4325,7 @@
         <v>1584800</v>
       </c>
       <c r="D127" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4339,7 +4339,7 @@
         <v>1455600</v>
       </c>
       <c r="D128" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4353,7 +4353,7 @@
         <v>1433300</v>
       </c>
       <c r="D129" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4367,7 +4367,7 @@
         <v>1414800</v>
       </c>
       <c r="D130" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4381,7 +4381,7 @@
         <v>1243000</v>
       </c>
       <c r="D131" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4395,7 +4395,7 @@
         <v>1235700</v>
       </c>
       <c r="D132" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4409,7 +4409,7 @@
         <v>1235000</v>
       </c>
       <c r="D133" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4423,7 +4423,7 @@
         <v>1175600</v>
       </c>
       <c r="D134" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4437,7 +4437,7 @@
         <v>1156800</v>
       </c>
       <c r="D135" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4451,7 +4451,7 @@
         <v>1146000</v>
       </c>
       <c r="D136" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4462,10 +4462,10 @@
         <v>459</v>
       </c>
       <c r="C137">
-        <v>1139200</v>
+        <v>1139300</v>
       </c>
       <c r="D137" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4479,7 +4479,7 @@
         <v>1123700</v>
       </c>
       <c r="D138" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4493,7 +4493,7 @@
         <v>1116100</v>
       </c>
       <c r="D139" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4507,7 +4507,7 @@
         <v>1064800</v>
       </c>
       <c r="D140" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4521,7 +4521,7 @@
         <v>991800</v>
       </c>
       <c r="D141" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4535,7 +4535,7 @@
         <v>988100</v>
       </c>
       <c r="D142" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4549,7 +4549,7 @@
         <v>975300</v>
       </c>
       <c r="D143" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4560,10 +4560,10 @@
         <v>466</v>
       </c>
       <c r="C144">
-        <v>973000</v>
+        <v>974400</v>
       </c>
       <c r="D144" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4577,7 +4577,7 @@
         <v>944700</v>
       </c>
       <c r="D145" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4591,7 +4591,7 @@
         <v>944300</v>
       </c>
       <c r="D146" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4605,7 +4605,7 @@
         <v>894700</v>
       </c>
       <c r="D147" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4619,7 +4619,7 @@
         <v>882000</v>
       </c>
       <c r="D148" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4633,7 +4633,7 @@
         <v>874800</v>
       </c>
       <c r="D149" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4647,7 +4647,7 @@
         <v>853400</v>
       </c>
       <c r="D150" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4661,7 +4661,7 @@
         <v>815900</v>
       </c>
       <c r="D151" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4675,7 +4675,7 @@
         <v>730600</v>
       </c>
       <c r="D152" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4686,10 +4686,10 @@
         <v>475</v>
       </c>
       <c r="C153">
-        <v>726200</v>
+        <v>728300</v>
       </c>
       <c r="D153" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4703,7 +4703,7 @@
         <v>725000</v>
       </c>
       <c r="D154" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4717,7 +4717,7 @@
         <v>683200</v>
       </c>
       <c r="D155" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4731,7 +4731,7 @@
         <v>657200</v>
       </c>
       <c r="D156" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4745,7 +4745,7 @@
         <v>618400</v>
       </c>
       <c r="D157" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4759,7 +4759,7 @@
         <v>602100</v>
       </c>
       <c r="D158" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4773,7 +4773,7 @@
         <v>600200</v>
       </c>
       <c r="D159" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4787,7 +4787,7 @@
         <v>585700</v>
       </c>
       <c r="D160" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4801,7 +4801,7 @@
         <v>553300</v>
       </c>
       <c r="D161" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4812,10 +4812,10 @@
         <v>484</v>
       </c>
       <c r="C162">
-        <v>533300</v>
+        <v>533200</v>
       </c>
       <c r="D162" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4829,7 +4829,7 @@
         <v>512300</v>
       </c>
       <c r="D163" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4843,7 +4843,7 @@
         <v>483800</v>
       </c>
       <c r="D164" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4857,7 +4857,7 @@
         <v>473300</v>
       </c>
       <c r="D165" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4871,7 +4871,7 @@
         <v>472600</v>
       </c>
       <c r="D166" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4885,7 +4885,7 @@
         <v>472500</v>
       </c>
       <c r="D167" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4899,7 +4899,7 @@
         <v>463600</v>
       </c>
       <c r="D168" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4913,7 +4913,7 @@
         <v>456000</v>
       </c>
       <c r="D169" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4927,7 +4927,7 @@
         <v>448200</v>
       </c>
       <c r="D170" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4941,7 +4941,7 @@
         <v>435400</v>
       </c>
       <c r="D171" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4955,7 +4955,7 @@
         <v>429000</v>
       </c>
       <c r="D172" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4969,7 +4969,7 @@
         <v>414100</v>
       </c>
       <c r="D173" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4983,7 +4983,7 @@
         <v>401200</v>
       </c>
       <c r="D174" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4997,7 +4997,7 @@
         <v>399100</v>
       </c>
       <c r="D175" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -5011,7 +5011,7 @@
         <v>384400</v>
       </c>
       <c r="D176" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -5025,7 +5025,7 @@
         <v>370500</v>
       </c>
       <c r="D177" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -5039,7 +5039,7 @@
         <v>369300</v>
       </c>
       <c r="D178" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -5053,7 +5053,7 @@
         <v>366000</v>
       </c>
       <c r="D179" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -5067,7 +5067,7 @@
         <v>355100</v>
       </c>
       <c r="D180" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5081,7 +5081,7 @@
         <v>349900</v>
       </c>
       <c r="D181" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5095,7 +5095,7 @@
         <v>336200</v>
       </c>
       <c r="D182" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5109,7 +5109,7 @@
         <v>328600</v>
       </c>
       <c r="D183" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5123,7 +5123,7 @@
         <v>327500</v>
       </c>
       <c r="D184" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5137,7 +5137,7 @@
         <v>326400</v>
       </c>
       <c r="D185" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5151,7 +5151,7 @@
         <v>324000</v>
       </c>
       <c r="D186" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5165,7 +5165,7 @@
         <v>322700</v>
       </c>
       <c r="D187" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5179,7 +5179,7 @@
         <v>314500</v>
       </c>
       <c r="D188" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5193,7 +5193,7 @@
         <v>304000</v>
       </c>
       <c r="D189" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5207,12 +5207,12 @@
         <v>299800</v>
       </c>
       <c r="D190" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B191" t="s">
         <v>513</v>
@@ -5221,7 +5221,7 @@
         <v>298700</v>
       </c>
       <c r="D191" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5235,7 +5235,7 @@
         <v>284200</v>
       </c>
       <c r="D192" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5249,7 +5249,7 @@
         <v>274700</v>
       </c>
       <c r="D193" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5263,7 +5263,7 @@
         <v>271200</v>
       </c>
       <c r="D194" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5277,7 +5277,7 @@
         <v>270200</v>
       </c>
       <c r="D195" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5291,7 +5291,7 @@
         <v>252400</v>
       </c>
       <c r="D196" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5305,7 +5305,7 @@
         <v>249300</v>
       </c>
       <c r="D197" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5319,7 +5319,7 @@
         <v>246800</v>
       </c>
       <c r="D198" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5333,7 +5333,7 @@
         <v>236600</v>
       </c>
       <c r="D199" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5344,10 +5344,10 @@
         <v>522</v>
       </c>
       <c r="C200">
-        <v>233900</v>
+        <v>234200</v>
       </c>
       <c r="D200" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5361,7 +5361,7 @@
         <v>232500</v>
       </c>
       <c r="D201" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5375,7 +5375,7 @@
         <v>219200</v>
       </c>
       <c r="D202" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5389,7 +5389,7 @@
         <v>206900</v>
       </c>
       <c r="D203" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5403,7 +5403,7 @@
         <v>206900</v>
       </c>
       <c r="D204" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5417,7 +5417,7 @@
         <v>203900</v>
       </c>
       <c r="D205" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5431,7 +5431,7 @@
         <v>202800</v>
       </c>
       <c r="D206" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5445,7 +5445,7 @@
         <v>202300</v>
       </c>
       <c r="D207" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5459,7 +5459,7 @@
         <v>196400</v>
       </c>
       <c r="D208" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5473,7 +5473,7 @@
         <v>194300</v>
       </c>
       <c r="D209" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5487,7 +5487,7 @@
         <v>191400</v>
       </c>
       <c r="D210" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5501,7 +5501,7 @@
         <v>189700</v>
       </c>
       <c r="D211" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5515,7 +5515,7 @@
         <v>188900</v>
       </c>
       <c r="D212" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5529,7 +5529,7 @@
         <v>187000</v>
       </c>
       <c r="D213" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5543,7 +5543,7 @@
         <v>183900</v>
       </c>
       <c r="D214" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5557,7 +5557,7 @@
         <v>176100</v>
       </c>
       <c r="D215" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5571,7 +5571,7 @@
         <v>164700</v>
       </c>
       <c r="D216" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5585,7 +5585,7 @@
         <v>162800</v>
       </c>
       <c r="D217" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5599,7 +5599,7 @@
         <v>133000</v>
       </c>
       <c r="D218" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5613,7 +5613,7 @@
         <v>125400</v>
       </c>
       <c r="D219" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5627,7 +5627,7 @@
         <v>123800</v>
       </c>
       <c r="D220" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5641,12 +5641,12 @@
         <v>111800</v>
       </c>
       <c r="D221" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B222" t="s">
         <v>544</v>
@@ -5655,7 +5655,7 @@
         <v>101200</v>
       </c>
       <c r="D222" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5669,7 +5669,7 @@
         <v>99600</v>
       </c>
       <c r="D223" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5683,7 +5683,7 @@
         <v>98600</v>
       </c>
       <c r="D224" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5697,7 +5697,7 @@
         <v>96200</v>
       </c>
       <c r="D225" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5711,7 +5711,7 @@
         <v>95100</v>
       </c>
       <c r="D226" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5725,7 +5725,7 @@
         <v>93700</v>
       </c>
       <c r="D227" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5739,7 +5739,7 @@
         <v>91800</v>
       </c>
       <c r="D228" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5753,7 +5753,7 @@
         <v>90700</v>
       </c>
       <c r="D229" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5764,10 +5764,10 @@
         <v>552</v>
       </c>
       <c r="C230">
-        <v>83000</v>
+        <v>83500</v>
       </c>
       <c r="D230" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5781,7 +5781,7 @@
         <v>71100</v>
       </c>
       <c r="D231" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5795,7 +5795,7 @@
         <v>69900</v>
       </c>
       <c r="D232" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5809,12 +5809,12 @@
         <v>69300</v>
       </c>
       <c r="D233" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B234" t="s">
         <v>556</v>
@@ -5823,7 +5823,7 @@
         <v>68400</v>
       </c>
       <c r="D234" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5837,7 +5837,7 @@
         <v>66600</v>
       </c>
       <c r="D235" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5851,7 +5851,7 @@
         <v>66600</v>
       </c>
       <c r="D236" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5865,7 +5865,7 @@
         <v>63400</v>
       </c>
       <c r="D237" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5879,7 +5879,7 @@
         <v>63200</v>
       </c>
       <c r="D238" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5893,7 +5893,7 @@
         <v>59800</v>
       </c>
       <c r="D239" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5907,7 +5907,7 @@
         <v>54600</v>
       </c>
       <c r="D240" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5921,7 +5921,7 @@
         <v>52800</v>
       </c>
       <c r="D241" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5932,10 +5932,10 @@
         <v>564</v>
       </c>
       <c r="C242">
-        <v>48000</v>
+        <v>48100</v>
       </c>
       <c r="D242" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5949,7 +5949,7 @@
         <v>46200</v>
       </c>
       <c r="D243" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5963,7 +5963,7 @@
         <v>45600</v>
       </c>
       <c r="D244" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5977,7 +5977,7 @@
         <v>45100</v>
       </c>
       <c r="D245" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5991,7 +5991,7 @@
         <v>39000</v>
       </c>
       <c r="D246" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -6005,7 +6005,7 @@
         <v>37600</v>
       </c>
       <c r="D247" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -6019,7 +6019,7 @@
         <v>36300</v>
       </c>
       <c r="D248" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -6033,7 +6033,7 @@
         <v>35600</v>
       </c>
       <c r="D249" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -6047,7 +6047,7 @@
         <v>33900</v>
       </c>
       <c r="D250" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -6061,7 +6061,7 @@
         <v>32800</v>
       </c>
       <c r="D251" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -6075,7 +6075,7 @@
         <v>32800</v>
       </c>
       <c r="D252" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -6089,7 +6089,7 @@
         <v>31800</v>
       </c>
       <c r="D253" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -6103,7 +6103,7 @@
         <v>27800</v>
       </c>
       <c r="D254" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -6117,7 +6117,7 @@
         <v>27500</v>
       </c>
       <c r="D255" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -6131,7 +6131,7 @@
         <v>25300</v>
       </c>
       <c r="D256" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -6145,7 +6145,7 @@
         <v>23100</v>
       </c>
       <c r="D257" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -6159,7 +6159,7 @@
         <v>20200</v>
       </c>
       <c r="D258" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -6173,7 +6173,7 @@
         <v>20100</v>
       </c>
       <c r="D259" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -6187,7 +6187,7 @@
         <v>19800</v>
       </c>
       <c r="D260" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -6201,7 +6201,7 @@
         <v>17300</v>
       </c>
       <c r="D261" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -6215,7 +6215,7 @@
         <v>17200</v>
       </c>
       <c r="D262" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -6229,7 +6229,7 @@
         <v>17000</v>
       </c>
       <c r="D263" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -6243,7 +6243,7 @@
         <v>16900</v>
       </c>
       <c r="D264" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -6257,7 +6257,7 @@
         <v>16400</v>
       </c>
       <c r="D265" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -6271,7 +6271,7 @@
         <v>15800</v>
       </c>
       <c r="D266" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -6285,7 +6285,7 @@
         <v>15000</v>
       </c>
       <c r="D267" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -6299,7 +6299,7 @@
         <v>14100</v>
       </c>
       <c r="D268" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -6313,7 +6313,7 @@
         <v>13900</v>
       </c>
       <c r="D269" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -6327,7 +6327,7 @@
         <v>13400</v>
       </c>
       <c r="D270" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -6341,7 +6341,7 @@
         <v>12800</v>
       </c>
       <c r="D271" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -6352,10 +6352,10 @@
         <v>594</v>
       </c>
       <c r="C272">
-        <v>12100</v>
+        <v>12200</v>
       </c>
       <c r="D272" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -6369,7 +6369,7 @@
         <v>12000</v>
       </c>
       <c r="D273" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -6383,7 +6383,7 @@
         <v>11800</v>
       </c>
       <c r="D274" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -6397,12 +6397,12 @@
         <v>11700</v>
       </c>
       <c r="D275" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B276" t="s">
         <v>598</v>
@@ -6411,7 +6411,7 @@
         <v>11000</v>
       </c>
       <c r="D276" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -6425,7 +6425,7 @@
         <v>10800</v>
       </c>
       <c r="D277" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -6439,7 +6439,7 @@
         <v>10300</v>
       </c>
       <c r="D278" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -6453,7 +6453,7 @@
         <v>10200</v>
       </c>
       <c r="D279" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -6467,7 +6467,7 @@
         <v>10000</v>
       </c>
       <c r="D280" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -6481,7 +6481,7 @@
         <v>9900</v>
       </c>
       <c r="D281" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -6495,7 +6495,7 @@
         <v>9200</v>
       </c>
       <c r="D282" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -6509,7 +6509,7 @@
         <v>9200</v>
       </c>
       <c r="D283" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -6523,7 +6523,7 @@
         <v>7600</v>
       </c>
       <c r="D284" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -6537,7 +6537,7 @@
         <v>7400</v>
       </c>
       <c r="D285" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -6551,7 +6551,7 @@
         <v>6600</v>
       </c>
       <c r="D286" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -6565,7 +6565,7 @@
         <v>6400</v>
       </c>
       <c r="D287" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -6579,7 +6579,7 @@
         <v>6100</v>
       </c>
       <c r="D288" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -6593,7 +6593,7 @@
         <v>5200</v>
       </c>
       <c r="D289" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -6607,7 +6607,7 @@
         <v>5100</v>
       </c>
       <c r="D290" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -6621,7 +6621,7 @@
         <v>4900</v>
       </c>
       <c r="D291" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -6635,7 +6635,7 @@
         <v>4800</v>
       </c>
       <c r="D292" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -6649,7 +6649,7 @@
         <v>4800</v>
       </c>
       <c r="D293" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -6663,7 +6663,7 @@
         <v>4700</v>
       </c>
       <c r="D294" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -6677,7 +6677,7 @@
         <v>4400</v>
       </c>
       <c r="D295" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -6691,7 +6691,7 @@
         <v>4400</v>
       </c>
       <c r="D296" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -6705,7 +6705,7 @@
         <v>4300</v>
       </c>
       <c r="D297" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -6719,7 +6719,7 @@
         <v>3800</v>
       </c>
       <c r="D298" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -6733,7 +6733,7 @@
         <v>3800</v>
       </c>
       <c r="D299" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -6747,7 +6747,7 @@
         <v>3800</v>
       </c>
       <c r="D300" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -6761,7 +6761,7 @@
         <v>3500</v>
       </c>
       <c r="D301" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -6775,7 +6775,7 @@
         <v>3300</v>
       </c>
       <c r="D302" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -6789,7 +6789,7 @@
         <v>2800</v>
       </c>
       <c r="D303" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -6803,7 +6803,7 @@
         <v>2700</v>
       </c>
       <c r="D304" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -6817,7 +6817,7 @@
         <v>2400</v>
       </c>
       <c r="D305" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -6831,7 +6831,7 @@
         <v>2300</v>
       </c>
       <c r="D306" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -6845,7 +6845,7 @@
         <v>2000</v>
       </c>
       <c r="D307" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -6859,7 +6859,7 @@
         <v>2000</v>
       </c>
       <c r="D308" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -6873,7 +6873,7 @@
         <v>1900</v>
       </c>
       <c r="D309" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -6887,7 +6887,7 @@
         <v>1900</v>
       </c>
       <c r="D310" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -6901,7 +6901,7 @@
         <v>1700</v>
       </c>
       <c r="D311" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -6915,7 +6915,7 @@
         <v>1700</v>
       </c>
       <c r="D312" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -6929,7 +6929,7 @@
         <v>1700</v>
       </c>
       <c r="D313" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -6943,7 +6943,7 @@
         <v>1700</v>
       </c>
       <c r="D314" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6957,7 +6957,7 @@
         <v>1600</v>
       </c>
       <c r="D315" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6971,7 +6971,7 @@
         <v>1600</v>
       </c>
       <c r="D316" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6985,7 +6985,7 @@
         <v>1400</v>
       </c>
       <c r="D317" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6999,7 +6999,7 @@
         <v>1200</v>
       </c>
       <c r="D318" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -7013,7 +7013,7 @@
         <v>1200</v>
       </c>
       <c r="D319" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -7027,7 +7027,7 @@
         <v>1200</v>
       </c>
       <c r="D320" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -7041,7 +7041,7 @@
         <v>1100</v>
       </c>
       <c r="D321" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -7055,7 +7055,7 @@
         <v>1100</v>
       </c>
       <c r="D322" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -7069,7 +7069,7 @@
         <v>1100</v>
       </c>
       <c r="D323" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -7083,7 +7083,7 @@
         <v>900</v>
       </c>
       <c r="D324" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -7097,7 +7097,7 @@
         <v>800</v>
       </c>
       <c r="D325" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -7111,7 +7111,7 @@
         <v>800</v>
       </c>
       <c r="D326" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -7125,7 +7125,7 @@
         <v>700</v>
       </c>
       <c r="D327" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -7139,7 +7139,7 @@
         <v>700</v>
       </c>
       <c r="D328" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -7153,7 +7153,7 @@
         <v>600</v>
       </c>
       <c r="D329" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -7167,7 +7167,7 @@
         <v>600</v>
       </c>
       <c r="D330" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -7181,7 +7181,7 @@
         <v>500</v>
       </c>
       <c r="D331" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -7195,7 +7195,7 @@
         <v>500</v>
       </c>
       <c r="D332" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -7209,7 +7209,7 @@
         <v>500</v>
       </c>
       <c r="D333" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -7223,7 +7223,7 @@
         <v>400</v>
       </c>
       <c r="D334" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -7237,7 +7237,7 @@
         <v>300</v>
       </c>
       <c r="D335" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -7251,7 +7251,7 @@
         <v>300</v>
       </c>
       <c r="D336" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -7265,7 +7265,7 @@
         <v>300</v>
       </c>
       <c r="D337" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -7279,7 +7279,7 @@
         <v>300</v>
       </c>
       <c r="D338" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -7293,7 +7293,7 @@
         <v>200</v>
       </c>
       <c r="D339" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -7307,7 +7307,7 @@
         <v>100</v>
       </c>
       <c r="D340" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -7321,7 +7321,7 @@
         <v>100</v>
       </c>
       <c r="D341" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -7335,7 +7335,7 @@
         <v>100</v>
       </c>
       <c r="D342" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -7349,7 +7349,7 @@
         <v>100</v>
       </c>
       <c r="D343" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -7363,7 +7363,7 @@
         <v>100</v>
       </c>
       <c r="D344" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -7377,7 +7377,7 @@
         <v>100</v>
       </c>
       <c r="D345" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -7391,7 +7391,7 @@
         <v>100</v>
       </c>
       <c r="D346" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -7405,7 +7405,7 @@
         <v>100</v>
       </c>
       <c r="D347" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -7419,7 +7419,7 @@
         <v>100</v>
       </c>
       <c r="D348" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -7433,7 +7433,7 @@
         <v>100</v>
       </c>
       <c r="D349" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -7447,7 +7447,7 @@
         <v>100</v>
       </c>
       <c r="D350" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -7461,7 +7461,7 @@
         <v>100</v>
       </c>
       <c r="D351" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -7475,7 +7475,7 @@
         <v>100</v>
       </c>
       <c r="D352" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -7489,7 +7489,7 @@
         <v>100</v>
       </c>
       <c r="D353" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -7503,7 +7503,7 @@
         <v>100</v>
       </c>
       <c r="D354" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -7517,7 +7517,7 @@
         <v>100</v>
       </c>
       <c r="D355" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -7531,7 +7531,7 @@
         <v>42</v>
       </c>
       <c r="D356" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -7545,7 +7545,7 @@
         <v>36</v>
       </c>
       <c r="D357" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -7559,7 +7559,7 @@
         <v>1000</v>
       </c>
       <c r="D358" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -7573,7 +7573,7 @@
         <v>800</v>
       </c>
       <c r="D359" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -7587,7 +7587,7 @@
         <v>500</v>
       </c>
       <c r="D360" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -7601,7 +7601,7 @@
         <v>400</v>
       </c>
       <c r="D361" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -7615,7 +7615,7 @@
         <v>300</v>
       </c>
       <c r="D362" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -7629,7 +7629,7 @@
         <v>300</v>
       </c>
       <c r="D363" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -7643,7 +7643,7 @@
         <v>300</v>
       </c>
       <c r="D364" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -7657,7 +7657,7 @@
         <v>200</v>
       </c>
       <c r="D365" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -7671,7 +7671,7 @@
         <v>200</v>
       </c>
       <c r="D366" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -7685,7 +7685,7 @@
         <v>200</v>
       </c>
       <c r="D367" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -7699,7 +7699,7 @@
         <v>200</v>
       </c>
       <c r="D368" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -7713,7 +7713,7 @@
         <v>200</v>
       </c>
       <c r="D369" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -7727,7 +7727,7 @@
         <v>100</v>
       </c>
       <c r="D370" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -7741,7 +7741,7 @@
         <v>100</v>
       </c>
       <c r="D371" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -7755,7 +7755,7 @@
         <v>100</v>
       </c>
       <c r="D372" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -7769,7 +7769,7 @@
         <v>100</v>
       </c>
       <c r="D373" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -7783,7 +7783,7 @@
         <v>100</v>
       </c>
       <c r="D374" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -7797,7 +7797,7 @@
         <v>100</v>
       </c>
       <c r="D375" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -7811,7 +7811,7 @@
         <v>5900</v>
       </c>
       <c r="D376" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -7825,7 +7825,7 @@
         <v>600</v>
       </c>
       <c r="D377" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -7839,7 +7839,7 @@
         <v>500</v>
       </c>
       <c r="D378" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -7853,7 +7853,7 @@
         <v>400</v>
       </c>
       <c r="D379" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -7867,7 +7867,7 @@
         <v>400</v>
       </c>
       <c r="D380" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -7881,7 +7881,7 @@
         <v>300</v>
       </c>
       <c r="D381" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -7895,7 +7895,7 @@
         <v>100</v>
       </c>
       <c r="D382" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -7909,7 +7909,7 @@
         <v>100</v>
       </c>
       <c r="D383" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -7923,7 +7923,7 @@
         <v>100</v>
       </c>
       <c r="D384" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -7937,7 +7937,7 @@
         <v>100</v>
       </c>
       <c r="D385" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -7951,7 +7951,7 @@
         <v>1500</v>
       </c>
       <c r="D386" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -7965,7 +7965,7 @@
         <v>800</v>
       </c>
       <c r="D387" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7979,7 +7979,7 @@
         <v>100</v>
       </c>
       <c r="D388" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7993,7 +7993,7 @@
         <v>14200</v>
       </c>
       <c r="D389" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -8007,7 +8007,7 @@
         <v>400</v>
       </c>
       <c r="D390" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -8021,7 +8021,7 @@
         <v>200</v>
       </c>
       <c r="D391" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -8035,7 +8035,7 @@
         <v>200</v>
       </c>
       <c r="D392" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -8049,7 +8049,7 @@
         <v>100</v>
       </c>
       <c r="D393" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -8063,7 +8063,7 @@
         <v>100</v>
       </c>
       <c r="D394" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -8077,7 +8077,7 @@
         <v>100</v>
       </c>
       <c r="D395" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -8091,7 +8091,7 @@
         <v>100</v>
       </c>
       <c r="D396" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -8105,7 +8105,7 @@
         <v>100</v>
       </c>
       <c r="D397" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -8119,7 +8119,7 @@
         <v>100</v>
       </c>
       <c r="D398" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -8133,7 +8133,7 @@
         <v>100</v>
       </c>
       <c r="D399" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -8147,7 +8147,7 @@
         <v>200</v>
       </c>
       <c r="D400" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -8161,7 +8161,7 @@
         <v>100</v>
       </c>
       <c r="D401" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -8175,7 +8175,7 @@
         <v>100</v>
       </c>
       <c r="D402" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -8189,7 +8189,7 @@
         <v>20000</v>
       </c>
       <c r="D403" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -8203,7 +8203,7 @@
         <v>100</v>
       </c>
       <c r="D404" s="2">
-        <v>45773</v>
+        <v>45774</v>
       </c>
     </row>
   </sheetData>

--- a/Bases/Lista de ações.xlsx
+++ b/Bases/Lista de ações.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="717">
   <si>
     <t>Nome da Empresa</t>
   </si>
@@ -304,12 +304,12 @@
     <t>GPS</t>
   </si>
   <si>
+    <t>Camil Alimentos</t>
+  </si>
+  <si>
     <t>Casas Bahia</t>
   </si>
   <si>
-    <t>Camil Alimentos</t>
-  </si>
-  <si>
     <t>Recrusul</t>
   </si>
   <si>
@@ -394,15 +394,15 @@
     <t>CPFL Energia</t>
   </si>
   <si>
+    <t>IRB Brasil RE</t>
+  </si>
+  <si>
+    <t>Mitre Realty</t>
+  </si>
+  <si>
     <t>Azevedo &amp; Travassos</t>
   </si>
   <si>
-    <t>IRB Brasil RE</t>
-  </si>
-  <si>
-    <t>Mitre Realty</t>
-  </si>
-  <si>
     <t>Zamp</t>
   </si>
   <si>
@@ -673,6 +673,9 @@
     <t>Terra Santa</t>
   </si>
   <si>
+    <t>Iguatemi</t>
+  </si>
+  <si>
     <t>Dexxos</t>
   </si>
   <si>
@@ -796,12 +799,12 @@
     <t>Nutriplant</t>
   </si>
   <si>
+    <t>REAG3</t>
+  </si>
+  <si>
     <t>Celesc</t>
   </si>
   <si>
-    <t>REAG3</t>
-  </si>
-  <si>
     <t>Cedro Têxtil</t>
   </si>
   <si>
@@ -889,9 +892,6 @@
     <t>Baumer</t>
   </si>
   <si>
-    <t>Iguatemi</t>
-  </si>
-  <si>
     <t>Equatorial Energia Pará</t>
   </si>
   <si>
@@ -1264,12 +1264,12 @@
     <t>GGPS3</t>
   </si>
   <si>
+    <t>CAML3</t>
+  </si>
+  <si>
     <t>BHIA3</t>
   </si>
   <si>
-    <t>CAML3</t>
-  </si>
-  <si>
     <t>RCSL4</t>
   </si>
   <si>
@@ -1360,15 +1360,15 @@
     <t>CPFE3</t>
   </si>
   <si>
+    <t>IRBR3</t>
+  </si>
+  <si>
+    <t>MTRE3</t>
+  </si>
+  <si>
     <t>AZEV3</t>
   </si>
   <si>
-    <t>IRBR3</t>
-  </si>
-  <si>
-    <t>MTRE3</t>
-  </si>
-  <si>
     <t>ZAMP3</t>
   </si>
   <si>
@@ -2165,9 +2165,6 @@
   </si>
   <si>
     <t>CBEE3</t>
-  </si>
-  <si>
-    <t>RPAD3</t>
   </si>
 </sst>
 </file>
@@ -2529,7 +2526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D400"/>
+  <dimension ref="A1:D399"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2554,10 +2551,10 @@
         <v>321</v>
       </c>
       <c r="C2">
-        <v>121193800</v>
+        <v>121193500</v>
       </c>
       <c r="D2" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2571,7 +2568,7 @@
         <v>117295800</v>
       </c>
       <c r="D3" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2582,10 +2579,10 @@
         <v>323</v>
       </c>
       <c r="C4">
-        <v>110985700</v>
+        <v>110968400</v>
       </c>
       <c r="D4" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2599,7 +2596,7 @@
         <v>87134400</v>
       </c>
       <c r="D5" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2613,7 +2610,7 @@
         <v>69490700</v>
       </c>
       <c r="D6" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2624,10 +2621,10 @@
         <v>326</v>
       </c>
       <c r="C7">
-        <v>62823300</v>
+        <v>62821800</v>
       </c>
       <c r="D7" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2641,7 +2638,7 @@
         <v>60942100</v>
       </c>
       <c r="D8" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2652,10 +2649,10 @@
         <v>328</v>
       </c>
       <c r="C9">
-        <v>58078200</v>
+        <v>58076500</v>
       </c>
       <c r="D9" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2666,10 +2663,10 @@
         <v>329</v>
       </c>
       <c r="C10">
-        <v>58004600</v>
+        <v>58004500</v>
       </c>
       <c r="D10" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2680,10 +2677,10 @@
         <v>330</v>
       </c>
       <c r="C11">
-        <v>49150000</v>
+        <v>49136200</v>
       </c>
       <c r="D11" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2697,7 +2694,7 @@
         <v>38056400</v>
       </c>
       <c r="D12" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2711,7 +2708,7 @@
         <v>37322000</v>
       </c>
       <c r="D13" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2725,7 +2722,7 @@
         <v>34768700</v>
       </c>
       <c r="D14" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2736,10 +2733,10 @@
         <v>334</v>
       </c>
       <c r="C15">
-        <v>30501400</v>
+        <v>30501200</v>
       </c>
       <c r="D15" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2753,7 +2750,7 @@
         <v>26973800</v>
       </c>
       <c r="D16" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2767,7 +2764,7 @@
         <v>25075600</v>
       </c>
       <c r="D17" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2781,7 +2778,7 @@
         <v>24979900</v>
       </c>
       <c r="D18" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2792,10 +2789,10 @@
         <v>338</v>
       </c>
       <c r="C19">
-        <v>24425900</v>
+        <v>24419400</v>
       </c>
       <c r="D19" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2809,7 +2806,7 @@
         <v>24161300</v>
       </c>
       <c r="D20" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2820,10 +2817,10 @@
         <v>340</v>
       </c>
       <c r="C21">
-        <v>23513400</v>
+        <v>23441600</v>
       </c>
       <c r="D21" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2837,7 +2834,7 @@
         <v>19842500</v>
       </c>
       <c r="D22" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2851,7 +2848,7 @@
         <v>18500200</v>
       </c>
       <c r="D23" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2862,10 +2859,10 @@
         <v>343</v>
       </c>
       <c r="C24">
-        <v>17467500</v>
+        <v>17466500</v>
       </c>
       <c r="D24" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2879,7 +2876,7 @@
         <v>15989200</v>
       </c>
       <c r="D25" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2893,7 +2890,7 @@
         <v>15558800</v>
       </c>
       <c r="D26" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2907,7 +2904,7 @@
         <v>15413000</v>
       </c>
       <c r="D27" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2921,7 +2918,7 @@
         <v>15323400</v>
       </c>
       <c r="D28" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2932,10 +2929,10 @@
         <v>348</v>
       </c>
       <c r="C29">
-        <v>15028400</v>
+        <v>15024800</v>
       </c>
       <c r="D29" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2949,7 +2946,7 @@
         <v>14974900</v>
       </c>
       <c r="D30" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2963,7 +2960,7 @@
         <v>13122800</v>
       </c>
       <c r="D31" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2977,7 +2974,7 @@
         <v>12802800</v>
       </c>
       <c r="D32" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2991,7 +2988,7 @@
         <v>12685300</v>
       </c>
       <c r="D33" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -3002,10 +2999,10 @@
         <v>353</v>
       </c>
       <c r="C34">
-        <v>12333500</v>
+        <v>12333300</v>
       </c>
       <c r="D34" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3019,7 +3016,7 @@
         <v>12227800</v>
       </c>
       <c r="D35" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3033,7 +3030,7 @@
         <v>11829600</v>
       </c>
       <c r="D36" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3044,10 +3041,10 @@
         <v>356</v>
       </c>
       <c r="C37">
-        <v>11369900</v>
+        <v>11369400</v>
       </c>
       <c r="D37" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3058,10 +3055,10 @@
         <v>357</v>
       </c>
       <c r="C38">
-        <v>11164000</v>
+        <v>11161000</v>
       </c>
       <c r="D38" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3075,7 +3072,7 @@
         <v>11015500</v>
       </c>
       <c r="D39" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3089,7 +3086,7 @@
         <v>10926300</v>
       </c>
       <c r="D40" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3103,7 +3100,7 @@
         <v>10911500</v>
       </c>
       <c r="D41" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3117,7 +3114,7 @@
         <v>10694300</v>
       </c>
       <c r="D42" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3131,7 +3128,7 @@
         <v>10679100</v>
       </c>
       <c r="D43" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3145,7 +3142,7 @@
         <v>10551500</v>
       </c>
       <c r="D44" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3159,7 +3156,7 @@
         <v>10331000</v>
       </c>
       <c r="D45" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3170,10 +3167,10 @@
         <v>365</v>
       </c>
       <c r="C46">
-        <v>10328800</v>
+        <v>10326400</v>
       </c>
       <c r="D46" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3184,10 +3181,10 @@
         <v>366</v>
       </c>
       <c r="C47">
-        <v>10057500</v>
+        <v>10055500</v>
       </c>
       <c r="D47" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3201,7 +3198,7 @@
         <v>9721600</v>
       </c>
       <c r="D48" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3215,7 +3212,7 @@
         <v>9657500</v>
       </c>
       <c r="D49" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3229,7 +3226,7 @@
         <v>8878500</v>
       </c>
       <c r="D50" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3243,7 +3240,7 @@
         <v>8789300</v>
       </c>
       <c r="D51" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3257,7 +3254,7 @@
         <v>8694900</v>
       </c>
       <c r="D52" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3271,7 +3268,7 @@
         <v>8582900</v>
       </c>
       <c r="D53" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3285,7 +3282,7 @@
         <v>8328500</v>
       </c>
       <c r="D54" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3299,7 +3296,7 @@
         <v>8188000</v>
       </c>
       <c r="D55" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3313,7 +3310,7 @@
         <v>8157400</v>
       </c>
       <c r="D56" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3327,7 +3324,7 @@
         <v>7991700</v>
       </c>
       <c r="D57" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3341,7 +3338,7 @@
         <v>7717100</v>
       </c>
       <c r="D58" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3352,10 +3349,10 @@
         <v>378</v>
       </c>
       <c r="C59">
-        <v>7698100</v>
+        <v>7697100</v>
       </c>
       <c r="D59" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3369,7 +3366,7 @@
         <v>7566100</v>
       </c>
       <c r="D60" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3383,7 +3380,7 @@
         <v>7416700</v>
       </c>
       <c r="D61" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3394,10 +3391,10 @@
         <v>381</v>
       </c>
       <c r="C62">
-        <v>7297700</v>
+        <v>7297400</v>
       </c>
       <c r="D62" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3411,7 +3408,7 @@
         <v>7269600</v>
       </c>
       <c r="D63" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3425,7 +3422,7 @@
         <v>7236400</v>
       </c>
       <c r="D64" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3439,7 +3436,7 @@
         <v>6671300</v>
       </c>
       <c r="D65" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3453,7 +3450,7 @@
         <v>6518700</v>
       </c>
       <c r="D66" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3467,7 +3464,7 @@
         <v>6503500</v>
       </c>
       <c r="D67" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3481,7 +3478,7 @@
         <v>6056900</v>
       </c>
       <c r="D68" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3492,10 +3489,10 @@
         <v>388</v>
       </c>
       <c r="C69">
-        <v>6039300</v>
+        <v>6033700</v>
       </c>
       <c r="D69" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3509,7 +3506,7 @@
         <v>5972700</v>
       </c>
       <c r="D70" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3523,7 +3520,7 @@
         <v>5966400</v>
       </c>
       <c r="D71" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3537,7 +3534,7 @@
         <v>5555100</v>
       </c>
       <c r="D72" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3551,7 +3548,7 @@
         <v>5486400</v>
       </c>
       <c r="D73" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3565,7 +3562,7 @@
         <v>5405000</v>
       </c>
       <c r="D74" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3579,7 +3576,7 @@
         <v>5311100</v>
       </c>
       <c r="D75" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3593,7 +3590,7 @@
         <v>5232500</v>
       </c>
       <c r="D76" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3607,7 +3604,7 @@
         <v>5158200</v>
       </c>
       <c r="D77" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3621,7 +3618,7 @@
         <v>5157000</v>
       </c>
       <c r="D78" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3635,7 +3632,7 @@
         <v>4900000</v>
       </c>
       <c r="D79" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3649,7 +3646,7 @@
         <v>4881500</v>
       </c>
       <c r="D80" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3660,10 +3657,10 @@
         <v>400</v>
       </c>
       <c r="C81">
-        <v>4763800</v>
+        <v>4763700</v>
       </c>
       <c r="D81" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3674,10 +3671,10 @@
         <v>401</v>
       </c>
       <c r="C82">
-        <v>4730600</v>
+        <v>4730200</v>
       </c>
       <c r="D82" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3691,7 +3688,7 @@
         <v>4682000</v>
       </c>
       <c r="D83" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3705,7 +3702,7 @@
         <v>4462300</v>
       </c>
       <c r="D84" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3716,10 +3713,10 @@
         <v>404</v>
       </c>
       <c r="C85">
-        <v>4426100</v>
+        <v>4424100</v>
       </c>
       <c r="D85" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3733,7 +3730,7 @@
         <v>4373100</v>
       </c>
       <c r="D86" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3747,7 +3744,7 @@
         <v>4214200</v>
       </c>
       <c r="D87" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3761,7 +3758,7 @@
         <v>4208100</v>
       </c>
       <c r="D88" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3775,7 +3772,7 @@
         <v>4201500</v>
       </c>
       <c r="D89" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3789,7 +3786,7 @@
         <v>4194500</v>
       </c>
       <c r="D90" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3803,7 +3800,7 @@
         <v>4069600</v>
       </c>
       <c r="D91" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3817,7 +3814,7 @@
         <v>3984900</v>
       </c>
       <c r="D92" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3831,7 +3828,7 @@
         <v>3891400</v>
       </c>
       <c r="D93" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3845,7 +3842,7 @@
         <v>3836700</v>
       </c>
       <c r="D94" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3859,7 +3856,7 @@
         <v>3783800</v>
       </c>
       <c r="D95" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3873,7 +3870,7 @@
         <v>3704500</v>
       </c>
       <c r="D96" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3884,10 +3881,10 @@
         <v>416</v>
       </c>
       <c r="C97">
-        <v>3652700</v>
+        <v>3651600</v>
       </c>
       <c r="D97" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3898,10 +3895,10 @@
         <v>417</v>
       </c>
       <c r="C98">
-        <v>3651600</v>
+        <v>3646700</v>
       </c>
       <c r="D98" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3915,7 +3912,7 @@
         <v>3619300</v>
       </c>
       <c r="D99" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3929,7 +3926,7 @@
         <v>3572600</v>
       </c>
       <c r="D100" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3943,7 +3940,7 @@
         <v>3384700</v>
       </c>
       <c r="D101" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3954,10 +3951,10 @@
         <v>421</v>
       </c>
       <c r="C102">
-        <v>3273500</v>
+        <v>3273300</v>
       </c>
       <c r="D102" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3968,10 +3965,10 @@
         <v>422</v>
       </c>
       <c r="C103">
-        <v>3174900</v>
+        <v>3173900</v>
       </c>
       <c r="D103" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3985,7 +3982,7 @@
         <v>2935500</v>
       </c>
       <c r="D104" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3999,7 +3996,7 @@
         <v>2900500</v>
       </c>
       <c r="D105" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -4013,7 +4010,7 @@
         <v>2865100</v>
       </c>
       <c r="D106" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -4027,7 +4024,7 @@
         <v>2744500</v>
       </c>
       <c r="D107" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -4041,7 +4038,7 @@
         <v>2673900</v>
       </c>
       <c r="D108" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4055,7 +4052,7 @@
         <v>2465700</v>
       </c>
       <c r="D109" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4069,7 +4066,7 @@
         <v>2448900</v>
       </c>
       <c r="D110" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4083,7 +4080,7 @@
         <v>2347200</v>
       </c>
       <c r="D111" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4097,7 +4094,7 @@
         <v>2252400</v>
       </c>
       <c r="D112" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4111,7 +4108,7 @@
         <v>2249100</v>
       </c>
       <c r="D113" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4125,7 +4122,7 @@
         <v>2245400</v>
       </c>
       <c r="D114" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4139,7 +4136,7 @@
         <v>2158600</v>
       </c>
       <c r="D115" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4153,7 +4150,7 @@
         <v>2134800</v>
       </c>
       <c r="D116" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4164,10 +4161,10 @@
         <v>436</v>
       </c>
       <c r="C117">
-        <v>2132900</v>
+        <v>2132600</v>
       </c>
       <c r="D117" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4181,7 +4178,7 @@
         <v>2106600</v>
       </c>
       <c r="D118" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4195,7 +4192,7 @@
         <v>1900600</v>
       </c>
       <c r="D119" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4209,7 +4206,7 @@
         <v>1827900</v>
       </c>
       <c r="D120" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4223,7 +4220,7 @@
         <v>1821600</v>
       </c>
       <c r="D121" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4237,7 +4234,7 @@
         <v>1810100</v>
       </c>
       <c r="D122" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4251,7 +4248,7 @@
         <v>1776200</v>
       </c>
       <c r="D123" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4265,7 +4262,7 @@
         <v>1771300</v>
       </c>
       <c r="D124" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4279,7 +4276,7 @@
         <v>1755500</v>
       </c>
       <c r="D125" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4293,7 +4290,7 @@
         <v>1715200</v>
       </c>
       <c r="D126" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4307,7 +4304,7 @@
         <v>1663800</v>
       </c>
       <c r="D127" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4318,10 +4315,10 @@
         <v>447</v>
       </c>
       <c r="C128">
-        <v>1633500</v>
+        <v>1633200</v>
       </c>
       <c r="D128" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4332,10 +4329,10 @@
         <v>448</v>
       </c>
       <c r="C129">
-        <v>1629800</v>
+        <v>1624500</v>
       </c>
       <c r="D129" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4346,10 +4343,10 @@
         <v>449</v>
       </c>
       <c r="C130">
-        <v>1624500</v>
+        <v>1600900</v>
       </c>
       <c r="D130" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4360,10 +4357,10 @@
         <v>450</v>
       </c>
       <c r="C131">
-        <v>1600900</v>
+        <v>1589800</v>
       </c>
       <c r="D131" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4377,7 +4374,7 @@
         <v>1567400</v>
       </c>
       <c r="D132" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4391,12 +4388,12 @@
         <v>1533600</v>
       </c>
       <c r="D133" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B134" t="s">
         <v>453</v>
@@ -4405,7 +4402,7 @@
         <v>1526500</v>
       </c>
       <c r="D134" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4419,7 +4416,7 @@
         <v>1486100</v>
       </c>
       <c r="D135" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4433,7 +4430,7 @@
         <v>1470400</v>
       </c>
       <c r="D136" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4447,7 +4444,7 @@
         <v>1452100</v>
       </c>
       <c r="D137" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4461,7 +4458,7 @@
         <v>1392000</v>
       </c>
       <c r="D138" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4475,7 +4472,7 @@
         <v>1367300</v>
       </c>
       <c r="D139" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4489,7 +4486,7 @@
         <v>1334200</v>
       </c>
       <c r="D140" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4503,7 +4500,7 @@
         <v>1294600</v>
       </c>
       <c r="D141" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4517,7 +4514,7 @@
         <v>1254600</v>
       </c>
       <c r="D142" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4531,7 +4528,7 @@
         <v>1213700</v>
       </c>
       <c r="D143" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4545,7 +4542,7 @@
         <v>1200400</v>
       </c>
       <c r="D144" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4556,10 +4553,10 @@
         <v>464</v>
       </c>
       <c r="C145">
-        <v>1177000</v>
+        <v>1176900</v>
       </c>
       <c r="D145" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4573,7 +4570,7 @@
         <v>1176800</v>
       </c>
       <c r="D146" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4587,7 +4584,7 @@
         <v>1176700</v>
       </c>
       <c r="D147" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4601,7 +4598,7 @@
         <v>1110800</v>
       </c>
       <c r="D148" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4615,7 +4612,7 @@
         <v>1081500</v>
       </c>
       <c r="D149" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4629,7 +4626,7 @@
         <v>1035200</v>
       </c>
       <c r="D150" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4643,7 +4640,7 @@
         <v>990000</v>
       </c>
       <c r="D151" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4657,7 +4654,7 @@
         <v>945500</v>
       </c>
       <c r="D152" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4671,7 +4668,7 @@
         <v>900300</v>
       </c>
       <c r="D153" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4685,7 +4682,7 @@
         <v>896100</v>
       </c>
       <c r="D154" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4699,7 +4696,7 @@
         <v>867400</v>
       </c>
       <c r="D155" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4713,7 +4710,7 @@
         <v>858600</v>
       </c>
       <c r="D156" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4727,7 +4724,7 @@
         <v>823400</v>
       </c>
       <c r="D157" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4741,7 +4738,7 @@
         <v>813400</v>
       </c>
       <c r="D158" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4755,7 +4752,7 @@
         <v>799500</v>
       </c>
       <c r="D159" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4769,7 +4766,7 @@
         <v>771600</v>
       </c>
       <c r="D160" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4783,7 +4780,7 @@
         <v>760200</v>
       </c>
       <c r="D161" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4797,7 +4794,7 @@
         <v>752600</v>
       </c>
       <c r="D162" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4811,7 +4808,7 @@
         <v>752300</v>
       </c>
       <c r="D163" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4825,7 +4822,7 @@
         <v>742100</v>
       </c>
       <c r="D164" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4839,7 +4836,7 @@
         <v>731600</v>
       </c>
       <c r="D165" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4853,7 +4850,7 @@
         <v>699400</v>
       </c>
       <c r="D166" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4867,7 +4864,7 @@
         <v>690500</v>
       </c>
       <c r="D167" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4881,7 +4878,7 @@
         <v>676400</v>
       </c>
       <c r="D168" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4895,7 +4892,7 @@
         <v>655400</v>
       </c>
       <c r="D169" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4909,7 +4906,7 @@
         <v>642700</v>
       </c>
       <c r="D170" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4923,7 +4920,7 @@
         <v>632500</v>
       </c>
       <c r="D171" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4937,7 +4934,7 @@
         <v>618000</v>
       </c>
       <c r="D172" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4951,7 +4948,7 @@
         <v>531900</v>
       </c>
       <c r="D173" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4965,7 +4962,7 @@
         <v>509200</v>
       </c>
       <c r="D174" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4979,7 +4976,7 @@
         <v>504100</v>
       </c>
       <c r="D175" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4993,7 +4990,7 @@
         <v>475800</v>
       </c>
       <c r="D176" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -5007,7 +5004,7 @@
         <v>438300</v>
       </c>
       <c r="D177" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -5021,7 +5018,7 @@
         <v>438200</v>
       </c>
       <c r="D178" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -5035,7 +5032,7 @@
         <v>422000</v>
       </c>
       <c r="D179" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -5049,7 +5046,7 @@
         <v>417600</v>
       </c>
       <c r="D180" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5063,7 +5060,7 @@
         <v>406800</v>
       </c>
       <c r="D181" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5077,7 +5074,7 @@
         <v>400700</v>
       </c>
       <c r="D182" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5091,7 +5088,7 @@
         <v>400200</v>
       </c>
       <c r="D183" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5105,7 +5102,7 @@
         <v>383300</v>
       </c>
       <c r="D184" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5119,7 +5116,7 @@
         <v>371300</v>
       </c>
       <c r="D185" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5133,7 +5130,7 @@
         <v>362400</v>
       </c>
       <c r="D186" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5147,7 +5144,7 @@
         <v>347300</v>
       </c>
       <c r="D187" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5161,7 +5158,7 @@
         <v>325400</v>
       </c>
       <c r="D188" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5175,7 +5172,7 @@
         <v>317000</v>
       </c>
       <c r="D189" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5189,7 +5186,7 @@
         <v>313300</v>
       </c>
       <c r="D190" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5203,7 +5200,7 @@
         <v>307200</v>
       </c>
       <c r="D191" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5217,7 +5214,7 @@
         <v>296400</v>
       </c>
       <c r="D192" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5231,7 +5228,7 @@
         <v>295000</v>
       </c>
       <c r="D193" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5245,7 +5242,7 @@
         <v>292200</v>
       </c>
       <c r="D194" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5259,7 +5256,7 @@
         <v>291600</v>
       </c>
       <c r="D195" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5273,7 +5270,7 @@
         <v>280100</v>
       </c>
       <c r="D196" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5287,7 +5284,7 @@
         <v>263200</v>
       </c>
       <c r="D197" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5301,7 +5298,7 @@
         <v>260400</v>
       </c>
       <c r="D198" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5315,7 +5312,7 @@
         <v>257700</v>
       </c>
       <c r="D199" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5329,7 +5326,7 @@
         <v>254400</v>
       </c>
       <c r="D200" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5343,7 +5340,7 @@
         <v>251100</v>
       </c>
       <c r="D201" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5357,7 +5354,7 @@
         <v>228100</v>
       </c>
       <c r="D202" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5371,7 +5368,7 @@
         <v>200800</v>
       </c>
       <c r="D203" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5385,7 +5382,7 @@
         <v>200000</v>
       </c>
       <c r="D204" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5399,7 +5396,7 @@
         <v>196500</v>
       </c>
       <c r="D205" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5413,7 +5410,7 @@
         <v>196300</v>
       </c>
       <c r="D206" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5427,7 +5424,7 @@
         <v>195400</v>
       </c>
       <c r="D207" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5441,7 +5438,7 @@
         <v>177200</v>
       </c>
       <c r="D208" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5455,7 +5452,7 @@
         <v>176400</v>
       </c>
       <c r="D209" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5469,7 +5466,7 @@
         <v>172000</v>
       </c>
       <c r="D210" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5483,7 +5480,7 @@
         <v>163900</v>
       </c>
       <c r="D211" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5497,7 +5494,7 @@
         <v>163200</v>
       </c>
       <c r="D212" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5511,7 +5508,7 @@
         <v>159800</v>
       </c>
       <c r="D213" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5525,7 +5522,7 @@
         <v>159500</v>
       </c>
       <c r="D214" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5539,7 +5536,7 @@
         <v>153000</v>
       </c>
       <c r="D215" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5553,7 +5550,7 @@
         <v>152500</v>
       </c>
       <c r="D216" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5567,7 +5564,7 @@
         <v>148900</v>
       </c>
       <c r="D217" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5581,7 +5578,7 @@
         <v>145700</v>
       </c>
       <c r="D218" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5595,7 +5592,7 @@
         <v>143500</v>
       </c>
       <c r="D219" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5609,7 +5606,7 @@
         <v>137800</v>
       </c>
       <c r="D220" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5623,7 +5620,7 @@
         <v>132400</v>
       </c>
       <c r="D221" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5637,7 +5634,7 @@
         <v>108500</v>
       </c>
       <c r="D222" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5648,10 +5645,10 @@
         <v>542</v>
       </c>
       <c r="C223">
-        <v>101500</v>
+        <v>101300</v>
       </c>
       <c r="D223" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5665,7 +5662,7 @@
         <v>98000</v>
       </c>
       <c r="D224" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5679,7 +5676,7 @@
         <v>97100</v>
       </c>
       <c r="D225" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5693,7 +5690,7 @@
         <v>74100</v>
       </c>
       <c r="D226" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5707,7 +5704,7 @@
         <v>66400</v>
       </c>
       <c r="D227" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5721,7 +5718,7 @@
         <v>64900</v>
       </c>
       <c r="D228" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5732,10 +5729,10 @@
         <v>548</v>
       </c>
       <c r="C229">
-        <v>63900</v>
+        <v>62700</v>
       </c>
       <c r="D229" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5749,7 +5746,7 @@
         <v>61700</v>
       </c>
       <c r="D230" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5763,7 +5760,7 @@
         <v>59900</v>
       </c>
       <c r="D231" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5777,7 +5774,7 @@
         <v>58100</v>
       </c>
       <c r="D232" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5791,7 +5788,7 @@
         <v>53700</v>
       </c>
       <c r="D233" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5805,7 +5802,7 @@
         <v>53300</v>
       </c>
       <c r="D234" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5819,7 +5816,7 @@
         <v>53300</v>
       </c>
       <c r="D235" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5833,7 +5830,7 @@
         <v>53100</v>
       </c>
       <c r="D236" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5847,7 +5844,7 @@
         <v>50400</v>
       </c>
       <c r="D237" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5858,15 +5855,15 @@
         <v>557</v>
       </c>
       <c r="C238">
-        <v>48100</v>
+        <v>47500</v>
       </c>
       <c r="D238" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="B239" t="s">
         <v>558</v>
@@ -5875,12 +5872,12 @@
         <v>47200</v>
       </c>
       <c r="D239" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B240" t="s">
         <v>559</v>
@@ -5889,12 +5886,12 @@
         <v>44600</v>
       </c>
       <c r="D240" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B241" t="s">
         <v>560</v>
@@ -5903,7 +5900,7 @@
         <v>42400</v>
       </c>
       <c r="D241" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5917,7 +5914,7 @@
         <v>41900</v>
       </c>
       <c r="D242" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5931,12 +5928,12 @@
         <v>40900</v>
       </c>
       <c r="D243" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B244" t="s">
         <v>563</v>
@@ -5945,12 +5942,12 @@
         <v>35900</v>
       </c>
       <c r="D244" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B245" t="s">
         <v>564</v>
@@ -5959,12 +5956,12 @@
         <v>35400</v>
       </c>
       <c r="D245" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B246" t="s">
         <v>565</v>
@@ -5973,7 +5970,7 @@
         <v>34100</v>
       </c>
       <c r="D246" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5987,7 +5984,7 @@
         <v>33100</v>
       </c>
       <c r="D247" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -6001,12 +5998,12 @@
         <v>32200</v>
       </c>
       <c r="D248" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B249" t="s">
         <v>568</v>
@@ -6015,12 +6012,12 @@
         <v>30400</v>
       </c>
       <c r="D249" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B250" t="s">
         <v>569</v>
@@ -6029,26 +6026,26 @@
         <v>28400</v>
       </c>
       <c r="D250" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B251" t="s">
         <v>570</v>
       </c>
       <c r="C251">
-        <v>27800</v>
+        <v>27500</v>
       </c>
       <c r="D251" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B252" t="s">
         <v>571</v>
@@ -6057,7 +6054,7 @@
         <v>27000</v>
       </c>
       <c r="D252" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -6071,12 +6068,12 @@
         <v>25600</v>
       </c>
       <c r="D253" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B254" t="s">
         <v>573</v>
@@ -6085,12 +6082,12 @@
         <v>24000</v>
       </c>
       <c r="D254" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B255" t="s">
         <v>574</v>
@@ -6099,12 +6096,12 @@
         <v>22800</v>
       </c>
       <c r="D255" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B256" t="s">
         <v>575</v>
@@ -6113,12 +6110,12 @@
         <v>16200</v>
       </c>
       <c r="D256" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B257" t="s">
         <v>576</v>
@@ -6127,12 +6124,12 @@
         <v>15300</v>
       </c>
       <c r="D257" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B258" t="s">
         <v>577</v>
@@ -6141,7 +6138,7 @@
         <v>15300</v>
       </c>
       <c r="D258" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -6155,7 +6152,7 @@
         <v>15100</v>
       </c>
       <c r="D259" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -6169,7 +6166,7 @@
         <v>14900</v>
       </c>
       <c r="D260" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -6183,12 +6180,12 @@
         <v>14200</v>
       </c>
       <c r="D261" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B262" t="s">
         <v>581</v>
@@ -6197,12 +6194,12 @@
         <v>13300</v>
       </c>
       <c r="D262" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B263" t="s">
         <v>582</v>
@@ -6211,7 +6208,7 @@
         <v>13300</v>
       </c>
       <c r="D263" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -6225,12 +6222,12 @@
         <v>13100</v>
       </c>
       <c r="D264" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B265" t="s">
         <v>584</v>
@@ -6239,12 +6236,12 @@
         <v>11500</v>
       </c>
       <c r="D265" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B266" t="s">
         <v>585</v>
@@ -6253,12 +6250,12 @@
         <v>11200</v>
       </c>
       <c r="D266" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B267" t="s">
         <v>586</v>
@@ -6267,12 +6264,12 @@
         <v>10800</v>
       </c>
       <c r="D267" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B268" t="s">
         <v>587</v>
@@ -6281,7 +6278,7 @@
         <v>10700</v>
       </c>
       <c r="D268" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -6295,12 +6292,12 @@
         <v>8800</v>
       </c>
       <c r="D269" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B270" t="s">
         <v>589</v>
@@ -6309,12 +6306,12 @@
         <v>8600</v>
       </c>
       <c r="D270" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B271" t="s">
         <v>590</v>
@@ -6323,12 +6320,12 @@
         <v>8100</v>
       </c>
       <c r="D271" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B272" t="s">
         <v>591</v>
@@ -6337,12 +6334,12 @@
         <v>8000</v>
       </c>
       <c r="D272" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B273" t="s">
         <v>592</v>
@@ -6351,7 +6348,7 @@
         <v>7000</v>
       </c>
       <c r="D273" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -6365,12 +6362,12 @@
         <v>6000</v>
       </c>
       <c r="D274" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B275" t="s">
         <v>594</v>
@@ -6379,12 +6376,12 @@
         <v>5900</v>
       </c>
       <c r="D275" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B276" t="s">
         <v>595</v>
@@ -6393,12 +6390,12 @@
         <v>5800</v>
       </c>
       <c r="D276" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B277" t="s">
         <v>596</v>
@@ -6407,7 +6404,7 @@
         <v>5500</v>
       </c>
       <c r="D277" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -6421,12 +6418,12 @@
         <v>5200</v>
       </c>
       <c r="D278" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B279" t="s">
         <v>598</v>
@@ -6435,12 +6432,12 @@
         <v>5200</v>
       </c>
       <c r="D279" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B280" t="s">
         <v>599</v>
@@ -6449,12 +6446,12 @@
         <v>5000</v>
       </c>
       <c r="D280" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B281" t="s">
         <v>600</v>
@@ -6463,12 +6460,12 @@
         <v>4900</v>
       </c>
       <c r="D281" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B282" t="s">
         <v>601</v>
@@ -6477,7 +6474,7 @@
         <v>4700</v>
       </c>
       <c r="D282" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -6491,12 +6488,12 @@
         <v>4400</v>
       </c>
       <c r="D283" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B284" t="s">
         <v>603</v>
@@ -6505,12 +6502,12 @@
         <v>4400</v>
       </c>
       <c r="D284" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B285" t="s">
         <v>604</v>
@@ -6519,7 +6516,7 @@
         <v>4200</v>
       </c>
       <c r="D285" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -6533,12 +6530,12 @@
         <v>4000</v>
       </c>
       <c r="D286" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B287" t="s">
         <v>606</v>
@@ -6547,12 +6544,12 @@
         <v>4000</v>
       </c>
       <c r="D287" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B288" t="s">
         <v>607</v>
@@ -6561,12 +6558,12 @@
         <v>3900</v>
       </c>
       <c r="D288" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B289" t="s">
         <v>608</v>
@@ -6575,7 +6572,7 @@
         <v>3800</v>
       </c>
       <c r="D289" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -6589,7 +6586,7 @@
         <v>3700</v>
       </c>
       <c r="D290" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -6603,12 +6600,12 @@
         <v>3600</v>
       </c>
       <c r="D291" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B292" t="s">
         <v>611</v>
@@ -6617,12 +6614,12 @@
         <v>3500</v>
       </c>
       <c r="D292" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B293" t="s">
         <v>612</v>
@@ -6631,12 +6628,12 @@
         <v>3500</v>
       </c>
       <c r="D293" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B294" t="s">
         <v>613</v>
@@ -6645,12 +6642,12 @@
         <v>3400</v>
       </c>
       <c r="D294" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B295" t="s">
         <v>614</v>
@@ -6659,7 +6656,7 @@
         <v>3300</v>
       </c>
       <c r="D295" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -6673,7 +6670,7 @@
         <v>3100</v>
       </c>
       <c r="D296" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -6687,12 +6684,12 @@
         <v>2900</v>
       </c>
       <c r="D297" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B298" t="s">
         <v>617</v>
@@ -6701,12 +6698,12 @@
         <v>2800</v>
       </c>
       <c r="D298" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B299" t="s">
         <v>618</v>
@@ -6715,12 +6712,12 @@
         <v>2700</v>
       </c>
       <c r="D299" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B300" t="s">
         <v>619</v>
@@ -6729,12 +6726,12 @@
         <v>2700</v>
       </c>
       <c r="D300" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B301" t="s">
         <v>620</v>
@@ -6743,12 +6740,12 @@
         <v>2700</v>
       </c>
       <c r="D301" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B302" t="s">
         <v>621</v>
@@ -6757,40 +6754,40 @@
         <v>2500</v>
       </c>
       <c r="D302" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B303" t="s">
-        <v>622</v>
+        <v>261</v>
       </c>
       <c r="C303">
         <v>2400</v>
       </c>
       <c r="D303" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B304" t="s">
-        <v>261</v>
+        <v>622</v>
       </c>
       <c r="C304">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="D304" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B305" t="s">
         <v>623</v>
@@ -6799,12 +6796,12 @@
         <v>2300</v>
       </c>
       <c r="D305" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B306" t="s">
         <v>624</v>
@@ -6813,12 +6810,12 @@
         <v>2300</v>
       </c>
       <c r="D306" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B307" t="s">
         <v>625</v>
@@ -6827,12 +6824,12 @@
         <v>2300</v>
       </c>
       <c r="D307" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B308" t="s">
         <v>626</v>
@@ -6841,7 +6838,7 @@
         <v>2200</v>
       </c>
       <c r="D308" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -6855,12 +6852,12 @@
         <v>2100</v>
       </c>
       <c r="D309" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B310" t="s">
         <v>628</v>
@@ -6869,12 +6866,12 @@
         <v>2000</v>
       </c>
       <c r="D310" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B311" t="s">
         <v>629</v>
@@ -6883,7 +6880,7 @@
         <v>1800</v>
       </c>
       <c r="D311" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -6897,12 +6894,12 @@
         <v>1700</v>
       </c>
       <c r="D312" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B313" t="s">
         <v>631</v>
@@ -6911,12 +6908,12 @@
         <v>1600</v>
       </c>
       <c r="D313" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B314" t="s">
         <v>632</v>
@@ -6925,12 +6922,12 @@
         <v>1600</v>
       </c>
       <c r="D314" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B315" t="s">
         <v>633</v>
@@ -6939,12 +6936,12 @@
         <v>1600</v>
       </c>
       <c r="D315" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B316" t="s">
         <v>634</v>
@@ -6953,12 +6950,12 @@
         <v>1300</v>
       </c>
       <c r="D316" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B317" t="s">
         <v>635</v>
@@ -6967,12 +6964,12 @@
         <v>1100</v>
       </c>
       <c r="D317" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B318" t="s">
         <v>636</v>
@@ -6981,12 +6978,12 @@
         <v>1000</v>
       </c>
       <c r="D318" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B319" t="s">
         <v>637</v>
@@ -6995,12 +6992,12 @@
         <v>900</v>
       </c>
       <c r="D319" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B320" t="s">
         <v>638</v>
@@ -7009,26 +7006,26 @@
         <v>900</v>
       </c>
       <c r="D320" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B321" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C321">
         <v>900</v>
       </c>
       <c r="D321" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B322" t="s">
         <v>639</v>
@@ -7037,12 +7034,12 @@
         <v>800</v>
       </c>
       <c r="D322" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B323" t="s">
         <v>640</v>
@@ -7051,12 +7048,12 @@
         <v>800</v>
       </c>
       <c r="D323" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B324" t="s">
         <v>641</v>
@@ -7065,12 +7062,12 @@
         <v>700</v>
       </c>
       <c r="D324" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B325" t="s">
         <v>642</v>
@@ -7079,12 +7076,12 @@
         <v>600</v>
       </c>
       <c r="D325" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B326" t="s">
         <v>643</v>
@@ -7093,12 +7090,12 @@
         <v>600</v>
       </c>
       <c r="D326" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B327" t="s">
         <v>644</v>
@@ -7107,12 +7104,12 @@
         <v>600</v>
       </c>
       <c r="D327" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B328" t="s">
         <v>645</v>
@@ -7121,12 +7118,12 @@
         <v>600</v>
       </c>
       <c r="D328" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B329" t="s">
         <v>646</v>
@@ -7135,12 +7132,12 @@
         <v>500</v>
       </c>
       <c r="D329" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B330" t="s">
         <v>647</v>
@@ -7149,12 +7146,12 @@
         <v>500</v>
       </c>
       <c r="D330" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B331" t="s">
         <v>648</v>
@@ -7163,12 +7160,12 @@
         <v>500</v>
       </c>
       <c r="D331" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B332" t="s">
         <v>649</v>
@@ -7177,7 +7174,7 @@
         <v>400</v>
       </c>
       <c r="D332" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -7191,12 +7188,12 @@
         <v>400</v>
       </c>
       <c r="D333" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B334" t="s">
         <v>651</v>
@@ -7205,12 +7202,12 @@
         <v>400</v>
       </c>
       <c r="D334" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B335" t="s">
         <v>652</v>
@@ -7219,12 +7216,12 @@
         <v>400</v>
       </c>
       <c r="D335" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B336" t="s">
         <v>653</v>
@@ -7233,7 +7230,7 @@
         <v>300</v>
       </c>
       <c r="D336" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -7247,12 +7244,12 @@
         <v>300</v>
       </c>
       <c r="D337" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B338" t="s">
         <v>655</v>
@@ -7261,12 +7258,12 @@
         <v>300</v>
       </c>
       <c r="D338" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B339" t="s">
         <v>656</v>
@@ -7275,12 +7272,12 @@
         <v>300</v>
       </c>
       <c r="D339" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B340" t="s">
         <v>657</v>
@@ -7289,12 +7286,12 @@
         <v>200</v>
       </c>
       <c r="D340" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B341" t="s">
         <v>658</v>
@@ -7303,12 +7300,12 @@
         <v>200</v>
       </c>
       <c r="D341" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B342" t="s">
         <v>659</v>
@@ -7317,12 +7314,12 @@
         <v>200</v>
       </c>
       <c r="D342" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B343" t="s">
         <v>660</v>
@@ -7331,12 +7328,12 @@
         <v>200</v>
       </c>
       <c r="D343" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B344" t="s">
         <v>661</v>
@@ -7345,7 +7342,7 @@
         <v>200</v>
       </c>
       <c r="D344" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -7359,12 +7356,12 @@
         <v>200</v>
       </c>
       <c r="D345" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B346" t="s">
         <v>663</v>
@@ -7373,12 +7370,12 @@
         <v>200</v>
       </c>
       <c r="D346" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B347" t="s">
         <v>664</v>
@@ -7387,12 +7384,12 @@
         <v>100</v>
       </c>
       <c r="D347" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B348" t="s">
         <v>665</v>
@@ -7401,12 +7398,12 @@
         <v>100</v>
       </c>
       <c r="D348" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B349" t="s">
         <v>666</v>
@@ -7415,12 +7412,12 @@
         <v>100</v>
       </c>
       <c r="D349" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>291</v>
+        <v>219</v>
       </c>
       <c r="B350" t="s">
         <v>667</v>
@@ -7429,7 +7426,7 @@
         <v>100</v>
       </c>
       <c r="D350" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -7443,7 +7440,7 @@
         <v>100</v>
       </c>
       <c r="D351" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -7457,12 +7454,12 @@
         <v>100</v>
       </c>
       <c r="D352" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B353" t="s">
         <v>670</v>
@@ -7471,7 +7468,7 @@
         <v>100</v>
       </c>
       <c r="D353" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -7485,7 +7482,7 @@
         <v>25</v>
       </c>
       <c r="D354" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -7499,7 +7496,7 @@
         <v>19</v>
       </c>
       <c r="D355" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -7513,7 +7510,7 @@
         <v>11200</v>
       </c>
       <c r="D356" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -7527,7 +7524,7 @@
         <v>3400</v>
       </c>
       <c r="D357" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -7541,7 +7538,7 @@
         <v>3200</v>
       </c>
       <c r="D358" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -7555,7 +7552,7 @@
         <v>1900</v>
       </c>
       <c r="D359" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -7569,7 +7566,7 @@
         <v>1100</v>
       </c>
       <c r="D360" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -7583,7 +7580,7 @@
         <v>1100</v>
       </c>
       <c r="D361" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -7597,7 +7594,7 @@
         <v>600</v>
       </c>
       <c r="D362" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -7611,7 +7608,7 @@
         <v>500</v>
       </c>
       <c r="D363" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -7625,12 +7622,12 @@
         <v>300</v>
       </c>
       <c r="D364" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B365" t="s">
         <v>682</v>
@@ -7639,12 +7636,12 @@
         <v>200</v>
       </c>
       <c r="D365" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B366" t="s">
         <v>683</v>
@@ -7653,7 +7650,7 @@
         <v>200</v>
       </c>
       <c r="D366" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -7667,12 +7664,12 @@
         <v>200</v>
       </c>
       <c r="D367" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B368" t="s">
         <v>685</v>
@@ -7681,7 +7678,7 @@
         <v>100</v>
       </c>
       <c r="D368" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -7695,7 +7692,7 @@
         <v>100</v>
       </c>
       <c r="D369" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -7709,12 +7706,12 @@
         <v>100</v>
       </c>
       <c r="D370" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B371" t="s">
         <v>688</v>
@@ -7723,7 +7720,7 @@
         <v>100</v>
       </c>
       <c r="D371" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -7737,7 +7734,7 @@
         <v>100</v>
       </c>
       <c r="D372" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -7751,7 +7748,7 @@
         <v>1000</v>
       </c>
       <c r="D373" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -7765,12 +7762,12 @@
         <v>900</v>
       </c>
       <c r="D374" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B375" t="s">
         <v>692</v>
@@ -7779,7 +7776,7 @@
         <v>400</v>
       </c>
       <c r="D375" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -7793,7 +7790,7 @@
         <v>200</v>
       </c>
       <c r="D376" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -7807,7 +7804,7 @@
         <v>200</v>
       </c>
       <c r="D377" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -7821,7 +7818,7 @@
         <v>100</v>
       </c>
       <c r="D378" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -7835,7 +7832,7 @@
         <v>100</v>
       </c>
       <c r="D379" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -7849,7 +7846,7 @@
         <v>100</v>
       </c>
       <c r="D380" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -7863,7 +7860,7 @@
         <v>100</v>
       </c>
       <c r="D381" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -7877,7 +7874,7 @@
         <v>100</v>
       </c>
       <c r="D382" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -7891,12 +7888,12 @@
         <v>100</v>
       </c>
       <c r="D383" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B384" t="s">
         <v>701</v>
@@ -7905,12 +7902,12 @@
         <v>100</v>
       </c>
       <c r="D384" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B385" t="s">
         <v>702</v>
@@ -7919,7 +7916,7 @@
         <v>100</v>
       </c>
       <c r="D385" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -7933,7 +7930,7 @@
         <v>100</v>
       </c>
       <c r="D386" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -7947,12 +7944,12 @@
         <v>1000</v>
       </c>
       <c r="D387" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B388" t="s">
         <v>705</v>
@@ -7961,7 +7958,7 @@
         <v>100</v>
       </c>
       <c r="D388" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7975,7 +7972,7 @@
         <v>100</v>
       </c>
       <c r="D389" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7989,7 +7986,7 @@
         <v>100</v>
       </c>
       <c r="D390" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -8003,12 +8000,12 @@
         <v>11708200</v>
       </c>
       <c r="D391" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B392" t="s">
         <v>709</v>
@@ -8017,7 +8014,7 @@
         <v>1600</v>
       </c>
       <c r="D392" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -8031,12 +8028,12 @@
         <v>1000</v>
       </c>
       <c r="D393" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B394" t="s">
         <v>711</v>
@@ -8045,7 +8042,7 @@
         <v>500</v>
       </c>
       <c r="D394" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -8059,7 +8056,7 @@
         <v>100</v>
       </c>
       <c r="D395" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -8073,7 +8070,7 @@
         <v>100</v>
       </c>
       <c r="D396" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -8087,7 +8084,7 @@
         <v>100</v>
       </c>
       <c r="D397" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -8101,7 +8098,7 @@
         <v>100</v>
       </c>
       <c r="D398" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -8115,21 +8112,7 @@
         <v>200</v>
       </c>
       <c r="D399" s="2">
-        <v>45786</v>
-      </c>
-    </row>
-    <row r="400" spans="1:4">
-      <c r="A400" t="s">
-        <v>270</v>
-      </c>
-      <c r="B400" t="s">
-        <v>717</v>
-      </c>
-      <c r="C400">
-        <v>500</v>
-      </c>
-      <c r="D400" s="2">
-        <v>45786</v>
+        <v>45788</v>
       </c>
     </row>
   </sheetData>
